--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -766,7 +766,7 @@
         <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
@@ -778,13 +778,13 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P2" t="n">
         <v>2.08</v>
@@ -799,10 +799,10 @@
         <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.69</v>
+        <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
         <v>1.17</v>
@@ -811,19 +811,19 @@
         <v>2.42</v>
       </c>
       <c r="X2" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
         <v>200</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -883,10 +883,10 @@
         <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>8.6</v>
@@ -895,10 +895,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA2" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -907,20 +907,20 @@
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G3" t="n">
         <v>4.4</v>
@@ -993,19 +993,19 @@
         <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V3" t="n">
         <v>1.89</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y3" t="n">
         <v>10.5</v>
@@ -1017,7 +1017,7 @@
         <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AC3" t="n">
         <v>8.800000000000001</v>
@@ -1035,7 +1035,7 @@
         <v>20</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AI3" t="n">
         <v>36</v>
@@ -1044,22 +1044,22 @@
         <v>100</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
         <v>65</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.4</v>
@@ -1074,47 +1074,47 @@
         <v>13.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.96</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
         <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="BG3" t="n">
         <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G4" t="n">
         <v>2.48</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="I11" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="J11" t="n">
-        <v>2.06</v>
+        <v>4.1</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G15" t="n">
         <v>1.77</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="I15" t="n">
         <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3303,7 +3303,7 @@
         <v>1.09</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O15" t="n">
         <v>1.41</v>
@@ -3321,7 +3321,7 @@
         <v>4.2</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
         <v>1.85</v>
@@ -3348,16 +3348,16 @@
         <v>7.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
         <v>26</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG15" t="n">
         <v>10.5</v>
@@ -3369,7 +3369,7 @@
         <v>120</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK15" t="n">
         <v>22</v>
@@ -3381,7 +3381,7 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
@@ -3393,13 +3393,13 @@
         <v>15</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU15" t="n">
         <v>7.8</v>
@@ -3408,19 +3408,19 @@
         <v>20</v>
       </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AX15" t="n">
         <v>8.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
         <v>21</v>
       </c>
       <c r="BA15" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BB15" t="n">
         <v>16</v>
@@ -3429,20 +3429,20 @@
         <v>18</v>
       </c>
       <c r="BD15" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BE15" t="n">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BF15" t="n">
         <v>12</v>
       </c>
       <c r="BG15" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H16" t="n">
         <v>3.3</v>
@@ -3485,7 +3485,7 @@
         <v>3.65</v>
       </c>
       <c r="J16" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
         <v>3.3</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G18" t="n">
         <v>1.75</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4309,22 +4309,22 @@
         <v>15.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA20" t="n">
         <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC20" t="n">
         <v>8</v>
       </c>
       <c r="AD20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF20" t="n">
         <v>15</v>
@@ -4351,7 +4351,7 @@
         <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO20" t="n">
         <v>36</v>
@@ -4366,7 +4366,7 @@
         <v>24</v>
       </c>
       <c r="AS20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
         <v>13.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY20" t="n">
         <v>10</v>
@@ -4390,13 +4390,13 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BC20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>29</v>
@@ -4405,14 +4405,14 @@
         <v>50</v>
       </c>
       <c r="BF20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>9.4</v>
       </c>
       <c r="J21" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K21" t="n">
         <v>5.7</v>
@@ -4464,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N21" t="n">
         <v>5.7</v>
@@ -4497,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y21" t="n">
         <v>36</v>
@@ -4524,7 +4524,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH21" t="n">
         <v>26</v>
@@ -4536,28 +4536,28 @@
         <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM21" t="n">
         <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AO21" t="n">
         <v>160</v>
       </c>
       <c r="AP21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR21" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AS21" t="n">
         <v>100</v>
@@ -4566,16 +4566,16 @@
         <v>9.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AW21" t="n">
         <v>40</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY21" t="n">
         <v>9.4</v>
@@ -4593,20 +4593,20 @@
         <v>12.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE21" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG21" t="n">
         <v>42</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
         <v>21</v>
       </c>
       <c r="AO22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP22" t="n">
         <v>18</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
         <v>1.69</v>
       </c>
       <c r="J23" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K23" t="n">
         <v>4.5</v>
@@ -4888,16 +4888,16 @@
         <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z23" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AA23" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC23" t="n">
         <v>9.4</v>
@@ -4906,7 +4906,7 @@
         <v>9.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AF23" t="n">
         <v>46</v>
@@ -4924,7 +4924,7 @@
         <v>170</v>
       </c>
       <c r="AK23" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AL23" t="n">
         <v>80</v>
@@ -4936,7 +4936,7 @@
         <v>120</v>
       </c>
       <c r="AO23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP23" t="n">
         <v>14.5</v>
@@ -4960,7 +4960,7 @@
         <v>9.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX23" t="n">
         <v>38</v>
@@ -4969,7 +4969,7 @@
         <v>19</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>32</v>
@@ -4981,7 +4981,7 @@
         <v>55</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE23" t="n">
         <v>44</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>2.52</v>
       </c>
       <c r="H26" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="I26" t="n">
         <v>2.96</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
         <v>2.06</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5804,19 +5804,19 @@
         <v>2.86</v>
       </c>
       <c r="G28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="I28" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="J28" t="n">
         <v>3.65</v>
       </c>
       <c r="K28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G29" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H29" t="n">
         <v>3.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N30" t="n">
         <v>5.9</v>
@@ -6267,7 +6267,7 @@
         <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
@@ -6282,7 +6282,7 @@
         <v>38</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -6309,7 +6309,7 @@
         <v>34</v>
       </c>
       <c r="AT30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU30" t="n">
         <v>8.800000000000001</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 01:18:33</t>
+          <t>2026-03-02 03:29:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,13 +763,13 @@
         <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
         <v>6.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
         <v>4.8</v>
@@ -784,7 +784,7 @@
         <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P2" t="n">
         <v>2.08</v>
@@ -820,10 +820,10 @@
         <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>10.5</v>
@@ -850,7 +850,7 @@
         <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
         <v>36</v>
@@ -859,22 +859,22 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AR2" t="n">
         <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -883,10 +883,10 @@
         <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.9</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
         <v>8.6</v>
@@ -895,10 +895,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.7</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -907,20 +907,20 @@
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         <v>1.72</v>
       </c>
       <c r="U3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
         <v>1.89</v>
@@ -1017,7 +1017,7 @@
         <v>26</v>
       </c>
       <c r="AB3" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.800000000000001</v>
@@ -1029,10 +1029,10 @@
         <v>22</v>
       </c>
       <c r="AF3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AH3" t="n">
         <v>970</v>
@@ -1041,7 +1041,7 @@
         <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
         <v>50</v>
@@ -1059,7 +1059,7 @@
         <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.4</v>
@@ -1068,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
@@ -1083,28 +1083,28 @@
         <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
         <v>36</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Macarthur FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
-        <v>2.48</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.86</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>1.54</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.46</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.27</v>
+        <v>1.91</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.94</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Juventus B</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AC Bra</t>
+          <t>Juventus B</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>AC Bra</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="I10" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU10" t="n">
         <v>7.8</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.6</v>
+        <v>2.54</v>
       </c>
       <c r="G11" t="n">
-        <v>5.6</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>1.65</v>
+        <v>3.15</v>
       </c>
       <c r="I11" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="J11" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="n">
-        <v>2.94</v>
+        <v>2.54</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>2.46</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.54</v>
+        <v>4.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.74</v>
+        <v>5.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.15</v>
+        <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>1.81</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,61 +3270,61 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>1.73</v>
       </c>
       <c r="G15" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
-        <v>5.9</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>2.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.22</v>
+        <v>1.49</v>
       </c>
       <c r="R15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,123 +3333,123 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.72</v>
+        <v>2.26</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.54</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.52</v>
+        <v>2.48</v>
       </c>
       <c r="G17" t="n">
-        <v>1.77</v>
+        <v>2.72</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.58</v>
+        <v>1.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.52</v>
+        <v>2.54</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K18" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.08</v>
+        <v>2.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>2.46</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2.76</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,66 +4235,66 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q20" t="n">
         <v>2.2</v>
       </c>
-      <c r="G20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.86</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,116 +4303,116 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -4434,61 +4434,61 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="H21" t="n">
-        <v>9.199999999999999</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>2.54</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,116 +4497,116 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>25</v>
+        <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
-        <v>990</v>
+        <v>70</v>
       </c>
       <c r="AB21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
-        <v>34</v>
+        <v>15.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="AF21" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>160</v>
+        <v>36</v>
       </c>
       <c r="AP21" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="AQ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG21" t="n">
         <v>30</v>
       </c>
-      <c r="AR21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>42</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -4628,61 +4628,61 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.92</v>
+        <v>1.4</v>
       </c>
       <c r="G22" t="n">
-        <v>2.96</v>
+        <v>1.41</v>
       </c>
       <c r="H22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S22" t="n">
         <v>2.54</v>
       </c>
-      <c r="I22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T22" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="U22" t="n">
-        <v>2.54</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,116 +4691,116 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Y22" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="Z22" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="AA22" t="n">
+        <v>990</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA22" t="n">
         <v>38</v>
       </c>
-      <c r="AB22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="BB22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC22" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS22" t="n">
+      <c r="BD22" t="n">
         <v>28</v>
       </c>
-      <c r="AT22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>25</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>29</v>
-      </c>
       <c r="BE22" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BF22" t="n">
-        <v>18</v>
+        <v>4.9</v>
       </c>
       <c r="BG22" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -4822,61 +4822,61 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5.6</v>
+        <v>2.92</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>2.96</v>
       </c>
       <c r="H23" t="n">
-        <v>1.68</v>
+        <v>2.54</v>
       </c>
       <c r="I23" t="n">
-        <v>1.69</v>
+        <v>2.58</v>
       </c>
       <c r="J23" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="K23" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="S23" t="n">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.99</v>
+        <v>1.61</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>2.54</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB23" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AC23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU23" t="n">
         <v>8</v>
       </c>
-      <c r="Z23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AE23" t="n">
+      <c r="AV23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF23" t="n">
         <v>17.5</v>
       </c>
-      <c r="AF23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>38</v>
-      </c>
       <c r="BG23" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,61 +5016,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ASD Pineto Calcio</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Forli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,116 +5079,116 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>ASD Pineto Calcio</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Forli</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,31 +5404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="G27" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="I27" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>2.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
@@ -5792,28 +5792,28 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="G28" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="H28" t="n">
-        <v>2.28</v>
+        <v>3.2</v>
       </c>
       <c r="I28" t="n">
-        <v>2.54</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>4.8</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,37 +5981,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.93</v>
+        <v>2.86</v>
       </c>
       <c r="G29" t="n">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="H29" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="I29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K29" t="n">
         <v>4.4</v>
       </c>
-      <c r="J29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,66 +6175,66 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="G30" t="n">
-        <v>2.68</v>
+        <v>2.32</v>
       </c>
       <c r="H30" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="I30" t="n">
-        <v>2.7</v>
+        <v>4.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.66</v>
+        <v>2.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="R30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6243,310 +6243,504 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 03:29:11</t>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N31" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-02 05:39:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Independiente Yumbo</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Bogota</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F32" t="n">
         <v>1.04</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G32" t="n">
         <v>1000</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H32" t="n">
         <v>1.04</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>1000</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>1.01</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>1000</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q32" t="n">
         <v>1.01</v>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-03-02 03:29:11</t>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-02 05:39:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="I3" t="n">
         <v>2.12</v>
@@ -966,10 +966,10 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1020,7 +1020,7 @@
         <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
@@ -1059,7 +1059,7 @@
         <v>15</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.4</v>
@@ -1083,28 +1083,28 @@
         <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>8</v>
-      </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
         <v>36</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
@@ -1175,7 +1175,7 @@
         <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q4" t="n">
         <v>1.62</v>
@@ -1184,13 +1184,13 @@
         <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
         <v>1.24</v>
@@ -1202,7 +1202,7 @@
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="n">
         <v>42</v>
@@ -1262,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>1.38</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.75</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.77</v>
       </c>
       <c r="H10" t="n">
         <v>5.9</v>
@@ -2321,10 +2321,10 @@
         <v>6.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2378,7 +2378,7 @@
         <v>7.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>26</v>
@@ -2420,7 +2420,7 @@
         <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AR10" t="n">
         <v>24</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G12" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="H12" t="n">
-        <v>2.54</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J12" t="n">
-        <v>2.56</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>2.98</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="G18" t="n">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="G19" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H20" t="n">
         <v>2.46</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G21" t="n">
         <v>2.22</v>
@@ -4455,7 +4455,7 @@
         <v>3.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>3.7</v>
@@ -4467,16 +4467,16 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
         <v>1.45</v>
@@ -4485,7 +4485,7 @@
         <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U21" t="n">
         <v>2.34</v>
@@ -4497,13 +4497,13 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y21" t="n">
         <v>15.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA21" t="n">
         <v>70</v>
@@ -4512,7 +4512,7 @@
         <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
         <v>15.5</v>
@@ -4548,7 +4548,7 @@
         <v>14.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP21" t="n">
         <v>15.5</v>
@@ -4560,7 +4560,7 @@
         <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4575,7 +4575,7 @@
         <v>32</v>
       </c>
       <c r="AX21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
@@ -4584,7 +4584,7 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB21" t="n">
         <v>24</v>
@@ -4596,17 +4596,17 @@
         <v>29</v>
       </c>
       <c r="BE21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG21" t="n">
         <v>30</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
         <v>12</v>
       </c>
       <c r="AK22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL22" t="n">
         <v>32</v>
@@ -4763,13 +4763,13 @@
         <v>11.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW22" t="n">
         <v>40</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="G23" t="n">
         <v>2.92</v>
       </c>
-      <c r="G23" t="n">
-        <v>2.96</v>
-      </c>
       <c r="H23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I23" t="n">
         <v>2.58</v>
@@ -4948,7 +4948,7 @@
         <v>16.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT23" t="n">
         <v>13.5</v>
@@ -4960,7 +4960,7 @@
         <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX23" t="n">
         <v>19</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5031,10 +5031,10 @@
         <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="J24" t="n">
         <v>4.4</v>
@@ -5052,13 +5052,13 @@
         <v>3.95</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R24" t="n">
         <v>1.37</v>
@@ -5091,7 +5091,7 @@
         <v>16.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC24" t="n">
         <v>9.6</v>
@@ -5106,7 +5106,7 @@
         <v>44</v>
       </c>
       <c r="AG24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -5115,7 +5115,7 @@
         <v>38</v>
       </c>
       <c r="AJ24" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK24" t="n">
         <v>85</v>
@@ -5127,7 +5127,7 @@
         <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO24" t="n">
         <v>11</v>
@@ -5157,10 +5157,10 @@
         <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AY24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ24" t="n">
         <v>20</v>
@@ -5172,10 +5172,10 @@
         <v>42</v>
       </c>
       <c r="BC24" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE24" t="n">
         <v>44</v>
@@ -5184,11 +5184,11 @@
         <v>38</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G28" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="H28" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="I28" t="n">
         <v>4.1</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.8</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,66 +6369,66 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.64</v>
+        <v>6.6</v>
       </c>
       <c r="G31" t="n">
-        <v>2.68</v>
+        <v>7.6</v>
       </c>
       <c r="H31" t="n">
-        <v>2.7</v>
+        <v>1.49</v>
       </c>
       <c r="I31" t="n">
-        <v>2.74</v>
+        <v>1.52</v>
       </c>
       <c r="J31" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="Q31" t="n">
         <v>1.59</v>
       </c>
       <c r="R31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6437,310 +6437,504 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 05:39:39</t>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N32" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-02 07:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Independiente Yumbo</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Bogota</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>1.04</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G33" t="n">
         <v>1000</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H33" t="n">
         <v>1.04</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>1000</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>1.01</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>1000</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>1.01</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-02 05:39:39</t>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-02 07:50:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
         <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -790,10 +790,10 @@
         <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
@@ -802,13 +802,13 @@
         <v>1.84</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X2" t="n">
         <v>970</v>
@@ -817,10 +817,10 @@
         <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
@@ -856,7 +856,7 @@
         <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
         <v>9</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -883,10 +883,10 @@
         <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX2" t="n">
         <v>8.6</v>
@@ -895,10 +895,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
         <v>13.5</v>
@@ -907,20 +907,20 @@
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G3" t="n">
         <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J3" t="n">
         <v>3.5</v>
@@ -969,7 +969,7 @@
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -999,7 +999,7 @@
         <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W3" t="n">
         <v>1.29</v>
@@ -1047,7 +1047,7 @@
         <v>50</v>
       </c>
       <c r="AL3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
         <v>110</v>
@@ -1068,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>13.5</v>
@@ -1107,14 +1107,14 @@
         <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
         <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
@@ -1202,7 +1202,7 @@
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
         <v>42</v>
@@ -1262,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
         <v>2.26</v>
@@ -1354,7 +1354,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="H6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I6" t="n">
         <v>16</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.75</v>
       </c>
       <c r="H10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
         <v>6.2</v>
@@ -2324,7 +2324,7 @@
         <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2381,7 +2381,7 @@
         <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I11" t="n">
         <v>3.4</v>
@@ -2518,7 +2518,7 @@
         <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="G12" t="n">
         <v>1.61</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I13" t="n">
         <v>3</v>
@@ -2906,7 +2906,7 @@
         <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2924,7 +2924,7 @@
         <v>2.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
         <v>4</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
         <v>1.73</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G17" t="n">
         <v>2.72</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.55</v>
+        <v>3.05</v>
       </c>
       <c r="G19" t="n">
-        <v>1.64</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>6.4</v>
+        <v>2.46</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4240,31 +4240,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="G20" t="n">
-        <v>3.45</v>
+        <v>1.64</v>
       </c>
       <c r="H20" t="n">
-        <v>2.46</v>
+        <v>6.6</v>
       </c>
       <c r="I20" t="n">
-        <v>2.76</v>
+        <v>8</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.18</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.22</v>
-      </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="I21" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4470,10 +4470,10 @@
         <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q21" t="n">
         <v>1.84</v>
@@ -4482,13 +4482,13 @@
         <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
         <v>1.7</v>
       </c>
       <c r="U21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4500,10 +4500,10 @@
         <v>17</v>
       </c>
       <c r="Y21" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA21" t="n">
         <v>70</v>
@@ -4533,7 +4533,7 @@
         <v>48</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
         <v>22</v>
@@ -4545,7 +4545,7 @@
         <v>75</v>
       </c>
       <c r="AN21" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO21" t="n">
         <v>38</v>
@@ -4554,13 +4554,13 @@
         <v>15.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4569,13 +4569,13 @@
         <v>7.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
         <v>10</v>
@@ -4584,29 +4584,29 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE21" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H22" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I22" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K22" t="n">
         <v>5.6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>5.7</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4661,25 +4661,25 @@
         <v>1.04</v>
       </c>
       <c r="N22" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P22" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="R22" t="n">
         <v>1.61</v>
       </c>
       <c r="S22" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
         <v>2.06</v>
@@ -4694,43 +4694,43 @@
         <v>25</v>
       </c>
       <c r="Y22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z22" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA22" t="n">
         <v>990</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE22" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL22" t="n">
         <v>32</v>
@@ -4739,37 +4739,37 @@
         <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AO22" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP22" t="n">
         <v>22</v>
       </c>
       <c r="AQ22" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AR22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS22" t="n">
         <v>100</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>40</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
@@ -4778,29 +4778,29 @@
         <v>21</v>
       </c>
       <c r="BA22" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC22" t="n">
         <v>12.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE22" t="n">
         <v>40</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG22" t="n">
         <v>42</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
         <v>1.61</v>
       </c>
       <c r="U23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4936,7 +4936,7 @@
         <v>21</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AP23" t="n">
         <v>18</v>
@@ -4963,7 +4963,7 @@
         <v>22</v>
       </c>
       <c r="AX23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY23" t="n">
         <v>11.5</v>
@@ -4978,7 +4978,7 @@
         <v>25</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD23" t="n">
         <v>28</v>
@@ -4987,14 +4987,14 @@
         <v>30</v>
       </c>
       <c r="BF23" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG23" t="n">
         <v>14</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5031,16 +5031,16 @@
         <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="I24" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K24" t="n">
         <v>4.4</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5052,10 +5052,10 @@
         <v>3.95</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q24" t="n">
         <v>1.97</v>
@@ -5082,13 +5082,13 @@
         <v>15.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z24" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AB24" t="n">
         <v>18</v>
@@ -5100,7 +5100,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
         <v>44</v>
@@ -5130,7 +5130,7 @@
         <v>110</v>
       </c>
       <c r="AO24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP24" t="n">
         <v>14.5</v>
@@ -5157,7 +5157,7 @@
         <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AY24" t="n">
         <v>20</v>
@@ -5175,20 +5175,20 @@
         <v>50</v>
       </c>
       <c r="BD24" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BE24" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="BF24" t="n">
         <v>38</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="G28" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H28" t="n">
-        <v>3.45</v>
+        <v>2.84</v>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.97</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.74</v>
+        <v>1.45</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
@@ -5986,31 +5986,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.86</v>
+        <v>2.14</v>
       </c>
       <c r="G29" t="n">
-        <v>3.55</v>
+        <v>2.36</v>
       </c>
       <c r="H29" t="n">
-        <v>2.26</v>
+        <v>3.45</v>
       </c>
       <c r="I29" t="n">
-        <v>2.54</v>
+        <v>4.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K29" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,37 +6175,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.93</v>
+        <v>2.86</v>
       </c>
       <c r="G30" t="n">
-        <v>2.32</v>
+        <v>3.55</v>
       </c>
       <c r="H30" t="n">
-        <v>3.4</v>
+        <v>2.26</v>
       </c>
       <c r="I30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K30" t="n">
         <v>4.4</v>
       </c>
-      <c r="J30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,36 +6369,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6.6</v>
+        <v>1.94</v>
       </c>
       <c r="G31" t="n">
-        <v>7.6</v>
+        <v>2.32</v>
       </c>
       <c r="H31" t="n">
-        <v>1.49</v>
+        <v>3.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1.52</v>
+        <v>4.4</v>
       </c>
       <c r="J31" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,66 +6563,66 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6631,310 +6631,698 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 07:50:51</t>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Scottish Premiership</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="J33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-02 10:04:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>42</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-02 10:04:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Independiente Yumbo</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Bogota</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F35" t="n">
         <v>1.04</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>1000</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H35" t="n">
         <v>1.04</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I35" t="n">
         <v>1000</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J35" t="n">
         <v>1.01</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K35" t="n">
         <v>1000</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q35" t="n">
         <v>1.01</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-02 07:50:51</t>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-02 10:04:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -814,7 +814,7 @@
         <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
         <v>48</v>
@@ -826,13 +826,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -844,7 +844,7 @@
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ2" t="n">
         <v>17</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
         <v>7.8</v>
@@ -883,44 +883,44 @@
         <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
         <v>7.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -966,10 +966,10 @@
         <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1175,10 +1175,10 @@
         <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
         <v>1.56</v>
@@ -1190,7 +1190,7 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.24</v>
@@ -1250,7 +1250,7 @@
         <v>7.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
@@ -1262,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1277,7 +1277,7 @@
         <v>48</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="n">
         <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G6" t="n">
         <v>1.36</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I10" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
         <v>2.22</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>4.2</v>
@@ -2354,7 +2354,7 @@
         <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>12</v>
       </c>
       <c r="Y10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z10" t="n">
         <v>50</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
         <v>8.6</v>
@@ -2387,7 +2387,7 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG10" t="n">
         <v>10</v>
@@ -2411,7 +2411,7 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2459,7 +2459,7 @@
         <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="n">
         <v>46</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>2.52</v>
       </c>
       <c r="G11" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
         <v>3.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.49</v>
       </c>
       <c r="G12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H12" t="n">
         <v>6.4</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -2891,40 +2891,40 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.22</v>
       </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="Q13" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="G14" t="n">
         <v>5.6</v>
@@ -3094,10 +3094,10 @@
         <v>1.65</v>
       </c>
       <c r="I14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
         <v>4.9</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
         <v>2.16</v>
@@ -3294,7 +3294,7 @@
         <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2.24</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>2.98</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -3867,10 +3867,10 @@
         <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I18" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
         <v>4.5</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="I19" t="n">
         <v>2.7</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="n">
         <v>1.64</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G21" t="n">
         <v>2.14</v>
       </c>
-      <c r="G21" t="n">
-        <v>2.18</v>
-      </c>
       <c r="H21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
         <v>3.85</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
         <v>3.75</v>
@@ -4467,25 +4467,25 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="T21" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U21" t="n">
         <v>2.36</v>
@@ -4497,19 +4497,19 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y21" t="n">
         <v>17</v>
       </c>
-      <c r="Y21" t="n">
-        <v>16.5</v>
-      </c>
       <c r="Z21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
         <v>70</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
         <v>8.199999999999999</v>
@@ -4533,7 +4533,7 @@
         <v>48</v>
       </c>
       <c r="AJ21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
         <v>22</v>
@@ -4542,7 +4542,7 @@
         <v>32</v>
       </c>
       <c r="AM21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN21" t="n">
         <v>13.5</v>
@@ -4557,22 +4557,22 @@
         <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS21" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX21" t="n">
         <v>13</v>
@@ -4581,32 +4581,32 @@
         <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BB21" t="n">
         <v>23</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -4679,10 +4679,10 @@
         <v>2.56</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4712,7 +4712,7 @@
         <v>32</v>
       </c>
       <c r="AE22" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF22" t="n">
         <v>9.4</v>
@@ -4724,13 +4724,13 @@
         <v>24</v>
       </c>
       <c r="AI22" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ22" t="n">
         <v>12.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL22" t="n">
         <v>32</v>
@@ -4742,28 +4742,28 @@
         <v>5.4</v>
       </c>
       <c r="AO22" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR22" t="n">
         <v>55</v>
       </c>
       <c r="AS22" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
         <v>40</v>
@@ -4775,10 +4775,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BB22" t="n">
         <v>11</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -4831,16 +4831,16 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G23" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H23" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I23" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="J23" t="n">
         <v>3.7</v>
@@ -4960,7 +4960,7 @@
         <v>10.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX23" t="n">
         <v>19.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
@@ -5058,19 +5058,19 @@
         <v>1.99</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
         <v>1.37</v>
       </c>
       <c r="S24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         <v>16</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
         <v>9.4</v>
@@ -5157,7 +5157,7 @@
         <v>16</v>
       </c>
       <c r="AX24" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AY24" t="n">
         <v>20</v>
@@ -5172,13 +5172,13 @@
         <v>42</v>
       </c>
       <c r="BC24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BD24" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE24" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="BF24" t="n">
         <v>38</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -6192,13 +6192,13 @@
         <v>2.86</v>
       </c>
       <c r="G30" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H30" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I30" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="J30" t="n">
         <v>3.65</v>
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
         <v>1.62</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>1.49</v>
       </c>
       <c r="I33" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="J33" t="n">
         <v>4.8</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G34" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H34" t="n">
         <v>2.68</v>
@@ -7010,7 +7010,7 @@
         <v>1.52</v>
       </c>
       <c r="U34" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7070,7 +7070,7 @@
         <v>14.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AP34" t="n">
         <v>22</v>
@@ -7106,7 +7106,7 @@
         <v>12.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB34" t="n">
         <v>32</v>
@@ -7115,20 +7115,20 @@
         <v>22</v>
       </c>
       <c r="BD34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE34" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BF34" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG34" t="n">
         <v>14</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 10:04:19</t>
+          <t>2026-03-02 11:37:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH35"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,146 +781,146 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.24</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>1.73</v>
       </c>
       <c r="T2" t="n">
-        <v>1.84</v>
+        <v>1.74</v>
       </c>
       <c r="U2" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
         <v>970</v>
       </c>
-      <c r="Y2" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>12</v>
-      </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>1.12</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.4</v>
+        <v>1.12</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.8</v>
+        <v>1.12</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>1.12</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.6</v>
+        <v>1.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>1.12</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>1.12</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>1.12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.6</v>
+        <v>1.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>1.12</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>1.12</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>1.12</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.4</v>
+        <v>1.12</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I3" t="n">
+        <v>110</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.4</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>1.91</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.27</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.72</v>
+        <v>1.05</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>1.05</v>
       </c>
       <c r="V3" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
         <v>970</v>
       </c>
-      <c r="Y3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>6</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.4</v>
+        <v>1.14</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>1.14</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>1.14</v>
       </c>
       <c r="AT3" t="n">
-        <v>13.5</v>
+        <v>1.14</v>
       </c>
       <c r="AU3" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="AW3" t="n">
-        <v>17.5</v>
+        <v>1.14</v>
       </c>
       <c r="AX3" t="n">
-        <v>7.4</v>
+        <v>1.14</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>1.14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.4</v>
+        <v>1.14</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>1.14</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.800000000000001</v>
+        <v>1.14</v>
       </c>
       <c r="BC3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.4</v>
+        <v>1.14</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>1.14</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>1.14</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1163,34 +1163,34 @@
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>1.07</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.61</v>
+        <v>1.18</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.22</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>1.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
         <v>1.24</v>
@@ -1202,16 +1202,16 @@
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
         <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
@@ -1235,7 +1235,7 @@
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1247,22 +1247,22 @@
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
         <v>48</v>
       </c>
       <c r="AP4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1274,7 +1274,7 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>48</v>
+        <v>7.2</v>
       </c>
       <c r="AX4" t="n">
         <v>10.5</v>
@@ -1283,10 +1283,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>46</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
@@ -1295,20 +1295,20 @@
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -1339,100 +1339,100 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>1.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I5" t="n">
         <v>4.1</v>
       </c>
-      <c r="I5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>1.34</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.62</v>
+        <v>1.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>4.2</v>
+        <v>1.49</v>
       </c>
       <c r="T5" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
@@ -1447,69 +1447,69 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Panathinaikos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K6" t="n">
+        <v>110</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.29</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="P6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>85</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC6" t="n">
         <v>13.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>16</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Juventus B</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AC Bra</t>
+          <t>Juventus B</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,66 +2295,66 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>AC Bra</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,123 +2363,123 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,61 +2494,61 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.52</v>
+        <v>1.75</v>
       </c>
       <c r="G11" t="n">
-        <v>2.76</v>
+        <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -2557,123 +2557,123 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="G12" t="n">
-        <v>1.63</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>1.39</v>
       </c>
       <c r="I12" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.24</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.54</v>
+        <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.05</v>
+        <v>1.66</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.18</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>1.18</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G16" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.46</v>
+        <v>1.17</v>
       </c>
       <c r="G17" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>1.17</v>
       </c>
       <c r="I17" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.54</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,37 +3847,37 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="G18" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>5.1</v>
+        <v>1.28</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K18" t="n">
         <v>4.5</v>
       </c>
-      <c r="K18" t="n">
-        <v>5.4</v>
-      </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.8</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.05</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="H19" t="n">
-        <v>2.44</v>
+        <v>1.42</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -4240,31 +4240,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>1.19</v>
       </c>
       <c r="G20" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6</v>
+        <v>1.19</v>
       </c>
       <c r="I20" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,66 +4429,66 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>1.27</v>
       </c>
       <c r="G21" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>1.42</v>
+        <v>1000</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="K22" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,116 +4691,116 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -4822,25 +4822,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="J23" t="n">
         <v>3.7</v>
@@ -4852,31 +4852,31 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="U23" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,116 +4885,116 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD23" t="n">
         <v>21</v>
       </c>
-      <c r="Y23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV23" t="n">
+      <c r="BE23" t="n">
+        <v>50</v>
+      </c>
+      <c r="BF23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>18</v>
-      </c>
       <c r="BG23" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -5016,61 +5016,61 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K24" t="n">
         <v>5.6</v>
       </c>
-      <c r="G24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="S24" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,123 +5079,123 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="Z24" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>17</v>
+        <v>990</v>
       </c>
       <c r="AB24" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>44</v>
-      </c>
       <c r="AG24" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="AH24" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>160</v>
+        <v>12.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>85</v>
+        <v>14</v>
       </c>
       <c r="AL24" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM24" t="n">
         <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>110</v>
+        <v>5.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX24" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV24" t="n">
+      <c r="AY24" t="n">
         <v>9.4</v>
       </c>
-      <c r="AW24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>20</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="BB24" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG24" t="n">
         <v>42</v>
       </c>
-      <c r="BC24" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>38</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,61 +5210,61 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ASD Pineto Calcio</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Forli</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,123 +5273,123 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,61 +5404,61 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,116 +5467,116 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>ASD Pineto Calcio</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Forli</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,31 +5986,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.98</v>
+        <v>1.24</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
@@ -6180,31 +6180,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.86</v>
+        <v>2.32</v>
       </c>
       <c r="G30" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="H30" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="I30" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="J30" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="K30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.32</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,36 +6369,36 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.94</v>
+        <v>1.29</v>
       </c>
       <c r="G31" t="n">
-        <v>2.32</v>
+        <v>1000</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="I31" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>1.03</v>
       </c>
       <c r="K31" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.4</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,36 +6563,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q32" t="n">
         <v>1.01</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,36 +6757,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>6.6</v>
+        <v>1.27</v>
       </c>
       <c r="G33" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>1.54</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="K33" t="n">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.48</v>
+        <v>1.15</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,66 +6951,66 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.66</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="R34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7019,310 +7019,698 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 11:37:52</t>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Scottish Premiership</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>17:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K35" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-02 13:49:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>680</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>85</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>36</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>14</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-02 13:49:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Independiente Yumbo</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Bogota</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F37" t="n">
         <v>1.04</v>
       </c>
-      <c r="G35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="G37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H37" t="n">
         <v>1.04</v>
       </c>
-      <c r="I35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J35" t="n">
+      <c r="I37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J37" t="n">
         <v>1.01</v>
       </c>
-      <c r="K35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
+      <c r="K37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q37" t="n">
         <v>1.01</v>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" t="inlineStr">
-        <is>
-          <t>2026-03-02 11:37:52</t>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-02 13:49:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.24</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>1.73</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.12</v>
+        <v>5.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.12</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.12</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.12</v>
+        <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.12</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.12</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.12</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.12</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.12</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.12</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.12</v>
+        <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.12</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>1.32</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM3" t="n">
         <v>110</v>
       </c>
-      <c r="J3" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN3" t="n">
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.14</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.14</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.14</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.14</v>
+        <v>6.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.14</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.14</v>
+        <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.14</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.14</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.14</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.14</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.14</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.14</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.14</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.14</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.14</v>
+        <v>7.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.14</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
@@ -1169,49 +1169,49 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>1.07</v>
+        <v>5.1</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V4" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.24</v>
-      </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
@@ -1223,46 +1223,46 @@
         <v>55</v>
       </c>
       <c r="AF4" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM4" t="n">
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1274,10 +1274,10 @@
         <v>17</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
@@ -1286,7 +1286,7 @@
         <v>15.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>44</v>
       </c>
       <c r="BB4" t="n">
         <v>16</v>
@@ -1295,20 +1295,20 @@
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.34</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.96</v>
       </c>
       <c r="I5" t="n">
         <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>1.34</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.49</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.49</v>
+        <v>5.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -1539,118 +1539,118 @@
         <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1.05</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>110</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W6" t="n">
         <v>3</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>100</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,44 +1659,44 @@
         <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
-        <v>90</v>
+        <v>8.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
         <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>85</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>100</v>
+        <v>8.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="J7" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>1.76</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I11" t="n">
         <v>5.9</v>
@@ -2521,152 +2521,152 @@
         <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S11" t="n">
         <v>4.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP11" t="n">
         <v>11</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AS11" t="n">
         <v>44</v>
       </c>
       <c r="AT11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>16.5</v>
+        <v>21</v>
       </c>
       <c r="AW11" t="n">
         <v>36</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="BA11" t="n">
         <v>40</v>
       </c>
       <c r="BB11" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BC11" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
         <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG11" t="n">
         <v>42</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O12" t="n">
         <v>1.39</v>
       </c>
-      <c r="G12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="I13" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.74</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -3279,170 +3279,170 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.18</v>
+        <v>2.36</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H15" t="n">
-        <v>1.18</v>
+        <v>2.38</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.17</v>
+        <v>1.82</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H17" t="n">
-        <v>1.17</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.42</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.28</v>
+        <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>1.28</v>
+        <v>3.45</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.42</v>
+        <v>2.46</v>
       </c>
       <c r="G19" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H19" t="n">
-        <v>1.42</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J19" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.19</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="H20" t="n">
-        <v>1.19</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="K20" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.27</v>
+        <v>1.56</v>
       </c>
       <c r="G21" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="H21" t="n">
         <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="J22" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -4861,22 +4861,22 @@
         <v>1.26</v>
       </c>
       <c r="P23" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T23" t="n">
         <v>1.67</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,67 +4885,67 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB23" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
         <v>11</v>
       </c>
       <c r="AH23" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
         <v>32</v>
       </c>
       <c r="AM23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP23" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
         <v>32</v>
@@ -4954,47 +4954,47 @@
         <v>10</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AX23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY23" t="n">
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -5028,13 +5028,13 @@
         <v>1.41</v>
       </c>
       <c r="G24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="H24" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
         <v>5.5</v>
@@ -5058,19 +5058,19 @@
         <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R24" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S24" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="T24" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,40 +5079,40 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y24" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA24" t="n">
         <v>990</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC24" t="n">
         <v>12.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="n">
         <v>12.5</v>
@@ -5121,22 +5121,22 @@
         <v>14</v>
       </c>
       <c r="AL24" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP24" t="n">
         <v>21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AR24" t="n">
         <v>50</v>
@@ -5145,13 +5145,13 @@
         <v>50</v>
       </c>
       <c r="AT24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU24" t="n">
         <v>11.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AW24" t="n">
         <v>40</v>
@@ -5175,7 +5175,7 @@
         <v>13</v>
       </c>
       <c r="BD24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE24" t="n">
         <v>40</v>
@@ -5184,11 +5184,11 @@
         <v>5.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -5246,25 +5246,25 @@
         <v>4.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
         <v>1.74</v>
       </c>
       <c r="R25" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U25" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,19 +5273,19 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
@@ -5294,13 +5294,13 @@
         <v>11.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
         <v>14.5</v>
@@ -5309,80 +5309,80 @@
         <v>32</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
         <v>65</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AT25" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW25" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>13.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BB25" t="n">
         <v>25</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="BD25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BF25" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -5443,7 +5443,7 @@
         <v>1.33</v>
       </c>
       <c r="P26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
@@ -5458,7 +5458,7 @@
         <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y26" t="n">
         <v>8</v>
@@ -5476,10 +5476,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AC26" t="n">
         <v>9.199999999999999</v>
@@ -5497,28 +5497,28 @@
         <v>22</v>
       </c>
       <c r="AH26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI26" t="n">
         <v>38</v>
       </c>
       <c r="AJ26" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="n">
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP26" t="n">
         <v>14.5</v>
@@ -5530,7 +5530,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT26" t="n">
         <v>16.5</v>
@@ -5545,10 +5545,10 @@
         <v>16.5</v>
       </c>
       <c r="AX26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ26" t="n">
         <v>21</v>
@@ -5569,14 +5569,14 @@
         <v>42</v>
       </c>
       <c r="BF26" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="BG26" t="n">
         <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -6189,19 +6189,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G30" t="n">
         <v>2.48</v>
       </c>
       <c r="H30" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="I30" t="n">
         <v>2.96</v>
       </c>
       <c r="J30" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K30" t="n">
         <v>4.3</v>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>2.96</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>2.58</v>
       </c>
       <c r="H31" t="n">
-        <v>1.29</v>
+        <v>2.98</v>
       </c>
       <c r="I31" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J31" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="K31" t="n">
         <v>950</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.27</v>
+        <v>2.7</v>
       </c>
       <c r="G32" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="H32" t="n">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="J32" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -6771,19 +6771,19 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.27</v>
+        <v>1.81</v>
       </c>
       <c r="G33" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="H33" t="n">
-        <v>1.27</v>
+        <v>3.1</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J33" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="K33" t="n">
         <v>950</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="G35" t="n">
         <v>7.6</v>
       </c>
       <c r="H35" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I35" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="J35" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K35" t="n">
-        <v>7.8</v>
+        <v>5.5</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -7189,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q35" t="n">
         <v>1.59</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G36" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H36" t="n">
         <v>2.7</v>
       </c>
-      <c r="H36" t="n">
-        <v>2.68</v>
-      </c>
       <c r="I36" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K36" t="n">
         <v>3.85</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.9</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7377,28 +7377,28 @@
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P36" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R36" t="n">
         <v>1.65</v>
       </c>
       <c r="S36" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="T36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U36" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -7407,19 +7407,19 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Y36" t="n">
-        <v>680</v>
+        <v>17.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB36" t="n">
-        <v>85</v>
+        <v>17.5</v>
       </c>
       <c r="AC36" t="n">
         <v>9.4</v>
@@ -7428,49 +7428,49 @@
         <v>12.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
         <v>13</v>
       </c>
       <c r="AI36" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM36" t="n">
         <v>48</v>
       </c>
       <c r="AN36" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO36" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AP36" t="n">
         <v>22</v>
       </c>
       <c r="AQ36" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT36" t="n">
         <v>16</v>
@@ -7479,10 +7479,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX36" t="n">
         <v>19.5</v>
@@ -7494,29 +7494,29 @@
         <v>12.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB36" t="n">
         <v>32</v>
       </c>
       <c r="BC36" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE36" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BF36" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG36" t="n">
         <v>13.5</v>
       </c>
-      <c r="BG36" t="n">
-        <v>14</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 13:49:13</t>
+          <t>2026-03-02 16:00:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="G2" t="n">
         <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -826,10 +826,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
         <v>85</v>
@@ -859,7 +859,7 @@
         <v>140</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
@@ -871,10 +871,10 @@
         <v>17</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -886,7 +886,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
         <v>9.199999999999999</v>
@@ -898,7 +898,7 @@
         <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -910,17 +910,17 @@
         <v>6.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -951,16 +951,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
@@ -972,7 +972,7 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
         <v>3.85</v>
@@ -987,7 +987,7 @@
         <v>1.88</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S3" t="n">
         <v>3.25</v>
@@ -999,10 +999,10 @@
         <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
@@ -1014,7 +1014,7 @@
         <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AB3" t="n">
         <v>970</v>
@@ -1059,7 +1059,7 @@
         <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.6</v>
@@ -1083,38 +1083,38 @@
         <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BG3" t="n">
         <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1247,7 @@
         <v>75</v>
       </c>
       <c r="AN4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
         <v>44</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
         <v>1.45</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
         <v>2.52</v>
@@ -1384,7 +1384,7 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
@@ -1462,7 +1462,7 @@
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>4.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="H7" t="n">
         <v>13.5</v>
@@ -1757,13 +1757,13 @@
         <v>1.29</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
         <v>1.86</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
         <v>3.25</v>
@@ -1778,10 +1778,10 @@
         <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="X7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Y7" t="n">
         <v>44</v>
@@ -1829,7 +1829,7 @@
         <v>370</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,25 +1838,25 @@
         <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX7" t="n">
         <v>6</v>
@@ -1865,32 +1865,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
         <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF7" t="n">
         <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H11" t="n">
         <v>5.7</v>
@@ -2515,13 +2515,13 @@
         <v>5.9</v>
       </c>
       <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.85</v>
       </c>
-      <c r="K11" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2542,7 +2542,7 @@
         <v>1.28</v>
       </c>
       <c r="S11" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
         <v>2.14</v>
@@ -2554,7 +2554,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2602,7 +2602,7 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN11" t="n">
         <v>14</v>
@@ -2617,7 +2617,7 @@
         <v>15</v>
       </c>
       <c r="AR11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS11" t="n">
         <v>44</v>
@@ -2644,7 +2644,7 @@
         <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB11" t="n">
         <v>16</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2715,10 +2715,10 @@
         <v>3.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
         <v>3.25</v>
@@ -2742,7 +2742,7 @@
         <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="V12" t="n">
         <v>1.41</v>
@@ -2751,10 +2751,10 @@
         <v>1.58</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
         <v>25</v>
@@ -2811,7 +2811,7 @@
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS12" t="n">
         <v>5.6</v>
@@ -2829,7 +2829,7 @@
         <v>5.3</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
@@ -2838,16 +2838,16 @@
         <v>4.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BC12" t="n">
         <v>5.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE12" t="n">
         <v>5.8</v>
@@ -2856,11 +2856,11 @@
         <v>21</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.4</v>
+        <v>30</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -2945,7 +2945,7 @@
         <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y13" t="n">
         <v>9.4</v>
@@ -2963,10 +2963,10 @@
         <v>12</v>
       </c>
       <c r="AD13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF13" t="n">
         <v>80</v>
@@ -2975,7 +2975,7 @@
         <v>36</v>
       </c>
       <c r="AH13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI13" t="n">
         <v>50</v>
@@ -2996,7 +2996,7 @@
         <v>220</v>
       </c>
       <c r="AO13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP13" t="n">
         <v>13</v>
@@ -3023,7 +3023,7 @@
         <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AY13" t="n">
         <v>22</v>
@@ -3032,29 +3032,29 @@
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.9</v>
@@ -3112,13 +3112,13 @@
         <v>2.06</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R14" t="n">
         <v>1.41</v>
@@ -3133,7 +3133,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
         <v>2.34</v>
@@ -3193,7 +3193,7 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>19</v>
@@ -3208,25 +3208,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW14" t="n">
         <v>50</v>
       </c>
       <c r="AX14" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB14" t="n">
         <v>10.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         <v>2.08</v>
       </c>
       <c r="O15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P15" t="n">
         <v>2.08</v>
@@ -3327,7 +3327,7 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
         <v>1.43</v>
@@ -3387,19 +3387,19 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
         <v>27</v>
       </c>
       <c r="AT15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
         <v>7.2</v>
@@ -3408,7 +3408,7 @@
         <v>9.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
         <v>16</v>
@@ -3426,10 +3426,10 @@
         <v>28</v>
       </c>
       <c r="BC15" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE15" t="n">
         <v>40</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
         <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.46</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3712,7 @@
         <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
         <v>1.28</v>
@@ -3769,68 +3769,68 @@
         <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.18</v>
+        <v>2.66</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.02</v>
+        <v>2.42</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.08</v>
+        <v>2.52</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="AX17" t="n">
         <v>10.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.1</v>
+        <v>2.52</v>
       </c>
       <c r="BD17" t="n">
         <v>19</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.24</v>
+        <v>2.72</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.28</v>
+        <v>5.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
         <v>3.45</v>
@@ -3882,7 +3882,7 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N18" t="n">
         <v>4.2</v>
@@ -3900,13 +3900,13 @@
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T18" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
         <v>1.29</v>
@@ -3921,43 +3921,43 @@
         <v>19</v>
       </c>
       <c r="Z18" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AA18" t="n">
         <v>80</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>48</v>
       </c>
       <c r="AF18" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
         <v>90</v>
@@ -3969,62 +3969,62 @@
         <v>40</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.3</v>
+        <v>4.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.6</v>
+        <v>19.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.3</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF18" t="n">
         <v>10</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>2.46</v>
       </c>
       <c r="G19" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H19" t="n">
         <v>3.3</v>
@@ -4073,16 +4073,16 @@
         <v>3.25</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P19" t="n">
         <v>1.53</v>
@@ -4091,134 +4091,134 @@
         <v>2.52</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4267,16 +4267,16 @@
         <v>5.3</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
         <v>2.78</v>
@@ -4285,134 +4285,134 @@
         <v>1.45</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.56</v>
+        <v>3.05</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65</v>
+        <v>3.45</v>
       </c>
       <c r="H21" t="n">
-        <v>6.6</v>
+        <v>2.48</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>2.74</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1.56</v>
       </c>
       <c r="G22" t="n">
-        <v>3.45</v>
+        <v>1.65</v>
       </c>
       <c r="H22" t="n">
-        <v>2.44</v>
+        <v>6.6</v>
       </c>
       <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X22" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>2.76</v>
       </c>
-      <c r="J22" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>FC Zurich</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Lausanne</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>110</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.85</v>
+        <v>2.44</v>
       </c>
       <c r="J23" t="n">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="K23" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>4.7</v>
+        <v>2.14</v>
       </c>
       <c r="O23" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.78</v>
+        <v>1.54</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>1.55</v>
       </c>
       <c r="T23" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X23" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.41</v>
+        <v>1.94</v>
       </c>
       <c r="G24" t="n">
-        <v>1.42</v>
+        <v>2.52</v>
       </c>
       <c r="H24" t="n">
-        <v>8.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="J24" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>1.81</v>
       </c>
       <c r="O24" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="R24" t="n">
-        <v>1.59</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.64</v>
+        <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="G25" t="n">
-        <v>2.86</v>
+        <v>2.48</v>
       </c>
       <c r="H25" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="I25" t="n">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N25" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>2.06</v>
       </c>
       <c r="T25" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="U25" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X25" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="Z25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>19.5</v>
       </c>
-      <c r="AA25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AR25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV25" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>11</v>
       </c>
       <c r="AW25" t="n">
         <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB25" t="n">
         <v>28</v>
       </c>
-      <c r="BB25" t="n">
-        <v>25</v>
-      </c>
       <c r="BC25" t="n">
-        <v>23</v>
+        <v>8.6</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BE25" t="n">
-        <v>32</v>
+        <v>10.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>17.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>1.02</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>3.85</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>3.65</v>
+        <v>1.3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
         <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
         <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="G30" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="H30" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="I30" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="J30" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K30" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P30" t="n">
-        <v>2.96</v>
+        <v>2.26</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="G31" t="n">
-        <v>2.58</v>
+        <v>1.42</v>
       </c>
       <c r="H31" t="n">
-        <v>2.98</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
-        <v>3.25</v>
+        <v>5.4</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>2.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FC Zurich</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lausanne</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I32" t="n">
         <v>3.9</v>
       </c>
-      <c r="H32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.78</v>
-      </c>
       <c r="J32" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="G33" t="n">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="I33" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K33" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P33" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q33" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R33" t="n">
         <v>1.47</v>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,186 +7150,186 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
+        <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>1.54</v>
+        <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
-        <v>2.46</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,378 +7339,572 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="G36" t="n">
-        <v>2.72</v>
+        <v>7.6</v>
       </c>
       <c r="H36" t="n">
-        <v>2.7</v>
+        <v>1.49</v>
       </c>
       <c r="I36" t="n">
-        <v>2.72</v>
+        <v>1.54</v>
       </c>
       <c r="J36" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="K36" t="n">
-        <v>3.85</v>
+        <v>5.5</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M36" t="n">
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>2.46</v>
       </c>
       <c r="O36" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R36" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="S36" t="n">
-        <v>2.46</v>
+        <v>2.18</v>
       </c>
       <c r="T36" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X36" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="AB36" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AD36" t="n">
         <v>12.5</v>
       </c>
       <c r="AE36" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH36" t="n">
         <v>25</v>
       </c>
-      <c r="AF36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>13</v>
-      </c>
       <c r="AI36" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AJ36" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="AL36" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD36" t="n">
         <v>48</v>
       </c>
-      <c r="AN36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>26</v>
-      </c>
       <c r="BE36" t="n">
-        <v>42</v>
+        <v>2.36</v>
       </c>
       <c r="BF36" t="n">
-        <v>13</v>
+        <v>2.36</v>
       </c>
       <c r="BG36" t="n">
-        <v>13.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 16:00:54</t>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>English Premier League</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>17:15:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Newcastle</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Man Utd</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N37" t="n">
+        <v>6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X37" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-02 18:12:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
           <t>Colombian Primera B</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Independiente Yumbo</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Bogota</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F38" t="n">
         <v>1.04</v>
       </c>
-      <c r="G37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="G38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H38" t="n">
         <v>1.04</v>
       </c>
-      <c r="I37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="I38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L38" t="n">
         <v>0</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M38" t="n">
         <v>0</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>0</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P38" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R37" t="n">
+      <c r="Q38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R38" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S38" t="n">
         <v>0</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T38" t="n">
         <v>0</v>
       </c>
-      <c r="U37" t="n">
+      <c r="U38" t="n">
         <v>0</v>
       </c>
-      <c r="V37" t="n">
+      <c r="V38" t="n">
         <v>0</v>
       </c>
-      <c r="W37" t="n">
+      <c r="W38" t="n">
         <v>0</v>
       </c>
-      <c r="X37" t="n">
+      <c r="X38" t="n">
         <v>0</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y38" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="Z38" t="n">
         <v>0</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AA38" t="n">
         <v>0</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AB38" t="n">
         <v>0</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AC38" t="n">
         <v>0</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AD38" t="n">
         <v>0</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AE38" t="n">
         <v>0</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AF38" t="n">
         <v>0</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AG38" t="n">
         <v>0</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AH38" t="n">
         <v>0</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AI38" t="n">
         <v>0</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AJ38" t="n">
         <v>0</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AK38" t="n">
         <v>0</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AL38" t="n">
         <v>0</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AM38" t="n">
         <v>0</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AN38" t="n">
         <v>0</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AO38" t="n">
         <v>0</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AP38" t="n">
         <v>0</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AQ38" t="n">
         <v>0</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AR38" t="n">
         <v>0</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AS38" t="n">
         <v>0</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AU38" t="n">
         <v>0</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AV38" t="n">
         <v>0</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AW38" t="n">
         <v>0</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AX38" t="n">
         <v>0</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="AY38" t="n">
         <v>0</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="AZ38" t="n">
         <v>0</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BA38" t="n">
         <v>0</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB38" t="n">
         <v>0</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BC38" t="n">
         <v>0</v>
       </c>
-      <c r="BD37" t="n">
+      <c r="BD38" t="n">
         <v>0</v>
       </c>
-      <c r="BE37" t="n">
+      <c r="BE38" t="n">
         <v>0</v>
       </c>
-      <c r="BF37" t="n">
+      <c r="BF38" t="n">
         <v>0</v>
       </c>
-      <c r="BG37" t="n">
+      <c r="BG38" t="n">
         <v>0</v>
       </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>2026-03-02 16:00:54</t>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-02 18:12:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -790,28 +790,28 @@
         <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
         <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
@@ -820,13 +820,13 @@
         <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD2" t="n">
         <v>950</v>
@@ -856,7 +856,7 @@
         <v>36</v>
       </c>
       <c r="AM2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN2" t="n">
         <v>11</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ2" t="n">
         <v>17</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -886,7 +886,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
         <v>9.199999999999999</v>
@@ -898,7 +898,7 @@
         <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -907,20 +907,20 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I3" t="n">
         <v>2.12</v>
@@ -1002,7 +1002,7 @@
         <v>1.89</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
@@ -1020,7 +1020,7 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
         <v>11</v>
@@ -1095,10 +1095,10 @@
         <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD3" t="n">
         <v>44</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.21</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1345,25 +1345,25 @@
         <v>2.54</v>
       </c>
       <c r="H5" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
         <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
         <v>1.52</v>
@@ -1372,7 +1372,7 @@
         <v>1.52</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1384,7 +1384,7 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
         <v>1.33</v>
@@ -1450,7 +1450,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
         <v>4.9</v>
@@ -1462,7 +1462,7 @@
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="AV5" t="n">
         <v>4.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="H6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>1.39</v>
@@ -1557,25 +1557,25 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="O6" t="n">
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S6" t="n">
         <v>3.3</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U6" t="n">
         <v>1.75</v>
@@ -1599,7 +1599,7 @@
         <v>430</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC6" t="n">
         <v>11</v>
@@ -1611,7 +1611,7 @@
         <v>200</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG6" t="n">
         <v>11</v>
@@ -1647,10 +1647,10 @@
         <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,10 +1659,10 @@
         <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6" t="n">
         <v>7</v>
@@ -1674,7 +1674,7 @@
         <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
         <v>10.5</v>
@@ -1686,17 +1686,17 @@
         <v>36</v>
       </c>
       <c r="BE6" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF6" t="n">
         <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G7" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H7" t="n">
         <v>13.5</v>
@@ -1778,7 +1778,7 @@
         <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
         <v>18</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O8" t="n">
         <v>1.35</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O9" t="n">
         <v>1.34</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
         <v>5.7</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
@@ -2527,7 +2527,7 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.41</v>
@@ -2536,7 +2536,7 @@
         <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
         <v>1.28</v>
@@ -2566,7 +2566,7 @@
         <v>44</v>
       </c>
       <c r="AA11" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AB11" t="n">
         <v>7</v>
@@ -2587,7 +2587,7 @@
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI11" t="n">
         <v>110</v>
@@ -2611,7 +2611,7 @@
         <v>150</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>15</v>
@@ -2626,10 +2626,10 @@
         <v>6.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW11" t="n">
         <v>36</v>
@@ -2644,7 +2644,7 @@
         <v>22</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB11" t="n">
         <v>16</v>
@@ -2653,7 +2653,7 @@
         <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE11" t="n">
         <v>46</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
         <v>2.72</v>
@@ -2712,7 +2712,7 @@
         <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2742,7 +2742,7 @@
         <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V12" t="n">
         <v>1.41</v>
@@ -2751,7 +2751,7 @@
         <v>1.58</v>
       </c>
       <c r="X12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -2811,10 +2811,10 @@
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -2823,44 +2823,44 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.3</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA12" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB12" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB12" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC12" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF12" t="n">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="BG12" t="n">
         <v>30</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="G13" t="n">
         <v>8.4</v>
@@ -2903,7 +2903,7 @@
         <v>1.62</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
         <v>5.1</v>
@@ -2984,13 +2984,13 @@
         <v>310</v>
       </c>
       <c r="AK13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL13" t="n">
         <v>140</v>
       </c>
       <c r="AM13" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN13" t="n">
         <v>220</v>
@@ -3014,7 +3014,7 @@
         <v>19.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV13" t="n">
         <v>8.800000000000001</v>
@@ -3023,7 +3023,7 @@
         <v>15</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY13" t="n">
         <v>22</v>
@@ -3041,7 +3041,7 @@
         <v>4.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE13" t="n">
         <v>4.5</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3109,16 +3109,16 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="O14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R14" t="n">
         <v>1.41</v>
@@ -3127,7 +3127,7 @@
         <v>2.36</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U14" t="n">
         <v>1.01</v>
@@ -3193,52 +3193,52 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3303,22 +3303,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
         <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
         <v>1.46</v>
@@ -3515,7 +3515,7 @@
         <v>2.22</v>
       </c>
       <c r="T16" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
         <v>1.01</v>
@@ -3578,65 +3578,65 @@
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.99</v>
+        <v>2.48</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.88</v>
+        <v>2.32</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.98</v>
+        <v>2.48</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.85</v>
+        <v>2.26</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AX16" t="n">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.04</v>
+        <v>2.56</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.06</v>
+        <v>2.58</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H18" t="n">
         <v>3.45</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
@@ -3894,22 +3894,22 @@
         <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R18" t="n">
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
         <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="V18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
         <v>1.77</v>
@@ -3954,7 +3954,7 @@
         <v>30</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL18" t="n">
         <v>38</v>
@@ -3969,7 +3969,7 @@
         <v>40</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AQ18" t="n">
         <v>12.5</v>
@@ -3981,13 +3981,13 @@
         <v>4.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="AV18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
         <v>4.5</v>
@@ -3996,19 +3996,19 @@
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>4.1</v>
       </c>
       <c r="BD18" t="n">
         <v>4.4</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G19" t="n">
         <v>2.64</v>
@@ -4070,7 +4070,7 @@
         <v>2.98</v>
       </c>
       <c r="K19" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4109,7 +4109,7 @@
         <v>1.61</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y19" t="n">
         <v>10.5</v>
@@ -4172,7 +4172,7 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -4184,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX19" t="n">
         <v>12.5</v>
@@ -4196,29 +4196,29 @@
         <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
       </c>
       <c r="BC19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BD19" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF19" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE19" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>1.69</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
         <v>6.2</v>
@@ -4369,16 +4369,16 @@
         <v>3</v>
       </c>
       <c r="AT20" t="n">
-        <v>10</v>
+        <v>2.52</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.86</v>
+        <v>42</v>
       </c>
       <c r="AX20" t="n">
         <v>9.800000000000001</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
         <v>3.25</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G22" t="n">
         <v>1.65</v>
@@ -4664,7 +4664,7 @@
         <v>2.06</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P22" t="n">
         <v>2.06</v>
@@ -4679,7 +4679,7 @@
         <v>2.72</v>
       </c>
       <c r="T22" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="U22" t="n">
         <v>1.87</v>
@@ -4760,7 +4760,7 @@
         <v>2.42</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV22" t="n">
         <v>2.8</v>
@@ -4772,7 +4772,7 @@
         <v>2.48</v>
       </c>
       <c r="AY22" t="n">
-        <v>2.48</v>
+        <v>8.4</v>
       </c>
       <c r="AZ22" t="n">
         <v>2.76</v>
@@ -4781,7 +4781,7 @@
         <v>3.05</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.66</v>
+        <v>12</v>
       </c>
       <c r="BC22" t="n">
         <v>2.68</v>
@@ -4793,14 +4793,14 @@
         <v>3.05</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG22" t="n">
         <v>3.05</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>3.55</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="I23" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="J23" t="n">
-        <v>2.98</v>
+        <v>2.68</v>
       </c>
       <c r="K23" t="n">
         <v>4.7</v>
@@ -4867,10 +4867,10 @@
         <v>1.54</v>
       </c>
       <c r="R23" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W23" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="G24" t="n">
         <v>2.52</v>
@@ -5034,13 +5034,13 @@
         <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3.55</v>
+        <v>2.6</v>
       </c>
       <c r="K24" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5055,10 +5055,10 @@
         <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="R24" t="n">
         <v>1.3</v>
@@ -5067,16 +5067,16 @@
         <v>2.84</v>
       </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G25" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H25" t="n">
         <v>2.88</v>
       </c>
       <c r="I25" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="J25" t="n">
         <v>3.95</v>
@@ -5264,13 +5264,13 @@
         <v>1.44</v>
       </c>
       <c r="U25" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X25" t="n">
         <v>32</v>
@@ -5294,7 +5294,7 @@
         <v>14</v>
       </c>
       <c r="AE25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF25" t="n">
         <v>22</v>
@@ -5339,7 +5339,7 @@
         <v>10.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU25" t="n">
         <v>9.4</v>
@@ -5351,7 +5351,7 @@
         <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AY25" t="n">
         <v>9.800000000000001</v>
@@ -5366,7 +5366,7 @@
         <v>28</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD25" t="n">
         <v>22</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.3</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
         <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
         <v>1.3</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.37</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6046,7 +6046,7 @@
         <v>2.42</v>
       </c>
       <c r="W29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
@@ -6118,7 +6118,7 @@
         <v>17</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV29" t="n">
         <v>9.4</v>
@@ -6148,7 +6148,7 @@
         <v>65</v>
       </c>
       <c r="BE29" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF29" t="n">
         <v>90</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.82</v>
       </c>
       <c r="G30" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H30" t="n">
         <v>2.62</v>
@@ -6228,19 +6228,19 @@
         <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T30" t="n">
         <v>1.62</v>
       </c>
       <c r="U30" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V30" t="n">
         <v>1.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X30" t="n">
         <v>19</v>
@@ -6282,7 +6282,7 @@
         <v>46</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL30" t="n">
         <v>36</v>
@@ -6294,7 +6294,7 @@
         <v>20</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP30" t="n">
         <v>17.5</v>
@@ -6303,7 +6303,7 @@
         <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS30" t="n">
         <v>34</v>
@@ -6321,7 +6321,7 @@
         <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AY30" t="n">
         <v>11.5</v>
@@ -6333,26 +6333,26 @@
         <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BC30" t="n">
         <v>25</v>
       </c>
       <c r="BD30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE30" t="n">
         <v>55</v>
       </c>
       <c r="BF30" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG30" t="n">
         <v>16</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6413,10 +6413,10 @@
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R31" t="n">
         <v>1.58</v>
@@ -6425,7 +6425,7 @@
         <v>2.68</v>
       </c>
       <c r="T31" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U31" t="n">
         <v>2.04</v>
@@ -6437,7 +6437,7 @@
         <v>3.35</v>
       </c>
       <c r="X31" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y31" t="n">
         <v>34</v>
@@ -6446,10 +6446,10 @@
         <v>80</v>
       </c>
       <c r="AA31" t="n">
-        <v>990</v>
+        <v>290</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>12</v>
@@ -6464,7 +6464,7 @@
         <v>9</v>
       </c>
       <c r="AG31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH31" t="n">
         <v>24</v>
@@ -6491,13 +6491,13 @@
         <v>120</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AS31" t="n">
         <v>50</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6589,10 +6589,10 @@
         <v>3.9</v>
       </c>
       <c r="J32" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.36</v>
@@ -6619,7 +6619,7 @@
         <v>2.98</v>
       </c>
       <c r="T32" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U32" t="n">
         <v>2.4</v>
@@ -6655,7 +6655,7 @@
         <v>40</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG32" t="n">
         <v>10.5</v>
@@ -6697,7 +6697,7 @@
         <v>60</v>
       </c>
       <c r="AT32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU32" t="n">
         <v>8</v>
@@ -6718,7 +6718,7 @@
         <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB32" t="n">
         <v>23</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G33" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I33" t="n">
         <v>2.18</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.2</v>
       </c>
       <c r="J33" t="n">
         <v>3.75</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L33" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
         <v>1.06</v>
@@ -6804,13 +6804,13 @@
         <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R33" t="n">
         <v>1.47</v>
       </c>
       <c r="S33" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
         <v>1.67</v>
@@ -6819,7 +6819,7 @@
         <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W33" t="n">
         <v>1.37</v>
@@ -6894,10 +6894,10 @@
         <v>15</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV33" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
         <v>19</v>
@@ -6927,14 +6927,14 @@
         <v>50</v>
       </c>
       <c r="BF33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG33" t="n">
         <v>12</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -6965,170 +6965,170 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I34" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="O34" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P34" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T34" t="n">
         <v>1.48</v>
       </c>
-      <c r="S34" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T34" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V34" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>1.74</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Y34" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="Z34" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB34" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AC34" t="n">
         <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF34" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AG34" t="n">
         <v>970</v>
       </c>
       <c r="AH34" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK34" t="n">
         <v>23</v>
       </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>28</v>
-      </c>
       <c r="AL34" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN34" t="n">
         <v>970</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.06</v>
+        <v>3.65</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.12</v>
+        <v>3.85</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="AT34" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.93</v>
+        <v>3.15</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.22</v>
+        <v>3.9</v>
       </c>
       <c r="AX34" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.96</v>
+        <v>3.25</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.22</v>
+        <v>3.95</v>
       </c>
       <c r="BB34" t="n">
-        <v>2.1</v>
+        <v>3.75</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.42</v>
@@ -7267,52 +7267,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7359,13 +7359,13 @@
         <v>7.6</v>
       </c>
       <c r="H36" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="I36" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="J36" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K36" t="n">
         <v>5.5</v>
@@ -7377,13 +7377,13 @@
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O36" t="n">
         <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q36" t="n">
         <v>1.59</v>
@@ -7395,128 +7395,128 @@
         <v>2.18</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="W36" t="n">
         <v>1.15</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Y36" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC36" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AD36" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AE36" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF36" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG36" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI36" t="n">
         <v>32</v>
       </c>
-      <c r="AH36" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>34</v>
-      </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AK36" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AL36" t="n">
         <v>85</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.36</v>
+        <v>20</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2</v>
+        <v>9.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.06</v>
+        <v>12</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.22</v>
+        <v>5.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="AV36" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.08</v>
+        <v>11.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>2.28</v>
+        <v>5.9</v>
       </c>
       <c r="AY36" t="n">
-        <v>19.5</v>
+        <v>5.3</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.16</v>
+        <v>17</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>2.36</v>
+        <v>6.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="BD36" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.36</v>
+        <v>6</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.36</v>
+        <v>55</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.36</v>
+        <v>4.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
         <v>1.19</v>
       </c>
       <c r="P37" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q37" t="n">
         <v>1.58</v>
@@ -7664,7 +7664,7 @@
         <v>20</v>
       </c>
       <c r="AS37" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT37" t="n">
         <v>16</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>
@@ -7727,17 +7727,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -7753,158 +7753,352 @@
         <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K38" t="n">
         <v>1000</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P38" t="n">
         <v>1.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 18:12:17</t>
+          <t>2026-03-02 20:22:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Colombian Primera B</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Independiente Yumbo</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Bogota</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-02 20:22:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -778,10 +778,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
@@ -796,7 +796,7 @@
         <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
@@ -811,13 +811,13 @@
         <v>2.38</v>
       </c>
       <c r="X2" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y2" t="n">
         <v>21</v>
       </c>
-      <c r="Y2" t="n">
-        <v>22</v>
-      </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA2" t="n">
         <v>180</v>
@@ -829,10 +829,10 @@
         <v>12</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -844,13 +844,13 @@
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL2" t="n">
         <v>36</v>
@@ -859,22 +859,22 @@
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -883,22 +883,22 @@
         <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>60</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY2" t="n">
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>6.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -907,20 +907,20 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -981,7 +981,7 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
         <v>1.88</v>
@@ -1011,19 +1011,19 @@
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
         <v>23</v>
@@ -1032,10 +1032,10 @@
         <v>32</v>
       </c>
       <c r="AG3" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
         <v>36</v>
@@ -1044,7 +1044,7 @@
         <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
@@ -1059,7 +1059,7 @@
         <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.6</v>
@@ -1068,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
@@ -1083,38 +1083,38 @@
         <v>17.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA3" t="n">
         <v>6.2</v>
       </c>
-      <c r="BA3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD3" t="n">
         <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="BF3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BG3" t="n">
         <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1175,16 +1175,16 @@
         <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
         <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
         <v>1.67</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H5" t="n">
         <v>3.2</v>
@@ -1354,16 +1354,16 @@
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
         <v>1.52</v>
@@ -1390,7 +1390,7 @@
         <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1447,7 +1447,7 @@
         <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.2</v>
@@ -1471,7 +1471,7 @@
         <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
         <v>4.1</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1536,22 +1536,22 @@
         <v>1.46</v>
       </c>
       <c r="G6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1563,7 +1563,7 @@
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q6" t="n">
         <v>1.9</v>
@@ -1572,7 +1572,7 @@
         <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
         <v>2.14</v>
@@ -1584,31 +1584,31 @@
         <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z6" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA6" t="n">
-        <v>430</v>
+        <v>470</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AE6" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AF6" t="n">
         <v>8.4</v>
@@ -1617,13 +1617,13 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AI6" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK6" t="n">
         <v>18</v>
@@ -1632,40 +1632,40 @@
         <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO6" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AY6" t="n">
         <v>9.199999999999999</v>
@@ -1674,29 +1674,29 @@
         <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>36</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
         <v>1.33</v>
@@ -1736,10 +1736,10 @@
         <v>13.5</v>
       </c>
       <c r="I7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="K7" t="n">
         <v>6.2</v>
@@ -1748,31 +1748,31 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
         <v>1.05</v>
@@ -1781,116 +1781,116 @@
         <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>430</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G11" t="n">
         <v>1.78</v>
       </c>
       <c r="H11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I11" t="n">
         <v>5.8</v>
@@ -2530,7 +2530,7 @@
         <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P11" t="n">
         <v>1.77</v>
@@ -2545,7 +2545,7 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U11" t="n">
         <v>1.84</v>
@@ -2560,7 +2560,7 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z11" t="n">
         <v>44</v>
@@ -2569,22 +2569,22 @@
         <v>170</v>
       </c>
       <c r="AB11" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC11" t="n">
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE11" t="n">
         <v>95</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
         <v>24</v>
@@ -2608,10 +2608,10 @@
         <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ11" t="n">
         <v>15</v>
@@ -2635,7 +2635,7 @@
         <v>36</v>
       </c>
       <c r="AX11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY11" t="n">
         <v>9.6</v>
@@ -2647,10 +2647,10 @@
         <v>40</v>
       </c>
       <c r="BB11" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD11" t="n">
         <v>38</v>
@@ -2659,14 +2659,14 @@
         <v>46</v>
       </c>
       <c r="BF11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG11" t="n">
         <v>42</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G12" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H12" t="n">
         <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
         <v>3.35</v>
@@ -2727,10 +2727,10 @@
         <v>1.39</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
         <v>1.29</v>
@@ -2748,28 +2748,28 @@
         <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X12" t="n">
         <v>13</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AE12" t="n">
         <v>42</v>
@@ -2778,43 +2778,43 @@
         <v>19</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AL12" t="n">
         <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AP12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ12" t="n">
         <v>10</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>9</v>
-      </c>
       <c r="AR12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT12" t="n">
         <v>8.6</v>
@@ -2823,44 +2823,44 @@
         <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW12" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AY12" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF12" t="n">
         <v>5.6</v>
       </c>
-      <c r="BC12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE12" t="n">
+      <c r="BG12" t="n">
         <v>6</v>
       </c>
-      <c r="BF12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>30</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
         <v>8.4</v>
@@ -2900,13 +2900,13 @@
         <v>1.51</v>
       </c>
       <c r="I13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.38</v>
@@ -2924,13 +2924,13 @@
         <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
         <v>2</v>
@@ -2939,13 +2939,13 @@
         <v>1.83</v>
       </c>
       <c r="V13" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="W13" t="n">
         <v>1.13</v>
       </c>
       <c r="X13" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
         <v>9.4</v>
@@ -2960,19 +2960,19 @@
         <v>28</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AG13" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AH13" t="n">
         <v>29</v>
@@ -2990,7 +2990,7 @@
         <v>140</v>
       </c>
       <c r="AM13" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN13" t="n">
         <v>220</v>
@@ -3011,7 +3011,7 @@
         <v>12</v>
       </c>
       <c r="AT13" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AU13" t="n">
         <v>8.6</v>
@@ -3020,41 +3020,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ13" t="n">
         <v>20</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG13" t="n">
         <v>6.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H14" t="n">
         <v>5</v>
@@ -3100,7 +3100,7 @@
         <v>3.9</v>
       </c>
       <c r="K14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,19 +3109,19 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
         <v>1.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q14" t="n">
         <v>1.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
         <v>2.36</v>
@@ -3130,7 +3130,7 @@
         <v>1.77</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
         <v>1.12</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H15" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3327,11 +3327,11 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.44</v>
       </c>
-      <c r="W15" t="n">
-        <v>1.43</v>
-      </c>
       <c r="X15" t="n">
         <v>1000</v>
       </c>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G16" t="n">
         <v>6.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="I16" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,22 +3497,22 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>5.3</v>
+        <v>2.24</v>
       </c>
       <c r="O16" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="P16" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R16" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.22</v>
+        <v>1.49</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3521,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="W16" t="n">
         <v>1.19</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="G17" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3703,7 +3703,7 @@
         <v>1.57</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
         <v>2.18</v>
@@ -3715,10 +3715,10 @@
         <v>2.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="W17" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="X17" t="n">
         <v>34</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
         <v>2.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
@@ -3900,10 +3900,10 @@
         <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
         <v>2.12</v>
@@ -3912,7 +3912,7 @@
         <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="X18" t="n">
         <v>22</v>
@@ -3981,10 +3981,10 @@
         <v>4.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
         <v>12</v>
@@ -3996,19 +3996,19 @@
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.2</v>
+        <v>19.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>4.4</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4061,25 +4061,25 @@
         <v>2.64</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I19" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
         <v>3.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
         <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O19" t="n">
         <v>1.52</v>
@@ -4088,13 +4088,13 @@
         <v>1.53</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="R19" t="n">
         <v>1.19</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="T19" t="n">
         <v>2.06</v>
@@ -4109,7 +4109,7 @@
         <v>1.61</v>
       </c>
       <c r="X19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="n">
         <v>10.5</v>
@@ -4124,7 +4124,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
         <v>16.5</v>
@@ -4136,13 +4136,13 @@
         <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
       </c>
       <c r="AI19" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ19" t="n">
         <v>42</v>
@@ -4151,7 +4151,7 @@
         <v>38</v>
       </c>
       <c r="AL19" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AM19" t="n">
         <v>200</v>
@@ -4160,10 +4160,10 @@
         <v>42</v>
       </c>
       <c r="AO19" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>8.4</v>
@@ -4172,7 +4172,7 @@
         <v>19</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT19" t="n">
         <v>6.6</v>
@@ -4184,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AX19" t="n">
         <v>12.5</v>
@@ -4196,29 +4196,29 @@
         <v>19.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
       </c>
       <c r="BC19" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BF19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG19" t="n">
         <v>7.2</v>
       </c>
-      <c r="BG19" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G20" t="n">
         <v>1.69</v>
@@ -4261,10 +4261,10 @@
         <v>6.2</v>
       </c>
       <c r="J20" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
@@ -4276,10 +4276,10 @@
         <v>6.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q20" t="n">
         <v>1.45</v>
@@ -4288,10 +4288,10 @@
         <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T20" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="U20" t="n">
         <v>2.4</v>
@@ -4300,119 +4300,119 @@
         <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z20" t="n">
         <v>60</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB20" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC20" t="n">
         <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK20" t="n">
         <v>16</v>
       </c>
-      <c r="AG20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>18.5</v>
-      </c>
       <c r="AL20" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AM20" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP20" t="n">
         <v>6.8</v>
       </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.76</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>2.76</v>
+        <v>6.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>40</v>
+        <v>7.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.52</v>
+        <v>11.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV20" t="n">
         <v>18</v>
       </c>
       <c r="AW20" t="n">
-        <v>42</v>
+        <v>7.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.84</v>
+        <v>34</v>
       </c>
       <c r="BB20" t="n">
-        <v>3</v>
+        <v>14.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.88</v>
+        <v>7.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.08</v>
+        <v>5</v>
       </c>
       <c r="BG20" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4455,13 +4455,13 @@
         <v>2.74</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -4482,10 +4482,10 @@
         <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
         <v>2.04</v>
@@ -4497,7 +4497,7 @@
         <v>1.41</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
         <v>10.5</v>
@@ -4530,7 +4530,7 @@
         <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ21" t="n">
         <v>60</v>
@@ -4560,7 +4560,7 @@
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT21" t="n">
         <v>9.800000000000001</v>
@@ -4584,29 +4584,29 @@
         <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC21" t="n">
         <v>32</v>
       </c>
       <c r="BD21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE21" t="n">
         <v>7.6</v>
       </c>
-      <c r="BE21" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF21" t="n">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="G22" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="H22" t="n">
         <v>6.6</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,16 +4661,16 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="O22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
         <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="R22" t="n">
         <v>1.18</v>
@@ -4682,13 +4682,13 @@
         <v>1.81</v>
       </c>
       <c r="U22" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V22" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="X22" t="n">
         <v>24</v>
@@ -4760,7 +4760,7 @@
         <v>2.42</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV22" t="n">
         <v>2.8</v>
@@ -4772,7 +4772,7 @@
         <v>2.48</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.4</v>
+        <v>2.48</v>
       </c>
       <c r="AZ22" t="n">
         <v>2.76</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G23" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="H23" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="I23" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="J23" t="n">
-        <v>2.68</v>
+        <v>3.85</v>
       </c>
       <c r="K23" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4861,16 +4861,16 @@
         <v>1.18</v>
       </c>
       <c r="P23" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="S23" t="n">
-        <v>1.54</v>
+        <v>2.48</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4879,10 +4879,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W23" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="I24" t="n">
         <v>4.4</v>
@@ -5040,7 +5040,7 @@
         <v>2.6</v>
       </c>
       <c r="K24" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,34 +5049,34 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="O24" t="n">
         <v>1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
         <v>1.96</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="T24" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U24" t="n">
         <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>2.46</v>
       </c>
       <c r="H25" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
         <v>3.1</v>
@@ -5255,19 +5255,19 @@
         <v>1.44</v>
       </c>
       <c r="R25" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T25" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="U25" t="n">
         <v>2.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
         <v>1.68</v>
@@ -5279,7 +5279,7 @@
         <v>25</v>
       </c>
       <c r="Z25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA25" t="n">
         <v>50</v>
@@ -5309,7 +5309,7 @@
         <v>29</v>
       </c>
       <c r="AJ25" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK25" t="n">
         <v>22</v>
@@ -5339,7 +5339,7 @@
         <v>10.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.199999999999999</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>9.4</v>
@@ -5351,16 +5351,16 @@
         <v>23</v>
       </c>
       <c r="AX25" t="n">
-        <v>18.5</v>
+        <v>8.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BB25" t="n">
         <v>28</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5634,19 +5634,19 @@
         <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P27" t="n">
         <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6028,13 +6028,13 @@
         <v>1.96</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R29" t="n">
         <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
         <v>1.98</v>
@@ -6142,7 +6142,7 @@
         <v>42</v>
       </c>
       <c r="BC29" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BD29" t="n">
         <v>65</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>2.84</v>
       </c>
       <c r="H30" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I30" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J30" t="n">
         <v>3.7</v>
@@ -6213,7 +6213,7 @@
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
         <v>1.24</v>
@@ -6243,7 +6243,7 @@
         <v>1.54</v>
       </c>
       <c r="X30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
         <v>14</v>
@@ -6279,7 +6279,7 @@
         <v>32</v>
       </c>
       <c r="AJ30" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK30" t="n">
         <v>27</v>
@@ -6303,7 +6303,7 @@
         <v>12.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>34</v>
@@ -6321,7 +6321,7 @@
         <v>23</v>
       </c>
       <c r="AX30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY30" t="n">
         <v>11.5</v>
@@ -6333,26 +6333,26 @@
         <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC30" t="n">
         <v>25</v>
       </c>
       <c r="BD30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BF30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G31" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="H31" t="n">
         <v>8.800000000000001</v>
@@ -6398,7 +6398,7 @@
         <v>5.4</v>
       </c>
       <c r="K31" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.31</v>
@@ -6440,16 +6440,16 @@
         <v>26</v>
       </c>
       <c r="Y31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z31" t="n">
         <v>80</v>
       </c>
       <c r="AA31" t="n">
-        <v>290</v>
+        <v>990</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
         <v>12</v>
@@ -6473,7 +6473,7 @@
         <v>100</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK31" t="n">
         <v>13.5</v>
@@ -6500,7 +6500,7 @@
         <v>65</v>
       </c>
       <c r="AS31" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AT31" t="n">
         <v>9.199999999999999</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
         <v>1.49</v>
       </c>
       <c r="S32" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T32" t="n">
         <v>1.68</v>
@@ -6634,7 +6634,7 @@
         <v>17.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z32" t="n">
         <v>29</v>
@@ -6652,7 +6652,7 @@
         <v>15.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF32" t="n">
         <v>14</v>
@@ -6664,7 +6664,7 @@
         <v>15.5</v>
       </c>
       <c r="AI32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ32" t="n">
         <v>25</v>
@@ -6697,7 +6697,7 @@
         <v>60</v>
       </c>
       <c r="AT32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU32" t="n">
         <v>8</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="G33" t="n">
         <v>3.7</v>
@@ -6783,7 +6783,7 @@
         <v>2.18</v>
       </c>
       <c r="J33" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K33" t="n">
         <v>3.85</v>
@@ -6813,7 +6813,7 @@
         <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U33" t="n">
         <v>2.4</v>
@@ -6828,7 +6828,7 @@
         <v>17.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z33" t="n">
         <v>14.5</v>
@@ -6885,7 +6885,7 @@
         <v>10.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS33" t="n">
         <v>24</v>
@@ -6924,17 +6924,17 @@
         <v>38</v>
       </c>
       <c r="BE33" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BF33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BG33" t="n">
         <v>12</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -6968,22 +6968,22 @@
         <v>1.94</v>
       </c>
       <c r="G34" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="H34" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="I34" t="n">
         <v>4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
         <v>5.1</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M34" t="n">
         <v>1.02</v>
@@ -7004,10 +7004,10 @@
         <v>1.57</v>
       </c>
       <c r="S34" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T34" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U34" t="n">
         <v>2.24</v>
@@ -7016,7 +7016,7 @@
         <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X34" t="n">
         <v>30</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7186,19 +7186,19 @@
         <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P35" t="n">
         <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7359,10 +7359,10 @@
         <v>7.6</v>
       </c>
       <c r="H36" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="I36" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="J36" t="n">
         <v>5.1</v>
@@ -7377,10 +7377,10 @@
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>2.48</v>
+        <v>5.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P36" t="n">
         <v>2.48</v>
@@ -7389,19 +7389,19 @@
         <v>1.59</v>
       </c>
       <c r="R36" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="S36" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="T36" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V36" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="W36" t="n">
         <v>1.15</v>
@@ -7410,70 +7410,70 @@
         <v>27</v>
       </c>
       <c r="Y36" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z36" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AC36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD36" t="n">
         <v>10</v>
       </c>
       <c r="AE36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF36" t="n">
         <v>70</v>
       </c>
       <c r="AG36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AH36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI36" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ36" t="n">
         <v>250</v>
       </c>
       <c r="AK36" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM36" t="n">
         <v>95</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>110</v>
       </c>
       <c r="AN36" t="n">
         <v>85</v>
       </c>
       <c r="AO36" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AP36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ36" t="n">
         <v>9.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS36" t="n">
         <v>12</v>
       </c>
       <c r="AT36" t="n">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="AU36" t="n">
         <v>10</v>
@@ -7482,41 +7482,41 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW36" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>5.9</v>
+        <v>50</v>
       </c>
       <c r="AY36" t="n">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="AZ36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.4</v>
+        <v>24</v>
       </c>
       <c r="BB36" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BC36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BE36" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BF36" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7574,25 +7574,25 @@
         <v>6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P37" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R37" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="S37" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T37" t="n">
         <v>1.52</v>
       </c>
       <c r="U37" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="V37" t="n">
         <v>1.58</v>
@@ -7613,10 +7613,10 @@
         <v>40</v>
       </c>
       <c r="AB37" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC37" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD37" t="n">
         <v>12</v>
@@ -7628,7 +7628,7 @@
         <v>21</v>
       </c>
       <c r="AG37" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH37" t="n">
         <v>13</v>
@@ -7679,7 +7679,7 @@
         <v>22</v>
       </c>
       <c r="AX37" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY37" t="n">
         <v>11.5</v>
@@ -7706,11 +7706,11 @@
         <v>13</v>
       </c>
       <c r="BG37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7768,19 +7768,19 @@
         <v>1.25</v>
       </c>
       <c r="O38" t="n">
-        <v>1.35</v>
+        <v>1.02</v>
       </c>
       <c r="P38" t="n">
         <v>1.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="R38" t="n">
         <v>1.13</v>
       </c>
       <c r="S38" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="G39" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H39" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I39" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="J39" t="n">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="K39" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,79 +7959,79 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.24</v>
+        <v>2.84</v>
       </c>
       <c r="O39" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="P39" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R39" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
-        <v>1.02</v>
+        <v>4.1</v>
       </c>
       <c r="T39" t="n">
         <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V39" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
       </c>
       <c r="AB39" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
       </c>
       <c r="AJ39" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL39" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AV39" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW39" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AY39" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BA39" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BB39" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BC39" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BD39" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BF39" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BG39" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 20:22:47</t>
+          <t>2026-03-02 22:33:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="n">
         <v>5.5</v>
@@ -778,10 +778,10 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
@@ -790,28 +790,28 @@
         <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
         <v>21</v>
@@ -826,7 +826,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD2" t="n">
         <v>23</v>
@@ -871,10 +871,10 @@
         <v>16.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -883,7 +883,7 @@
         <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
         <v>60</v>
@@ -895,10 +895,10 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -907,20 +907,20 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BG2" t="n">
-        <v>7</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J3" t="n">
         <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,19 +975,19 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S3" t="n">
         <v>3.25</v>
@@ -996,13 +996,13 @@
         <v>1.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
@@ -1035,7 +1035,7 @@
         <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI3" t="n">
         <v>36</v>
@@ -1059,7 +1059,7 @@
         <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.6</v>
@@ -1068,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
@@ -1080,7 +1080,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
         <v>6.2</v>
@@ -1089,22 +1089,22 @@
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
         <v>6.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
         <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
         <v>38</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -1187,16 +1187,16 @@
         <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
@@ -1262,7 +1262,7 @@
         <v>34</v>
       </c>
       <c r="AS4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1289,7 +1289,7 @@
         <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
         <v>14.5</v>
@@ -1298,7 +1298,7 @@
         <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF4" t="n">
         <v>7.2</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H5" t="n">
         <v>3.2</v>
@@ -1354,16 +1354,16 @@
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
         <v>1.52</v>
@@ -1378,19 +1378,19 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1423,7 +1423,7 @@
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI5" t="n">
         <v>80</v>
@@ -1462,7 +1462,7 @@
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
         <v>4.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>1.48</v>
       </c>
       <c r="H6" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
@@ -1551,7 +1551,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1644,7 +1644,7 @@
         <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR6" t="n">
         <v>7.2</v>
@@ -1671,7 +1671,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA6" t="n">
         <v>7.4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>1.33</v>
       </c>
       <c r="H7" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" t="n">
         <v>5.3</v>
@@ -1751,13 +1751,13 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
         <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q7" t="n">
         <v>1.7</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -1912,12 +1912,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Juventus B</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1948,19 +1948,19 @@
         <v>1.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
         <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R8" t="n">
         <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Juventus B</t>
+          <t>AC Bra</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2142,19 +2142,19 @@
         <v>1.25</v>
       </c>
       <c r="O9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
         <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AC Bra</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -2336,19 +2336,19 @@
         <v>1.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P10" t="n">
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.77</v>
       </c>
       <c r="G11" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H11" t="n">
         <v>5.6</v>
@@ -2530,7 +2530,7 @@
         <v>3.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P11" t="n">
         <v>1.77</v>
@@ -2554,7 +2554,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Duisburg</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="G12" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="I12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.45</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>1.98</v>
       </c>
       <c r="O12" t="n">
-        <v>1.39</v>
+        <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="X12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>German 3 Liga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>PAOK</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>1.71</v>
       </c>
       <c r="G13" t="n">
-        <v>8.4</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
-        <v>1.51</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>2.42</v>
       </c>
       <c r="O13" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.83</v>
+        <v>2.22</v>
       </c>
       <c r="V13" t="n">
-        <v>2.64</v>
+        <v>1.21</v>
       </c>
       <c r="W13" t="n">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.4</v>
+        <v>29</v>
       </c>
       <c r="Z13" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="AA13" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="AB13" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="AC13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AX13" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>310</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>220</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AY13" t="n">
-        <v>21</v>
+        <v>2.36</v>
       </c>
       <c r="AZ13" t="n">
-        <v>20</v>
+        <v>2.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="BB13" t="n">
-        <v>5.5</v>
+        <v>2.56</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.3</v>
+        <v>2.52</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.4</v>
+        <v>2.72</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.6</v>
+        <v>2.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>TSV Havelse</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.75</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1.58</v>
       </c>
       <c r="I14" t="n">
-        <v>9.4</v>
+        <v>1.94</v>
       </c>
       <c r="J14" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3109,146 +3109,146 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="T14" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>2.06</v>
       </c>
       <c r="W14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X14" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>2.34</v>
       </c>
-      <c r="X14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Duisburg</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="H15" t="n">
-        <v>2.42</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>1.98</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TSV Havelse</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.5</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
-        <v>6.4</v>
+        <v>1.75</v>
       </c>
       <c r="H16" t="n">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.94</v>
+        <v>9.4</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,153 +3497,153 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="O16" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>1.49</v>
+        <v>2.36</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V16" t="n">
-        <v>2.06</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.19</v>
+        <v>2.34</v>
       </c>
       <c r="X16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
         <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
         <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>PAOK</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.71</v>
+        <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>8.4</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>1.51</v>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>1.61</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>310</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>140</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR17" t="n">
         <v>7.6</v>
       </c>
-      <c r="L17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="X17" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AS17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT17" t="n">
         <v>18</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AU17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW17" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AX17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>20</v>
       </c>
-      <c r="AG17" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BA17" t="n">
-        <v>2.68</v>
+        <v>5</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.56</v>
+        <v>5.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.52</v>
+        <v>5.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>19</v>
+        <v>5.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.72</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>German 3 Liga</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="H18" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S18" t="n">
-        <v>2.82</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="X18" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Y18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF18" t="n">
         <v>19</v>
       </c>
-      <c r="Z18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>17</v>
-      </c>
       <c r="AG18" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
         <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="AO18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>5.5</v>
       </c>
       <c r="AS18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>12</v>
-      </c>
       <c r="AW18" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>4.9</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="BC18" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>10</v>
+        <v>5.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4046,179 +4046,179 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.48</v>
+        <v>1.58</v>
       </c>
       <c r="G19" t="n">
-        <v>2.64</v>
+        <v>1.69</v>
       </c>
       <c r="H19" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>2.64</v>
+        <v>6.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.52</v>
+        <v>1.15</v>
       </c>
       <c r="P19" t="n">
-        <v>1.53</v>
+        <v>2.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6</v>
+        <v>1.45</v>
       </c>
       <c r="R19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V19" t="n">
         <v>1.19</v>
       </c>
-      <c r="S19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.37</v>
-      </c>
       <c r="W19" t="n">
-        <v>1.61</v>
+        <v>2.46</v>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>32</v>
       </c>
       <c r="Z19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD19" t="n">
         <v>24</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>16.5</v>
       </c>
       <c r="AE19" t="n">
         <v>60</v>
       </c>
       <c r="AF19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK19" t="n">
         <v>16</v>
       </c>
-      <c r="AG19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>38</v>
-      </c>
       <c r="AL19" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AM19" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="AN19" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="AO19" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS19" t="n">
         <v>8.4</v>
       </c>
-      <c r="AR19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AT19" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AW19" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AX19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>12.5</v>
       </c>
-      <c r="AY19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BD19" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BE19" t="n">
         <v>7.8</v>
       </c>
       <c r="BF19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG19" t="n">
         <v>32</v>
       </c>
-      <c r="BG19" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.58</v>
+        <v>2.48</v>
       </c>
       <c r="G20" t="n">
-        <v>1.69</v>
+        <v>2.64</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>3.35</v>
       </c>
       <c r="I20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
         <v>6.2</v>
       </c>
-      <c r="J20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X20" t="n">
+      <c r="AV20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB20" t="n">
         <v>32</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="BC20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF20" t="n">
         <v>32</v>
       </c>
-      <c r="Z20" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>140</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>26</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>5</v>
-      </c>
       <c r="BG20" t="n">
-        <v>32</v>
+        <v>7.2</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.05</v>
+        <v>1.51</v>
       </c>
       <c r="G21" t="n">
-        <v>3.45</v>
+        <v>1.68</v>
       </c>
       <c r="H21" t="n">
-        <v>2.48</v>
+        <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>2.74</v>
+        <v>8.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T21" t="n">
         <v>1.81</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.79</v>
-      </c>
       <c r="U21" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.58</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>1.41</v>
+        <v>2.32</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
-        <v>17.5</v>
+        <v>75</v>
       </c>
       <c r="AA21" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
         <v>12</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="AE21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK21" t="n">
         <v>23</v>
       </c>
-      <c r="AG21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>42</v>
-      </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>2.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.6</v>
+        <v>2.76</v>
       </c>
       <c r="AR21" t="n">
-        <v>14</v>
+        <v>2.92</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.8</v>
+        <v>3.05</v>
       </c>
       <c r="AT21" t="n">
-        <v>9.800000000000001</v>
+        <v>2.42</v>
       </c>
       <c r="AU21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BF21" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV21" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BG21" t="n">
-        <v>6.4</v>
+        <v>3.05</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.51</v>
+        <v>3.05</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68</v>
+        <v>3.45</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6</v>
+        <v>2.48</v>
       </c>
       <c r="I22" t="n">
-        <v>8.6</v>
+        <v>2.74</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.72</v>
+        <v>3.8</v>
       </c>
       <c r="T22" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="U22" t="n">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="W22" t="n">
-        <v>2.32</v>
+        <v>1.41</v>
       </c>
       <c r="X22" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>75</v>
+        <v>17.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB22" t="n">
         <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>11</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF22" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AG22" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="AK22" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.76</v>
+        <v>8.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.92</v>
+        <v>14</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.42</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU22" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.05</v>
+        <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>2.48</v>
+        <v>18.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>2.48</v>
+        <v>12</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.76</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.05</v>
+        <v>7.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.68</v>
+        <v>32</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.86</v>
+        <v>7.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="BF22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG22" t="n">
         <v>6.4</v>
       </c>
-      <c r="BG22" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
         <v>2.14</v>
       </c>
       <c r="O23" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P23" t="n">
         <v>2.12</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="G24" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="H24" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="J24" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24" t="n">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>1.82</v>
+        <v>2.96</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>2.86</v>
+        <v>2.08</v>
       </c>
       <c r="T24" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="U24" t="n">
-        <v>1.89</v>
+        <v>2.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Swiss Super League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>2.46</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9</v>
+        <v>1.04</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>1.02</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>7</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>2.96</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>2.08</v>
+        <v>1.36</v>
       </c>
       <c r="T25" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.96</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -5634,19 +5634,19 @@
         <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
         <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
         <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T27" t="n">
         <v>1.01</v>
@@ -5770,14 +5770,14 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Swiss Super League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>1.94</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>2.44</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,34 +5825,34 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.82</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.37</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S28" t="n">
-        <v>1.37</v>
+        <v>2.86</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q29" t="n">
         <v>1.99</v>
@@ -6061,7 +6061,7 @@
         <v>16.5</v>
       </c>
       <c r="AB29" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC29" t="n">
         <v>8.800000000000001</v>
@@ -6091,13 +6091,13 @@
         <v>85</v>
       </c>
       <c r="AL29" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM29" t="n">
         <v>130</v>
       </c>
       <c r="AN29" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO29" t="n">
         <v>11</v>
@@ -6115,7 +6115,7 @@
         <v>15.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU29" t="n">
         <v>8.4</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
         <v>2.94</v>
       </c>
       <c r="T30" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U30" t="n">
         <v>2.5</v>
@@ -6267,7 +6267,7 @@
         <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG30" t="n">
         <v>12.5</v>
@@ -6285,28 +6285,28 @@
         <v>27</v>
       </c>
       <c r="AL30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM30" t="n">
         <v>65</v>
       </c>
       <c r="AN30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
         <v>17.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
         <v>17</v>
       </c>
       <c r="AS30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT30" t="n">
         <v>13.5</v>
@@ -6333,7 +6333,7 @@
         <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC30" t="n">
         <v>25</v>
@@ -6342,7 +6342,7 @@
         <v>32</v>
       </c>
       <c r="BE30" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF30" t="n">
         <v>18.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G31" t="n">
         <v>1.43</v>
@@ -6407,7 +6407,7 @@
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
@@ -6425,7 +6425,7 @@
         <v>2.68</v>
       </c>
       <c r="T31" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U31" t="n">
         <v>2.04</v>
@@ -6437,7 +6437,7 @@
         <v>3.35</v>
       </c>
       <c r="X31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y31" t="n">
         <v>32</v>
@@ -6455,7 +6455,7 @@
         <v>12</v>
       </c>
       <c r="AD31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
         <v>120</v>
@@ -6464,10 +6464,10 @@
         <v>9</v>
       </c>
       <c r="AG31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
         <v>100</v>
@@ -6479,7 +6479,7 @@
         <v>13.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM31" t="n">
         <v>120</v>
@@ -6503,7 +6503,7 @@
         <v>110</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU31" t="n">
         <v>11</v>
@@ -6512,7 +6512,7 @@
         <v>29</v>
       </c>
       <c r="AW31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
@@ -6536,7 +6536,7 @@
         <v>28</v>
       </c>
       <c r="BE31" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BF31" t="n">
         <v>5.3</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6631,13 +6631,13 @@
         <v>1.89</v>
       </c>
       <c r="X32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y32" t="n">
         <v>16.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA32" t="n">
         <v>70</v>
@@ -6649,7 +6649,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE32" t="n">
         <v>38</v>
@@ -6667,13 +6667,13 @@
         <v>44</v>
       </c>
       <c r="AJ32" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM32" t="n">
         <v>70</v>
@@ -6688,13 +6688,13 @@
         <v>16</v>
       </c>
       <c r="AQ32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR32" t="n">
         <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AT32" t="n">
         <v>11</v>
@@ -6706,7 +6706,7 @@
         <v>14.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX32" t="n">
         <v>13.5</v>
@@ -6718,7 +6718,7 @@
         <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB32" t="n">
         <v>23</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6924,7 @@
         <v>38</v>
       </c>
       <c r="BE33" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BF33" t="n">
         <v>27</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.94</v>
       </c>
       <c r="G34" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H34" t="n">
         <v>3.45</v>
@@ -7016,7 +7016,7 @@
         <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="X34" t="n">
         <v>30</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
         <v>1.18</v>
       </c>
       <c r="P37" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q37" t="n">
         <v>1.57</v>
@@ -7604,7 +7604,7 @@
         <v>23</v>
       </c>
       <c r="Y37" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z37" t="n">
         <v>21</v>
@@ -7622,7 +7622,7 @@
         <v>12</v>
       </c>
       <c r="AE37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF37" t="n">
         <v>21</v>
@@ -7634,16 +7634,16 @@
         <v>13</v>
       </c>
       <c r="AI37" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ37" t="n">
         <v>38</v>
       </c>
       <c r="AK37" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL37" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM37" t="n">
         <v>48</v>
@@ -7664,7 +7664,7 @@
         <v>20</v>
       </c>
       <c r="AS37" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT37" t="n">
         <v>16</v>
@@ -7691,7 +7691,7 @@
         <v>26</v>
       </c>
       <c r="BB37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC37" t="n">
         <v>22</v>
@@ -7700,7 +7700,7 @@
         <v>26</v>
       </c>
       <c r="BE37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF37" t="n">
         <v>13</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>
@@ -7938,19 +7938,19 @@
         <v>1.72</v>
       </c>
       <c r="G39" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H39" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I39" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J39" t="n">
-        <v>2.76</v>
+        <v>2.96</v>
       </c>
       <c r="K39" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,7 +7959,7 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O39" t="n">
         <v>1.43</v>
@@ -7977,22 +7977,22 @@
         <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U39" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W39" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X39" t="n">
         <v>14.5</v>
       </c>
       <c r="Y39" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z39" t="n">
         <v>65</v>
@@ -8007,13 +8007,13 @@
         <v>11</v>
       </c>
       <c r="AD39" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
       </c>
       <c r="AF39" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG39" t="n">
         <v>14.5</v>
@@ -8028,7 +8028,7 @@
         <v>28</v>
       </c>
       <c r="AK39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL39" t="n">
         <v>70</v>
@@ -8046,7 +8046,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR39" t="n">
         <v>2.5</v>
@@ -8067,7 +8067,7 @@
         <v>2.6</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AY39" t="n">
         <v>2.2</v>
@@ -8098,7 +8098,783 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-02 22:33:42</t>
+          <t>2026-03-03 00:44:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N40" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-03 00:44:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Queretaro</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K41" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>220</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-03-03 00:44:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Fortaleza FC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Jaguares de Cordoba</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-03-03 00:44:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Tigres</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G43" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V43" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X43" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-03-03 00:44:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G2" t="n">
         <v>1.71</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.28</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R2" t="n">
         <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -954,55 +954,55 @@
         <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I3" t="n">
         <v>2.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
         <v>3.75</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
         <v>1.92</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
@@ -1023,7 +1023,7 @@
         <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
         <v>23</v>
@@ -1059,7 +1059,7 @@
         <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.6</v>
@@ -1080,31 +1080,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BD3" t="n">
         <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
         <v>38</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
         <v>4.9</v>
@@ -1157,10 +1157,10 @@
         <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1190,7 +1190,7 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
@@ -1244,13 +1244,13 @@
         <v>27</v>
       </c>
       <c r="AM4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
@@ -1259,7 +1259,7 @@
         <v>19.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AS4" t="n">
         <v>14.5</v>
@@ -1304,11 +1304,11 @@
         <v>7.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
@@ -1363,10 +1363,10 @@
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
         <v>1.52</v>
@@ -1378,25 +1378,25 @@
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W5" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="X5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
         <v>27</v>
@@ -1441,7 +1441,7 @@
         <v>280</v>
       </c>
       <c r="AN5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AO5" t="n">
         <v>100</v>
@@ -1456,7 +1456,7 @@
         <v>4.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
@@ -1468,19 +1468,19 @@
         <v>4.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ5" t="n">
         <v>5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB5" t="n">
         <v>5.1</v>
@@ -1492,17 +1492,17 @@
         <v>5.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="G6" t="n">
         <v>1.48</v>
@@ -1548,7 +1548,7 @@
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
         <v>1.37</v>
@@ -1566,7 +1566,7 @@
         <v>1.94</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>1.35</v>
@@ -1605,7 +1605,7 @@
         <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE6" t="n">
         <v>220</v>
@@ -1650,7 +1650,7 @@
         <v>7.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1674,7 +1674,7 @@
         <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -1683,7 +1683,7 @@
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE6" t="n">
         <v>7.6</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
         <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
         <v>1.61</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -2533,7 +2533,7 @@
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q11" t="n">
         <v>2.24</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -2721,16 +2721,16 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="R12" t="n">
         <v>1.25</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>2.3</v>
@@ -3288,7 +3288,7 @@
         <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
@@ -3321,16 +3321,16 @@
         <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
         <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -3339,13 +3339,13 @@
         <v>19</v>
       </c>
       <c r="Z15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA15" t="n">
         <v>80</v>
       </c>
       <c r="AB15" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
         <v>10.5</v>
@@ -3354,13 +3354,13 @@
         <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF15" t="n">
         <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
         <v>19</v>
@@ -3396,53 +3396,53 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BA15" t="n">
         <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>19.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.1</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF15" t="n">
         <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
         <v>3.65</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P17" t="n">
         <v>1.92</v>
@@ -3733,7 +3733,7 @@
         <v>17</v>
       </c>
       <c r="AB17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC17" t="n">
         <v>10.5</v>
@@ -3799,7 +3799,7 @@
         <v>14.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AY17" t="n">
         <v>21</v>
@@ -3814,23 +3814,23 @@
         <v>5.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE17" t="n">
         <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG17" t="n">
         <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
         <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V21" t="n">
         <v>1.13</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
         <v>2.48</v>
       </c>
       <c r="I22" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="J22" t="n">
         <v>3</v>
@@ -4655,37 +4655,37 @@
         <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="U22" t="n">
         <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W22" t="n">
         <v>1.41</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>2.9</v>
       </c>
       <c r="I24" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J24" t="n">
         <v>3.95</v>
@@ -5061,7 +5061,7 @@
         <v>1.44</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="S24" t="n">
         <v>2.08</v>
@@ -5070,10 +5070,10 @@
         <v>1.39</v>
       </c>
       <c r="U24" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
         <v>1.68</v>
@@ -5127,10 +5127,10 @@
         <v>48</v>
       </c>
       <c r="AN24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO24" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP24" t="n">
         <v>24</v>
@@ -5139,10 +5139,10 @@
         <v>19.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS24" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AT24" t="n">
         <v>17</v>
@@ -5157,7 +5157,7 @@
         <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY24" t="n">
         <v>11</v>
@@ -5178,7 +5178,7 @@
         <v>22</v>
       </c>
       <c r="BE24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF24" t="n">
         <v>8.800000000000001</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="G28" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H28" t="n">
         <v>3.25</v>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
         <v>950</v>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O28" t="n">
         <v>1.29</v>
       </c>
       <c r="P28" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
         <v>1.96</v>
@@ -5843,16 +5843,16 @@
         <v>2.86</v>
       </c>
       <c r="T28" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U28" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V28" t="n">
         <v>1.31</v>
       </c>
       <c r="W28" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6118,7 +6118,7 @@
         <v>16.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV29" t="n">
         <v>9.4</v>
@@ -6148,7 +6148,7 @@
         <v>65</v>
       </c>
       <c r="BE29" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BF29" t="n">
         <v>90</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
         <v>1.54</v>
       </c>
       <c r="X30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y30" t="n">
         <v>14</v>
@@ -6306,7 +6306,7 @@
         <v>17</v>
       </c>
       <c r="AS30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT30" t="n">
         <v>13.5</v>
@@ -6318,7 +6318,7 @@
         <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX30" t="n">
         <v>19</v>
@@ -6348,11 +6348,11 @@
         <v>18.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G31" t="n">
         <v>1.43</v>
@@ -6407,13 +6407,13 @@
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.21</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q31" t="n">
         <v>1.63</v>
@@ -6494,7 +6494,7 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR31" t="n">
         <v>65</v>
@@ -6512,7 +6512,7 @@
         <v>29</v>
       </c>
       <c r="AW31" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
@@ -6536,7 +6536,7 @@
         <v>28</v>
       </c>
       <c r="BE31" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BF31" t="n">
         <v>5.3</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
         <v>1.78</v>
       </c>
       <c r="R32" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
         <v>2.96</v>
@@ -6694,7 +6694,7 @@
         <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AT32" t="n">
         <v>11</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O33" t="n">
         <v>1.26</v>
@@ -6804,16 +6804,16 @@
         <v>2.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T33" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U33" t="n">
         <v>2.4</v>
@@ -6825,7 +6825,7 @@
         <v>1.37</v>
       </c>
       <c r="X33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y33" t="n">
         <v>11.5</v>
@@ -6837,7 +6837,7 @@
         <v>27</v>
       </c>
       <c r="AB33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC33" t="n">
         <v>8.199999999999999</v>
@@ -6921,7 +6921,7 @@
         <v>34</v>
       </c>
       <c r="BD33" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE33" t="n">
         <v>50</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G34" t="n">
         <v>2.26</v>
       </c>
       <c r="H34" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J34" t="n">
         <v>3.5</v>
@@ -7001,13 +7001,13 @@
         <v>1.48</v>
       </c>
       <c r="R34" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S34" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U34" t="n">
         <v>2.24</v>
@@ -7016,19 +7016,19 @@
         <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y34" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z34" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA34" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB34" t="n">
         <v>970</v>
@@ -7040,7 +7040,7 @@
         <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF34" t="n">
         <v>970</v>
@@ -7052,13 +7052,13 @@
         <v>970</v>
       </c>
       <c r="AI34" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ34" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL34" t="n">
         <v>34</v>
@@ -7079,10 +7079,10 @@
         <v>3.65</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT34" t="n">
         <v>3.4</v>
@@ -7094,10 +7094,10 @@
         <v>3.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AY34" t="n">
         <v>3.25</v>
@@ -7109,16 +7109,16 @@
         <v>3.95</v>
       </c>
       <c r="BB34" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF34" t="n">
         <v>7.2</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7359,16 +7359,16 @@
         <v>7.6</v>
       </c>
       <c r="H36" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="I36" t="n">
         <v>1.53</v>
       </c>
       <c r="J36" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L36" t="n">
         <v>1.26</v>
@@ -7398,10 +7398,10 @@
         <v>1.72</v>
       </c>
       <c r="U36" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V36" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="W36" t="n">
         <v>1.15</v>
@@ -7431,7 +7431,7 @@
         <v>15</v>
       </c>
       <c r="AF36" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG36" t="n">
         <v>28</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
         <v>2.72</v>
       </c>
       <c r="H37" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I37" t="n">
         <v>2.72</v>
@@ -7583,7 +7583,7 @@
         <v>1.57</v>
       </c>
       <c r="R37" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S37" t="n">
         <v>2.42</v>
@@ -7592,7 +7592,7 @@
         <v>1.52</v>
       </c>
       <c r="U37" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="V37" t="n">
         <v>1.58</v>
@@ -7613,7 +7613,7 @@
         <v>40</v>
       </c>
       <c r="AB37" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC37" t="n">
         <v>9.199999999999999</v>
@@ -7643,7 +7643,7 @@
         <v>23</v>
       </c>
       <c r="AL37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM37" t="n">
         <v>48</v>
@@ -7664,7 +7664,7 @@
         <v>20</v>
       </c>
       <c r="AS37" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AT37" t="n">
         <v>16</v>
@@ -7691,7 +7691,7 @@
         <v>26</v>
       </c>
       <c r="BB37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC37" t="n">
         <v>22</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7774,13 +7774,13 @@
         <v>1.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R38" t="n">
         <v>1.13</v>
       </c>
       <c r="S38" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="T38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
         <v>7.4</v>
       </c>
       <c r="J39" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="K39" t="n">
         <v>4.8</v>
@@ -7983,7 +7983,7 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W39" t="n">
         <v>2.04</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
         <v>3</v>
       </c>
       <c r="I40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J40" t="n">
         <v>2.98</v>
@@ -8177,7 +8177,7 @@
         <v>1.67</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W40" t="n">
         <v>1.52</v>
@@ -8192,7 +8192,7 @@
         <v>21</v>
       </c>
       <c r="AA40" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AB40" t="n">
         <v>7.8</v>
@@ -8234,7 +8234,7 @@
         <v>60</v>
       </c>
       <c r="AO40" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP40" t="n">
         <v>6.8</v>
@@ -8246,7 +8246,7 @@
         <v>16.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>8.6</v>
+        <v>50</v>
       </c>
       <c r="AT40" t="n">
         <v>6.6</v>
@@ -8258,7 +8258,7 @@
         <v>12.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX40" t="n">
         <v>13.5</v>
@@ -8270,29 +8270,29 @@
         <v>21</v>
       </c>
       <c r="BA40" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB40" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="BC40" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BD40" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE40" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG40" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8389,7 @@
         <v>360</v>
       </c>
       <c r="AB41" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC41" t="n">
         <v>12</v>
@@ -8440,7 +8440,7 @@
         <v>8</v>
       </c>
       <c r="AS41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT41" t="n">
         <v>7.6</v>
@@ -8464,7 +8464,7 @@
         <v>20</v>
       </c>
       <c r="BA41" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB41" t="n">
         <v>10</v>
@@ -8476,17 +8476,17 @@
         <v>27</v>
       </c>
       <c r="BE41" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF41" t="n">
         <v>5.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8517,19 +8517,19 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="G42" t="n">
         <v>2.06</v>
       </c>
       <c r="H42" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I42" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.25</v>
+        <v>2.62</v>
       </c>
       <c r="K42" t="n">
         <v>4.1</v>
@@ -8541,19 +8541,19 @@
         <v>1.01</v>
       </c>
       <c r="N42" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O42" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="P42" t="n">
         <v>1.24</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="R42" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S42" t="n">
         <v>4</v>
@@ -8562,13 +8562,13 @@
         <v>1.01</v>
       </c>
       <c r="U42" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="V42" t="n">
         <v>1.16</v>
       </c>
       <c r="W42" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="X42" t="n">
         <v>1000</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>
@@ -8732,13 +8732,13 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>1.92</v>
+        <v>3.65</v>
       </c>
       <c r="O43" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P43" t="n">
         <v>1.92</v>
@@ -8747,134 +8747,134 @@
         <v>1.94</v>
       </c>
       <c r="R43" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S43" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T43" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="U43" t="n">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="V43" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W43" t="n">
         <v>1.23</v>
       </c>
       <c r="X43" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB43" t="n">
         <v>17</v>
       </c>
-      <c r="Y43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB43" t="n">
+      <c r="AC43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG43" t="n">
         <v>19.5</v>
       </c>
-      <c r="AC43" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>22</v>
-      </c>
       <c r="AH43" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="n">
         <v>75</v>
       </c>
       <c r="AL43" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO43" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP43" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>3.15</v>
+        <v>7.6</v>
       </c>
       <c r="AR43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX43" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AS43" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AY43" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AZ43" t="n">
-        <v>3.8</v>
+        <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>4.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB43" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BC43" t="n">
-        <v>4.3</v>
+        <v>10</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BE43" t="n">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BF43" t="n">
-        <v>4.6</v>
+        <v>60</v>
       </c>
       <c r="BG43" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 00:44:37</t>
+          <t>2026-03-03 02:55:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -766,7 +766,7 @@
         <v>5.6</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
@@ -775,28 +775,28 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
         <v>1.86</v>
@@ -823,7 +823,7 @@
         <v>180</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -847,7 +847,7 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AK2" t="n">
         <v>18.5</v>
@@ -865,16 +865,16 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
         <v>16.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -883,7 +883,7 @@
         <v>8.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AW2" t="n">
         <v>60</v>
@@ -895,10 +895,10 @@
         <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -907,20 +907,20 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>2.04</v>
       </c>
-      <c r="I3" t="n">
-        <v>2.08</v>
-      </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K3" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -993,16 +993,16 @@
         <v>3.35</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V3" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
@@ -1011,10 +1011,10 @@
         <v>10.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AB3" t="n">
         <v>16.5</v>
@@ -1041,10 +1041,10 @@
         <v>36</v>
       </c>
       <c r="AJ3" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
@@ -1053,13 +1053,13 @@
         <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO3" t="n">
         <v>15.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>13.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>8.6</v>
@@ -1068,7 +1068,7 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>13</v>
@@ -1080,7 +1080,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
         <v>6.4</v>
@@ -1089,7 +1089,7 @@
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA3" t="n">
         <v>6.4</v>
@@ -1104,7 +1104,7 @@
         <v>44</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
         <v>38</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1154,13 +1154,13 @@
         <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.29</v>
@@ -1190,13 +1190,13 @@
         <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
@@ -1235,7 +1235,7 @@
         <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1247,10 +1247,10 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
@@ -1262,7 +1262,7 @@
         <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1289,7 +1289,7 @@
         <v>44</v>
       </c>
       <c r="BB4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC4" t="n">
         <v>14.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
@@ -1357,19 +1357,19 @@
         <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
         <v>2.74</v>
@@ -1381,34 +1381,34 @@
         <v>5.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>1.59</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="X5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB5" t="n">
         <v>7.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
@@ -1417,10 +1417,10 @@
         <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
@@ -1429,16 +1429,16 @@
         <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL5" t="n">
         <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AN5" t="n">
         <v>42</v>
@@ -1447,62 +1447,62 @@
         <v>100</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT5" t="n">
         <v>6.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.43</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H6" t="n">
         <v>9.6</v>
@@ -1551,7 +1551,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1563,7 +1563,7 @@
         <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>1.92</v>
@@ -1596,7 +1596,7 @@
         <v>100</v>
       </c>
       <c r="AA6" t="n">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="AB6" t="n">
         <v>7.8</v>
@@ -1605,10 +1605,10 @@
         <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE6" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF6" t="n">
         <v>8.4</v>
@@ -1617,7 +1617,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>180</v>
@@ -1632,13 +1632,13 @@
         <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN6" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AO6" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AP6" t="n">
         <v>13</v>
@@ -1647,10 +1647,10 @@
         <v>19.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,10 +1659,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
         <v>6.8</v>
@@ -1674,7 +1674,7 @@
         <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
@@ -1683,20 +1683,20 @@
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BF6" t="n">
         <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1736,13 +1736,13 @@
         <v>12.5</v>
       </c>
       <c r="I7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J7" t="n">
         <v>5.3</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1751,16 +1751,16 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
@@ -1775,122 +1775,122 @@
         <v>1.61</v>
       </c>
       <c r="V7" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
         <v>4</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.16</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="K8" t="n">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.34</v>
+        <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>1.34</v>
+        <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>1.84</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>3.15</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>1.25</v>
+        <v>2.82</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.35</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>1.35</v>
+        <v>2.76</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.41</v>
@@ -2653,7 +2653,7 @@
         <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
         <v>46</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>2.82</v>
       </c>
       <c r="H12" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="J12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU12" t="n">
         <v>3.45</v>
       </c>
-      <c r="K12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K13" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
         <v>2.42</v>
@@ -2927,134 +2927,134 @@
         <v>1.57</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U13" t="n">
-        <v>2.22</v>
+        <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="X13" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO13" t="n">
         <v>34</v>
       </c>
-      <c r="Y13" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AP13" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AD13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AW13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC13" t="n">
         <v>15</v>
       </c>
-      <c r="AH13" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.52</v>
-      </c>
       <c r="BD13" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.72</v>
+        <v>8.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="I14" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="K14" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14" t="n">
-        <v>2.24</v>
+        <v>5.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="S14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U14" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="V14" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="W14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X14" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y14" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AA14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
         <v>34</v>
       </c>
-      <c r="AC14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF14" t="n">
+      <c r="AJ14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL14" t="n">
         <v>60</v>
       </c>
-      <c r="AG14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>70</v>
-      </c>
       <c r="AM14" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.52</v>
+        <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.34</v>
+        <v>9.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.44</v>
+        <v>13.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.5</v>
+        <v>17.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.3</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.58</v>
+        <v>3.9</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.46</v>
+        <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.42</v>
+        <v>12.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.52</v>
+        <v>19</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.6</v>
+        <v>36</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.6</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.7</v>
+        <v>3.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
         <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J15" t="n">
         <v>3.55</v>
@@ -3297,7 +3297,7 @@
         <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3321,16 +3321,16 @@
         <v>2.82</v>
       </c>
       <c r="T15" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -3360,7 +3360,7 @@
         <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH15" t="n">
         <v>19</v>
@@ -3387,7 +3387,7 @@
         <v>40</v>
       </c>
       <c r="AP15" t="n">
-        <v>4</v>
+        <v>15.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>12.5</v>
@@ -3396,7 +3396,7 @@
         <v>21</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT15" t="n">
         <v>8.800000000000001</v>
@@ -3408,7 +3408,7 @@
         <v>11.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AX15" t="n">
         <v>11</v>
@@ -3417,32 +3417,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.9</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC15" t="n">
         <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF15" t="n">
         <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.47</v>
       </c>
-      <c r="G16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H16" t="n">
-        <v>5</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.42</v>
-      </c>
       <c r="S16" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="T16" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="U16" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3670,22 +3670,22 @@
         <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.06</v>
@@ -3709,7 +3709,7 @@
         <v>3.3</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U17" t="n">
         <v>1.83</v>
@@ -3718,13 +3718,13 @@
         <v>2.64</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>16</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
         <v>11</v>
@@ -3745,13 +3745,13 @@
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AG17" t="n">
         <v>30</v>
       </c>
       <c r="AH17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>50</v>
@@ -3799,38 +3799,38 @@
         <v>14.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AY17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ17" t="n">
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BG17" t="n">
         <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -3861,76 +3861,76 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.1</v>
       </c>
-      <c r="I18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.05</v>
-      </c>
       <c r="K18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>2.06</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="X18" t="n">
         <v>13</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA18" t="n">
         <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
         <v>970</v>
@@ -3939,13 +3939,13 @@
         <v>42</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
         <v>55</v>
@@ -3954,10 +3954,10 @@
         <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
@@ -3969,62 +3969,62 @@
         <v>42</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.7</v>
+        <v>10</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AY18" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>5.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD18" t="n">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4055,58 +4055,58 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="H19" t="n">
         <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J19" t="n">
         <v>4.6</v>
       </c>
       <c r="K19" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O19" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P19" t="n">
         <v>2.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R19" t="n">
         <v>1.73</v>
       </c>
       <c r="S19" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V19" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W19" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X19" t="n">
         <v>32</v>
@@ -4133,7 +4133,7 @@
         <v>60</v>
       </c>
       <c r="AF19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG19" t="n">
         <v>11.5</v>
@@ -4163,19 +4163,19 @@
         <v>50</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>18</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
@@ -4208,7 +4208,7 @@
         <v>20</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
         <v>5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G20" t="n">
         <v>2.64</v>
       </c>
       <c r="H20" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J20" t="n">
         <v>3</v>
@@ -4273,13 +4273,13 @@
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O20" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q20" t="n">
         <v>2.6</v>
@@ -4291,19 +4291,19 @@
         <v>5.4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
         <v>1.61</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y20" t="n">
         <v>10.5</v>
@@ -4336,7 +4336,7 @@
         <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
         <v>42</v>
@@ -4366,7 +4366,7 @@
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT20" t="n">
         <v>6.6</v>
@@ -4378,7 +4378,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX20" t="n">
         <v>12.5</v>
@@ -4390,29 +4390,29 @@
         <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB20" t="n">
         <v>32</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE20" t="n">
         <v>7.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.8</v>
       </c>
       <c r="BF20" t="n">
         <v>32</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="G21" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="H21" t="n">
         <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
         <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>2.32</v>
+        <v>2.56</v>
       </c>
       <c r="X21" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="Z21" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE21" t="n">
         <v>12</v>
       </c>
-      <c r="AC21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB21" t="n">
+      <c r="BF21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BG21" t="n">
         <v>12</v>
       </c>
-      <c r="BC21" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>3.05</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4637,34 +4637,34 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J22" t="n">
         <v>3.05</v>
       </c>
-      <c r="G22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3</v>
-      </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
         <v>1.82</v>
@@ -4673,22 +4673,22 @@
         <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
         <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V22" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X22" t="n">
         <v>13.5</v>
@@ -4733,13 +4733,13 @@
         <v>42</v>
       </c>
       <c r="AL22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM22" t="n">
         <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO22" t="n">
         <v>29</v>
@@ -4754,7 +4754,7 @@
         <v>14</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT22" t="n">
         <v>9.800000000000001</v>
@@ -4778,29 +4778,29 @@
         <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC22" t="n">
         <v>32</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="H23" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I23" t="n">
         <v>2.46</v>
@@ -4846,7 +4846,7 @@
         <v>3.85</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4876,13 +4876,13 @@
         <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V23" t="n">
         <v>1.69</v>
       </c>
       <c r="W23" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.32</v>
       </c>
       <c r="G24" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="H24" t="n">
         <v>2.9</v>
@@ -5037,7 +5037,7 @@
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
@@ -5055,19 +5055,19 @@
         <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S24" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="T24" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="U24" t="n">
         <v>3</v>
@@ -5076,22 +5076,22 @@
         <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="X24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Y24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
         <v>28</v>
       </c>
       <c r="AA24" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AC24" t="n">
         <v>11</v>
@@ -5112,7 +5112,7 @@
         <v>13.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ24" t="n">
         <v>34</v>
@@ -5127,10 +5127,10 @@
         <v>48</v>
       </c>
       <c r="AN24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO24" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AP24" t="n">
         <v>24</v>
@@ -5139,10 +5139,10 @@
         <v>19.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>9.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AT24" t="n">
         <v>17</v>
@@ -5151,13 +5151,13 @@
         <v>9.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW24" t="n">
         <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>9</v>
+        <v>18.5</v>
       </c>
       <c r="AY24" t="n">
         <v>11</v>
@@ -5175,20 +5175,20 @@
         <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG24" t="n">
         <v>11</v>
       </c>
-      <c r="BF24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>12</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K25" t="n">
         <v>1000</v>
@@ -5246,19 +5246,19 @@
         <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5413,64 +5413,64 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>1.62</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.3</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.86</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3</v>
+        <v>2.92</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -5479,104 +5479,104 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>2.54</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
         <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.3</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="G28" t="n">
         <v>2.4</v>
@@ -5816,7 +5816,7 @@
         <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>4.7</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,10 +5825,10 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.84</v>
+        <v>3.85</v>
       </c>
       <c r="O28" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P28" t="n">
         <v>1.84</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
         <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -6025,7 +6025,7 @@
         <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q29" t="n">
         <v>1.99</v>
@@ -6034,13 +6034,13 @@
         <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T29" t="n">
         <v>1.98</v>
       </c>
       <c r="U29" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V29" t="n">
         <v>2.42</v>
@@ -6052,7 +6052,7 @@
         <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z29" t="n">
         <v>9.199999999999999</v>
@@ -6064,7 +6064,7 @@
         <v>18</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
         <v>9.800000000000001</v>
@@ -6079,7 +6079,7 @@
         <v>22</v>
       </c>
       <c r="AH29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI29" t="n">
         <v>36</v>
@@ -6088,10 +6088,10 @@
         <v>160</v>
       </c>
       <c r="AK29" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL29" t="n">
         <v>85</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>80</v>
       </c>
       <c r="AM29" t="n">
         <v>130</v>
@@ -6115,25 +6115,25 @@
         <v>15.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU29" t="n">
         <v>8.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW29" t="n">
         <v>16.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY29" t="n">
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
         <v>34</v>
@@ -6148,7 +6148,7 @@
         <v>65</v>
       </c>
       <c r="BE29" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="BF29" t="n">
         <v>90</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>2.84</v>
       </c>
       <c r="H30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.66</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.68</v>
       </c>
       <c r="J30" t="n">
         <v>3.7</v>
@@ -6207,7 +6207,7 @@
         <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
@@ -6219,7 +6219,7 @@
         <v>1.24</v>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
         <v>1.76</v>
@@ -6318,7 +6318,7 @@
         <v>11</v>
       </c>
       <c r="AW30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX30" t="n">
         <v>19</v>
@@ -6333,7 +6333,7 @@
         <v>30</v>
       </c>
       <c r="BB30" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC30" t="n">
         <v>25</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I31" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="I31" t="n">
-        <v>9</v>
       </c>
       <c r="J31" t="n">
         <v>5.4</v>
@@ -6416,7 +6416,7 @@
         <v>2.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R31" t="n">
         <v>1.58</v>
@@ -6431,19 +6431,19 @@
         <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="X31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y31" t="n">
         <v>32</v>
       </c>
       <c r="Z31" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA31" t="n">
         <v>990</v>
@@ -6464,46 +6464,46 @@
         <v>9</v>
       </c>
       <c r="AG31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
         <v>100</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK31" t="n">
         <v>13.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AM31" t="n">
         <v>120</v>
       </c>
       <c r="AN31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AO31" t="n">
         <v>120</v>
       </c>
       <c r="AP31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR31" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS31" t="n">
         <v>110</v>
       </c>
       <c r="AT31" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU31" t="n">
         <v>11</v>
@@ -6512,22 +6512,22 @@
         <v>29</v>
       </c>
       <c r="AW31" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
         <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BB31" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC31" t="n">
         <v>13</v>
@@ -6536,17 +6536,17 @@
         <v>28</v>
       </c>
       <c r="BE31" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG31" t="n">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
         <v>1.78</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
         <v>2.96</v>
@@ -6649,10 +6649,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF32" t="n">
         <v>14</v>
@@ -6661,7 +6661,7 @@
         <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI32" t="n">
         <v>44</v>
@@ -6694,7 +6694,7 @@
         <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AT32" t="n">
         <v>11</v>
@@ -6706,7 +6706,7 @@
         <v>14.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX32" t="n">
         <v>13.5</v>
@@ -6733,14 +6733,14 @@
         <v>55</v>
       </c>
       <c r="BF32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG32" t="n">
         <v>30</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="G33" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="H33" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="I33" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="J33" t="n">
         <v>3.7</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.35</v>
@@ -6795,7 +6795,7 @@
         <v>1.06</v>
       </c>
       <c r="N33" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O33" t="n">
         <v>1.26</v>
@@ -6807,7 +6807,7 @@
         <v>1.78</v>
       </c>
       <c r="R33" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S33" t="n">
         <v>2.98</v>
@@ -6819,10 +6819,10 @@
         <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="W33" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X33" t="n">
         <v>17</v>
@@ -6831,7 +6831,7 @@
         <v>11.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA33" t="n">
         <v>27</v>
@@ -6849,10 +6849,10 @@
         <v>21</v>
       </c>
       <c r="AF33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH33" t="n">
         <v>16</v>
@@ -6882,7 +6882,7 @@
         <v>16</v>
       </c>
       <c r="AQ33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR33" t="n">
         <v>13.5</v>
@@ -6897,7 +6897,7 @@
         <v>8</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
         <v>19</v>
@@ -6915,26 +6915,26 @@
         <v>28</v>
       </c>
       <c r="BB33" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BC33" t="n">
         <v>34</v>
       </c>
       <c r="BD33" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE33" t="n">
         <v>50</v>
       </c>
       <c r="BF33" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BG33" t="n">
         <v>12</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G34" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H34" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I34" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J34" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K34" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L34" t="n">
         <v>1.24</v>
@@ -6995,28 +6995,28 @@
         <v>1.19</v>
       </c>
       <c r="P34" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
         <v>1.56</v>
       </c>
       <c r="S34" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T34" t="n">
         <v>1.48</v>
       </c>
       <c r="U34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V34" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W34" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="X34" t="n">
         <v>29</v>
@@ -7028,7 +7028,7 @@
         <v>32</v>
       </c>
       <c r="AA34" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB34" t="n">
         <v>970</v>
@@ -7040,7 +7040,7 @@
         <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AF34" t="n">
         <v>970</v>
@@ -7052,7 +7052,7 @@
         <v>970</v>
       </c>
       <c r="AI34" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AJ34" t="n">
         <v>32</v>
@@ -7070,65 +7070,65 @@
         <v>970</v>
       </c>
       <c r="AO34" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP34" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="AR34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV34" t="n">
         <v>3.8</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AW34" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB34" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BC34" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF34" t="n">
         <v>7.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
         <v>1000</v>
       </c>
       <c r="J35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -7186,19 +7186,19 @@
         <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P35" t="n">
         <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="G36" t="n">
         <v>7.6</v>
@@ -7362,13 +7362,13 @@
         <v>1.5</v>
       </c>
       <c r="I36" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K36" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L36" t="n">
         <v>1.26</v>
@@ -7377,31 +7377,31 @@
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="O36" t="n">
         <v>1.18</v>
       </c>
       <c r="P36" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q36" t="n">
         <v>1.59</v>
       </c>
       <c r="R36" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S36" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T36" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U36" t="n">
         <v>2.14</v>
       </c>
       <c r="V36" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="W36" t="n">
         <v>1.15</v>
@@ -7416,7 +7416,7 @@
         <v>10.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AB36" t="n">
         <v>32</v>
@@ -7434,7 +7434,7 @@
         <v>65</v>
       </c>
       <c r="AG36" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH36" t="n">
         <v>22</v>
@@ -7443,7 +7443,7 @@
         <v>29</v>
       </c>
       <c r="AJ36" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AK36" t="n">
         <v>90</v>
@@ -7455,10 +7455,10 @@
         <v>95</v>
       </c>
       <c r="AN36" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AO36" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AP36" t="n">
         <v>21</v>
@@ -7497,26 +7497,26 @@
         <v>24</v>
       </c>
       <c r="BB36" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BE36" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG36" t="n">
         <v>5.1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7556,7 +7556,7 @@
         <v>2.68</v>
       </c>
       <c r="I37" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="J37" t="n">
         <v>3.8</v>
@@ -7565,7 +7565,7 @@
         <v>3.85</v>
       </c>
       <c r="L37" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="M37" t="n">
         <v>1.04</v>
@@ -7580,7 +7580,7 @@
         <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R37" t="n">
         <v>1.67</v>
@@ -7592,7 +7592,7 @@
         <v>1.52</v>
       </c>
       <c r="U37" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="V37" t="n">
         <v>1.58</v>
@@ -7613,10 +7613,10 @@
         <v>40</v>
       </c>
       <c r="AB37" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC37" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD37" t="n">
         <v>12</v>
@@ -7670,7 +7670,7 @@
         <v>16</v>
       </c>
       <c r="AU37" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV37" t="n">
         <v>11.5</v>
@@ -7691,7 +7691,7 @@
         <v>26</v>
       </c>
       <c r="BB37" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC37" t="n">
         <v>22</v>
@@ -7706,11 +7706,11 @@
         <v>13</v>
       </c>
       <c r="BG37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7741,170 +7741,170 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>3.2</v>
       </c>
       <c r="G38" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H38" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>2.74</v>
       </c>
       <c r="K38" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="O38" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P38" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="R38" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>1.45</v>
+        <v>3.45</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V38" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W38" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH38" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM38" t="n">
         <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO38" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -7941,22 +7941,22 @@
         <v>1.96</v>
       </c>
       <c r="H39" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J39" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N39" t="n">
         <v>2.86</v>
@@ -7968,7 +7968,7 @@
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="R39" t="n">
         <v>1.21</v>
@@ -7995,7 +7995,7 @@
         <v>22</v>
       </c>
       <c r="Z39" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA39" t="n">
         <v>1000</v>
@@ -8043,62 +8043,62 @@
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ39" t="n">
         <v>11</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AU39" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AV39" t="n">
-        <v>17</v>
+        <v>2.44</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AX39" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AY39" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AZ39" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BC39" t="n">
         <v>2.42</v>
       </c>
-      <c r="BA39" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BD39" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BF39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G40" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="H40" t="n">
         <v>3</v>
@@ -8147,7 +8147,7 @@
         <v>3.2</v>
       </c>
       <c r="L40" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="M40" t="n">
         <v>1.14</v>
@@ -8159,7 +8159,7 @@
         <v>1.62</v>
       </c>
       <c r="P40" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q40" t="n">
         <v>2.8</v>
@@ -8174,13 +8174,13 @@
         <v>2.24</v>
       </c>
       <c r="U40" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V40" t="n">
         <v>1.41</v>
       </c>
       <c r="W40" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X40" t="n">
         <v>8</v>
@@ -8246,7 +8246,7 @@
         <v>16.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>50</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT40" t="n">
         <v>6.6</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G41" t="n">
         <v>1.47</v>
       </c>
       <c r="H41" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="J41" t="n">
         <v>4.8</v>
       </c>
       <c r="K41" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8359,7 +8359,7 @@
         <v>1.72</v>
       </c>
       <c r="R41" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S41" t="n">
         <v>2.82</v>
@@ -8371,7 +8371,7 @@
         <v>1.85</v>
       </c>
       <c r="V41" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W41" t="n">
         <v>3.1</v>
@@ -8383,10 +8383,10 @@
         <v>30</v>
       </c>
       <c r="Z41" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA41" t="n">
-        <v>360</v>
+        <v>330</v>
       </c>
       <c r="AB41" t="n">
         <v>9</v>
@@ -8395,13 +8395,13 @@
         <v>12</v>
       </c>
       <c r="AD41" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AE41" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF41" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG41" t="n">
         <v>11</v>
@@ -8410,16 +8410,16 @@
         <v>27</v>
       </c>
       <c r="AI41" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK41" t="n">
         <v>970</v>
       </c>
       <c r="AL41" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM41" t="n">
         <v>170</v>
@@ -8428,19 +8428,19 @@
         <v>6.8</v>
       </c>
       <c r="AO41" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ41" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR41" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS41" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT41" t="n">
         <v>7.6</v>
@@ -8452,7 +8452,7 @@
         <v>24</v>
       </c>
       <c r="AW41" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX41" t="n">
         <v>7.4</v>
@@ -8464,7 +8464,7 @@
         <v>20</v>
       </c>
       <c r="BA41" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB41" t="n">
         <v>10</v>
@@ -8476,17 +8476,17 @@
         <v>27</v>
       </c>
       <c r="BE41" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF41" t="n">
         <v>5.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8517,170 +8517,170 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G42" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="H42" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="I42" t="n">
         <v>7.2</v>
       </c>
       <c r="J42" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="K42" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>1.25</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P42" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="R42" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U42" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="V42" t="n">
         <v>1.16</v>
       </c>
       <c r="W42" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE42" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF42" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH42" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK42" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL42" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN42" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>
@@ -8714,10 +8714,10 @@
         <v>4.6</v>
       </c>
       <c r="G43" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H43" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="I43" t="n">
         <v>1.93</v>
@@ -8735,7 +8735,7 @@
         <v>1.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O43" t="n">
         <v>1.32</v>
@@ -8747,13 +8747,13 @@
         <v>1.94</v>
       </c>
       <c r="R43" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T43" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U43" t="n">
         <v>2.02</v>
@@ -8762,10 +8762,10 @@
         <v>2.08</v>
       </c>
       <c r="W43" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X43" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="Y43" t="n">
         <v>8.800000000000001</v>
@@ -8780,7 +8780,7 @@
         <v>17</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD43" t="n">
         <v>10.5</v>
@@ -8795,7 +8795,7 @@
         <v>19.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AI43" t="n">
         <v>38</v>
@@ -8804,13 +8804,13 @@
         <v>140</v>
       </c>
       <c r="AK43" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AL43" t="n">
         <v>70</v>
       </c>
       <c r="AM43" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN43" t="n">
         <v>95</v>
@@ -8843,7 +8843,7 @@
         <v>17.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY43" t="n">
         <v>17</v>
@@ -8852,29 +8852,29 @@
         <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB43" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC43" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BD43" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="BE43" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF43" t="n">
-        <v>60</v>
+        <v>9.4</v>
       </c>
       <c r="BG43" t="n">
         <v>11</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 02:55:20</t>
+          <t>2026-03-03 05:05:51</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
@@ -775,40 +775,40 @@
         <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
         <v>1.87</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
         <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -817,13 +817,13 @@
         <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AA2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>11.5</v>
@@ -835,92 +835,92 @@
         <v>80</v>
       </c>
       <c r="AF2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG2" t="n">
         <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>18.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AM2" t="n">
         <v>130</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>60</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF2" t="n">
         <v>8.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.6</v>
+        <v>55</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -954,13 +954,13 @@
         <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J3" t="n">
         <v>3.65</v>
@@ -975,103 +975,103 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AB3" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ3" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AN3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR3" t="n">
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>7.4</v>
@@ -1080,41 +1080,41 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD3" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3" t="n">
-        <v>38</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1175,43 +1175,43 @@
         <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
         <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA4" t="n">
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
         <v>10</v>
@@ -1220,10 +1220,10 @@
         <v>19.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
@@ -1232,13 +1232,13 @@
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL4" t="n">
         <v>27</v>
@@ -1247,46 +1247,46 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
         <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB4" t="n">
         <v>16.5</v>
@@ -1295,20 +1295,20 @@
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1342,94 +1342,94 @@
         <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="H5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
         <v>12</v>
       </c>
       <c r="Y5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Z5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG5" t="n">
         <v>970</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>14</v>
       </c>
       <c r="AH5" t="n">
         <v>950</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK5" t="n">
         <v>38</v>
@@ -1438,71 +1438,71 @@
         <v>70</v>
       </c>
       <c r="AM5" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BD5" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G6" t="n">
         <v>1.47</v>
@@ -1542,10 +1542,10 @@
         <v>9.6</v>
       </c>
       <c r="I6" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K6" t="n">
         <v>5</v>
@@ -1560,7 +1560,7 @@
         <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
@@ -1572,97 +1572,97 @@
         <v>1.35</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U6" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="V6" t="n">
         <v>1.1</v>
       </c>
       <c r="W6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>480</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH6" t="n">
         <v>32</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>450</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>210</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>30</v>
       </c>
       <c r="AI6" t="n">
         <v>180</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AL6" t="n">
         <v>48</v>
       </c>
       <c r="AM6" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO6" t="n">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>19.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="AX6" t="n">
         <v>6.8</v>
@@ -1674,29 +1674,29 @@
         <v>24</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="BB6" t="n">
         <v>10</v>
       </c>
       <c r="BC6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BF6" t="n">
         <v>6.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="I7" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="K7" t="n">
         <v>6.4</v>
@@ -1751,40 +1751,40 @@
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q7" t="n">
         <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="U7" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="X7" t="n">
         <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="n">
         <v>180</v>
@@ -1793,58 +1793,58 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AC7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>410</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AG7" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>380</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>310</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN7" t="n">
         <v>7.4</v>
       </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="AR7" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>8</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6.2</v>
@@ -1853,44 +1853,44 @@
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.8</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
         <v>13.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
@@ -1963,10 +1963,10 @@
         <v>3.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U8" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="V8" t="n">
         <v>1.58</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="K9" t="n">
         <v>4.4</v>
@@ -2145,10 +2145,10 @@
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -2157,22 +2157,22 @@
         <v>3.15</v>
       </c>
       <c r="T9" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U9" t="n">
         <v>1.85</v>
       </c>
-      <c r="U9" t="n">
-        <v>1.84</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W9" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="X9" t="n">
         <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
         <v>55</v>
@@ -2181,19 +2181,19 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
@@ -2205,13 +2205,13 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>24</v>
       </c>
       <c r="AL9" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AQ9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY9" t="n">
         <v>3.6</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AZ9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB9" t="n">
         <v>4</v>
       </c>
-      <c r="AS9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="BC9" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BD9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>2.06</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="H10" t="n">
         <v>3.5</v>
@@ -2321,19 +2321,19 @@
         <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="K10" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O10" t="n">
         <v>1.35</v>
@@ -2342,25 +2342,25 @@
         <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R10" t="n">
         <v>1.28</v>
       </c>
       <c r="S10" t="n">
-        <v>2.76</v>
+        <v>3.4</v>
       </c>
       <c r="T10" t="n">
         <v>1.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="X10" t="n">
         <v>14.5</v>
@@ -2378,7 +2378,7 @@
         <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
         <v>18.5</v>
@@ -2402,7 +2402,7 @@
         <v>34</v>
       </c>
       <c r="AK10" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL10" t="n">
         <v>50</v>
@@ -2417,62 +2417,62 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AR10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="BA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" t="n">
         <v>4.7</v>
       </c>
-      <c r="AX10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.4</v>
       </c>
-      <c r="BC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG10" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I11" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="n">
         <v>3.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -2533,7 +2533,7 @@
         <v>1.41</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
         <v>2.24</v>
@@ -2554,7 +2554,7 @@
         <v>1.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X11" t="n">
         <v>11.5</v>
@@ -2569,19 +2569,19 @@
         <v>170</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC11" t="n">
         <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>95</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -2611,7 +2611,7 @@
         <v>130</v>
       </c>
       <c r="AP11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>15</v>
@@ -2653,7 +2653,7 @@
         <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE11" t="n">
         <v>46</v>
@@ -2662,11 +2662,11 @@
         <v>13</v>
       </c>
       <c r="BG11" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="G12" t="n">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="H12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I12" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,37 +2721,37 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="U12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V12" t="n">
         <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -2760,7 +2760,7 @@
         <v>24</v>
       </c>
       <c r="AA12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB12" t="n">
         <v>970</v>
@@ -2769,7 +2769,7 @@
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>32</v>
@@ -2790,19 +2790,19 @@
         <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP12" t="n">
         <v>4.1</v>
@@ -2817,10 +2817,10 @@
         <v>4.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV12" t="n">
         <v>3.8</v>
@@ -2829,38 +2829,38 @@
         <v>4.4</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BA12" t="n">
         <v>4.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BD12" t="n">
         <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I13" t="n">
         <v>4.5</v>
@@ -2912,149 +2912,149 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N13" t="n">
-        <v>5.2</v>
+        <v>2.42</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P13" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
         <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
         <v>2</v>
       </c>
       <c r="X13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>4.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H14" t="n">
         <v>1.67</v>
@@ -3097,10 +3097,10 @@
         <v>1.81</v>
       </c>
       <c r="J14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
         <v>1.24</v>
@@ -3118,16 +3118,16 @@
         <v>2.48</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R14" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S14" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="T14" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="U14" t="n">
         <v>2.34</v>
@@ -3136,7 +3136,7 @@
         <v>2.22</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
         <v>32</v>
@@ -3196,7 +3196,7 @@
         <v>19</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR14" t="n">
         <v>9.6</v>
@@ -3205,25 +3205,25 @@
         <v>13.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14" t="n">
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>3.9</v>
+        <v>30</v>
       </c>
       <c r="AY14" t="n">
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
         <v>19</v>
@@ -3232,10 +3232,10 @@
         <v>4.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>36</v>
+        <v>3.95</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
         <v>4</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3279,25 +3279,25 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K15" t="n">
         <v>4.2</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3312,137 +3312,137 @@
         <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R15" t="n">
         <v>1.44</v>
       </c>
       <c r="S15" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD15" t="n">
         <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
         <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL15" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN15" t="n">
         <v>15</v>
       </c>
       <c r="AO15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP15" t="n">
-        <v>15.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW15" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.5</v>
-      </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF15" t="n">
         <v>10</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="G16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="L16" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="M16" t="n">
         <v>1.04</v>
@@ -3503,28 +3503,28 @@
         <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R16" t="n">
         <v>1.47</v>
       </c>
       <c r="S16" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="T16" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
         <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
         <v>25</v>
@@ -3545,7 +3545,7 @@
         <v>13</v>
       </c>
       <c r="AD16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE16" t="n">
         <v>110</v>
@@ -3581,13 +3581,13 @@
         <v>120</v>
       </c>
       <c r="AP16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS16" t="n">
         <v>4.1</v>
@@ -3596,16 +3596,16 @@
         <v>8.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV16" t="n">
         <v>18</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY16" t="n">
         <v>7.4</v>
@@ -3623,7 +3623,7 @@
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BE16" t="n">
         <v>4.1</v>
@@ -3632,11 +3632,11 @@
         <v>5.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3676,13 +3676,13 @@
         <v>1.52</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="J17" t="n">
         <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L17" t="n">
         <v>1.39</v>
@@ -3697,34 +3697,34 @@
         <v>1.31</v>
       </c>
       <c r="P17" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R17" t="n">
         <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T17" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="V17" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z17" t="n">
         <v>11</v>
@@ -3736,22 +3736,22 @@
         <v>27</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AG17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH17" t="n">
         <v>30</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>50</v>
@@ -3772,7 +3772,7 @@
         <v>220</v>
       </c>
       <c r="AO17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
         <v>13</v>
@@ -3781,13 +3781,13 @@
         <v>6.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS17" t="n">
         <v>12</v>
       </c>
       <c r="AT17" t="n">
-        <v>18</v>
+        <v>3.75</v>
       </c>
       <c r="AU17" t="n">
         <v>8.6</v>
@@ -3796,10 +3796,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="AY17" t="n">
         <v>22</v>
@@ -3808,29 +3808,29 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3864,7 @@
         <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H18" t="n">
         <v>3.15</v>
@@ -3876,22 +3876,22 @@
         <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O18" t="n">
         <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q18" t="n">
         <v>2.18</v>
@@ -3912,10 +3912,10 @@
         <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X18" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y18" t="n">
         <v>11.5</v>
@@ -3933,7 +3933,7 @@
         <v>7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AE18" t="n">
         <v>42</v>
@@ -3942,7 +3942,7 @@
         <v>970</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
         <v>970</v>
@@ -3957,7 +3957,7 @@
         <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
         <v>120</v>
@@ -3975,10 +3975,10 @@
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT18" t="n">
         <v>8.800000000000001</v>
@@ -3987,10 +3987,10 @@
         <v>6.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX18" t="n">
         <v>14.5</v>
@@ -3999,32 +3999,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="BA18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB18" t="n">
         <v>10</v>
       </c>
-      <c r="BB18" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BC18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD18" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF18" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.4</v>
+        <v>30</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G19" t="n">
         <v>1.66</v>
@@ -4064,7 +4064,7 @@
         <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J19" t="n">
         <v>4.6</v>
@@ -4085,22 +4085,22 @@
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S19" t="n">
         <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.2</v>
@@ -4115,7 +4115,7 @@
         <v>32</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA19" t="n">
         <v>140</v>
@@ -4124,13 +4124,13 @@
         <v>14.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
         <v>24</v>
       </c>
       <c r="AE19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AF19" t="n">
         <v>13.5</v>
@@ -4139,13 +4139,13 @@
         <v>11.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
         <v>55</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK19" t="n">
         <v>16</v>
@@ -4154,37 +4154,37 @@
         <v>26</v>
       </c>
       <c r="AM19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO19" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR19" t="n">
         <v>8</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU19" t="n">
         <v>10</v>
       </c>
       <c r="AV19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX19" t="n">
         <v>11</v>
@@ -4196,7 +4196,7 @@
         <v>14.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -4205,20 +4205,20 @@
         <v>12.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>3</v>
@@ -4270,22 +4270,22 @@
         <v>1.5</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O20" t="n">
         <v>1.54</v>
       </c>
       <c r="P20" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="R20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
         <v>5.4</v>
@@ -4294,7 +4294,7 @@
         <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V20" t="n">
         <v>1.38</v>
@@ -4303,7 +4303,7 @@
         <v>1.61</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y20" t="n">
         <v>10.5</v>
@@ -4318,7 +4318,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AD20" t="n">
         <v>16.5</v>
@@ -4330,13 +4330,13 @@
         <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH20" t="n">
         <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ20" t="n">
         <v>42</v>
@@ -4345,7 +4345,7 @@
         <v>38</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
         <v>200</v>
@@ -4357,62 +4357,62 @@
         <v>80</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR20" t="n">
         <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV20" t="n">
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX20" t="n">
         <v>12.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
         <v>19.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB20" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>32</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G21" t="n">
         <v>1.64</v>
@@ -4452,10 +4452,10 @@
         <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K21" t="n">
         <v>4.5</v>
@@ -4470,25 +4470,25 @@
         <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
         <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="U21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.16</v>
@@ -4509,10 +4509,10 @@
         <v>210</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD21" t="n">
         <v>25</v>
@@ -4524,7 +4524,7 @@
         <v>10</v>
       </c>
       <c r="AG21" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AH21" t="n">
         <v>22</v>
@@ -4554,16 +4554,16 @@
         <v>15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.199999999999999</v>
+        <v>17.5</v>
       </c>
       <c r="AR21" t="n">
         <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
         <v>8.6</v>
@@ -4575,7 +4575,7 @@
         <v>11.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY21" t="n">
         <v>8.800000000000001</v>
@@ -4596,17 +4596,17 @@
         <v>9.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
         <v>3.4</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I22" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -4667,10 +4667,10 @@
         <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
         <v>1.3</v>
@@ -4679,19 +4679,19 @@
         <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W22" t="n">
         <v>1.42</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
         <v>10.5</v>
@@ -4706,7 +4706,7 @@
         <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
         <v>13</v>
@@ -4724,7 +4724,7 @@
         <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ22" t="n">
         <v>60</v>
@@ -4733,13 +4733,13 @@
         <v>42</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM22" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO22" t="n">
         <v>29</v>
@@ -4754,7 +4754,7 @@
         <v>14</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AT22" t="n">
         <v>9.800000000000001</v>
@@ -4763,13 +4763,13 @@
         <v>6.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
       </c>
       <c r="AX22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AY22" t="n">
         <v>12</v>
@@ -4778,29 +4778,29 @@
         <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BC22" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF22" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BG22" t="n">
         <v>7</v>
       </c>
-      <c r="BG22" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -4831,19 +4831,19 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H23" t="n">
         <v>2.34</v>
       </c>
       <c r="I23" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K23" t="n">
         <v>3.95</v>
@@ -4855,25 +4855,25 @@
         <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O23" t="n">
         <v>1.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T23" t="n">
         <v>1.53</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.01</v>
       </c>
       <c r="U23" t="n">
         <v>2.4</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
         <v>2.42</v>
@@ -5037,7 +5037,7 @@
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
         <v>4.3</v>
@@ -5055,13 +5055,13 @@
         <v>1.14</v>
       </c>
       <c r="P24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R24" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="S24" t="n">
         <v>2.04</v>
@@ -5073,7 +5073,7 @@
         <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.7</v>
@@ -5082,7 +5082,7 @@
         <v>34</v>
       </c>
       <c r="Y24" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z24" t="n">
         <v>28</v>
@@ -5091,13 +5091,13 @@
         <v>46</v>
       </c>
       <c r="AB24" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AC24" t="n">
         <v>11</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE24" t="n">
         <v>27</v>
@@ -5106,7 +5106,7 @@
         <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH24" t="n">
         <v>13.5</v>
@@ -5118,46 +5118,46 @@
         <v>34</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
         <v>25</v>
       </c>
       <c r="AM24" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AN24" t="n">
         <v>9.6</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR24" t="n">
         <v>24</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>20</v>
-      </c>
       <c r="AS24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT24" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU24" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW24" t="n">
         <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY24" t="n">
         <v>11</v>
@@ -5166,10 +5166,10 @@
         <v>12</v>
       </c>
       <c r="BA24" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BB24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC24" t="n">
         <v>18.5</v>
@@ -5178,17 +5178,17 @@
         <v>21</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.04</v>
+        <v>1.85</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H25" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>2.84</v>
       </c>
       <c r="O25" t="n">
         <v>1.37</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.37</v>
+        <v>2.02</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>1.37</v>
+        <v>3.45</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>1.48</v>
       </c>
       <c r="G26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K26" t="n">
         <v>4.9</v>
-      </c>
-      <c r="I26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.37</v>
@@ -5452,7 +5452,7 @@
         <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="T26" t="n">
         <v>1.97</v>
@@ -5461,16 +5461,16 @@
         <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W26" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X26" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -5479,37 +5479,37 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG26" t="n">
         <v>11</v>
       </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AH26" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
@@ -5521,62 +5521,62 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.92</v>
+        <v>3.85</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.8</v>
+        <v>5.9</v>
       </c>
       <c r="AW26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX26" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX26" t="n">
-        <v>3.05</v>
-      </c>
       <c r="AY26" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="BC26" t="n">
-        <v>3.55</v>
+        <v>5.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BF26" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5801,61 +5801,61 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="G28" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="H28" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="I28" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="n">
         <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S28" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="T28" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="U28" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="V28" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y28" t="n">
         <v>1000</v>
@@ -5867,10 +5867,10 @@
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
         <v>1000</v>
@@ -5879,10 +5879,10 @@
         <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH28" t="n">
         <v>1000</v>
@@ -5900,71 +5900,71 @@
         <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>5.7</v>
       </c>
       <c r="G29" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H29" t="n">
         <v>1.69</v>
@@ -6013,7 +6013,7 @@
         <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.07</v>
@@ -6028,13 +6028,13 @@
         <v>1.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>1.36</v>
       </c>
       <c r="S29" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T29" t="n">
         <v>1.98</v>
@@ -6046,13 +6046,13 @@
         <v>2.42</v>
       </c>
       <c r="W29" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X29" t="n">
         <v>14.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z29" t="n">
         <v>9.199999999999999</v>
@@ -6115,7 +6115,7 @@
         <v>15.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU29" t="n">
         <v>8.6</v>
@@ -6127,7 +6127,7 @@
         <v>16.5</v>
       </c>
       <c r="AX29" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AY29" t="n">
         <v>20</v>
@@ -6139,7 +6139,7 @@
         <v>34</v>
       </c>
       <c r="BB29" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BC29" t="n">
         <v>70</v>
@@ -6148,7 +6148,7 @@
         <v>65</v>
       </c>
       <c r="BE29" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="BF29" t="n">
         <v>90</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>2.84</v>
       </c>
       <c r="H30" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.64</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.66</v>
       </c>
       <c r="J30" t="n">
         <v>3.7</v>
@@ -6207,31 +6207,31 @@
         <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M30" t="n">
         <v>1.05</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O30" t="n">
         <v>1.24</v>
       </c>
       <c r="P30" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R30" t="n">
         <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T30" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U30" t="n">
         <v>2.5</v>
@@ -6243,7 +6243,7 @@
         <v>1.54</v>
       </c>
       <c r="X30" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y30" t="n">
         <v>14</v>
@@ -6252,7 +6252,7 @@
         <v>18.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB30" t="n">
         <v>14.5</v>
@@ -6294,7 +6294,7 @@
         <v>19.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP30" t="n">
         <v>17.5</v>
@@ -6345,14 +6345,14 @@
         <v>55</v>
       </c>
       <c r="BF30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BG30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G31" t="n">
         <v>1.43</v>
       </c>
-      <c r="G31" t="n">
-        <v>1.44</v>
-      </c>
       <c r="H31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
         <v>5.4</v>
@@ -6416,7 +6416,7 @@
         <v>2.48</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R31" t="n">
         <v>1.58</v>
@@ -6425,13 +6425,13 @@
         <v>2.68</v>
       </c>
       <c r="T31" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U31" t="n">
         <v>2.04</v>
       </c>
       <c r="V31" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W31" t="n">
         <v>3.3</v>
@@ -6443,7 +6443,7 @@
         <v>32</v>
       </c>
       <c r="Z31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="n">
         <v>990</v>
@@ -6497,10 +6497,10 @@
         <v>29</v>
       </c>
       <c r="AR31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AS31" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AT31" t="n">
         <v>9.199999999999999</v>
@@ -6512,7 +6512,7 @@
         <v>29</v>
       </c>
       <c r="AW31" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AX31" t="n">
         <v>8.6</v>
@@ -6539,14 +6539,14 @@
         <v>42</v>
       </c>
       <c r="BF31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG31" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6613,7 +6613,7 @@
         <v>1.78</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
         <v>2.96</v>
@@ -6694,7 +6694,7 @@
         <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AT32" t="n">
         <v>11</v>
@@ -6709,7 +6709,7 @@
         <v>34</v>
       </c>
       <c r="AX32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY32" t="n">
         <v>10</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H33" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I33" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J33" t="n">
         <v>3.7</v>
@@ -6792,7 +6792,7 @@
         <v>1.35</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N33" t="n">
         <v>4.6</v>
@@ -6801,16 +6801,16 @@
         <v>1.26</v>
       </c>
       <c r="P33" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q33" t="n">
         <v>1.78</v>
       </c>
       <c r="R33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S33" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
         <v>1.67</v>
@@ -6819,7 +6819,7 @@
         <v>2.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W33" t="n">
         <v>1.38</v>
@@ -6864,10 +6864,10 @@
         <v>65</v>
       </c>
       <c r="AK33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL33" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM33" t="n">
         <v>75</v>
@@ -6918,23 +6918,23 @@
         <v>48</v>
       </c>
       <c r="BC33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD33" t="n">
         <v>38</v>
       </c>
       <c r="BE33" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="BF33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG33" t="n">
         <v>12</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="G34" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="H34" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L34" t="n">
         <v>1.24</v>
@@ -6989,58 +6989,58 @@
         <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P34" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="R34" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S34" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="T34" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U34" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="V34" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="W34" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="X34" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Y34" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z34" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AA34" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AB34" t="n">
         <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD34" t="n">
         <v>970</v>
       </c>
       <c r="AE34" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AF34" t="n">
         <v>970</v>
@@ -7052,83 +7052,83 @@
         <v>970</v>
       </c>
       <c r="AI34" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AJ34" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK34" t="n">
         <v>24</v>
       </c>
       <c r="AL34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM34" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AN34" t="n">
         <v>970</v>
       </c>
       <c r="AO34" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>3.95</v>
+        <v>16</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AT34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3.7</v>
       </c>
-      <c r="AU34" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AV34" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.8</v>
+        <v>10.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.55</v>
+        <v>8.6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.1</v>
+        <v>17</v>
       </c>
       <c r="BC34" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BF34" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7159,59 +7159,59 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="G35" t="n">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="I35" t="n">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="J35" t="n">
-        <v>1.03</v>
+        <v>2.8</v>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="O35" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P35" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="W35" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X35" t="n">
         <v>1000</v>
       </c>
@@ -7267,62 +7267,62 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7353,61 +7353,61 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="I36" t="n">
         <v>1.51</v>
       </c>
       <c r="J36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K36" t="n">
         <v>5.1</v>
       </c>
-      <c r="K36" t="n">
-        <v>5.2</v>
-      </c>
       <c r="L36" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M36" t="n">
         <v>1.04</v>
       </c>
       <c r="N36" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
         <v>1.18</v>
       </c>
       <c r="P36" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="R36" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S36" t="n">
         <v>2.34</v>
       </c>
       <c r="T36" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U36" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V36" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="W36" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Y36" t="n">
         <v>11.5</v>
@@ -7419,22 +7419,22 @@
         <v>14</v>
       </c>
       <c r="AB36" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AC36" t="n">
         <v>12.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AE36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF36" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AG36" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AH36" t="n">
         <v>22</v>
@@ -7443,28 +7443,28 @@
         <v>29</v>
       </c>
       <c r="AJ36" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AK36" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AL36" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AM36" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN36" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="n">
         <v>5.7</v>
       </c>
       <c r="AP36" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ36" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR36" t="n">
         <v>9.199999999999999</v>
@@ -7473,50 +7473,50 @@
         <v>12</v>
       </c>
       <c r="AT36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AU36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV36" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW36" t="n">
         <v>12.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA36" t="n">
         <v>24</v>
       </c>
       <c r="BB36" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC36" t="n">
         <v>12.5</v>
       </c>
       <c r="BD36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BE36" t="n">
         <v>12.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG36" t="n">
         <v>5.1</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G37" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="H37" t="n">
         <v>2.68</v>
@@ -7565,7 +7565,7 @@
         <v>3.85</v>
       </c>
       <c r="L37" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="M37" t="n">
         <v>1.04</v>
@@ -7580,7 +7580,7 @@
         <v>2.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R37" t="n">
         <v>1.67</v>
@@ -7598,7 +7598,7 @@
         <v>1.58</v>
       </c>
       <c r="W37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="X37" t="n">
         <v>23</v>
@@ -7649,7 +7649,7 @@
         <v>48</v>
       </c>
       <c r="AN37" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO37" t="n">
         <v>14.5</v>
@@ -7691,7 +7691,7 @@
         <v>26</v>
       </c>
       <c r="BB37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC37" t="n">
         <v>22</v>
@@ -7700,17 +7700,17 @@
         <v>26</v>
       </c>
       <c r="BE37" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG37" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7879,7 +7879,7 @@
         <v>3.55</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA38" t="n">
         <v>4</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G39" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="H39" t="n">
         <v>5.5</v>
@@ -7950,13 +7950,13 @@
         <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L39" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M39" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N39" t="n">
         <v>2.86</v>
@@ -7968,137 +7968,137 @@
         <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.14</v>
+        <v>2.26</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S39" t="n">
         <v>4.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V39" t="n">
         <v>1.16</v>
       </c>
       <c r="W39" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="X39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB39" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y39" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BC39" t="n">
-        <v>2.42</v>
+        <v>17</v>
       </c>
       <c r="BD39" t="n">
-        <v>2.52</v>
+        <v>4.8</v>
       </c>
       <c r="BE39" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="BF39" t="n">
-        <v>2.62</v>
+        <v>12.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.62</v>
+        <v>5.1</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8129,13 +8129,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="G40" t="n">
         <v>2.9</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I40" t="n">
         <v>3.4</v>
@@ -8144,7 +8144,7 @@
         <v>2.98</v>
       </c>
       <c r="K40" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L40" t="n">
         <v>1.62</v>
@@ -8162,37 +8162,37 @@
         <v>1.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R40" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S40" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U40" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V40" t="n">
         <v>1.41</v>
       </c>
       <c r="W40" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X40" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y40" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA40" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AB40" t="n">
         <v>7.8</v>
@@ -8201,64 +8201,64 @@
         <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AE40" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF40" t="n">
         <v>17</v>
       </c>
       <c r="AG40" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AI40" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ40" t="n">
         <v>55</v>
       </c>
       <c r="AK40" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AL40" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM40" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AN40" t="n">
         <v>60</v>
       </c>
       <c r="AO40" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP40" t="n">
         <v>6.8</v>
       </c>
       <c r="AQ40" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS40" t="n">
-        <v>8.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AT40" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU40" t="n">
         <v>6.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW40" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX40" t="n">
         <v>13.5</v>
@@ -8270,29 +8270,29 @@
         <v>21</v>
       </c>
       <c r="BA40" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BB40" t="n">
-        <v>40</v>
+        <v>6.6</v>
       </c>
       <c r="BC40" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BD40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BE40" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BF40" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8326,13 +8326,13 @@
         <v>1.41</v>
       </c>
       <c r="G41" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J41" t="n">
         <v>4.8</v>
@@ -8347,25 +8347,25 @@
         <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O41" t="n">
         <v>1.24</v>
       </c>
       <c r="P41" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R41" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S41" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T41" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U41" t="n">
         <v>1.85</v>
@@ -8374,22 +8374,22 @@
         <v>1.11</v>
       </c>
       <c r="W41" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z41" t="n">
         <v>80</v>
       </c>
       <c r="AA41" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AB41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC41" t="n">
         <v>12</v>
@@ -8398,10 +8398,10 @@
         <v>34</v>
       </c>
       <c r="AE41" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AF41" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AG41" t="n">
         <v>11</v>
@@ -8413,80 +8413,80 @@
         <v>130</v>
       </c>
       <c r="AJ41" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK41" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL41" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM41" t="n">
         <v>170</v>
       </c>
       <c r="AN41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>210</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS41" t="n">
         <v>6.8</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>200</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>9.6</v>
       </c>
       <c r="AT41" t="n">
         <v>7.6</v>
       </c>
       <c r="AU41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>24</v>
+        <v>5.8</v>
       </c>
       <c r="AW41" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX41" t="n">
         <v>7.4</v>
       </c>
       <c r="AY41" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="AZ41" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>9.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BB41" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC41" t="n">
         <v>13</v>
       </c>
       <c r="BD41" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="BE41" t="n">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="BG41" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8517,16 +8517,16 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G42" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H42" t="n">
         <v>6.4</v>
       </c>
       <c r="I42" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="J42" t="n">
         <v>3.6</v>
@@ -8547,82 +8547,82 @@
         <v>1.44</v>
       </c>
       <c r="P42" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="R42" t="n">
         <v>1.22</v>
       </c>
       <c r="S42" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T42" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="U42" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="V42" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W42" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y42" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z42" t="n">
         <v>60</v>
       </c>
       <c r="AA42" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB42" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AE42" t="n">
         <v>170</v>
       </c>
       <c r="AF42" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI42" t="n">
         <v>180</v>
       </c>
       <c r="AJ42" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AL42" t="n">
         <v>60</v>
       </c>
       <c r="AM42" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AN42" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AO42" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AP42" t="n">
         <v>9.4</v>
@@ -8631,10 +8631,10 @@
         <v>14.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="AS42" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="AT42" t="n">
         <v>5.7</v>
@@ -8646,7 +8646,7 @@
         <v>21</v>
       </c>
       <c r="AW42" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="AX42" t="n">
         <v>7.4</v>
@@ -8658,7 +8658,7 @@
         <v>23</v>
       </c>
       <c r="BA42" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="BB42" t="n">
         <v>14</v>
@@ -8667,20 +8667,20 @@
         <v>18.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BF42" t="n">
         <v>11</v>
       </c>
       <c r="BG42" t="n">
-        <v>9.199999999999999</v>
+        <v>4.6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>
@@ -8717,19 +8717,19 @@
         <v>5.2</v>
       </c>
       <c r="H43" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I43" t="n">
         <v>1.93</v>
       </c>
       <c r="J43" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K43" t="n">
         <v>4.1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M43" t="n">
         <v>1.07</v>
@@ -8738,31 +8738,31 @@
         <v>3.7</v>
       </c>
       <c r="O43" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P43" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q43" t="n">
         <v>1.92</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.94</v>
       </c>
       <c r="R43" t="n">
         <v>1.36</v>
       </c>
       <c r="S43" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T43" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U43" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V43" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="W43" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X43" t="n">
         <v>18</v>
@@ -8780,7 +8780,7 @@
         <v>17</v>
       </c>
       <c r="AC43" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD43" t="n">
         <v>10.5</v>
@@ -8795,7 +8795,7 @@
         <v>19.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI43" t="n">
         <v>38</v>
@@ -8804,7 +8804,7 @@
         <v>140</v>
       </c>
       <c r="AK43" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AL43" t="n">
         <v>70</v>
@@ -8813,22 +8813,22 @@
         <v>130</v>
       </c>
       <c r="AN43" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO43" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP43" t="n">
         <v>13</v>
       </c>
-      <c r="AP43" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AQ43" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR43" t="n">
         <v>10</v>
       </c>
       <c r="AS43" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT43" t="n">
         <v>14.5</v>
@@ -8843,38 +8843,38 @@
         <v>17.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY43" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AZ43" t="n">
         <v>17</v>
       </c>
       <c r="BA43" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB43" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC43" t="n">
-        <v>55</v>
+        <v>8.6</v>
       </c>
       <c r="BD43" t="n">
-        <v>55</v>
+        <v>8.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG43" t="n">
         <v>9.4</v>
       </c>
-      <c r="BG43" t="n">
-        <v>11</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 05:05:51</t>
+          <t>2026-03-03 07:16:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH44"/>
+  <dimension ref="A1:BH45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H2" t="n">
         <v>5.4</v>
@@ -787,28 +787,28 @@
         <v>1.29</v>
       </c>
       <c r="P2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.06</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.04</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X2" t="n">
         <v>20</v>
@@ -826,7 +826,7 @@
         <v>9</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>23</v>
@@ -838,7 +838,7 @@
         <v>11</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -847,7 +847,7 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK2" t="n">
         <v>19</v>
@@ -865,19 +865,19 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU2" t="n">
         <v>8.4</v>
@@ -886,7 +886,7 @@
         <v>18</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -898,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="BB2" t="n">
         <v>14.5</v>
@@ -907,20 +907,20 @@
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
         <v>4.3</v>
@@ -966,7 +966,7 @@
         <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.39</v>
@@ -978,13 +978,13 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>1.42</v>
@@ -996,13 +996,13 @@
         <v>1.78</v>
       </c>
       <c r="U3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V3" t="n">
         <v>1.98</v>
       </c>
       <c r="W3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>16.5</v>
@@ -1029,7 +1029,7 @@
         <v>20</v>
       </c>
       <c r="AF3" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG3" t="n">
         <v>17</v>
@@ -1056,10 +1056,10 @@
         <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
         <v>9.4</v>
@@ -1098,23 +1098,23 @@
         <v>12.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="BE3" t="n">
         <v>12.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BG3" t="n">
         <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="G4" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
         <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.21</v>
@@ -1178,31 +1178,31 @@
         <v>2.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z4" t="n">
         <v>44</v>
@@ -1232,10 +1232,10 @@
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>16</v>
@@ -1247,7 +1247,7 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO4" t="n">
         <v>50</v>
@@ -1259,10 +1259,10 @@
         <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AT4" t="n">
         <v>10.5</v>
@@ -1274,7 +1274,7 @@
         <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX4" t="n">
         <v>10.5</v>
@@ -1286,7 +1286,7 @@
         <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
         <v>16.5</v>
@@ -1298,17 +1298,17 @@
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF4" t="n">
         <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>38</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.23</v>
       </c>
       <c r="G5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>8.800000000000001</v>
@@ -1363,34 +1363,34 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
         <v>1.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="X5" t="n">
         <v>60</v>
@@ -1405,37 +1405,37 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AC5" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AD5" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>980</v>
       </c>
       <c r="AH5" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AI5" t="n">
         <v>100</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AK5" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AL5" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AM5" t="n">
         <v>95</v>
@@ -1444,16 +1444,16 @@
         <v>3.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5" t="n">
         <v>5.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS5" t="n">
         <v>5.5</v>
@@ -1462,7 +1462,7 @@
         <v>4.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
         <v>5</v>
@@ -1474,10 +1474,10 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BA5" t="n">
         <v>5.3</v>
@@ -1489,20 +1489,20 @@
         <v>4.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF5" t="n">
         <v>2.56</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I6" t="n">
         <v>3.85</v>
@@ -1548,22 +1548,22 @@
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.51</v>
       </c>
       <c r="P6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
         <v>2.72</v>
@@ -1575,7 +1575,7 @@
         <v>5.3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U6" t="n">
         <v>1.62</v>
@@ -1584,7 +1584,7 @@
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X6" t="n">
         <v>12</v>
@@ -1593,10 +1593,10 @@
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AA6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB6" t="n">
         <v>7.8</v>
@@ -1608,16 +1608,16 @@
         <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
         <v>15.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="AI6" t="n">
         <v>80</v>
@@ -1626,7 +1626,7 @@
         <v>42</v>
       </c>
       <c r="AK6" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AL6" t="n">
         <v>70</v>
@@ -1638,19 +1638,19 @@
         <v>40</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,44 +1659,44 @@
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>5.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.2</v>
+        <v>22</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.46</v>
       </c>
       <c r="H7" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I7" t="n">
         <v>11</v>
@@ -1751,7 +1751,7 @@
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
@@ -1760,13 +1760,13 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
         <v>2.12</v>
@@ -1778,10 +1778,10 @@
         <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y7" t="n">
         <v>29</v>
@@ -1793,7 +1793,7 @@
         <v>460</v>
       </c>
       <c r="AB7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC7" t="n">
         <v>11.5</v>
@@ -1817,7 +1817,7 @@
         <v>180</v>
       </c>
       <c r="AJ7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK7" t="n">
         <v>17.5</v>
@@ -1838,13 +1838,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT7" t="n">
         <v>6.4</v>
@@ -1853,10 +1853,10 @@
         <v>9.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX7" t="n">
         <v>6.8</v>
@@ -1868,7 +1868,7 @@
         <v>24</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB7" t="n">
         <v>10</v>
@@ -1880,17 +1880,17 @@
         <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF7" t="n">
         <v>6.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="G8" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="K8" t="n">
         <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -1963,7 +1963,7 @@
         <v>3.05</v>
       </c>
       <c r="T8" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
         <v>1.62</v>
@@ -1972,7 +1972,7 @@
         <v>1.06</v>
       </c>
       <c r="W8" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="X8" t="n">
         <v>21</v>
@@ -1987,7 +1987,7 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
         <v>15.5</v>
@@ -1996,7 +1996,7 @@
         <v>55</v>
       </c>
       <c r="AE8" t="n">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="AF8" t="n">
         <v>7.6</v>
@@ -2005,10 +2005,10 @@
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI8" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AJ8" t="n">
         <v>12</v>
@@ -2029,62 +2029,62 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX8" t="n">
         <v>6</v>
       </c>
-      <c r="AT8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AY8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4.1</v>
       </c>
-      <c r="AZ8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2115,40 +2115,40 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="I9" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M9" t="n">
         <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R9" t="n">
         <v>1.27</v>
@@ -2157,46 +2157,46 @@
         <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V9" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="X9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AA9" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC9" t="n">
         <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AG9" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH9" t="n">
         <v>22</v>
@@ -2205,80 +2205,80 @@
         <v>55</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AO9" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.8</v>
+        <v>2.82</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.5</v>
+        <v>3.15</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.6</v>
+        <v>2.88</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.4</v>
+        <v>2.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.800000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AX9" t="n">
-        <v>17</v>
+        <v>3.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.5</v>
+        <v>3.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.9</v>
+        <v>3.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="BG9" t="n">
-        <v>20</v>
+        <v>3.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2309,79 +2309,79 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="H10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
         <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>1.42</v>
       </c>
       <c r="M10" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S10" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="T10" t="n">
-        <v>1.93</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W10" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="X10" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2393,16 +2393,16 @@
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
@@ -2411,68 +2411,68 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
         <v>14</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC10" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.6</v>
+        <v>5.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2503,40 +2503,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
         <v>4.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O11" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
         <v>1.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>1.2</v>
@@ -2545,22 +2545,22 @@
         <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.02</v>
+        <v>1.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="X11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z11" t="n">
         <v>28</v>
@@ -2569,34 +2569,34 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,28 +2611,28 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>20</v>
+        <v>5.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU11" t="n">
         <v>6.2</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -2641,32 +2641,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.77</v>
       </c>
       <c r="G12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H12" t="n">
         <v>5.8</v>
@@ -2709,7 +2709,7 @@
         <v>5.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
         <v>3.85</v>
@@ -2724,13 +2724,13 @@
         <v>3.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P12" t="n">
         <v>1.78</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R12" t="n">
         <v>1.28</v>
@@ -2748,7 +2748,7 @@
         <v>1.2</v>
       </c>
       <c r="W12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X12" t="n">
         <v>11.5</v>
@@ -2784,7 +2784,7 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
         <v>17.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
         <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
         <v>1.53</v>
@@ -2939,10 +2939,10 @@
         <v>2.24</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X13" t="n">
         <v>23</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3127,7 @@
         <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="U14" t="n">
         <v>2.46</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3321,10 +3321,10 @@
         <v>2.34</v>
       </c>
       <c r="T15" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
         <v>2.2</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3515,13 +3515,13 @@
         <v>2.82</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
         <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
         <v>1.79</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3694,19 +3694,19 @@
         <v>4.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R17" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="T17" t="n">
         <v>1.67</v>
@@ -3775,10 +3775,10 @@
         <v>120</v>
       </c>
       <c r="AP17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>17.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>20</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
@@ -3790,28 +3790,28 @@
         <v>8.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
         <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
         <v>11.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I18" t="n">
         <v>1.5</v>
       </c>
-      <c r="I18" t="n">
-        <v>1.51</v>
-      </c>
       <c r="J18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
         <v>5</v>
@@ -3909,7 +3909,7 @@
         <v>1.8</v>
       </c>
       <c r="V18" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
         <v>1.12</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H19" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
         <v>3.1</v>
@@ -4073,7 +4073,7 @@
         <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M19" t="n">
         <v>1.09</v>
@@ -4088,7 +4088,7 @@
         <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
         <v>1.3</v>
@@ -4103,25 +4103,25 @@
         <v>2.06</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="X19" t="n">
         <v>13</v>
       </c>
       <c r="Y19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AA19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC19" t="n">
         <v>7.2</v>
@@ -4130,13 +4130,13 @@
         <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
         <v>970</v>
       </c>
       <c r="AG19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
         <v>970</v>
@@ -4148,16 +4148,16 @@
         <v>40</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>48</v>
@@ -4166,7 +4166,7 @@
         <v>10</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR19" t="n">
         <v>15</v>
@@ -4175,7 +4175,7 @@
         <v>10</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
@@ -4193,32 +4193,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BA19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE19" t="n">
         <v>10</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>10.5</v>
       </c>
       <c r="BF19" t="n">
         <v>21</v>
       </c>
       <c r="BG19" t="n">
-        <v>9.4</v>
+        <v>32</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>5.4</v>
       </c>
       <c r="I20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J20" t="n">
         <v>4.6</v>
@@ -4267,7 +4267,7 @@
         <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
@@ -4279,7 +4279,7 @@
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q20" t="n">
         <v>1.5</v>
@@ -4306,7 +4306,7 @@
         <v>36</v>
       </c>
       <c r="Y20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z20" t="n">
         <v>55</v>
@@ -4321,7 +4321,7 @@
         <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>65</v>
@@ -4330,13 +4330,13 @@
         <v>13.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
         <v>17.5</v>
@@ -4348,7 +4348,7 @@
         <v>26</v>
       </c>
       <c r="AM20" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
         <v>5.9</v>
@@ -4360,13 +4360,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20" t="n">
         <v>11.5</v>
@@ -4375,10 +4375,10 @@
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -4390,7 +4390,7 @@
         <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB20" t="n">
         <v>14.5</v>
@@ -4402,17 +4402,17 @@
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
         <v>5.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G21" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H21" t="n">
         <v>3.4</v>
@@ -4455,7 +4455,7 @@
         <v>3.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
         <v>3.1</v>
@@ -4467,10 +4467,10 @@
         <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O21" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P21" t="n">
         <v>1.56</v>
@@ -4494,13 +4494,13 @@
         <v>1.38</v>
       </c>
       <c r="W21" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z21" t="n">
         <v>24</v>
@@ -4536,7 +4536,7 @@
         <v>42</v>
       </c>
       <c r="AK21" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL21" t="n">
         <v>65</v>
@@ -4572,7 +4572,7 @@
         <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4584,19 +4584,19 @@
         <v>19.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB21" t="n">
         <v>32</v>
       </c>
       <c r="BC21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF21" t="n">
         <v>30</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>1.58</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H22" t="n">
         <v>6.6</v>
@@ -4649,22 +4649,22 @@
         <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
         <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P22" t="n">
         <v>2.06</v>
@@ -4679,19 +4679,19 @@
         <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V22" t="n">
         <v>1.16</v>
       </c>
       <c r="W22" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="X22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="n">
         <v>26</v>
@@ -4703,7 +4703,7 @@
         <v>210</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC22" t="n">
         <v>9.800000000000001</v>
@@ -4715,7 +4715,7 @@
         <v>110</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG22" t="n">
         <v>10</v>
@@ -4745,16 +4745,16 @@
         <v>130</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>19</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT22" t="n">
         <v>7.6</v>
@@ -4766,7 +4766,7 @@
         <v>19</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AX22" t="n">
         <v>8.6</v>
@@ -4775,10 +4775,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB22" t="n">
         <v>13.5</v>
@@ -4787,20 +4787,20 @@
         <v>14.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF22" t="n">
         <v>7.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
         <v>3.4</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I23" t="n">
         <v>2.58</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>3.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O23" t="n">
         <v>1.38</v>
@@ -4864,19 +4864,19 @@
         <v>1.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S23" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="T23" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U23" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
         <v>1.63</v>
@@ -4885,7 +4885,7 @@
         <v>1.42</v>
       </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
         <v>10</v>
@@ -4906,7 +4906,7 @@
         <v>12</v>
       </c>
       <c r="AE23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF23" t="n">
         <v>23</v>
@@ -4936,7 +4936,7 @@
         <v>44</v>
       </c>
       <c r="AO23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4972,29 +4972,29 @@
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC23" t="n">
         <v>34</v>
       </c>
       <c r="BD23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BG23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>3.25</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I24" t="n">
         <v>2.24</v>
@@ -5043,40 +5043,40 @@
         <v>4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U24" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W24" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X24" t="n">
         <v>26</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Lugano</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Young Boys</t>
+          <t>Sion</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="G25" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="I25" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU25" t="n">
         <v>7</v>
       </c>
-      <c r="O25" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="U25" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X25" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y25" t="n">
+      <c r="AV25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW25" t="n">
         <v>36</v>
       </c>
-      <c r="Z25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>32</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>28</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS25" t="n">
+      <c r="AX25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BA25" t="n">
         <v>36</v>
       </c>
-      <c r="AT25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA25" t="n">
+      <c r="BB25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG25" t="n">
         <v>10</v>
       </c>
-      <c r="BB25" t="n">
-        <v>29</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>36</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -5413,58 +5413,58 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G26" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R26" t="n">
         <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W26" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="X26" t="n">
         <v>10.5</v>
@@ -5533,13 +5533,13 @@
         <v>5.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW26" t="n">
         <v>5.1</v>
@@ -5548,7 +5548,7 @@
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
         <v>20</v>
@@ -5557,10 +5557,10 @@
         <v>5.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BD26" t="n">
         <v>5</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>US Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.73</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>1.86</v>
+        <v>2.9</v>
       </c>
       <c r="H27" t="n">
-        <v>5.4</v>
+        <v>2.96</v>
       </c>
       <c r="I27" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.72</v>
       </c>
-      <c r="Q27" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.04</v>
-      </c>
       <c r="U27" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V27" t="n">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>2.14</v>
+        <v>1.55</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE27" t="n">
         <v>55</v>
       </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF27" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="AH27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AL27" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.5</v>
+        <v>2.46</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.2</v>
+        <v>2.12</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>18.5</v>
+        <v>2.24</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.4</v>
+        <v>2.44</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.4</v>
+        <v>2.3</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>2.22</v>
       </c>
       <c r="AZ27" t="n">
-        <v>3.95</v>
+        <v>2.32</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.4</v>
+        <v>2.46</v>
       </c>
       <c r="BB27" t="n">
-        <v>3.9</v>
+        <v>2.44</v>
       </c>
       <c r="BC27" t="n">
-        <v>18</v>
+        <v>2.42</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.2</v>
+        <v>2.46</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="BF27" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.5</v>
+        <v>2.44</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -5792,31 +5792,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ASD Pineto Calcio</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Forli</t>
+          <t>US Pianese</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.96</v>
+        <v>1.73</v>
       </c>
       <c r="G28" t="n">
-        <v>3.6</v>
+        <v>1.98</v>
       </c>
       <c r="H28" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2.84</v>
+        <v>6.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L28" t="n">
         <v>1.38</v>
@@ -5825,146 +5825,146 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
         <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>1.54</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>1.39</v>
+        <v>2.18</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
         <v>12</v>
       </c>
-      <c r="AC28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>23</v>
-      </c>
       <c r="AG28" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AI28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AK28" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="AL28" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="AO28" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>16.5</v>
+        <v>3.35</v>
       </c>
       <c r="AY28" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>15.5</v>
+        <v>4</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lugano</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sion</t>
+          <t>Young Boys</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="G29" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="H29" t="n">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="I29" t="n">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="M29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.96</v>
+        <v>1.42</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.81</v>
       </c>
       <c r="S29" t="n">
-        <v>3.25</v>
+        <v>2.02</v>
       </c>
       <c r="T29" t="n">
-        <v>1.72</v>
+        <v>1.45</v>
       </c>
       <c r="U29" t="n">
-        <v>2.24</v>
+        <v>2.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC29" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH29" t="n">
         <v>14</v>
       </c>
-      <c r="AG29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM29" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AP29" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="AT29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY29" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AU29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW29" t="n">
+      <c r="AZ29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE29" t="n">
         <v>36</v>
       </c>
-      <c r="AX29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BF29" t="n">
-        <v>11.5</v>
+        <v>6</v>
       </c>
       <c r="BG29" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,179 +6180,179 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Brighton</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leverkusen</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5.7</v>
+        <v>3.55</v>
       </c>
       <c r="G30" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="H30" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="J30" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K30" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="M30" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>2.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="S30" t="n">
-        <v>3.6</v>
+        <v>2.94</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="U30" t="n">
-        <v>1.99</v>
+        <v>2.42</v>
       </c>
       <c r="V30" t="n">
-        <v>2.42</v>
+        <v>1.79</v>
       </c>
       <c r="W30" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="X30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AG30" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AH30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU30" t="n">
         <v>8</v>
       </c>
-      <c r="Z30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI30" t="n">
+      <c r="AV30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD30" t="n">
         <v>36</v>
       </c>
-      <c r="AJ30" t="n">
-        <v>160</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>110</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>38</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>80</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>70</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>65</v>
-      </c>
       <c r="BE30" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="BF30" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="BG30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brighton</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.84</v>
+        <v>5.6</v>
       </c>
       <c r="G31" t="n">
-        <v>2.86</v>
+        <v>5.7</v>
       </c>
       <c r="H31" t="n">
-        <v>2.62</v>
+        <v>1.7</v>
       </c>
       <c r="I31" t="n">
-        <v>2.66</v>
+        <v>1.71</v>
       </c>
       <c r="J31" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K31" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L31" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="P31" t="n">
-        <v>2.28</v>
+        <v>1.96</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>2.52</v>
+        <v>1.99</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="W31" t="n">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="X31" t="n">
-        <v>19.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="Z31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AB31" t="n">
         <v>18</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI31" t="n">
         <v>36</v>
       </c>
-      <c r="AB31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF31" t="n">
+      <c r="AJ31" t="n">
+        <v>160</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY31" t="n">
         <v>20</v>
       </c>
-      <c r="AG31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL31" t="n">
+      <c r="AZ31" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA31" t="n">
         <v>34</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="BB31" t="n">
+        <v>80</v>
+      </c>
+      <c r="BC31" t="n">
         <v>65</v>
       </c>
-      <c r="AN31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>25</v>
-      </c>
       <c r="BD31" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="BE31" t="n">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="BF31" t="n">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="BG31" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -6568,179 +6568,179 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Man City</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.42</v>
+        <v>2.84</v>
       </c>
       <c r="G32" t="n">
-        <v>1.43</v>
+        <v>2.86</v>
       </c>
       <c r="H32" t="n">
-        <v>8.800000000000001</v>
+        <v>2.62</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>2.64</v>
       </c>
       <c r="J32" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
-        <v>5.5</v>
+        <v>3.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="M32" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N32" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="O32" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T32" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="U32" t="n">
-        <v>2.02</v>
+        <v>2.52</v>
       </c>
       <c r="V32" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="W32" t="n">
-        <v>3.3</v>
+        <v>1.53</v>
       </c>
       <c r="X32" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="Y32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AI32" t="n">
         <v>32</v>
       </c>
-      <c r="Z32" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AJ32" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA32" t="n">
         <v>30</v>
       </c>
-      <c r="AE32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL32" t="n">
+      <c r="BB32" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD32" t="n">
         <v>32</v>
       </c>
-      <c r="AM32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AR32" t="n">
+      <c r="BE32" t="n">
         <v>55</v>
       </c>
-      <c r="AS32" t="n">
-        <v>90</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>85</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>42</v>
-      </c>
       <c r="BF32" t="n">
-        <v>5.3</v>
+        <v>19</v>
       </c>
       <c r="BG32" t="n">
-        <v>100</v>
+        <v>16.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -6762,186 +6762,186 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Man City</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>West Ham</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>1.42</v>
       </c>
       <c r="G33" t="n">
-        <v>2.12</v>
+        <v>1.43</v>
       </c>
       <c r="H33" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>3.9</v>
+        <v>9</v>
       </c>
       <c r="J33" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="K33" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="M33" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="R33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S33" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="T33" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="U33" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="V33" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="X33" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="Y33" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Z33" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>85</v>
+      </c>
+      <c r="BB33" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX33" t="n">
+      <c r="BC33" t="n">
         <v>13</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>18.5</v>
       </c>
       <c r="BD33" t="n">
         <v>28</v>
       </c>
       <c r="BE33" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BF33" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG33" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,25 +6956,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Leverkusen</t>
+          <t>West Ham</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="G34" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="H34" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="I34" t="n">
-        <v>2.24</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>3.7</v>
@@ -6983,159 +6983,159 @@
         <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M34" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O34" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P34" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R34" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S34" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T34" t="n">
         <v>1.67</v>
       </c>
       <c r="U34" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="V34" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="W34" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="X34" t="n">
         <v>17</v>
       </c>
       <c r="Y34" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB34" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="AC34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD34" t="n">
         <v>16</v>
       </c>
-      <c r="AC34" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD34" t="n">
+      <c r="AE34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG34" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>14.5</v>
       </c>
       <c r="AH34" t="n">
         <v>15.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AJ34" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AK34" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="AL34" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AM34" t="n">
         <v>70</v>
       </c>
       <c r="AN34" t="n">
-        <v>32</v>
+        <v>12.5</v>
       </c>
       <c r="AO34" t="n">
-        <v>13.5</v>
+        <v>34</v>
       </c>
       <c r="AP34" t="n">
         <v>16</v>
       </c>
       <c r="AQ34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT34" t="n">
         <v>11</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>15</v>
       </c>
       <c r="AU34" t="n">
         <v>8</v>
       </c>
       <c r="AV34" t="n">
-        <v>10</v>
+        <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="AX34" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="AY34" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ34" t="n">
         <v>14.5</v>
       </c>
       <c r="BA34" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD34" t="n">
         <v>28</v>
       </c>
-      <c r="BB34" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>38</v>
-      </c>
       <c r="BE34" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG34" t="n">
         <v>26</v>
       </c>
-      <c r="BG34" t="n">
-        <v>12</v>
-      </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>English National League</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gateshead</t>
+          <t>ASD Pineto Calcio</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Forli</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="G35" t="n">
-        <v>1.98</v>
+        <v>2.92</v>
       </c>
       <c r="H35" t="n">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>3.55</v>
       </c>
       <c r="J35" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L35" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="M35" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N35" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="P35" t="n">
-        <v>2.36</v>
+        <v>1.69</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.53</v>
+        <v>2.18</v>
       </c>
       <c r="R35" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="S35" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AV35" t="n">
         <v>2.3</v>
       </c>
-      <c r="T35" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X35" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AW35" t="n">
-        <v>5.3</v>
+        <v>2.52</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.5</v>
+        <v>2.34</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.2</v>
+        <v>2.24</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.4</v>
+        <v>2.38</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.4</v>
+        <v>2.56</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.8</v>
+        <v>2.52</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>2.56</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.5</v>
+        <v>2.66</v>
       </c>
       <c r="BF35" t="n">
-        <v>7</v>
+        <v>2.48</v>
       </c>
       <c r="BG35" t="n">
-        <v>20</v>
+        <v>2.66</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>English National League</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="F36" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H36" t="n">
         <v>4</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X36" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS36" t="n">
         <v>5.7</v>
       </c>
-      <c r="H36" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AT36" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AU36" t="n">
-        <v>2.98</v>
+        <v>3.7</v>
       </c>
       <c r="AV36" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="AX36" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AZ36" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="BA36" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB36" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC36" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BD36" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BG36" t="n">
-        <v>3.75</v>
+        <v>20</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Scottish Premiership</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7538,186 +7538,186 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="G37" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="H37" t="n">
-        <v>1.51</v>
+        <v>1.97</v>
       </c>
       <c r="I37" t="n">
-        <v>1.54</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
-        <v>4.7</v>
+        <v>2.52</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="M37" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>2.58</v>
       </c>
       <c r="O37" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="P37" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.61</v>
+        <v>2.16</v>
       </c>
       <c r="R37" t="n">
-        <v>1.59</v>
+        <v>1.23</v>
       </c>
       <c r="S37" t="n">
-        <v>2.34</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="U37" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="V37" t="n">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="W37" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>20</v>
+        <v>3.2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>10</v>
+        <v>2.9</v>
       </c>
       <c r="AR37" t="n">
-        <v>9.4</v>
+        <v>3.3</v>
       </c>
       <c r="AS37" t="n">
-        <v>12.5</v>
+        <v>3.85</v>
       </c>
       <c r="AT37" t="n">
-        <v>25</v>
+        <v>3.4</v>
       </c>
       <c r="AU37" t="n">
-        <v>10</v>
+        <v>2.96</v>
       </c>
       <c r="AV37" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="AW37" t="n">
-        <v>13</v>
+        <v>3.85</v>
       </c>
       <c r="AX37" t="n">
-        <v>13.5</v>
+        <v>3.95</v>
       </c>
       <c r="AY37" t="n">
-        <v>22</v>
+        <v>3.7</v>
       </c>
       <c r="AZ37" t="n">
-        <v>17.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA37" t="n">
-        <v>24</v>
+        <v>4.1</v>
       </c>
       <c r="BB37" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC37" t="n">
-        <v>14.5</v>
+        <v>4.1</v>
       </c>
       <c r="BD37" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="BF37" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Scottish Premiership</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,39 +7727,39 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Aberdeen</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Man Utd</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.74</v>
+        <v>6.6</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76</v>
+        <v>7.2</v>
       </c>
       <c r="H38" t="n">
-        <v>2.66</v>
+        <v>1.51</v>
       </c>
       <c r="I38" t="n">
-        <v>2.68</v>
+        <v>1.54</v>
       </c>
       <c r="J38" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="K38" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="L38" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M38" t="n">
         <v>1.04</v>
@@ -7771,147 +7771,147 @@
         <v>1.19</v>
       </c>
       <c r="P38" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R38" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="S38" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T38" t="n">
-        <v>1.52</v>
+        <v>1.72</v>
       </c>
       <c r="U38" t="n">
-        <v>2.82</v>
+        <v>2.2</v>
       </c>
       <c r="V38" t="n">
-        <v>1.59</v>
+        <v>2.84</v>
       </c>
       <c r="W38" t="n">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="X38" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Y38" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Z38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>14</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>65</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH38" t="n">
         <v>21</v>
       </c>
-      <c r="AA38" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB38" t="n">
+      <c r="AI38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>240</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>17.5</v>
       </c>
-      <c r="AC38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>13</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>27</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK38" t="n">
+      <c r="BA38" t="n">
         <v>24</v>
       </c>
-      <c r="AL38" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>48</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>15</v>
-      </c>
-      <c r="AO38" t="n">
+      <c r="BB38" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC38" t="n">
         <v>14.5</v>
       </c>
-      <c r="AP38" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>22</v>
-      </c>
       <c r="BD38" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BE38" t="n">
-        <v>44</v>
+        <v>14.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG38" t="n">
-        <v>13.5</v>
+        <v>5.5</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7921,184 +7921,184 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Barranquilla</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Man Utd</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="G39" t="n">
-        <v>4.8</v>
+        <v>2.78</v>
       </c>
       <c r="H39" t="n">
-        <v>2.06</v>
+        <v>2.64</v>
       </c>
       <c r="I39" t="n">
         <v>2.66</v>
       </c>
       <c r="J39" t="n">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="K39" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L39" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="M39" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N39" t="n">
-        <v>2.58</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="P39" t="n">
-        <v>1.58</v>
+        <v>2.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="R39" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="S39" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="T39" t="n">
-        <v>1.88</v>
+        <v>1.52</v>
       </c>
       <c r="U39" t="n">
-        <v>1.8</v>
+        <v>2.82</v>
       </c>
       <c r="V39" t="n">
         <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="X39" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="Y39" t="n">
-        <v>9.6</v>
+        <v>17</v>
       </c>
       <c r="Z39" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AA39" t="n">
         <v>38</v>
       </c>
       <c r="AB39" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AC39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>48</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU39" t="n">
         <v>9</v>
       </c>
-      <c r="AD39" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF39" t="n">
+      <c r="AV39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB39" t="n">
         <v>34</v>
       </c>
-      <c r="AG39" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH39" t="n">
+      <c r="BC39" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD39" t="n">
         <v>26</v>
       </c>
-      <c r="AI39" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE39" t="n">
-        <v>4.2</v>
+        <v>44</v>
       </c>
       <c r="BF39" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>3.8</v>
+        <v>13</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
@@ -8115,191 +8115,191 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Independiente Yumbo</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>2.04</v>
+        <v>4.5</v>
       </c>
       <c r="H40" t="n">
-        <v>4.7</v>
+        <v>2.16</v>
       </c>
       <c r="I40" t="n">
-        <v>6.8</v>
+        <v>2.8</v>
       </c>
       <c r="J40" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="K40" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L40" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="M40" t="n">
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O40" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P40" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R40" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S40" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.97</v>
+        <v>1.85</v>
       </c>
       <c r="U40" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="V40" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="W40" t="n">
-        <v>1.97</v>
+        <v>1.28</v>
       </c>
       <c r="X40" t="n">
         <v>13</v>
       </c>
       <c r="Y40" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AC40" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD40" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF40" t="n">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="AG40" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AH40" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI40" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ40" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="AK40" t="n">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="AL40" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="AO40" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP40" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AQ40" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB40" t="n">
         <v>4.1</v>
       </c>
-      <c r="AR40" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BC40" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BD40" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BE40" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF40" t="n">
         <v>4.1</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -8309,191 +8309,191 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Independiente Yumbo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.66</v>
+        <v>1.67</v>
       </c>
       <c r="G41" t="n">
-        <v>2.84</v>
+        <v>1.99</v>
       </c>
       <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J41" t="n">
         <v>3.05</v>
       </c>
-      <c r="I41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3</v>
-      </c>
       <c r="K41" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="L41" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="M41" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>2.38</v>
+        <v>2.68</v>
       </c>
       <c r="O41" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.88</v>
+        <v>2.12</v>
       </c>
       <c r="R41" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="S41" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="T41" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="V41" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="W41" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.6</v>
+        <v>18.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AA41" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC41" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="AE41" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH41" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AK41" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="AL41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM41" t="n">
         <v>1000</v>
       </c>
-      <c r="AM41" t="n">
-        <v>290</v>
-      </c>
       <c r="AN41" t="n">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="AO41" t="n">
         <v>1000</v>
       </c>
       <c r="AP41" t="n">
-        <v>6.8</v>
+        <v>3.7</v>
       </c>
       <c r="AQ41" t="n">
-        <v>7.4</v>
+        <v>4</v>
       </c>
       <c r="AR41" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS41" t="n">
-        <v>29</v>
+        <v>5.1</v>
       </c>
       <c r="AT41" t="n">
-        <v>6.6</v>
+        <v>3.1</v>
       </c>
       <c r="AU41" t="n">
-        <v>6.4</v>
+        <v>3.35</v>
       </c>
       <c r="AV41" t="n">
-        <v>13.5</v>
+        <v>4.4</v>
       </c>
       <c r="AW41" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="AX41" t="n">
-        <v>13.5</v>
+        <v>3.6</v>
       </c>
       <c r="AY41" t="n">
-        <v>12</v>
+        <v>3.65</v>
       </c>
       <c r="AZ41" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="BA41" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="BB41" t="n">
-        <v>25</v>
+        <v>4.2</v>
       </c>
       <c r="BC41" t="n">
-        <v>25</v>
+        <v>4.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>55</v>
+        <v>4.8</v>
       </c>
       <c r="BE41" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF41" t="n">
-        <v>40</v>
+        <v>4.1</v>
       </c>
       <c r="BG41" t="n">
-        <v>46</v>
+        <v>5.1</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -8503,191 +8503,191 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Monterrey</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Queretaro</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="F42" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V42" t="n">
         <v>1.44</v>
       </c>
-      <c r="G42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I42" t="n">
-        <v>9</v>
-      </c>
-      <c r="J42" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N42" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W42" t="n">
-        <v>2.88</v>
+        <v>1.56</v>
       </c>
       <c r="X42" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="Y42" t="n">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="n">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="AB42" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH42" t="n">
         <v>32</v>
       </c>
-      <c r="AE42" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>250</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE42" t="n">
         <v>11</v>
       </c>
-      <c r="AH42" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>170</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>8</v>
-      </c>
       <c r="BF42" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="BG42" t="n">
-        <v>7.8</v>
+        <v>32</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -8702,186 +8702,186 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fortaleza FC</t>
+          <t>Monterrey</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Queretaro</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="G43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q43" t="n">
         <v>1.74</v>
       </c>
-      <c r="H43" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="I43" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K43" t="n">
-        <v>4</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N43" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="O43" t="n">
+      <c r="R43" t="n">
         <v>1.44</v>
       </c>
-      <c r="P43" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.22</v>
-      </c>
       <c r="S43" t="n">
-        <v>4.5</v>
+        <v>2.76</v>
       </c>
       <c r="T43" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="U43" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="V43" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W43" t="n">
-        <v>2.34</v>
+        <v>3</v>
       </c>
       <c r="X43" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="Z43" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA43" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AB43" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AD43" t="n">
         <v>30</v>
       </c>
       <c r="AE43" t="n">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AF43" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG43" t="n">
         <v>11</v>
       </c>
       <c r="AH43" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI43" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AJ43" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="AK43" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AL43" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM43" t="n">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="AN43" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="AO43" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="AP43" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AQ43" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW43" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS43" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AV43" t="n">
+      <c r="AX43" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW43" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AY43" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ43" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD43" t="n">
         <v>7.6</v>
       </c>
-      <c r="BA43" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BB43" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC43" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD43" t="n">
+      <c r="BE43" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG43" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BE43" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 09:27:42</t>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mexican Liga MX</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -8896,179 +8896,373 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Puebla</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tigres</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>4.6</v>
+        <v>1.66</v>
       </c>
       <c r="G44" t="n">
-        <v>5.3</v>
+        <v>1.73</v>
       </c>
       <c r="H44" t="n">
-        <v>1.81</v>
+        <v>6.2</v>
       </c>
       <c r="I44" t="n">
-        <v>1.94</v>
+        <v>7.4</v>
       </c>
       <c r="J44" t="n">
         <v>3.65</v>
       </c>
       <c r="K44" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L44" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="M44" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="P44" t="n">
-        <v>1.93</v>
+        <v>1.66</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="R44" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="S44" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="T44" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="U44" t="n">
-        <v>2.04</v>
+        <v>1.7</v>
       </c>
       <c r="V44" t="n">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="W44" t="n">
-        <v>1.23</v>
+        <v>2.38</v>
       </c>
       <c r="X44" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>280</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN44" t="n">
         <v>15.5</v>
       </c>
-      <c r="Y44" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>75</v>
-      </c>
       <c r="AO44" t="n">
-        <v>13</v>
+        <v>270</v>
       </c>
       <c r="AP44" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="AQ44" t="n">
-        <v>7.8</v>
+        <v>14.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AS44" t="n">
-        <v>18</v>
+        <v>8.6</v>
       </c>
       <c r="AT44" t="n">
-        <v>14.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU44" t="n">
         <v>7.6</v>
       </c>
       <c r="AV44" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AW44" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="AX44" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY44" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ44" t="n">
-        <v>17</v>
+        <v>6.8</v>
       </c>
       <c r="BA44" t="n">
         <v>8.4</v>
       </c>
       <c r="BB44" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:39:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Tigres</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G45" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K45" t="n">
+        <v>4</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N45" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X45" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR45" t="n">
         <v>10</v>
       </c>
-      <c r="BC44" t="n">
+      <c r="AS45" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG45" t="n">
         <v>9.4</v>
       </c>
-      <c r="BD44" t="n">
-        <v>55</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BG44" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BH44" t="inlineStr">
-        <is>
-          <t>2026-03-03 09:27:42</t>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-03-03 11:39:37</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
@@ -781,37 +781,37 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y2" t="n">
         <v>20</v>
@@ -820,73 +820,73 @@
         <v>44</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB2" t="n">
         <v>9</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
         <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK2" t="n">
         <v>18</v>
       </c>
-      <c r="AK2" t="n">
-        <v>19</v>
-      </c>
       <c r="AL2" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU2" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AV2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -895,32 +895,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="BF2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>9.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -957,88 +957,88 @@
         <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="I3" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="V3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="W3" t="n">
         <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="Y3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ3" t="n">
         <v>90</v>
@@ -1050,71 +1050,71 @@
         <v>55</v>
       </c>
       <c r="AM3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN3" t="n">
         <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>30</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE3" t="n">
         <v>14.5</v>
       </c>
-      <c r="AU3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BG3" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G4" t="n">
         <v>1.73</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.74</v>
-      </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
         <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.3</v>
@@ -1169,46 +1169,46 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S4" t="n">
         <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
         <v>44</v>
       </c>
       <c r="AA4" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB4" t="n">
         <v>12</v>
@@ -1247,7 +1247,7 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO4" t="n">
         <v>50</v>
@@ -1256,10 +1256,10 @@
         <v>20</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
         <v>16</v>
@@ -1268,16 +1268,16 @@
         <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
         <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
@@ -1289,26 +1289,26 @@
         <v>46</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
         <v>14.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BF4" t="n">
         <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="H5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="J5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>1.16</v>
@@ -1369,10 +1369,10 @@
         <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
         <v>2.04</v>
@@ -1381,25 +1381,25 @@
         <v>1.74</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U5" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V5" t="n">
         <v>1.07</v>
       </c>
       <c r="W5" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="X5" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="Y5" t="n">
-        <v>70</v>
+        <v>950</v>
       </c>
       <c r="Z5" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1414,7 +1414,7 @@
         <v>980</v>
       </c>
       <c r="AE5" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
         <v>980</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AJ5" t="n">
         <v>980</v>
@@ -1438,22 +1438,22 @@
         <v>980</v>
       </c>
       <c r="AM5" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AO5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5.1</v>
+        <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS5" t="n">
         <v>5.5</v>
@@ -1462,28 +1462,28 @@
         <v>4.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AY5" t="n">
         <v>4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>3.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC5" t="n">
         <v>4.1</v>
@@ -1492,17 +1492,17 @@
         <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1533,34 +1533,34 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
       </c>
       <c r="N6" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="O6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P6" t="n">
         <v>1.53</v>
@@ -1581,13 +1581,13 @@
         <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
         <v>10.5</v>
@@ -1611,7 +1611,7 @@
         <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG6" t="n">
         <v>980</v>
@@ -1647,10 +1647,10 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,10 +1659,10 @@
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.9</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX6" t="n">
         <v>10.5</v>
@@ -1671,32 +1671,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB6" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6</v>
-      </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
         <v>22</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1739,19 +1739,19 @@
         <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
         <v>1.3</v>
@@ -1760,10 +1760,10 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
         <v>3.3</v>
@@ -1772,7 +1772,7 @@
         <v>2.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
         <v>1.1</v>
@@ -1781,46 +1781,46 @@
         <v>3.2</v>
       </c>
       <c r="X7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y7" t="n">
         <v>29</v>
       </c>
       <c r="Z7" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA7" t="n">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AB7" t="n">
         <v>7.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
         <v>38</v>
       </c>
       <c r="AE7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AF7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH7" t="n">
         <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>46</v>
@@ -1829,68 +1829,68 @@
         <v>220</v>
       </c>
       <c r="AN7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AW7" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY7" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>10.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J8" t="n">
         <v>5.3</v>
@@ -1939,76 +1939,76 @@
         <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="Q8" t="n">
         <v>1.94</v>
       </c>
       <c r="R8" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="U8" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="V8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W8" t="n">
         <v>3.9</v>
       </c>
       <c r="X8" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Z8" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC8" t="n">
         <v>15.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AE8" t="n">
-        <v>380</v>
+        <v>490</v>
       </c>
       <c r="AF8" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AG8" t="n">
         <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AI8" t="n">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="AJ8" t="n">
         <v>11.5</v>
@@ -2017,74 +2017,74 @@
         <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM8" t="n">
-        <v>350</v>
+        <v>420</v>
       </c>
       <c r="AN8" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AU8" t="n">
         <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -2106,109 +2106,109 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Pesaro</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AC Bra</t>
+          <t>Carpi</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="G9" t="n">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="J9" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.25</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="V9" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="W9" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR9" t="n">
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="AU9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW9" t="n">
         <v>6.8</v>
       </c>
-      <c r="AV9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW9" t="n">
+      <c r="AX9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>5.8</v>
       </c>
-      <c r="AX9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>15</v>
-      </c>
       <c r="BA9" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
-        <v>20</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>18.5</v>
+        <v>6.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>13.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Carpi</t>
+          <t>Juventus B</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.38</v>
       </c>
-      <c r="H10" t="n">
-        <v>3.9</v>
-      </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>2.64</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.54</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="U10" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.58</v>
       </c>
       <c r="W10" t="n">
-        <v>1.72</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB10" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU10" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="AY10" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.7</v>
+        <v>4.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pesaro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Juventus B</t>
+          <t>AC Bra</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>2.38</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>2.7</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T11" t="n">
         <v>1.83</v>
       </c>
       <c r="U11" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="X11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="AG11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>25</v>
       </c>
-      <c r="AG11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>70</v>
-      </c>
       <c r="AK11" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>50</v>
+        <v>19.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.4</v>
+        <v>13</v>
       </c>
       <c r="AR11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF11" t="n">
         <v>12</v>
       </c>
-      <c r="AS11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BG11" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -2697,37 +2697,37 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H12" t="n">
         <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.8</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.85</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q12" t="n">
         <v>2.26</v>
@@ -2745,10 +2745,10 @@
         <v>1.84</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X12" t="n">
         <v>11.5</v>
@@ -2766,7 +2766,7 @@
         <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>23</v>
@@ -2784,10 +2784,10 @@
         <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
@@ -2796,7 +2796,7 @@
         <v>46</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN12" t="n">
         <v>14</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
         <v>3.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
         <v>1.79</v>
@@ -2936,22 +2936,22 @@
         <v>1.84</v>
       </c>
       <c r="U13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V13" t="n">
         <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
         <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z13" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AA13" t="n">
         <v>60</v>
@@ -2960,55 +2960,55 @@
         <v>10</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD13" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AF13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH13" t="n">
         <v>19.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AM13" t="n">
         <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3020,41 +3020,41 @@
         <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY13" t="n">
         <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="BG13" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="G14" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="I14" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="J14" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P14" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG14" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AH14" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AJ14" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AL14" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AM14" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AN14" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AO14" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AP14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ14" t="n">
         <v>6.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX14" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AZ14" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
         <v>1.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="Q15" t="n">
         <v>1.68</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
         <v>25</v>
@@ -3345,13 +3345,13 @@
         <v>220</v>
       </c>
       <c r="AB15" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC15" t="n">
         <v>13</v>
       </c>
       <c r="AD15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
         <v>110</v>
@@ -3381,16 +3381,16 @@
         <v>130</v>
       </c>
       <c r="AN15" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO15" t="n">
         <v>120</v>
       </c>
       <c r="AP15" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR15" t="n">
         <v>4</v>
@@ -3399,25 +3399,25 @@
         <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU15" t="n">
         <v>7.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW15" t="n">
         <v>4.1</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY15" t="n">
         <v>7.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
         <v>4</v>
@@ -3435,14 +3435,14 @@
         <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG15" t="n">
         <v>4.1</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G16" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H16" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J16" t="n">
         <v>3.65</v>
@@ -3497,7 +3497,7 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O16" t="n">
         <v>1.24</v>
@@ -3506,82 +3506,82 @@
         <v>2.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X16" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="Z16" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AA16" t="n">
         <v>70</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD16" t="n">
         <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="AI16" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AJ16" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AK16" t="n">
         <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN16" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AO16" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AP16" t="n">
-        <v>15.5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ16" t="n">
         <v>13.5</v>
@@ -3590,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -3599,16 +3599,16 @@
         <v>7.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>30</v>
+        <v>6.8</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
         <v>12.5</v>
@@ -3617,26 +3617,26 @@
         <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>6.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.9</v>
+        <v>55</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>4.5</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
         <v>1.66</v>
       </c>
       <c r="I17" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K17" t="n">
         <v>4.9</v>
@@ -3691,40 +3691,40 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="R17" t="n">
         <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T17" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="V17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X17" t="n">
         <v>32</v>
       </c>
       <c r="Y17" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z17" t="n">
         <v>16</v>
@@ -3763,7 +3763,7 @@
         <v>65</v>
       </c>
       <c r="AL17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
         <v>85</v>
@@ -3784,37 +3784,37 @@
         <v>9.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>15.5</v>
+        <v>3.6</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
         <v>9</v>
       </c>
       <c r="AW17" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AX17" t="n">
         <v>3.9</v>
       </c>
       <c r="AY17" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
         <v>12.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.75</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
         <v>4.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
         <v>3.95</v>
@@ -3823,14 +3823,14 @@
         <v>4</v>
       </c>
       <c r="BF17" t="n">
-        <v>30</v>
+        <v>3.95</v>
       </c>
       <c r="BG17" t="n">
         <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G18" t="n">
         <v>1.99</v>
       </c>
       <c r="H18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J18" t="n">
         <v>3.95</v>
@@ -3888,19 +3888,19 @@
         <v>5.2</v>
       </c>
       <c r="O18" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S18" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
         <v>1.59</v>
@@ -3909,7 +3909,7 @@
         <v>2.46</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
         <v>2</v>
@@ -3969,13 +3969,13 @@
         <v>38</v>
       </c>
       <c r="AP18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.5</v>
+        <v>25</v>
       </c>
       <c r="AS18" t="n">
         <v>4.9</v>
@@ -3984,7 +3984,7 @@
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV18" t="n">
         <v>13</v>
@@ -3996,7 +3996,7 @@
         <v>11</v>
       </c>
       <c r="AY18" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ18" t="n">
         <v>12.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H19" t="n">
         <v>2.64</v>
       </c>
       <c r="I19" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="J19" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M19" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P19" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
         <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="X19" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AA19" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AB19" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AF19" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AG19" t="n">
         <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AI19" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AJ19" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AK19" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN19" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AO19" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AP19" t="n">
         <v>4.2</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>3.95</v>
       </c>
       <c r="AR19" t="n">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT19" t="n">
-        <v>10.5</v>
+        <v>3.95</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV19" t="n">
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="AZ19" t="n">
         <v>12</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G20" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H20" t="n">
         <v>6.6</v>
       </c>
       <c r="I20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J20" t="n">
         <v>4.2</v>
@@ -4267,7 +4267,7 @@
         <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -4291,7 +4291,7 @@
         <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U20" t="n">
         <v>1.98</v>
@@ -4300,16 +4300,16 @@
         <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y20" t="n">
         <v>26</v>
       </c>
       <c r="Z20" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA20" t="n">
         <v>220</v>
@@ -4336,7 +4336,7 @@
         <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ20" t="n">
         <v>17.5</v>
@@ -4345,7 +4345,7 @@
         <v>19.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AM20" t="n">
         <v>140</v>
@@ -4357,13 +4357,13 @@
         <v>130</v>
       </c>
       <c r="AP20" t="n">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS20" t="n">
         <v>7.4</v>
@@ -4375,7 +4375,7 @@
         <v>8.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="AW20" t="n">
         <v>7.2</v>
@@ -4387,13 +4387,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BA20" t="n">
         <v>7</v>
       </c>
       <c r="BB20" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC20" t="n">
         <v>5.5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G21" t="n">
         <v>3.4</v>
@@ -4455,25 +4455,25 @@
         <v>2.58</v>
       </c>
       <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.35</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
         <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q21" t="n">
         <v>2.18</v>
@@ -4482,19 +4482,19 @@
         <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
         <v>1.63</v>
       </c>
       <c r="W21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X21" t="n">
         <v>11.5</v>
@@ -4503,7 +4503,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Z21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
         <v>38</v>
@@ -4539,7 +4539,7 @@
         <v>42</v>
       </c>
       <c r="AL21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
         <v>120</v>
@@ -4581,22 +4581,22 @@
         <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
         <v>34</v>
       </c>
       <c r="BD21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF21" t="n">
         <v>34</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -4649,16 +4649,16 @@
         <v>5.8</v>
       </c>
       <c r="J22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
         <v>6.2</v>
@@ -4667,7 +4667,7 @@
         <v>1.16</v>
       </c>
       <c r="P22" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q22" t="n">
         <v>1.5</v>
@@ -4676,13 +4676,13 @@
         <v>1.73</v>
       </c>
       <c r="S22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T22" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
@@ -4691,7 +4691,7 @@
         <v>2.52</v>
       </c>
       <c r="X22" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="Y22" t="n">
         <v>32</v>
@@ -4733,19 +4733,19 @@
         <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AM22" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN22" t="n">
         <v>5.9</v>
       </c>
       <c r="AO22" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AP22" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>8</v>
@@ -4781,7 +4781,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BB22" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC22" t="n">
         <v>12.5</v>
@@ -4793,14 +4793,14 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BG22" t="n">
         <v>36</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G23" t="n">
         <v>2.66</v>
@@ -4840,13 +4840,13 @@
         <v>3.4</v>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="L23" t="n">
         <v>1.5</v>
@@ -4861,10 +4861,10 @@
         <v>1.54</v>
       </c>
       <c r="P23" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R23" t="n">
         <v>1.2</v>
@@ -4876,10 +4876,10 @@
         <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W23" t="n">
         <v>1.6</v>
@@ -4888,7 +4888,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z23" t="n">
         <v>24</v>
@@ -4900,7 +4900,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
         <v>16.5</v>
@@ -4930,7 +4930,7 @@
         <v>65</v>
       </c>
       <c r="AM23" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN23" t="n">
         <v>42</v>
@@ -4939,7 +4939,7 @@
         <v>80</v>
       </c>
       <c r="AP23" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ23" t="n">
         <v>8.800000000000001</v>
@@ -4948,7 +4948,7 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AT23" t="n">
         <v>7</v>
@@ -4960,7 +4960,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX23" t="n">
         <v>12.5</v>
@@ -4972,29 +4972,29 @@
         <v>19.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB23" t="n">
         <v>32</v>
       </c>
       <c r="BC23" t="n">
-        <v>8.6</v>
+        <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE23" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF23" t="n">
         <v>30</v>
       </c>
       <c r="BG23" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -5031,10 +5031,10 @@
         <v>3.55</v>
       </c>
       <c r="H24" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="I24" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J24" t="n">
         <v>3.85</v>
@@ -5043,7 +5043,7 @@
         <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
         <v>1.04</v>
@@ -5055,28 +5055,28 @@
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q24" t="n">
         <v>1.65</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T24" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="U24" t="n">
         <v>2.52</v>
       </c>
       <c r="V24" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W24" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
         <v>27</v>
@@ -5094,7 +5094,7 @@
         <v>21</v>
       </c>
       <c r="AC24" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD24" t="n">
         <v>12</v>
@@ -5133,7 +5133,7 @@
         <v>13</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
         <v>11</v>
@@ -5142,7 +5142,7 @@
         <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT24" t="n">
         <v>14.5</v>
@@ -5157,7 +5157,7 @@
         <v>18</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AY24" t="n">
         <v>12.5</v>
@@ -5166,29 +5166,29 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD24" t="n">
         <v>5.3</v>
       </c>
-      <c r="BC24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD24" t="n">
+      <c r="BE24" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF24" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.8</v>
       </c>
       <c r="BG24" t="n">
         <v>10</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G25" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="H25" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="I25" t="n">
         <v>3.9</v>
@@ -5234,49 +5234,49 @@
         <v>3.55</v>
       </c>
       <c r="K25" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L25" t="n">
         <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="U25" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="V25" t="n">
         <v>1.34</v>
       </c>
       <c r="W25" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
         <v>1000</v>
@@ -5285,10 +5285,10 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD25" t="n">
         <v>1000</v>
@@ -5297,10 +5297,10 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH25" t="n">
         <v>1000</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AS25" t="n">
         <v>11</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AX25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>7.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>9.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF25" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
         <v>10</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H26" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I26" t="n">
         <v>3.05</v>
@@ -5449,25 +5449,25 @@
         <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="S26" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T26" t="n">
         <v>1.45</v>
       </c>
       <c r="U26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X26" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="Y26" t="n">
         <v>36</v>
@@ -5476,7 +5476,7 @@
         <v>28</v>
       </c>
       <c r="AA26" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AB26" t="n">
         <v>32</v>
@@ -5497,13 +5497,13 @@
         <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AJ26" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AK26" t="n">
         <v>21</v>
@@ -5515,28 +5515,28 @@
         <v>60</v>
       </c>
       <c r="AN26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO26" t="n">
         <v>13.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR26" t="n">
         <v>24</v>
       </c>
       <c r="AS26" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV26" t="n">
         <v>12.5</v>
@@ -5545,19 +5545,19 @@
         <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY26" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BB26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC26" t="n">
         <v>18.5</v>
@@ -5569,14 +5569,14 @@
         <v>36</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -5607,88 +5607,88 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U27" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="V27" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>2.26</v>
       </c>
       <c r="X27" t="n">
         <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="Z27" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
         <v>9</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE27" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH27" t="n">
         <v>29</v>
@@ -5697,80 +5697,80 @@
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK27" t="n">
         <v>26</v>
       </c>
-      <c r="AK27" t="n">
-        <v>29</v>
-      </c>
       <c r="AL27" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>16.5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>21</v>
+        <v>5.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BB27" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G28" t="n">
         <v>2.72</v>
@@ -5813,13 +5813,13 @@
         <v>3.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
@@ -5840,16 +5840,16 @@
         <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
         <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="V28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W28" t="n">
         <v>1.58</v>
@@ -5864,7 +5864,7 @@
         <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
         <v>11</v>
@@ -5909,62 +5909,62 @@
         <v>48</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY28" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF28" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG28" t="n">
         <v>4.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -5995,40 +5995,40 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="G29" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="H29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I29" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
         <v>1.39</v>
       </c>
       <c r="P29" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R29" t="n">
         <v>1.28</v>
@@ -6043,10 +6043,10 @@
         <v>1.83</v>
       </c>
       <c r="V29" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
@@ -6073,7 +6073,7 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG29" t="n">
         <v>12.5</v>
@@ -6088,7 +6088,7 @@
         <v>25</v>
       </c>
       <c r="AK29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL29" t="n">
         <v>55</v>
@@ -6109,56 +6109,56 @@
         <v>14</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT29" t="n">
         <v>6.4</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="AY29" t="n">
         <v>9</v>
       </c>
       <c r="AZ29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB29" t="n">
         <v>4</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>3.95</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G30" t="n">
         <v>2.16</v>
       </c>
-      <c r="G30" t="n">
-        <v>2.18</v>
-      </c>
       <c r="H30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I30" t="n">
         <v>3.7</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>3.75</v>
       </c>
-      <c r="J30" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
@@ -6219,31 +6219,31 @@
         <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
         <v>1.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S30" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T30" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U30" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y30" t="n">
         <v>17</v>
@@ -6252,7 +6252,7 @@
         <v>28</v>
       </c>
       <c r="AA30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB30" t="n">
         <v>12</v>
@@ -6264,7 +6264,7 @@
         <v>16</v>
       </c>
       <c r="AE30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF30" t="n">
         <v>14.5</v>
@@ -6279,10 +6279,10 @@
         <v>42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="n">
         <v>30</v>
@@ -6297,10 +6297,10 @@
         <v>34</v>
       </c>
       <c r="AP30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>16</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>16.5</v>
       </c>
       <c r="AR30" t="n">
         <v>26</v>
@@ -6318,41 +6318,41 @@
         <v>14.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA30" t="n">
         <v>38</v>
       </c>
       <c r="BB30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
         <v>28</v>
       </c>
       <c r="BE30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF30" t="n">
         <v>11.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -6383,28 +6383,28 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G31" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J31" t="n">
         <v>3.05</v>
       </c>
-      <c r="I31" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J31" t="n">
-        <v>3</v>
-      </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
         <v>3</v>
@@ -6413,79 +6413,79 @@
         <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R31" t="n">
         <v>1.26</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="U31" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V31" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="X31" t="n">
         <v>13</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
         <v>23</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC31" t="n">
         <v>7.6</v>
       </c>
       <c r="AD31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE31" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>17</v>
-      </c>
       <c r="AG31" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
         <v>60</v>
       </c>
       <c r="AJ31" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO31" t="n">
         <v>50</v>
@@ -6500,10 +6500,10 @@
         <v>18.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU31" t="n">
         <v>6.2</v>
@@ -6512,7 +6512,7 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AX31" t="n">
         <v>13.5</v>
@@ -6524,29 +6524,29 @@
         <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.4</v>
+        <v>36</v>
       </c>
       <c r="BE31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF31" t="n">
         <v>7</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>5.9</v>
       </c>
       <c r="BG31" t="n">
         <v>34</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -6577,64 +6577,64 @@
         </is>
       </c>
       <c r="F32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G32" t="n">
         <v>3.5</v>
       </c>
-      <c r="G32" t="n">
-        <v>3.55</v>
-      </c>
       <c r="H32" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I32" t="n">
         <v>2.26</v>
       </c>
-      <c r="I32" t="n">
-        <v>2.28</v>
-      </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
       </c>
       <c r="N32" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O32" t="n">
         <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="S32" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T32" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="U32" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z32" t="n">
         <v>15</v>
@@ -6643,7 +6643,7 @@
         <v>28</v>
       </c>
       <c r="AB32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC32" t="n">
         <v>8.199999999999999</v>
@@ -6652,7 +6652,7 @@
         <v>11</v>
       </c>
       <c r="AE32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF32" t="n">
         <v>26</v>
@@ -6661,7 +6661,7 @@
         <v>14.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI32" t="n">
         <v>32</v>
@@ -6676,13 +6676,13 @@
         <v>42</v>
       </c>
       <c r="AM32" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN32" t="n">
         <v>32</v>
       </c>
       <c r="AO32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AP32" t="n">
         <v>15.5</v>
@@ -6691,16 +6691,16 @@
         <v>11</v>
       </c>
       <c r="AR32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU32" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV32" t="n">
         <v>10</v>
@@ -6709,19 +6709,19 @@
         <v>19</v>
       </c>
       <c r="AX32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY32" t="n">
         <v>13</v>
       </c>
       <c r="AZ32" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA32" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BC32" t="n">
         <v>32</v>
@@ -6730,17 +6730,17 @@
         <v>38</v>
       </c>
       <c r="BE32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -6777,10 +6777,10 @@
         <v>5.7</v>
       </c>
       <c r="H33" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I33" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J33" t="n">
         <v>4.2</v>
@@ -6801,16 +6801,16 @@
         <v>1.33</v>
       </c>
       <c r="P33" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
         <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
         <v>1.98</v>
@@ -6825,19 +6825,19 @@
         <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA33" t="n">
         <v>16.5</v>
       </c>
       <c r="AB33" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC33" t="n">
         <v>9</v>
@@ -6846,16 +6846,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE33" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF33" t="n">
         <v>42</v>
       </c>
       <c r="AG33" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI33" t="n">
         <v>36</v>
@@ -6867,13 +6867,13 @@
         <v>80</v>
       </c>
       <c r="AL33" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM33" t="n">
         <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO33" t="n">
         <v>11</v>
@@ -6888,7 +6888,7 @@
         <v>9</v>
       </c>
       <c r="AS33" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AT33" t="n">
         <v>17</v>
@@ -6900,7 +6900,7 @@
         <v>9.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AX33" t="n">
         <v>38</v>
@@ -6909,13 +6909,13 @@
         <v>20</v>
       </c>
       <c r="AZ33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA33" t="n">
         <v>34</v>
       </c>
       <c r="BB33" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="BC33" t="n">
         <v>65</v>
@@ -6924,7 +6924,7 @@
         <v>65</v>
       </c>
       <c r="BE33" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="BF33" t="n">
         <v>90</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -6965,61 +6965,61 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G34" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="H34" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="I34" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J34" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K34" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M34" t="n">
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O34" t="n">
         <v>1.24</v>
       </c>
       <c r="P34" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R34" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S34" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T34" t="n">
         <v>1.62</v>
       </c>
       <c r="U34" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V34" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W34" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="X34" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="n">
         <v>13.5</v>
@@ -7028,13 +7028,13 @@
         <v>18</v>
       </c>
       <c r="AA34" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AB34" t="n">
         <v>14.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD34" t="n">
         <v>11.5</v>
@@ -7043,7 +7043,7 @@
         <v>25</v>
       </c>
       <c r="AF34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG34" t="n">
         <v>12.5</v>
@@ -7055,10 +7055,10 @@
         <v>32</v>
       </c>
       <c r="AJ34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK34" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL34" t="n">
         <v>34</v>
@@ -7070,7 +7070,7 @@
         <v>21</v>
       </c>
       <c r="AO34" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP34" t="n">
         <v>17.5</v>
@@ -7079,7 +7079,7 @@
         <v>13</v>
       </c>
       <c r="AR34" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS34" t="n">
         <v>34</v>
@@ -7097,7 +7097,7 @@
         <v>23</v>
       </c>
       <c r="AX34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY34" t="n">
         <v>12</v>
@@ -7112,7 +7112,7 @@
         <v>40</v>
       </c>
       <c r="BC34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD34" t="n">
         <v>32</v>
@@ -7121,14 +7121,14 @@
         <v>55</v>
       </c>
       <c r="BF34" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG34" t="n">
         <v>16.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>1.43</v>
       </c>
       <c r="H35" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
         <v>5.4</v>
@@ -7186,22 +7186,22 @@
         <v>5.3</v>
       </c>
       <c r="O35" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P35" t="n">
         <v>2.46</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R35" t="n">
         <v>1.57</v>
       </c>
       <c r="S35" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U35" t="n">
         <v>2.02</v>
@@ -7219,13 +7219,13 @@
         <v>32</v>
       </c>
       <c r="Z35" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA35" t="n">
-        <v>990</v>
+        <v>250</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC35" t="n">
         <v>12</v>
@@ -7261,10 +7261,10 @@
         <v>120</v>
       </c>
       <c r="AN35" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AO35" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP35" t="n">
         <v>22</v>
@@ -7276,7 +7276,7 @@
         <v>65</v>
       </c>
       <c r="AS35" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AT35" t="n">
         <v>9.199999999999999</v>
@@ -7285,10 +7285,10 @@
         <v>11</v>
       </c>
       <c r="AV35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW35" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX35" t="n">
         <v>8.6</v>
@@ -7300,10 +7300,10 @@
         <v>22</v>
       </c>
       <c r="BA35" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BB35" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC35" t="n">
         <v>13</v>
@@ -7312,17 +7312,17 @@
         <v>28</v>
       </c>
       <c r="BE35" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="BF35" t="n">
         <v>5.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -7356,7 +7356,7 @@
         <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H36" t="n">
         <v>3.25</v>
@@ -7365,7 +7365,7 @@
         <v>990</v>
       </c>
       <c r="J36" t="n">
-        <v>2.84</v>
+        <v>1.62</v>
       </c>
       <c r="K36" t="n">
         <v>500</v>
@@ -7377,22 +7377,22 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P36" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="R36" t="n">
         <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.99</v>
+        <v>1.46</v>
       </c>
       <c r="T36" t="n">
         <v>1.05</v>
@@ -7404,7 +7404,7 @@
         <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -7577,7 +7577,7 @@
         <v>1.19</v>
       </c>
       <c r="P37" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q37" t="n">
         <v>1.53</v>
@@ -7595,94 +7595,94 @@
         <v>2.26</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W37" t="n">
         <v>2.02</v>
       </c>
       <c r="X37" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="Y37" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="Z37" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AA37" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB37" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AC37" t="n">
         <v>9.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE37" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AF37" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AG37" t="n">
         <v>14.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AI37" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AJ37" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AK37" t="n">
-        <v>21</v>
+        <v>980</v>
       </c>
       <c r="AL37" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AM37" t="n">
         <v>60</v>
       </c>
       <c r="AN37" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AO37" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AQ37" t="n">
         <v>4.8</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="AS37" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT37" t="n">
         <v>4.3</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AV37" t="n">
         <v>4.6</v>
       </c>
       <c r="AW37" t="n">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ37" t="n">
         <v>4.4</v>
@@ -7691,26 +7691,26 @@
         <v>5.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC37" t="n">
         <v>4.7</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF37" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="G38" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H38" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="I38" t="n">
         <v>2.2</v>
@@ -7756,43 +7756,43 @@
         <v>2.84</v>
       </c>
       <c r="K38" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L38" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N38" t="n">
-        <v>2.52</v>
+        <v>2.28</v>
       </c>
       <c r="O38" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="P38" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="T38" t="n">
-        <v>1.86</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V38" t="n">
         <v>1.84</v>
       </c>
       <c r="W38" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>3.2</v>
+        <v>1.49</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="AR38" t="n">
-        <v>3.3</v>
+        <v>1.97</v>
       </c>
       <c r="AS38" t="n">
-        <v>3.85</v>
+        <v>1.44</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.4</v>
+        <v>1.77</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.96</v>
+        <v>2.28</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.85</v>
+        <v>1.27</v>
       </c>
       <c r="AX38" t="n">
-        <v>3.95</v>
+        <v>1.29</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.7</v>
+        <v>1.27</v>
       </c>
       <c r="AZ38" t="n">
-        <v>3.75</v>
+        <v>1.28</v>
       </c>
       <c r="BA38" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="BB38" t="n">
-        <v>4.2</v>
+        <v>1.32</v>
       </c>
       <c r="BC38" t="n">
-        <v>4.1</v>
+        <v>1.31</v>
       </c>
       <c r="BD38" t="n">
-        <v>4.2</v>
+        <v>1.31</v>
       </c>
       <c r="BE38" t="n">
-        <v>4.2</v>
+        <v>1.32</v>
       </c>
       <c r="BF38" t="n">
-        <v>4.2</v>
+        <v>1.32</v>
       </c>
       <c r="BG38" t="n">
-        <v>3.75</v>
+        <v>1.32</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="G39" t="n">
         <v>7.8</v>
@@ -7944,16 +7944,16 @@
         <v>1.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J39" t="n">
         <v>4.8</v>
       </c>
       <c r="K39" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L39" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M39" t="n">
         <v>1.04</v>
@@ -7965,31 +7965,31 @@
         <v>1.19</v>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R39" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S39" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="T39" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U39" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V39" t="n">
         <v>2.92</v>
       </c>
       <c r="W39" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Y39" t="n">
         <v>11.5</v>
@@ -8007,10 +8007,10 @@
         <v>11.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF39" t="n">
         <v>65</v>
@@ -8028,16 +8028,16 @@
         <v>240</v>
       </c>
       <c r="AK39" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL39" t="n">
         <v>80</v>
       </c>
       <c r="AM39" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN39" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO39" t="n">
         <v>6</v>
@@ -8049,7 +8049,7 @@
         <v>10</v>
       </c>
       <c r="AR39" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS39" t="n">
         <v>12.5</v>
@@ -8061,13 +8061,13 @@
         <v>10</v>
       </c>
       <c r="AV39" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX39" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY39" t="n">
         <v>22</v>
@@ -8079,26 +8079,26 @@
         <v>24</v>
       </c>
       <c r="BB39" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BD39" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BF39" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BG39" t="n">
         <v>5.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -8135,16 +8135,16 @@
         <v>2.8</v>
       </c>
       <c r="H40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I40" t="n">
         <v>2.62</v>
       </c>
-      <c r="I40" t="n">
-        <v>2.64</v>
-      </c>
       <c r="J40" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K40" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L40" t="n">
         <v>1.29</v>
@@ -8168,22 +8168,22 @@
         <v>1.67</v>
       </c>
       <c r="S40" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T40" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U40" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="V40" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W40" t="n">
         <v>1.55</v>
       </c>
       <c r="X40" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y40" t="n">
         <v>17</v>
@@ -8192,7 +8192,7 @@
         <v>21</v>
       </c>
       <c r="AA40" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB40" t="n">
         <v>17.5</v>
@@ -8201,7 +8201,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD40" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE40" t="n">
         <v>23</v>
@@ -8210,7 +8210,7 @@
         <v>22</v>
       </c>
       <c r="AG40" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH40" t="n">
         <v>13</v>
@@ -8222,7 +8222,7 @@
         <v>40</v>
       </c>
       <c r="AK40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL40" t="n">
         <v>28</v>
@@ -8234,7 +8234,7 @@
         <v>15</v>
       </c>
       <c r="AO40" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP40" t="n">
         <v>22</v>
@@ -8246,22 +8246,22 @@
         <v>19.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU40" t="n">
         <v>9</v>
       </c>
       <c r="AV40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX40" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY40" t="n">
         <v>12</v>
@@ -8273,13 +8273,13 @@
         <v>26</v>
       </c>
       <c r="BB40" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD40" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE40" t="n">
         <v>44</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -8338,7 +8338,7 @@
         <v>2.74</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.41</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -8517,64 +8517,64 @@
         </is>
       </c>
       <c r="F42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.67</v>
       </c>
-      <c r="G42" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H42" t="n">
-        <v>5</v>
-      </c>
-      <c r="I42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K42" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N42" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.7</v>
-      </c>
       <c r="V42" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="X42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y42" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z42" t="n">
         <v>55</v>
@@ -8589,7 +8589,7 @@
         <v>9.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE42" t="n">
         <v>1000</v>
@@ -8598,7 +8598,7 @@
         <v>11.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH42" t="n">
         <v>29</v>
@@ -8607,10 +8607,10 @@
         <v>1000</v>
       </c>
       <c r="AJ42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK42" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL42" t="n">
         <v>60</v>
@@ -8619,52 +8619,52 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AS42" t="n">
         <v>5.1</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.1</v>
+        <v>5.8</v>
       </c>
       <c r="AU42" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>4.4</v>
+        <v>17.5</v>
       </c>
       <c r="AW42" t="n">
         <v>5</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.6</v>
+        <v>7.6</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BA42" t="n">
         <v>5</v>
       </c>
       <c r="BB42" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.3</v>
+        <v>17.5</v>
       </c>
       <c r="BD42" t="n">
         <v>4.8</v>
@@ -8673,14 +8673,14 @@
         <v>5.1</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>2.7</v>
       </c>
       <c r="G43" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H43" t="n">
         <v>3.05</v>
@@ -8723,7 +8723,7 @@
         <v>3.3</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K43" t="n">
         <v>3.15</v>
@@ -8753,7 +8753,7 @@
         <v>6.4</v>
       </c>
       <c r="T43" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U43" t="n">
         <v>1.69</v>
@@ -8762,19 +8762,19 @@
         <v>1.44</v>
       </c>
       <c r="W43" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X43" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Y43" t="n">
         <v>8.4</v>
       </c>
       <c r="Z43" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AB43" t="n">
         <v>7.6</v>
@@ -8786,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="AE43" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AF43" t="n">
         <v>16.5</v>
@@ -8804,19 +8804,19 @@
         <v>55</v>
       </c>
       <c r="AK43" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM43" t="n">
         <v>270</v>
       </c>
       <c r="AN43" t="n">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP43" t="n">
         <v>6.8</v>
@@ -8849,7 +8849,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ43" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA43" t="n">
         <v>38</v>
@@ -8861,20 +8861,20 @@
         <v>36</v>
       </c>
       <c r="BD43" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="BE43" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF43" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="BG43" t="n">
         <v>32</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -8905,170 +8905,170 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="G44" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H44" t="n">
+        <v>7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N44" t="n">
+        <v>4</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X44" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>980</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>980</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT44" t="n">
         <v>7.4</v>
       </c>
-      <c r="I44" t="n">
+      <c r="AU44" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="J44" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K44" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L44" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N44" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P44" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T44" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W44" t="n">
-        <v>3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>270</v>
-      </c>
-      <c r="AB44" t="n">
+      <c r="AV44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE44" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC44" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>160</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ44" t="n">
+      <c r="BF44" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA44" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BG44" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -9102,10 +9102,10 @@
         <v>1.59</v>
       </c>
       <c r="G45" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H45" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="I45" t="n">
         <v>8</v>
@@ -9117,13 +9117,13 @@
         <v>4.1</v>
       </c>
       <c r="L45" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>1.45</v>
@@ -9135,37 +9135,37 @@
         <v>2.34</v>
       </c>
       <c r="R45" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S45" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U45" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="V45" t="n">
         <v>1.14</v>
       </c>
       <c r="W45" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X45" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y45" t="n">
         <v>20</v>
       </c>
       <c r="Z45" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AA45" t="n">
         <v>340</v>
       </c>
       <c r="AB45" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC45" t="n">
         <v>11</v>
@@ -9180,28 +9180,28 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG45" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH45" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI45" t="n">
         <v>190</v>
       </c>
       <c r="AJ45" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK45" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="n">
         <v>55</v>
       </c>
       <c r="AM45" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AN45" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AO45" t="n">
         <v>330</v>
@@ -9213,10 +9213,10 @@
         <v>16</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.9</v>
+        <v>50</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AT45" t="n">
         <v>5.7</v>
@@ -9228,7 +9228,7 @@
         <v>20</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AX45" t="n">
         <v>7.4</v>
@@ -9240,7 +9240,7 @@
         <v>22</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BB45" t="n">
         <v>12.5</v>
@@ -9249,20 +9249,20 @@
         <v>17</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BF45" t="n">
         <v>10.5</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>
@@ -9293,170 +9293,170 @@
         </is>
       </c>
       <c r="F46" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G46" t="n">
         <v>4.7</v>
       </c>
-      <c r="G46" t="n">
-        <v>5.3</v>
-      </c>
       <c r="H46" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="I46" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L46" t="n">
         <v>1.4</v>
       </c>
       <c r="M46" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N46" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O46" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P46" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V46" t="n">
         <v>1.94</v>
       </c>
-      <c r="R46" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V46" t="n">
-        <v>2.1</v>
-      </c>
       <c r="W46" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="X46" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Y46" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Z46" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AA46" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE46" t="n">
         <v>24</v>
       </c>
-      <c r="AB46" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>23</v>
-      </c>
       <c r="AF46" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AG46" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AH46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI46" t="n">
         <v>46</v>
       </c>
       <c r="AJ46" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AK46" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL46" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AM46" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN46" t="n">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="AO46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP46" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT46" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ46" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR46" t="n">
+      <c r="AU46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV46" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AS46" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AT46" t="n">
+      <c r="AW46" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY46" t="n">
         <v>14.5</v>
       </c>
-      <c r="AU46" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>17</v>
-      </c>
       <c r="AZ46" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BC46" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BD46" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-03 13:50:53</t>
+          <t>2026-03-03 18:12:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.7</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.72</v>
-      </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
         <v>4.3</v>
@@ -790,10 +790,10 @@
         <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
@@ -802,79 +802,79 @@
         <v>1.88</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V2" t="n">
         <v>1.2</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
         <v>20</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB2" t="n">
         <v>9</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF2" t="n">
         <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL2" t="n">
         <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -895,10 +895,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
@@ -910,17 +910,17 @@
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BG2" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G3" t="n">
         <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="I3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="J3" t="n">
         <v>3.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="T3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W3" t="n">
         <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="Y3" t="n">
         <v>11</v>
@@ -1017,16 +1017,16 @@
         <v>22</v>
       </c>
       <c r="AB3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AF3" t="n">
         <v>34</v>
@@ -1044,7 +1044,7 @@
         <v>90</v>
       </c>
       <c r="AK3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AL3" t="n">
         <v>55</v>
@@ -1053,16 +1053,16 @@
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AO3" t="n">
         <v>10.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>12</v>
@@ -1077,10 +1077,10 @@
         <v>8.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX3" t="n">
         <v>30</v>
@@ -1089,32 +1089,32 @@
         <v>15.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="BD3" t="n">
         <v>42</v>
       </c>
       <c r="BE3" t="n">
-        <v>14.5</v>
+        <v>60</v>
       </c>
       <c r="BF3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="G4" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="J4" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.3</v>
@@ -1169,76 +1169,76 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z4" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AA4" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD4" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI4" t="n">
         <v>60</v>
       </c>
-      <c r="AF4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>55</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL4" t="n">
         <v>27</v>
@@ -1247,68 +1247,68 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AO4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA4" t="n">
         <v>50</v>
       </c>
-      <c r="AP4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>46</v>
-      </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE4" t="n">
         <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="G5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="H5" t="n">
         <v>10.5</v>
       </c>
       <c r="I5" t="n">
-        <v>16.5</v>
+        <v>11.5</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>1.1</v>
       </c>
       <c r="P5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="T5" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="X5" t="n">
         <v>950</v>
@@ -1399,7 +1399,7 @@
         <v>950</v>
       </c>
       <c r="Z5" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ5" t="n">
         <v>980</v>
@@ -1438,71 +1438,71 @@
         <v>980</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC5" t="n">
         <v>5.2</v>
       </c>
-      <c r="AR5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.3</v>
+        <v>2.56</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="I6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
         <v>3.15</v>
@@ -1551,7 +1551,7 @@
         <v>3.3</v>
       </c>
       <c r="L6" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
@@ -1566,13 +1566,13 @@
         <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T6" t="n">
         <v>2.12</v>
@@ -1581,10 +1581,10 @@
         <v>1.62</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
         <v>11</v>
@@ -1593,7 +1593,7 @@
         <v>10.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
         <v>90</v>
@@ -1608,19 +1608,19 @@
         <v>980</v>
       </c>
       <c r="AE6" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
-        <v>14.5</v>
+        <v>25</v>
       </c>
       <c r="AG6" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AJ6" t="n">
         <v>980</v>
@@ -1629,7 +1629,7 @@
         <v>980</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>170</v>
       </c>
       <c r="AM6" t="n">
         <v>250</v>
@@ -1647,10 +1647,10 @@
         <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1662,22 +1662,22 @@
         <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC6" t="n">
         <v>6.4</v>
@@ -1686,17 +1686,17 @@
         <v>7</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
         <v>22</v>
       </c>
       <c r="BG6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G7" t="n">
         <v>1.45</v>
@@ -1736,10 +1736,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -1763,7 +1763,7 @@
         <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
         <v>3.3</v>
@@ -1775,10 +1775,10 @@
         <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
@@ -1790,7 +1790,7 @@
         <v>95</v>
       </c>
       <c r="AA7" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AB7" t="n">
         <v>7.8</v>
@@ -1805,7 +1805,7 @@
         <v>200</v>
       </c>
       <c r="AF7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG7" t="n">
         <v>10.5</v>
@@ -1820,31 +1820,31 @@
         <v>12</v>
       </c>
       <c r="AK7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM7" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
         <v>7.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -1856,7 +1856,7 @@
         <v>32</v>
       </c>
       <c r="AW7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -1868,29 +1868,29 @@
         <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB7" t="n">
         <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF7" t="n">
         <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>1.28</v>
       </c>
       <c r="G8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="H8" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="I8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" t="n">
         <v>5.3</v>
@@ -1939,7 +1939,7 @@
         <v>6.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.06</v>
@@ -1963,16 +1963,16 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="U8" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="X8" t="n">
         <v>18.5</v>
@@ -2017,13 +2017,13 @@
         <v>19</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AM8" t="n">
         <v>420</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,13 +2032,13 @@
         <v>13</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
         <v>5.7</v>
@@ -2047,10 +2047,10 @@
         <v>11</v>
       </c>
       <c r="AV8" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
         <v>5.8</v>
@@ -2065,13 +2065,13 @@
         <v>6.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
         <v>15</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE8" t="n">
         <v>6.2</v>
@@ -2080,11 +2080,11 @@
         <v>5.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2121,19 +2121,19 @@
         <v>2.54</v>
       </c>
       <c r="H9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.25</v>
       </c>
       <c r="L9" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="M9" t="n">
         <v>1.12</v>
@@ -2148,13 +2148,13 @@
         <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
         <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T9" t="n">
         <v>2.16</v>
@@ -2184,7 +2184,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
         <v>19.5</v>
@@ -2205,10 +2205,10 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2223,7 +2223,7 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9" t="n">
         <v>9.199999999999999</v>
@@ -2232,7 +2232,7 @@
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
@@ -2241,10 +2241,10 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2253,32 +2253,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD9" t="n">
         <v>7</v>
       </c>
-      <c r="BB9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE9" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2315,19 +2315,19 @@
         <v>3.45</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I10" t="n">
         <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
@@ -2363,7 +2363,7 @@
         <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y10" t="n">
         <v>11</v>
@@ -2384,7 +2384,7 @@
         <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
         <v>25</v>
@@ -2417,7 +2417,7 @@
         <v>32</v>
       </c>
       <c r="AP10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ10" t="n">
         <v>8.199999999999999</v>
@@ -2426,19 +2426,19 @@
         <v>12</v>
       </c>
       <c r="AS10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW10" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.4</v>
       </c>
       <c r="AX10" t="n">
         <v>16.5</v>
@@ -2447,32 +2447,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
         <v>21</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
         <v>1.87</v>
       </c>
       <c r="X11" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y11" t="n">
         <v>16.5</v>
@@ -2569,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>8.199999999999999</v>
@@ -2587,7 +2587,7 @@
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2620,7 +2620,7 @@
         <v>21</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
         <v>8.199999999999999</v>
@@ -2632,7 +2632,7 @@
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
@@ -2641,10 +2641,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -2653,20 +2653,20 @@
         <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF11" t="n">
         <v>12</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="n">
         <v>5.7</v>
@@ -2715,7 +2715,7 @@
         <v>3.8</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
         <v>1.09</v>
@@ -2727,10 +2727,10 @@
         <v>1.41</v>
       </c>
       <c r="P12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
         <v>1.28</v>
@@ -2742,10 +2742,10 @@
         <v>2.12</v>
       </c>
       <c r="U12" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W12" t="n">
         <v>2.26</v>
@@ -2763,7 +2763,7 @@
         <v>170</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC12" t="n">
         <v>8.199999999999999</v>
@@ -2778,13 +2778,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ12" t="n">
         <v>18.5</v>
@@ -2796,7 +2796,7 @@
         <v>46</v>
       </c>
       <c r="AM12" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN12" t="n">
         <v>14</v>
@@ -2817,7 +2817,7 @@
         <v>44</v>
       </c>
       <c r="AT12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU12" t="n">
         <v>7.8</v>
@@ -2838,7 +2838,7 @@
         <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB12" t="n">
         <v>16.5</v>
@@ -2850,7 +2850,7 @@
         <v>40</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="G13" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>3.1</v>
@@ -2909,7 +2909,7 @@
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -2918,13 +2918,13 @@
         <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P13" t="n">
         <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
@@ -2933,128 +2933,128 @@
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y13" t="n">
         <v>13</v>
       </c>
-      <c r="Y13" t="n">
-        <v>12</v>
-      </c>
       <c r="Z13" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AA13" t="n">
-        <v>60</v>
+        <v>340</v>
       </c>
       <c r="AB13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AH13" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>290</v>
       </c>
       <c r="AJ13" t="n">
         <v>980</v>
       </c>
       <c r="AK13" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="AL13" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN13" t="n">
         <v>980</v>
       </c>
       <c r="AO13" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>10</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AR13" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BA13" t="n">
-        <v>38</v>
+        <v>8.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BD13" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="BF13" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3088,37 +3088,37 @@
         <v>8.6</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>1.44</v>
       </c>
       <c r="I14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K14" t="n">
         <v>5.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O14" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
         <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
         <v>1.38</v>
@@ -3133,7 +3133,7 @@
         <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="W14" t="n">
         <v>1.11</v>
@@ -3151,46 +3151,46 @@
         <v>12.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD14" t="n">
         <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF14" t="n">
         <v>85</v>
       </c>
       <c r="AG14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH14" t="n">
         <v>36</v>
       </c>
-      <c r="AH14" t="n">
-        <v>30</v>
-      </c>
       <c r="AI14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AK14" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AL14" t="n">
         <v>180</v>
       </c>
       <c r="AM14" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AN14" t="n">
         <v>250</v>
       </c>
       <c r="AO14" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AP14" t="n">
         <v>14</v>
@@ -3214,41 +3214,41 @@
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AY14" t="n">
         <v>29</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BB14" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BC14" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BD14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF14" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BG14" t="n">
         <v>6.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G15" t="n">
         <v>1.64</v>
@@ -3294,7 +3294,7 @@
         <v>4.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.33</v>
@@ -3306,7 +3306,7 @@
         <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P15" t="n">
         <v>2.24</v>
@@ -3318,7 +3318,7 @@
         <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.67</v>
@@ -3333,19 +3333,19 @@
         <v>2.56</v>
       </c>
       <c r="X15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y15" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Z15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA15" t="n">
         <v>220</v>
       </c>
       <c r="AB15" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
         <v>13</v>
@@ -3357,7 +3357,7 @@
         <v>110</v>
       </c>
       <c r="AF15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG15" t="n">
         <v>12.5</v>
@@ -3375,10 +3375,10 @@
         <v>19.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN15" t="n">
         <v>8.800000000000001</v>
@@ -3390,59 +3390,59 @@
         <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
         <v>8.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX15" t="n">
         <v>8.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ15" t="n">
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BB15" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3476,43 +3476,43 @@
         <v>2.06</v>
       </c>
       <c r="G16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H16" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
         <v>1.66</v>
@@ -3524,13 +3524,13 @@
         <v>1.35</v>
       </c>
       <c r="W16" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="X16" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="Y16" t="n">
-        <v>980</v>
+        <v>16.5</v>
       </c>
       <c r="Z16" t="n">
         <v>980</v>
@@ -3539,10 +3539,10 @@
         <v>70</v>
       </c>
       <c r="AB16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>18</v>
@@ -3551,13 +3551,13 @@
         <v>980</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
         <v>980</v>
@@ -3566,13 +3566,13 @@
         <v>980</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AL16" t="n">
         <v>980</v>
       </c>
       <c r="AM16" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="n">
         <v>13.5</v>
@@ -3581,7 +3581,7 @@
         <v>980</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.8</v>
+        <v>15</v>
       </c>
       <c r="AQ16" t="n">
         <v>13.5</v>
@@ -3590,7 +3590,7 @@
         <v>21</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT16" t="n">
         <v>9.6</v>
@@ -3602,7 +3602,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -3620,23 +3620,23 @@
         <v>19.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.2</v>
+        <v>17.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>55</v>
+        <v>8.4</v>
       </c>
       <c r="BF16" t="n">
         <v>10</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G17" t="n">
         <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="I17" t="n">
         <v>1.8</v>
@@ -3685,7 +3685,7 @@
         <v>4.9</v>
       </c>
       <c r="L17" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -3697,16 +3697,16 @@
         <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S17" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="T17" t="n">
         <v>1.65</v>
@@ -3736,7 +3736,7 @@
         <v>29</v>
       </c>
       <c r="AC17" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD17" t="n">
         <v>13</v>
@@ -3745,10 +3745,10 @@
         <v>20</v>
       </c>
       <c r="AF17" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
@@ -3763,10 +3763,10 @@
         <v>65</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>250</v>
       </c>
       <c r="AM17" t="n">
-        <v>85</v>
+        <v>330</v>
       </c>
       <c r="AN17" t="n">
         <v>55</v>
@@ -3784,7 +3784,7 @@
         <v>9.6</v>
       </c>
       <c r="AS17" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3799,10 +3799,10 @@
         <v>12</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>12.5</v>
@@ -3811,26 +3811,26 @@
         <v>19</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.95</v>
+        <v>7</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -3861,43 +3861,43 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G18" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="H18" t="n">
         <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M18" t="n">
         <v>1.03</v>
       </c>
       <c r="N18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O18" t="n">
         <v>1.19</v>
       </c>
       <c r="P18" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
         <v>1.58</v>
       </c>
       <c r="R18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S18" t="n">
         <v>2.44</v>
@@ -3912,7 +3912,7 @@
         <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X18" t="n">
         <v>28</v>
@@ -3945,7 +3945,7 @@
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
         <v>50</v>
@@ -3963,22 +3963,22 @@
         <v>75</v>
       </c>
       <c r="AN18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO18" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
         <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AR18" t="n">
-        <v>25</v>
+        <v>4.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
         <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>11</v>
@@ -4002,10 +4002,10 @@
         <v>12.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB18" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC18" t="n">
         <v>13.5</v>
@@ -4014,17 +4014,17 @@
         <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BF18" t="n">
         <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="G19" t="n">
         <v>2.84</v>
@@ -4064,13 +4064,13 @@
         <v>2.64</v>
       </c>
       <c r="I19" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="J19" t="n">
         <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L19" t="n">
         <v>1.32</v>
@@ -4079,7 +4079,7 @@
         <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.26</v>
@@ -4088,37 +4088,37 @@
         <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="U19" t="n">
         <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W19" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="Y19" t="n">
         <v>15</v>
       </c>
       <c r="Z19" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AA19" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>14.5</v>
@@ -4130,52 +4130,52 @@
         <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AG19" t="n">
         <v>14</v>
       </c>
       <c r="AH19" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>980</v>
       </c>
       <c r="AJ19" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK19" t="n">
         <v>32</v>
       </c>
       <c r="AL19" t="n">
-        <v>980</v>
+        <v>95</v>
       </c>
       <c r="AM19" t="n">
-        <v>85</v>
+        <v>330</v>
       </c>
       <c r="AN19" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AO19" t="n">
         <v>980</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="AR19" t="n">
         <v>4.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.8</v>
@@ -4184,13 +4184,13 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="AX19" t="n">
         <v>4.3</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="AZ19" t="n">
         <v>12</v>
@@ -4202,10 +4202,10 @@
         <v>4.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE19" t="n">
         <v>5.1</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4249,49 +4249,49 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="H20" t="n">
         <v>6.6</v>
       </c>
       <c r="I20" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U20" t="n">
         <v>1.98</v>
@@ -4300,22 +4300,22 @@
         <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="X20" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y20" t="n">
         <v>26</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AA20" t="n">
         <v>220</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
         <v>9.800000000000001</v>
@@ -4324,95 +4324,95 @@
         <v>29</v>
       </c>
       <c r="AE20" t="n">
-        <v>110</v>
+        <v>510</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK20" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>980</v>
+        <v>85</v>
       </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>430</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO20" t="n">
         <v>130</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.9</v>
+        <v>19.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
         <v>8.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AW20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF20" t="n">
         <v>7.2</v>
       </c>
-      <c r="AX20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF20" t="n">
+      <c r="BG20" t="n">
         <v>7.8</v>
       </c>
-      <c r="BG20" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
         <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
         <v>2.58</v>
       </c>
       <c r="J21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.3</v>
       </c>
-      <c r="K21" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
@@ -4470,7 +4470,7 @@
         <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P21" t="n">
         <v>1.78</v>
@@ -4494,7 +4494,7 @@
         <v>1.63</v>
       </c>
       <c r="W21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X21" t="n">
         <v>11.5</v>
@@ -4545,7 +4545,7 @@
         <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AO21" t="n">
         <v>27</v>
@@ -4563,7 +4563,7 @@
         <v>30</v>
       </c>
       <c r="AT21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU21" t="n">
         <v>6.8</v>
@@ -4581,32 +4581,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB21" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="BC21" t="n">
         <v>34</v>
       </c>
       <c r="BD21" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BE21" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="BF21" t="n">
-        <v>34</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
         <v>22</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G22" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H22" t="n">
         <v>5.3</v>
@@ -4673,7 +4673,7 @@
         <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
         <v>2.24</v>
@@ -4685,19 +4685,19 @@
         <v>2.46</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W22" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X22" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="Y22" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="Z22" t="n">
-        <v>55</v>
+        <v>350</v>
       </c>
       <c r="AA22" t="n">
         <v>140</v>
@@ -4712,7 +4712,7 @@
         <v>22</v>
       </c>
       <c r="AE22" t="n">
-        <v>65</v>
+        <v>320</v>
       </c>
       <c r="AF22" t="n">
         <v>13.5</v>
@@ -4724,7 +4724,7 @@
         <v>18.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>250</v>
       </c>
       <c r="AJ22" t="n">
         <v>17.5</v>
@@ -4733,10 +4733,10 @@
         <v>16</v>
       </c>
       <c r="AL22" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="AN22" t="n">
         <v>5.9</v>
@@ -4745,16 +4745,16 @@
         <v>980</v>
       </c>
       <c r="AP22" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
         <v>11.5</v>
@@ -4763,10 +4763,10 @@
         <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AX22" t="n">
         <v>11</v>
@@ -4778,10 +4778,10 @@
         <v>14.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BC22" t="n">
         <v>12.5</v>
@@ -4790,17 +4790,17 @@
         <v>21</v>
       </c>
       <c r="BE22" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BF22" t="n">
         <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G23" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H23" t="n">
         <v>3.4</v>
@@ -4849,7 +4849,7 @@
         <v>3.05</v>
       </c>
       <c r="L23" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.13</v>
@@ -4864,7 +4864,7 @@
         <v>1.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R23" t="n">
         <v>1.2</v>
@@ -4879,22 +4879,22 @@
         <v>1.84</v>
       </c>
       <c r="V23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
         <v>1.6</v>
       </c>
       <c r="X23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB23" t="n">
         <v>8.199999999999999</v>
@@ -4903,25 +4903,25 @@
         <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF23" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK23" t="n">
         <v>38</v>
@@ -4930,13 +4930,13 @@
         <v>65</v>
       </c>
       <c r="AM23" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN23" t="n">
         <v>42</v>
       </c>
       <c r="AO23" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP23" t="n">
         <v>7.8</v>
@@ -4948,31 +4948,31 @@
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="AT23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU23" t="n">
         <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="AX23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ23" t="n">
         <v>19.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BB23" t="n">
         <v>32</v>
@@ -4981,20 +4981,20 @@
         <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>9.800000000000001</v>
+        <v>50</v>
       </c>
       <c r="BE23" t="n">
+        <v>13</v>
+      </c>
+      <c r="BF23" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF23" t="n">
-        <v>30</v>
-      </c>
       <c r="BG23" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>3.25</v>
       </c>
       <c r="G24" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I24" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K24" t="n">
         <v>4.1</v>
@@ -5055,7 +5055,7 @@
         <v>1.21</v>
       </c>
       <c r="P24" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q24" t="n">
         <v>1.65</v>
@@ -5064,131 +5064,131 @@
         <v>1.55</v>
       </c>
       <c r="S24" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U24" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V24" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W24" t="n">
         <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB24" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AO24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="AS24" t="n">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="AT24" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX24" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="AY24" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="BB24" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BC24" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
-        <v>5.3</v>
+        <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="BF24" t="n">
-        <v>5.1</v>
+        <v>19.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>2.14</v>
       </c>
       <c r="G25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H25" t="n">
         <v>3.65</v>
@@ -5231,19 +5231,19 @@
         <v>3.9</v>
       </c>
       <c r="J25" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
         <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
         <v>1.33</v>
@@ -5267,10 +5267,10 @@
         <v>2.1</v>
       </c>
       <c r="V25" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W25" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="X25" t="n">
         <v>14.5</v>
@@ -5279,7 +5279,7 @@
         <v>13.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
@@ -5291,19 +5291,19 @@
         <v>8.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG25" t="n">
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5312,13 +5312,13 @@
         <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>330</v>
       </c>
       <c r="AN25" t="n">
         <v>1000</v>
@@ -5327,19 +5327,19 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR25" t="n">
-        <v>8.6</v>
+        <v>22</v>
       </c>
       <c r="AS25" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="AT25" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AU25" t="n">
         <v>7.6</v>
@@ -5348,7 +5348,7 @@
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
         <v>10.5</v>
@@ -5360,29 +5360,29 @@
         <v>16.5</v>
       </c>
       <c r="BA25" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD25" t="n">
         <v>10</v>
       </c>
-      <c r="BB25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H26" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="I26" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.21</v>
@@ -5437,10 +5437,10 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="O26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P26" t="n">
         <v>2.98</v>
@@ -5458,22 +5458,22 @@
         <v>1.45</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W26" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X26" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="Y26" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="Z26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA26" t="n">
         <v>60</v>
@@ -5500,7 +5500,7 @@
         <v>13.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AJ26" t="n">
         <v>44</v>
@@ -5512,7 +5512,7 @@
         <v>25</v>
       </c>
       <c r="AM26" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="AN26" t="n">
         <v>9.6</v>
@@ -5521,7 +5521,7 @@
         <v>13.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>20</v>
@@ -5533,7 +5533,7 @@
         <v>38</v>
       </c>
       <c r="AT26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU26" t="n">
         <v>9.800000000000001</v>
@@ -5545,7 +5545,7 @@
         <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY26" t="n">
         <v>9.800000000000001</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G27" t="n">
         <v>1.79</v>
@@ -5616,31 +5616,31 @@
         <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O27" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P27" t="n">
         <v>1.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R27" t="n">
         <v>1.22</v>
@@ -5655,7 +5655,7 @@
         <v>1.69</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W27" t="n">
         <v>2.26</v>
@@ -5664,7 +5664,7 @@
         <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z27" t="n">
         <v>60</v>
@@ -5673,7 +5673,7 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC27" t="n">
         <v>9</v>
@@ -5682,7 +5682,7 @@
         <v>32</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF27" t="n">
         <v>9.4</v>
@@ -5700,7 +5700,7 @@
         <v>21</v>
       </c>
       <c r="AK27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
         <v>60</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT27" t="n">
         <v>5.5</v>
@@ -5736,7 +5736,7 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX27" t="n">
         <v>7.8</v>
@@ -5745,10 +5745,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5.9</v>
+        <v>14</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
         <v>15</v>
@@ -5757,20 +5757,20 @@
         <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF27" t="n">
         <v>13</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G28" t="n">
         <v>2.72</v>
@@ -5813,25 +5813,25 @@
         <v>3.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O28" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q28" t="n">
         <v>2.16</v>
@@ -5846,10 +5846,10 @@
         <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W28" t="n">
         <v>1.58</v>
@@ -5864,10 +5864,10 @@
         <v>24</v>
       </c>
       <c r="AA28" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
         <v>8.800000000000001</v>
@@ -5879,10 +5879,10 @@
         <v>46</v>
       </c>
       <c r="AF28" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
         <v>22</v>
@@ -5900,71 +5900,71 @@
         <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN28" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO28" t="n">
         <v>48</v>
       </c>
       <c r="AP28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.2</v>
+        <v>40</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>30</v>
+        <v>5.1</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.2</v>
+        <v>40</v>
       </c>
       <c r="BB28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG28" t="n">
         <v>30</v>
       </c>
-      <c r="BC28" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>1.67</v>
       </c>
       <c r="G29" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H29" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
@@ -6013,7 +6013,7 @@
         <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M29" t="n">
         <v>1.08</v>
@@ -6037,7 +6037,7 @@
         <v>4</v>
       </c>
       <c r="T29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U29" t="n">
         <v>1.83</v>
@@ -6046,7 +6046,7 @@
         <v>1.16</v>
       </c>
       <c r="W29" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
@@ -6064,7 +6064,7 @@
         <v>8.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
         <v>27</v>
@@ -6109,10 +6109,10 @@
         <v>14</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AT29" t="n">
         <v>6.4</v>
@@ -6121,10 +6121,10 @@
         <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
         <v>8.4</v>
@@ -6133,32 +6133,32 @@
         <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BC29" t="n">
         <v>18</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>2.16</v>
       </c>
       <c r="H30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J30" t="n">
         <v>3.75</v>
@@ -6222,7 +6222,7 @@
         <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R30" t="n">
         <v>1.51</v>
@@ -6237,7 +6237,7 @@
         <v>2.46</v>
       </c>
       <c r="V30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
         <v>1.86</v>
@@ -6249,7 +6249,7 @@
         <v>17</v>
       </c>
       <c r="Z30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA30" t="n">
         <v>65</v>
@@ -6258,16 +6258,16 @@
         <v>12</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE30" t="n">
         <v>36</v>
       </c>
       <c r="AF30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="n">
         <v>10.5</v>
@@ -6285,10 +6285,10 @@
         <v>20</v>
       </c>
       <c r="AL30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM30" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AN30" t="n">
         <v>12.5</v>
@@ -6312,10 +6312,10 @@
         <v>11</v>
       </c>
       <c r="AU30" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV30" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
         <v>32</v>
@@ -6339,7 +6339,7 @@
         <v>19</v>
       </c>
       <c r="BD30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE30" t="n">
         <v>55</v>
@@ -6348,11 +6348,11 @@
         <v>11.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -6383,25 +6383,25 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="H31" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K31" t="n">
         <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
         <v>1.09</v>
@@ -6434,7 +6434,7 @@
         <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X31" t="n">
         <v>13</v>
@@ -6458,7 +6458,7 @@
         <v>15.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF31" t="n">
         <v>16.5</v>
@@ -6482,7 +6482,7 @@
         <v>50</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN31" t="n">
         <v>29</v>
@@ -6500,7 +6500,7 @@
         <v>18.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AT31" t="n">
         <v>7.8</v>
@@ -6530,7 +6530,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BD31" t="n">
         <v>36</v>
@@ -6539,14 +6539,14 @@
         <v>8.6</v>
       </c>
       <c r="BF31" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="BG31" t="n">
         <v>34</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -6577,25 +6577,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G32" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I32" t="n">
         <v>2.24</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.26</v>
       </c>
       <c r="J32" t="n">
         <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M32" t="n">
         <v>1.06</v>
@@ -6607,7 +6607,7 @@
         <v>1.26</v>
       </c>
       <c r="P32" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q32" t="n">
         <v>1.8</v>
@@ -6622,13 +6622,13 @@
         <v>1.68</v>
       </c>
       <c r="U32" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V32" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W32" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X32" t="n">
         <v>17</v>
@@ -6673,7 +6673,7 @@
         <v>36</v>
       </c>
       <c r="AL32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM32" t="n">
         <v>75</v>
@@ -6691,13 +6691,13 @@
         <v>11</v>
       </c>
       <c r="AR32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU32" t="n">
         <v>7.8</v>
@@ -6709,7 +6709,7 @@
         <v>19</v>
       </c>
       <c r="AX32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY32" t="n">
         <v>13</v>
@@ -6730,7 +6730,7 @@
         <v>38</v>
       </c>
       <c r="BE32" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BF32" t="n">
         <v>27</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6777,16 @@
         <v>5.7</v>
       </c>
       <c r="H33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I33" t="n">
         <v>1.71</v>
       </c>
-      <c r="I33" t="n">
-        <v>1.72</v>
-      </c>
       <c r="J33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K33" t="n">
         <v>4.2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.3</v>
       </c>
       <c r="L33" t="n">
         <v>1.43</v>
@@ -6795,25 +6795,25 @@
         <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O33" t="n">
         <v>1.33</v>
       </c>
       <c r="P33" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="Q33" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U33" t="n">
         <v>2</v>
@@ -6825,13 +6825,13 @@
         <v>1.21</v>
       </c>
       <c r="X33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AA33" t="n">
         <v>16.5</v>
@@ -6840,7 +6840,7 @@
         <v>18</v>
       </c>
       <c r="AC33" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD33" t="n">
         <v>9.800000000000001</v>
@@ -6855,7 +6855,7 @@
         <v>21</v>
       </c>
       <c r="AH33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
         <v>36</v>
@@ -6870,22 +6870,22 @@
         <v>80</v>
       </c>
       <c r="AM33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
         <v>100</v>
       </c>
       <c r="AO33" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP33" t="n">
         <v>14</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS33" t="n">
         <v>16</v>
@@ -6897,10 +6897,10 @@
         <v>8.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW33" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX33" t="n">
         <v>38</v>
@@ -6912,19 +6912,19 @@
         <v>21</v>
       </c>
       <c r="BA33" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BB33" t="n">
         <v>80</v>
       </c>
       <c r="BC33" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BD33" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BE33" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="BF33" t="n">
         <v>90</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G34" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H34" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I34" t="n">
         <v>2.56</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.6</v>
       </c>
       <c r="J34" t="n">
         <v>3.7</v>
@@ -6989,13 +6989,13 @@
         <v>1.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O34" t="n">
         <v>1.24</v>
       </c>
       <c r="P34" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
         <v>1.76</v>
@@ -7013,13 +7013,13 @@
         <v>2.52</v>
       </c>
       <c r="V34" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W34" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="X34" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="Y34" t="n">
         <v>13.5</v>
@@ -7028,13 +7028,13 @@
         <v>18</v>
       </c>
       <c r="AA34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB34" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD34" t="n">
         <v>11.5</v>
@@ -7067,7 +7067,7 @@
         <v>65</v>
       </c>
       <c r="AN34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO34" t="n">
         <v>17</v>
@@ -7076,16 +7076,16 @@
         <v>17.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AS34" t="n">
         <v>34</v>
       </c>
       <c r="AT34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU34" t="n">
         <v>7.8</v>
@@ -7124,11 +7124,11 @@
         <v>20</v>
       </c>
       <c r="BG34" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -7201,10 +7201,10 @@
         <v>2.7</v>
       </c>
       <c r="T35" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U35" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V35" t="n">
         <v>1.12</v>
@@ -7222,16 +7222,16 @@
         <v>75</v>
       </c>
       <c r="AA35" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AE35" t="n">
         <v>120</v>
@@ -7240,7 +7240,7 @@
         <v>9</v>
       </c>
       <c r="AG35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH35" t="n">
         <v>23</v>
@@ -7264,28 +7264,28 @@
         <v>5.7</v>
       </c>
       <c r="AO35" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AP35" t="n">
         <v>22</v>
       </c>
       <c r="AQ35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AS35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW35" t="n">
         <v>50</v>
@@ -7294,13 +7294,13 @@
         <v>8.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ35" t="n">
         <v>22</v>
       </c>
       <c r="BA35" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="BB35" t="n">
         <v>11.5</v>
@@ -7312,17 +7312,17 @@
         <v>28</v>
       </c>
       <c r="BE35" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="BF35" t="n">
         <v>5.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -7353,170 +7353,170 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="G36" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="H36" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="I36" t="n">
-        <v>990</v>
+        <v>4.3</v>
       </c>
       <c r="J36" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>500</v>
+        <v>3.45</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.16</v>
+        <v>2.7</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="P36" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.46</v>
+        <v>2.38</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S36" t="n">
-        <v>1.46</v>
+        <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.05</v>
+        <v>1.98</v>
       </c>
       <c r="U36" t="n">
-        <v>1.05</v>
+        <v>1.73</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>480</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM36" t="n">
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -7547,19 +7547,19 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="G37" t="n">
         <v>1.98</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J37" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K37" t="n">
         <v>4.2</v>
@@ -7568,7 +7568,7 @@
         <v>1.24</v>
       </c>
       <c r="M37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N37" t="n">
         <v>5.2</v>
@@ -7577,10 +7577,10 @@
         <v>1.19</v>
       </c>
       <c r="P37" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R37" t="n">
         <v>1.57</v>
@@ -7589,13 +7589,13 @@
         <v>2.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="U37" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V37" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="W37" t="n">
         <v>2.02</v>
@@ -7610,7 +7610,7 @@
         <v>980</v>
       </c>
       <c r="AA37" t="n">
-        <v>95</v>
+        <v>900</v>
       </c>
       <c r="AB37" t="n">
         <v>980</v>
@@ -7625,13 +7625,13 @@
         <v>980</v>
       </c>
       <c r="AF37" t="n">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="AH37" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AI37" t="n">
         <v>980</v>
@@ -7640,77 +7640,77 @@
         <v>980</v>
       </c>
       <c r="AK37" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL37" t="n">
         <v>980</v>
       </c>
       <c r="AM37" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN37" t="n">
         <v>60</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>980</v>
       </c>
       <c r="AO37" t="n">
         <v>980</v>
       </c>
       <c r="AP37" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>24</v>
+        <v>7.4</v>
       </c>
       <c r="AS37" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY37" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ37" t="n">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="BA37" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>4.9</v>
+        <v>17</v>
       </c>
       <c r="BC37" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="BE37" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF37" t="n">
         <v>7.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.2</v>
+        <v>23</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -7744,19 +7744,19 @@
         <v>4.4</v>
       </c>
       <c r="G38" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H38" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="J38" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L38" t="n">
         <v>1.47</v>
@@ -7765,16 +7765,16 @@
         <v>1.13</v>
       </c>
       <c r="N38" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O38" t="n">
         <v>1.55</v>
       </c>
       <c r="P38" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R38" t="n">
         <v>1.18</v>
@@ -7789,10 +7789,10 @@
         <v>1.71</v>
       </c>
       <c r="V38" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W38" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7810,7 +7810,7 @@
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AX38" t="n">
         <v>1.49</v>
       </c>
-      <c r="AQ38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AY38" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.32</v>
+        <v>1.48</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="G39" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I39" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J39" t="n">
         <v>4.8</v>
       </c>
       <c r="K39" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
         <v>1.28</v>
@@ -7965,13 +7965,13 @@
         <v>1.19</v>
       </c>
       <c r="P39" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R39" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S39" t="n">
         <v>2.46</v>
@@ -7983,7 +7983,7 @@
         <v>2.16</v>
       </c>
       <c r="V39" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="W39" t="n">
         <v>1.15</v>
@@ -8022,7 +8022,7 @@
         <v>21</v>
       </c>
       <c r="AI39" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AJ39" t="n">
         <v>240</v>
@@ -8034,16 +8034,16 @@
         <v>80</v>
       </c>
       <c r="AM39" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN39" t="n">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="AO39" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ39" t="n">
         <v>10</v>
@@ -8055,7 +8055,7 @@
         <v>12.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU39" t="n">
         <v>10</v>
@@ -8067,38 +8067,38 @@
         <v>13</v>
       </c>
       <c r="AX39" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="AY39" t="n">
         <v>22</v>
       </c>
       <c r="AZ39" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA39" t="n">
         <v>24</v>
       </c>
       <c r="BB39" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC39" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BD39" t="n">
-        <v>12.5</v>
+        <v>28</v>
       </c>
       <c r="BE39" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BF39" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="BG39" t="n">
         <v>5.5</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -8129,16 +8129,16 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="G40" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="H40" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="I40" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="J40" t="n">
         <v>3.85</v>
@@ -8147,7 +8147,7 @@
         <v>3.9</v>
       </c>
       <c r="L40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M40" t="n">
         <v>1.04</v>
@@ -8156,19 +8156,19 @@
         <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P40" t="n">
         <v>2.66</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R40" t="n">
         <v>1.67</v>
       </c>
       <c r="S40" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T40" t="n">
         <v>1.51</v>
@@ -8177,10 +8177,10 @@
         <v>2.84</v>
       </c>
       <c r="V40" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X40" t="n">
         <v>24</v>
@@ -8210,7 +8210,7 @@
         <v>22</v>
       </c>
       <c r="AG40" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH40" t="n">
         <v>13</v>
@@ -8222,7 +8222,7 @@
         <v>40</v>
       </c>
       <c r="AK40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL40" t="n">
         <v>28</v>
@@ -8231,10 +8231,10 @@
         <v>48</v>
       </c>
       <c r="AN40" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP40" t="n">
         <v>22</v>
@@ -8246,19 +8246,19 @@
         <v>19.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT40" t="n">
         <v>17</v>
       </c>
       <c r="AU40" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV40" t="n">
         <v>11</v>
       </c>
       <c r="AW40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX40" t="n">
         <v>21</v>
@@ -8270,7 +8270,7 @@
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB40" t="n">
         <v>36</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -8323,19 +8323,19 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="G41" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="H41" t="n">
         <v>2.16</v>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="J41" t="n">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="K41" t="n">
         <v>3.7</v>
@@ -8371,122 +8371,122 @@
         <v>1.84</v>
       </c>
       <c r="V41" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="W41" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="X41" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD41" t="n">
         <v>13</v>
       </c>
-      <c r="Y41" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z41" t="n">
+      <c r="AE41" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG41" t="n">
         <v>17.5</v>
       </c>
-      <c r="AA41" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>19</v>
-      </c>
       <c r="AH41" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI41" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK41" t="n">
         <v>60</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>65</v>
-      </c>
       <c r="AL41" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM41" t="n">
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AO41" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP41" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AQ41" t="n">
-        <v>3.05</v>
+        <v>4.9</v>
       </c>
       <c r="AR41" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS41" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="AT41" t="n">
-        <v>3.3</v>
+        <v>6.4</v>
       </c>
       <c r="AU41" t="n">
-        <v>2.92</v>
+        <v>4.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="AW41" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="AX41" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AY41" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA41" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="BB41" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BC41" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BE41" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BF41" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
       <c r="BG41" t="n">
-        <v>3.85</v>
+        <v>5.1</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G42" t="n">
         <v>1.93</v>
@@ -8526,16 +8526,16 @@
         <v>5.3</v>
       </c>
       <c r="I42" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J42" t="n">
         <v>3.3</v>
       </c>
       <c r="K42" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L42" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M42" t="n">
         <v>1.1</v>
@@ -8559,19 +8559,19 @@
         <v>4.1</v>
       </c>
       <c r="T42" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="U42" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="V42" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W42" t="n">
         <v>2.06</v>
       </c>
       <c r="X42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y42" t="n">
         <v>17.5</v>
@@ -8586,7 +8586,7 @@
         <v>7.8</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD42" t="n">
         <v>27</v>
@@ -8601,7 +8601,7 @@
         <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
@@ -8631,10 +8631,10 @@
         <v>11.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AS42" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT42" t="n">
         <v>5.8</v>
@@ -8646,41 +8646,41 @@
         <v>17.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AX42" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY42" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ42" t="n">
         <v>18.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BB42" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BC42" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BF42" t="n">
         <v>13</v>
       </c>
       <c r="BG42" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G43" t="n">
         <v>2.88</v>
@@ -8726,7 +8726,7 @@
         <v>2.98</v>
       </c>
       <c r="K43" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L43" t="n">
         <v>1.63</v>
@@ -8735,16 +8735,16 @@
         <v>1.14</v>
       </c>
       <c r="N43" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O43" t="n">
         <v>1.63</v>
       </c>
       <c r="P43" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="R43" t="n">
         <v>1.16</v>
@@ -8756,7 +8756,7 @@
         <v>2.28</v>
       </c>
       <c r="U43" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V43" t="n">
         <v>1.44</v>
@@ -8774,7 +8774,7 @@
         <v>19.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>350</v>
+        <v>270</v>
       </c>
       <c r="AB43" t="n">
         <v>7.6</v>
@@ -8786,10 +8786,10 @@
         <v>16</v>
       </c>
       <c r="AE43" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AF43" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AG43" t="n">
         <v>14.5</v>
@@ -8801,19 +8801,19 @@
         <v>110</v>
       </c>
       <c r="AJ43" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AK43" t="n">
-        <v>130</v>
+        <v>980</v>
       </c>
       <c r="AL43" t="n">
         <v>85</v>
       </c>
       <c r="AM43" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AN43" t="n">
-        <v>330</v>
+        <v>260</v>
       </c>
       <c r="AO43" t="n">
         <v>75</v>
@@ -8831,7 +8831,7 @@
         <v>28</v>
       </c>
       <c r="AT43" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU43" t="n">
         <v>6.4</v>
@@ -8852,10 +8852,10 @@
         <v>21</v>
       </c>
       <c r="BA43" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB43" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BC43" t="n">
         <v>36</v>
@@ -8864,7 +8864,7 @@
         <v>36</v>
       </c>
       <c r="BE43" t="n">
-        <v>12.5</v>
+        <v>50</v>
       </c>
       <c r="BF43" t="n">
         <v>28</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -8908,70 +8908,70 @@
         <v>1.52</v>
       </c>
       <c r="G44" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="H44" t="n">
         <v>7</v>
       </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J44" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
         <v>4.8</v>
       </c>
       <c r="L44" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M44" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="O44" t="n">
         <v>1.28</v>
       </c>
       <c r="P44" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R44" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T44" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U44" t="n">
         <v>1.98</v>
       </c>
       <c r="V44" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W44" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="X44" t="n">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y44" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="Z44" t="n">
         <v>65</v>
       </c>
       <c r="AA44" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC44" t="n">
         <v>10.5</v>
@@ -8986,22 +8986,22 @@
         <v>10.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH44" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AI44" t="n">
         <v>110</v>
       </c>
       <c r="AJ44" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AK44" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL44" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AM44" t="n">
         <v>140</v>
@@ -9013,40 +9013,40 @@
         <v>150</v>
       </c>
       <c r="AP44" t="n">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="AQ44" t="n">
         <v>20</v>
       </c>
       <c r="AR44" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS44" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU44" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW44" t="n">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>9</v>
       </c>
       <c r="AX44" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY44" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ44" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA44" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB44" t="n">
         <v>13</v>
@@ -9058,17 +9058,17 @@
         <v>7.6</v>
       </c>
       <c r="BE44" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF44" t="n">
         <v>7.2</v>
       </c>
       <c r="BG44" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -9114,10 +9114,10 @@
         <v>3.9</v>
       </c>
       <c r="K45" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L45" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M45" t="n">
         <v>1.09</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>
@@ -9293,64 +9293,64 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G46" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H46" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I46" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="J46" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K46" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L46" t="n">
         <v>1.4</v>
       </c>
       <c r="M46" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N46" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="O46" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P46" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q46" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="R46" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T46" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U46" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V46" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="W46" t="n">
         <v>1.28</v>
       </c>
       <c r="X46" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="Z46" t="n">
         <v>14</v>
@@ -9359,10 +9359,10 @@
         <v>26</v>
       </c>
       <c r="AB46" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AC46" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD46" t="n">
         <v>12.5</v>
@@ -9371,10 +9371,10 @@
         <v>24</v>
       </c>
       <c r="AF46" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AG46" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH46" t="n">
         <v>22</v>
@@ -9386,7 +9386,7 @@
         <v>110</v>
       </c>
       <c r="AK46" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL46" t="n">
         <v>60</v>
@@ -9404,59 +9404,59 @@
         <v>12</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS46" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT46" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AU46" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AV46" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW46" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX46" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY46" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BB46" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BC46" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD46" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE46" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BF46" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG46" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-03 18:12:13</t>
+          <t>2026-03-03 20:20:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
@@ -790,25 +790,25 @@
         <v>2.08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
         <v>2.08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
@@ -823,10 +823,10 @@
         <v>160</v>
       </c>
       <c r="AB2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC2" t="n">
         <v>9</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>22</v>
@@ -838,16 +838,16 @@
         <v>10.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK2" t="n">
         <v>17</v>
@@ -856,25 +856,25 @@
         <v>34</v>
       </c>
       <c r="AM2" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="AN2" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP2" t="n">
         <v>15.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AS2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>8.199999999999999</v>
@@ -883,10 +883,10 @@
         <v>8.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AX2" t="n">
         <v>9.4</v>
@@ -898,7 +898,7 @@
         <v>19</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
@@ -910,17 +910,17 @@
         <v>30</v>
       </c>
       <c r="BE2" t="n">
-        <v>19.5</v>
+        <v>85</v>
       </c>
       <c r="BF2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG2" t="n">
-        <v>75</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -951,151 +951,151 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="M3" t="n">
         <v>1.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
         <v>1.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V3" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
         <v>11</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB3" t="n">
         <v>18.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
         <v>10.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG3" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
         <v>29</v>
       </c>
       <c r="AJ3" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AK3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
         <v>75</v>
       </c>
       <c r="AN3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AO3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>10</v>
       </c>
       <c r="AR3" t="n">
         <v>12</v>
       </c>
       <c r="AS3" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
         <v>18</v>
       </c>
       <c r="AX3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AY3" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3" t="n">
         <v>14.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB3" t="n">
-        <v>16.5</v>
+        <v>65</v>
       </c>
       <c r="BC3" t="n">
         <v>40</v>
@@ -1110,11 +1110,11 @@
         <v>36</v>
       </c>
       <c r="BG3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="H4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="J4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K4" t="n">
         <v>4.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.3</v>
@@ -1169,130 +1169,130 @@
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R4" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="T4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U4" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="Z4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
         <v>11.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE4" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI4" t="n">
         <v>60</v>
       </c>
       <c r="AJ4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK4" t="n">
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM4" t="n">
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AR4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AS4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT4" t="n">
         <v>10</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC4" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
         <v>24</v>
@@ -1301,14 +1301,14 @@
         <v>32</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG4" t="n">
         <v>16</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1339,34 +1339,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="n">
         <v>10.5</v>
       </c>
       <c r="I5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="K5" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P5" t="n">
         <v>3.65</v>
@@ -1375,13 +1375,13 @@
         <v>1.28</v>
       </c>
       <c r="R5" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
         <v>1.73</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U5" t="n">
         <v>2.12</v>
@@ -1393,7 +1393,7 @@
         <v>4.4</v>
       </c>
       <c r="X5" t="n">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="Y5" t="n">
         <v>950</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
         <v>980</v>
@@ -1459,10 +1459,10 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>4.2</v>
@@ -1471,38 +1471,38 @@
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
         <v>4.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.6</v>
+        <v>5.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.56</v>
+        <v>1.71</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
@@ -1572,7 +1572,7 @@
         <v>1.18</v>
       </c>
       <c r="S6" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T6" t="n">
         <v>2.12</v>
@@ -1587,7 +1587,7 @@
         <v>1.71</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
         <v>10.5</v>
@@ -1596,7 +1596,7 @@
         <v>46</v>
       </c>
       <c r="AA6" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AB6" t="n">
         <v>7.8</v>
@@ -1605,10 +1605,10 @@
         <v>8</v>
       </c>
       <c r="AD6" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AE6" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
         <v>25</v>
@@ -1620,7 +1620,7 @@
         <v>65</v>
       </c>
       <c r="AI6" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
         <v>980</v>
@@ -1629,28 +1629,28 @@
         <v>980</v>
       </c>
       <c r="AL6" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>980</v>
       </c>
       <c r="AO6" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
         <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT6" t="n">
         <v>6.4</v>
@@ -1659,44 +1659,44 @@
         <v>6.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6.2</v>
+        <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="BD6" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BF6" t="n">
-        <v>22</v>
+        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
@@ -1763,10 +1763,10 @@
         <v>1.9</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T7" t="n">
         <v>2.16</v>
@@ -1775,25 +1775,25 @@
         <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="X7" t="n">
         <v>15.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA7" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
         <v>11</v>
@@ -1802,7 +1802,7 @@
         <v>38</v>
       </c>
       <c r="AE7" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF7" t="n">
         <v>7.6</v>
@@ -1814,10 +1814,10 @@
         <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>170</v>
+        <v>520</v>
       </c>
       <c r="AJ7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK7" t="n">
         <v>16.5</v>
@@ -1826,13 +1826,13 @@
         <v>44</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AP7" t="n">
         <v>13.5</v>
@@ -1841,10 +1841,10 @@
         <v>24</v>
       </c>
       <c r="AR7" t="n">
-        <v>12.5</v>
+        <v>48</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT7" t="n">
         <v>6.6</v>
@@ -1856,7 +1856,7 @@
         <v>32</v>
       </c>
       <c r="AW7" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AX7" t="n">
         <v>7</v>
@@ -1868,7 +1868,7 @@
         <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.5</v>
+        <v>19</v>
       </c>
       <c r="BB7" t="n">
         <v>10.5</v>
@@ -1877,20 +1877,20 @@
         <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BF7" t="n">
         <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>15.5</v>
       </c>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="J8" t="n">
         <v>5.3</v>
@@ -1951,7 +1951,7 @@
         <v>1.35</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
         <v>1.94</v>
@@ -1963,10 +1963,10 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
@@ -1975,116 +1975,116 @@
         <v>4</v>
       </c>
       <c r="X8" t="n">
-        <v>18.5</v>
+        <v>980</v>
       </c>
       <c r="Y8" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="Z8" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.8</v>
+        <v>980</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.5</v>
+        <v>980</v>
       </c>
       <c r="AD8" t="n">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AE8" t="n">
-        <v>490</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>6.8</v>
+        <v>980</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>980</v>
       </c>
       <c r="AH8" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AI8" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11.5</v>
+        <v>980</v>
       </c>
       <c r="AK8" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="AL8" t="n">
-        <v>160</v>
+        <v>260</v>
       </c>
       <c r="AM8" t="n">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>15.5</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AS8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AT8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>11</v>
-      </c>
       <c r="AV8" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>36</v>
+        <v>1.79</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.8</v>
+        <v>1.79</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>1.82</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.8</v>
+        <v>2.18</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>3.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K9" t="n">
         <v>3.25</v>
@@ -2145,7 +2145,7 @@
         <v>1.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
         <v>2.58</v>
@@ -2169,37 +2169,37 @@
         <v>1.65</v>
       </c>
       <c r="X9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="n">
         <v>10.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>19.5</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG9" t="n">
         <v>12.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2208,7 +2208,7 @@
         <v>38</v>
       </c>
       <c r="AK9" t="n">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
@@ -2232,7 +2232,7 @@
         <v>21</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT9" t="n">
         <v>6.6</v>
@@ -2241,10 +2241,10 @@
         <v>6.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AW9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX9" t="n">
         <v>12</v>
@@ -2256,29 +2256,29 @@
         <v>11.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
         <v>3.6</v>
@@ -2357,7 +2357,7 @@
         <v>1.98</v>
       </c>
       <c r="V10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W10" t="n">
         <v>1.4</v>
@@ -2366,52 +2366,52 @@
         <v>12.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AB10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE10" t="n">
         <v>32</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL10" t="n">
         <v>60</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>65</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO10" t="n">
         <v>32</v>
@@ -2423,10 +2423,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
@@ -2438,41 +2438,41 @@
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>21</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G11" t="n">
         <v>2.14</v>
@@ -2512,16 +2512,16 @@
         <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -2533,7 +2533,7 @@
         <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
         <v>1.94</v>
@@ -2557,13 +2557,13 @@
         <v>1.87</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y11" t="n">
         <v>16.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2575,10 +2575,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF11" t="n">
         <v>13.5</v>
@@ -2587,7 +2587,7 @@
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2596,16 +2596,16 @@
         <v>25</v>
       </c>
       <c r="AK11" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2614,28 +2614,28 @@
         <v>11.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
         <v>8.800000000000001</v>
@@ -2644,7 +2644,7 @@
         <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
@@ -2653,20 +2653,20 @@
         <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H12" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I12" t="n">
         <v>5.7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.75</v>
@@ -2733,19 +2733,19 @@
         <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S12" t="n">
         <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W12" t="n">
         <v>2.26</v>
@@ -2769,10 +2769,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF12" t="n">
         <v>9.199999999999999</v>
@@ -2781,13 +2781,13 @@
         <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
@@ -2796,10 +2796,10 @@
         <v>46</v>
       </c>
       <c r="AM12" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO12" t="n">
         <v>130</v>
@@ -2826,13 +2826,13 @@
         <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AX12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>22</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
         <v>3.3</v>
@@ -2918,13 +2918,13 @@
         <v>3.35</v>
       </c>
       <c r="O13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
         <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R13" t="n">
         <v>1.3</v>
@@ -2942,82 +2942,82 @@
         <v>1.43</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>340</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC13" t="n">
         <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="AF13" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AK13" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
         <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
         <v>34</v>
@@ -3026,35 +3026,35 @@
         <v>14</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BB13" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="BC13" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BD13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BF13" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3085,49 +3085,49 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="I14" t="n">
         <v>1.48</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M14" t="n">
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O14" t="n">
         <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
         <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
         <v>1.78</v>
@@ -3136,10 +3136,10 @@
         <v>3.1</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y14" t="n">
         <v>7.6</v>
@@ -3151,7 +3151,7 @@
         <v>12.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AC14" t="n">
         <v>11</v>
@@ -3160,22 +3160,22 @@
         <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AG14" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AI14" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ14" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AK14" t="n">
         <v>160</v>
@@ -3184,13 +3184,13 @@
         <v>180</v>
       </c>
       <c r="AM14" t="n">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="AN14" t="n">
         <v>250</v>
       </c>
       <c r="AO14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP14" t="n">
         <v>14</v>
@@ -3199,13 +3199,13 @@
         <v>6.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU14" t="n">
         <v>9.800000000000001</v>
@@ -3217,38 +3217,38 @@
         <v>14.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ14" t="n">
         <v>24</v>
       </c>
       <c r="BA14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BB14" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD14" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE14" t="n">
         <v>15.5</v>
       </c>
-      <c r="BE14" t="n">
-        <v>28</v>
-      </c>
       <c r="BF14" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>1.54</v>
       </c>
       <c r="G15" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="H15" t="n">
         <v>6</v>
@@ -3309,10 +3309,10 @@
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
         <v>1.47</v>
@@ -3324,13 +3324,13 @@
         <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W15" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="X15" t="n">
         <v>22</v>
@@ -3387,13 +3387,13 @@
         <v>120</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS15" t="n">
         <v>5</v>
@@ -3420,7 +3420,7 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
         <v>12.5</v>
@@ -3429,20 +3429,20 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
         <v>3.7</v>
@@ -3503,16 +3503,16 @@
         <v>1.26</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R16" t="n">
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T16" t="n">
         <v>1.66</v>
@@ -3521,22 +3521,22 @@
         <v>2.28</v>
       </c>
       <c r="V16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="X16" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="Y16" t="n">
         <v>16.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AA16" t="n">
-        <v>70</v>
+        <v>900</v>
       </c>
       <c r="AB16" t="n">
         <v>11.5</v>
@@ -3545,13 +3545,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="AE16" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
         <v>11.5</v>
@@ -3563,19 +3563,19 @@
         <v>980</v>
       </c>
       <c r="AJ16" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>980</v>
+        <v>200</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO16" t="n">
         <v>980</v>
@@ -3584,43 +3584,43 @@
         <v>15</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>30</v>
+        <v>7.6</v>
       </c>
       <c r="AX16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>7.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="n">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>7.4</v>
@@ -3629,14 +3629,14 @@
         <v>8.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N17" t="n">
         <v>5.4</v>
@@ -3703,16 +3703,16 @@
         <v>1.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="T17" t="n">
         <v>1.65</v>
       </c>
       <c r="U17" t="n">
-        <v>2.32</v>
+        <v>1.05</v>
       </c>
       <c r="V17" t="n">
         <v>2.24</v>
@@ -3721,58 +3721,58 @@
         <v>1.23</v>
       </c>
       <c r="X17" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AC17" t="n">
         <v>11.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AG17" t="n">
         <v>21</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI17" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AJ17" t="n">
+        <v>700</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>320</v>
+      </c>
+      <c r="AL17" t="n">
         <v>130</v>
       </c>
-      <c r="AK17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>250</v>
-      </c>
       <c r="AM17" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN17" t="n">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AP17" t="n">
         <v>21</v>
@@ -3781,10 +3781,10 @@
         <v>10.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AT17" t="n">
         <v>20</v>
@@ -3796,41 +3796,41 @@
         <v>9</v>
       </c>
       <c r="AW17" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY17" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BG17" t="n">
         <v>6.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="G18" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="H18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.9</v>
       </c>
-      <c r="I18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>4</v>
-      </c>
       <c r="K18" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.25</v>
@@ -3909,122 +3909,122 @@
         <v>2.46</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W18" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="X18" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL18" t="n">
         <v>28</v>
       </c>
-      <c r="Y18" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL18" t="n">
+      <c r="AM18" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO18" t="n">
         <v>32</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>34</v>
       </c>
       <c r="AP18" t="n">
         <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.8</v>
+        <v>16</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.9</v>
+        <v>9.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BB18" t="n">
         <v>18.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>2.64</v>
       </c>
       <c r="I19" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="J19" t="n">
         <v>3.5</v>
@@ -4073,7 +4073,7 @@
         <v>3.85</v>
       </c>
       <c r="L19" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
         <v>1.05</v>
@@ -4088,137 +4088,137 @@
         <v>2.08</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
         <v>2.96</v>
       </c>
       <c r="T19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U19" t="n">
         <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X19" t="n">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="Y19" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AA19" t="n">
         <v>900</v>
       </c>
       <c r="AB19" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="AF19" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AG19" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="n">
         <v>980</v>
       </c>
       <c r="AJ19" t="n">
-        <v>900</v>
+        <v>240</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AL19" t="n">
-        <v>95</v>
+        <v>980</v>
       </c>
       <c r="AM19" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN19" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AX19" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AY19" t="n">
         <v>7</v>
       </c>
       <c r="AZ19" t="n">
-        <v>12</v>
+        <v>8.4</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.8</v>
+        <v>9.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="BF19" t="n">
-        <v>14</v>
+        <v>4.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4249,49 +4249,49 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G20" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J20" t="n">
         <v>4.3</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R20" t="n">
         <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U20" t="n">
         <v>1.98</v>
@@ -4300,73 +4300,73 @@
         <v>1.16</v>
       </c>
       <c r="W20" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X20" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="Z20" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AA20" t="n">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB20" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD20" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="AE20" t="n">
-        <v>510</v>
+        <v>700</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
         <v>230</v>
       </c>
       <c r="AJ20" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AL20" t="n">
         <v>85</v>
       </c>
       <c r="AM20" t="n">
-        <v>430</v>
+        <v>700</v>
       </c>
       <c r="AN20" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AO20" t="n">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AP20" t="n">
         <v>15</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR20" t="n">
         <v>20</v>
       </c>
       <c r="AS20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AT20" t="n">
         <v>8</v>
@@ -4375,44 +4375,44 @@
         <v>8.6</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AW20" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AY20" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="BE20" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>3.4</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I21" t="n">
         <v>2.58</v>
@@ -4458,7 +4458,7 @@
         <v>3.25</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4470,13 +4470,13 @@
         <v>3.35</v>
       </c>
       <c r="O21" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
         <v>1.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R21" t="n">
         <v>1.3</v>
@@ -4485,7 +4485,7 @@
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
         <v>2.08</v>
@@ -4509,7 +4509,7 @@
         <v>38</v>
       </c>
       <c r="AB21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC21" t="n">
         <v>7.4</v>
@@ -4521,7 +4521,7 @@
         <v>30</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
         <v>14.5</v>
@@ -4530,7 +4530,7 @@
         <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AJ21" t="n">
         <v>60</v>
@@ -4539,28 +4539,28 @@
         <v>42</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM21" t="n">
         <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>8.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -4572,25 +4572,25 @@
         <v>10.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX21" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB21" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="BD21" t="n">
         <v>23</v>
@@ -4599,14 +4599,14 @@
         <v>29</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG21" t="n">
         <v>22</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>1.64</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
         <v>5.8</v>
@@ -4652,7 +4652,7 @@
         <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4682,10 +4682,10 @@
         <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V22" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W22" t="n">
         <v>2.56</v>
@@ -4697,7 +4697,7 @@
         <v>75</v>
       </c>
       <c r="Z22" t="n">
-        <v>350</v>
+        <v>55</v>
       </c>
       <c r="AA22" t="n">
         <v>140</v>
@@ -4706,10 +4706,10 @@
         <v>14.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE22" t="n">
         <v>320</v>
@@ -4721,10 +4721,10 @@
         <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI22" t="n">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AJ22" t="n">
         <v>17.5</v>
@@ -4736,46 +4736,46 @@
         <v>46</v>
       </c>
       <c r="AM22" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO22" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="AQ22" t="n">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU22" t="n">
         <v>10</v>
       </c>
       <c r="AV22" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW22" t="n">
         <v>23</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>23</v>
@@ -4790,17 +4790,17 @@
         <v>21</v>
       </c>
       <c r="BE22" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BF22" t="n">
         <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -4831,79 +4831,79 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G23" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K23" t="n">
         <v>3.05</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M23" t="n">
         <v>1.13</v>
       </c>
       <c r="N23" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="O23" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P23" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="V23" t="n">
         <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AA23" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>55</v>
@@ -4921,34 +4921,34 @@
         <v>85</v>
       </c>
       <c r="AJ23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK23" t="n">
         <v>40</v>
       </c>
-      <c r="AK23" t="n">
-        <v>38</v>
-      </c>
       <c r="AL23" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM23" t="n">
         <v>190</v>
       </c>
       <c r="AN23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AO23" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP23" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AR23" t="n">
         <v>19</v>
       </c>
       <c r="AS23" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>7.2</v>
@@ -4957,10 +4957,10 @@
         <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AX23" t="n">
         <v>13.5</v>
@@ -4969,32 +4969,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE23" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA23" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>13</v>
-      </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BG23" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
         <v>3.4</v>
@@ -5058,10 +5058,10 @@
         <v>2.44</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R24" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
         <v>2.62</v>
@@ -5079,13 +5079,13 @@
         <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AA24" t="n">
         <v>30</v>
@@ -5094,25 +5094,25 @@
         <v>18.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD24" t="n">
         <v>11.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AJ24" t="n">
         <v>60</v>
@@ -5127,7 +5127,7 @@
         <v>65</v>
       </c>
       <c r="AN24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO24" t="n">
         <v>12.5</v>
@@ -5145,7 +5145,7 @@
         <v>25</v>
       </c>
       <c r="AT24" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU24" t="n">
         <v>8.4</v>
@@ -5154,13 +5154,13 @@
         <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>18.5</v>
+        <v>10.5</v>
       </c>
       <c r="AX24" t="n">
         <v>23</v>
       </c>
       <c r="AY24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ24" t="n">
         <v>13.5</v>
@@ -5169,7 +5169,7 @@
         <v>25</v>
       </c>
       <c r="BB24" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BC24" t="n">
         <v>23</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5222,10 +5222,10 @@
         <v>2.14</v>
       </c>
       <c r="G25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H25" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="I25" t="n">
         <v>3.9</v>
@@ -5234,7 +5234,7 @@
         <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5243,22 +5243,22 @@
         <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O25" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P25" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q25" t="n">
         <v>1.98</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T25" t="n">
         <v>1.81</v>
@@ -5267,25 +5267,25 @@
         <v>2.1</v>
       </c>
       <c r="V25" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W25" t="n">
         <v>1.86</v>
       </c>
       <c r="X25" t="n">
-        <v>14.5</v>
+        <v>46</v>
       </c>
       <c r="Y25" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="Z25" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>8.4</v>
@@ -5297,70 +5297,70 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="AG25" t="n">
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK25" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AL25" t="n">
         <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>330</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
         <v>14.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
@@ -5375,14 +5375,14 @@
         <v>12</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="BG25" t="n">
         <v>10.5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G26" t="n">
         <v>2.36</v>
@@ -5425,7 +5425,7 @@
         <v>3.15</v>
       </c>
       <c r="J26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
         <v>4.2</v>
@@ -5437,28 +5437,28 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.14</v>
       </c>
       <c r="P26" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S26" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T26" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U26" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V26" t="n">
         <v>1.47</v>
@@ -5467,7 +5467,7 @@
         <v>1.73</v>
       </c>
       <c r="X26" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="Y26" t="n">
         <v>24</v>
@@ -5476,10 +5476,10 @@
         <v>29</v>
       </c>
       <c r="AA26" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>32</v>
+        <v>19.5</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -5488,49 +5488,49 @@
         <v>14.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>13.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AK26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>21</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AR26" t="n">
         <v>25</v>
       </c>
-      <c r="AM26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>24</v>
-      </c>
       <c r="AS26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT26" t="n">
         <v>17</v>
@@ -5539,44 +5539,44 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
         <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.1</v>
@@ -5655,49 +5655,49 @@
         <v>1.69</v>
       </c>
       <c r="V27" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z27" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE27" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AK27" t="n">
         <v>24</v>
@@ -5709,34 +5709,34 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS27" t="n">
         <v>9</v>
       </c>
-      <c r="AQ27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AT27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU27" t="n">
         <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX27" t="n">
         <v>7.8</v>
@@ -5745,32 +5745,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="BA27" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB27" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC27" t="n">
         <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G28" t="n">
         <v>2.72</v>
@@ -5819,7 +5819,7 @@
         <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
@@ -5834,7 +5834,7 @@
         <v>1.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R28" t="n">
         <v>1.27</v>
@@ -5843,7 +5843,7 @@
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U28" t="n">
         <v>2</v>
@@ -5855,85 +5855,85 @@
         <v>1.58</v>
       </c>
       <c r="X28" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y28" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z28" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA28" t="n">
-        <v>65</v>
+        <v>350</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG28" t="n">
         <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI28" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AK28" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM28" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO28" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AP28" t="n">
         <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="AT28" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX28" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
         <v>10.5</v>
@@ -5942,29 +5942,29 @@
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BC28" t="n">
         <v>14.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BG28" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G29" t="n">
         <v>1.77</v>
@@ -6004,7 +6004,7 @@
         <v>5.8</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="n">
         <v>3.65</v>
@@ -6043,61 +6043,61 @@
         <v>1.83</v>
       </c>
       <c r="V29" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W29" t="n">
         <v>2.3</v>
       </c>
       <c r="X29" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>18.5</v>
+        <v>32</v>
       </c>
       <c r="Z29" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AC29" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AE29" t="n">
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="AI29" t="n">
         <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
@@ -6106,13 +6106,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AT29" t="n">
         <v>6.4</v>
@@ -6121,10 +6121,10 @@
         <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="AX29" t="n">
         <v>8.4</v>
@@ -6133,32 +6133,32 @@
         <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.9</v>
+        <v>10.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BF29" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -6201,10 +6201,10 @@
         <v>3.75</v>
       </c>
       <c r="J30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.37</v>
@@ -6222,7 +6222,7 @@
         <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R30" t="n">
         <v>1.51</v>
@@ -6261,7 +6261,7 @@
         <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
         <v>36</v>
@@ -6273,7 +6273,7 @@
         <v>10.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI30" t="n">
         <v>42</v>
@@ -6294,7 +6294,7 @@
         <v>12.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP30" t="n">
         <v>17</v>
@@ -6306,7 +6306,7 @@
         <v>26</v>
       </c>
       <c r="AS30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6315,7 +6315,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW30" t="n">
         <v>32</v>
@@ -6324,7 +6324,7 @@
         <v>14</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ30" t="n">
         <v>14</v>
@@ -6342,7 +6342,7 @@
         <v>27</v>
       </c>
       <c r="BE30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF30" t="n">
         <v>11.5</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -6407,19 +6407,19 @@
         <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
         <v>1.39</v>
       </c>
       <c r="P31" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
         <v>2.18</v>
       </c>
       <c r="R31" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -6437,19 +6437,19 @@
         <v>1.6</v>
       </c>
       <c r="X31" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
         <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA31" t="n">
         <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
         <v>7.6</v>
@@ -6458,7 +6458,7 @@
         <v>15.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AF31" t="n">
         <v>16.5</v>
@@ -6467,31 +6467,31 @@
         <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK31" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN31" t="n">
         <v>32</v>
       </c>
-      <c r="AL31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>29</v>
-      </c>
       <c r="AO31" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AP31" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AQ31" t="n">
         <v>9.4</v>
@@ -6500,7 +6500,7 @@
         <v>18.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT31" t="n">
         <v>7.8</v>
@@ -6512,10 +6512,10 @@
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6533,20 +6533,20 @@
         <v>14.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BE31" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>23</v>
+        <v>7.2</v>
       </c>
       <c r="BG31" t="n">
-        <v>34</v>
+        <v>7.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>3.45</v>
       </c>
       <c r="G32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H32" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="J32" t="n">
         <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>1.36</v>
@@ -6604,13 +6604,13 @@
         <v>4.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P32" t="n">
         <v>2.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R32" t="n">
         <v>1.47</v>
@@ -6625,13 +6625,13 @@
         <v>2.38</v>
       </c>
       <c r="V32" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="W32" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y32" t="n">
         <v>12</v>
@@ -6658,7 +6658,7 @@
         <v>26</v>
       </c>
       <c r="AG32" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH32" t="n">
         <v>16</v>
@@ -6673,13 +6673,13 @@
         <v>36</v>
       </c>
       <c r="AL32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM32" t="n">
         <v>75</v>
       </c>
       <c r="AN32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO32" t="n">
         <v>14.5</v>
@@ -6697,7 +6697,7 @@
         <v>25</v>
       </c>
       <c r="AT32" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU32" t="n">
         <v>7.8</v>
@@ -6706,10 +6706,10 @@
         <v>10</v>
       </c>
       <c r="AW32" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX32" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY32" t="n">
         <v>13</v>
@@ -6730,7 +6730,7 @@
         <v>38</v>
       </c>
       <c r="BE32" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BF32" t="n">
         <v>27</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -6774,19 +6774,19 @@
         <v>5.6</v>
       </c>
       <c r="G33" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H33" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I33" t="n">
         <v>1.7</v>
       </c>
-      <c r="I33" t="n">
-        <v>1.71</v>
-      </c>
       <c r="J33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L33" t="n">
         <v>1.43</v>
@@ -6816,19 +6816,19 @@
         <v>1.99</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V33" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
         <v>9.4</v>
@@ -6840,7 +6840,7 @@
         <v>18</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD33" t="n">
         <v>9.800000000000001</v>
@@ -6870,10 +6870,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO33" t="n">
         <v>10.5</v>
@@ -6891,16 +6891,16 @@
         <v>16</v>
       </c>
       <c r="AT33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV33" t="n">
         <v>9.4</v>
       </c>
       <c r="AW33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AX33" t="n">
         <v>38</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G34" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H34" t="n">
         <v>2.54</v>
@@ -6998,7 +6998,7 @@
         <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R34" t="n">
         <v>1.51</v>
@@ -7007,7 +7007,7 @@
         <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U34" t="n">
         <v>2.52</v>
@@ -7016,22 +7016,22 @@
         <v>1.64</v>
       </c>
       <c r="W34" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X34" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Y34" t="n">
         <v>13.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA34" t="n">
         <v>36</v>
       </c>
       <c r="AB34" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC34" t="n">
         <v>8.199999999999999</v>
@@ -7040,7 +7040,7 @@
         <v>11.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AF34" t="n">
         <v>21</v>
@@ -7055,7 +7055,7 @@
         <v>32</v>
       </c>
       <c r="AJ34" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK34" t="n">
         <v>28</v>
@@ -7070,7 +7070,7 @@
         <v>22</v>
       </c>
       <c r="AO34" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP34" t="n">
         <v>17.5</v>
@@ -7079,10 +7079,10 @@
         <v>12.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT34" t="n">
         <v>14</v>
@@ -7109,10 +7109,10 @@
         <v>30</v>
       </c>
       <c r="BB34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC34" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD34" t="n">
         <v>32</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -7177,31 +7177,31 @@
         <v>5.5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M35" t="n">
         <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="O35" t="n">
         <v>1.22</v>
       </c>
       <c r="P35" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="R35" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S35" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T35" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U35" t="n">
         <v>2.06</v>
@@ -7222,10 +7222,10 @@
         <v>75</v>
       </c>
       <c r="AA35" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC35" t="n">
         <v>11.5</v>
@@ -7237,16 +7237,16 @@
         <v>120</v>
       </c>
       <c r="AF35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI35" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ35" t="n">
         <v>12</v>
@@ -7261,10 +7261,10 @@
         <v>120</v>
       </c>
       <c r="AN35" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AO35" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AP35" t="n">
         <v>22</v>
@@ -7273,13 +7273,13 @@
         <v>29</v>
       </c>
       <c r="AR35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS35" t="n">
         <v>60</v>
       </c>
-      <c r="AS35" t="n">
-        <v>100</v>
-      </c>
       <c r="AT35" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU35" t="n">
         <v>10.5</v>
@@ -7288,19 +7288,19 @@
         <v>29</v>
       </c>
       <c r="AW35" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="AX35" t="n">
         <v>8.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA35" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BB35" t="n">
         <v>11.5</v>
@@ -7309,20 +7309,20 @@
         <v>13</v>
       </c>
       <c r="BD35" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE35" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG35" t="n">
         <v>100</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G36" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="H36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I36" t="n">
         <v>4.3</v>
@@ -7377,7 +7377,7 @@
         <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O36" t="n">
         <v>1.47</v>
@@ -7392,49 +7392,49 @@
         <v>1.21</v>
       </c>
       <c r="S36" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="V36" t="n">
         <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X36" t="n">
         <v>11</v>
       </c>
       <c r="Y36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z36" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE36" t="n">
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="AF36" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG36" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH36" t="n">
         <v>23</v>
@@ -7458,19 +7458,19 @@
         <v>32</v>
       </c>
       <c r="AO36" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP36" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AS36" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT36" t="n">
         <v>6.6</v>
@@ -7482,10 +7482,10 @@
         <v>14</v>
       </c>
       <c r="AW36" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX36" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY36" t="n">
         <v>9.800000000000001</v>
@@ -7494,7 +7494,7 @@
         <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB36" t="n">
         <v>11.5</v>
@@ -7503,20 +7503,20 @@
         <v>13</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE36" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BF36" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -7556,10 +7556,10 @@
         <v>4.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J37" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K37" t="n">
         <v>4.2</v>
@@ -7568,7 +7568,7 @@
         <v>1.24</v>
       </c>
       <c r="M37" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N37" t="n">
         <v>5.2</v>
@@ -7577,22 +7577,22 @@
         <v>1.19</v>
       </c>
       <c r="P37" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S37" t="n">
         <v>2.42</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.4</v>
       </c>
       <c r="T37" t="n">
         <v>1.56</v>
       </c>
       <c r="U37" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="V37" t="n">
         <v>1.27</v>
@@ -7613,22 +7613,22 @@
         <v>900</v>
       </c>
       <c r="AB37" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AC37" t="n">
         <v>9.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AE37" t="n">
         <v>980</v>
       </c>
       <c r="AF37" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="AG37" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="AH37" t="n">
         <v>15</v>
@@ -7637,7 +7637,7 @@
         <v>980</v>
       </c>
       <c r="AJ37" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AK37" t="n">
         <v>65</v>
@@ -7646,10 +7646,10 @@
         <v>980</v>
       </c>
       <c r="AM37" t="n">
-        <v>250</v>
+        <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO37" t="n">
         <v>980</v>
@@ -7661,10 +7661,10 @@
         <v>6.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AT37" t="n">
         <v>7.6</v>
@@ -7676,10 +7676,10 @@
         <v>8.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX37" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AY37" t="n">
         <v>5.8</v>
@@ -7691,26 +7691,26 @@
         <v>7.6</v>
       </c>
       <c r="BB37" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="BC37" t="n">
         <v>9</v>
       </c>
       <c r="BD37" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BE37" t="n">
         <v>7.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="BG37" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="G38" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H38" t="n">
         <v>1.99</v>
@@ -7756,34 +7756,34 @@
         <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L38" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
         <v>1.13</v>
       </c>
       <c r="N38" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O38" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P38" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R38" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S38" t="n">
         <v>4.8</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U38" t="n">
         <v>1.71</v>
@@ -7795,28 +7795,28 @@
         <v>1.22</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y38" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z38" t="n">
         <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB38" t="n">
         <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AD38" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.59</v>
+        <v>5.1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.76</v>
+        <v>6.2</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.48</v>
+        <v>7.8</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.76</v>
+        <v>6.4</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.79</v>
+        <v>4.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.54</v>
+        <v>6.4</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.47</v>
+        <v>7.4</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.49</v>
+        <v>8.6</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.47</v>
+        <v>7.4</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.52</v>
+        <v>1.83</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.48</v>
+        <v>2.52</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -7941,10 +7941,10 @@
         <v>7.6</v>
       </c>
       <c r="H39" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I39" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J39" t="n">
         <v>4.8</v>
@@ -7959,7 +7959,7 @@
         <v>1.04</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="O39" t="n">
         <v>1.19</v>
@@ -7968,28 +7968,28 @@
         <v>2.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R39" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S39" t="n">
         <v>2.46</v>
       </c>
       <c r="T39" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U39" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V39" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="W39" t="n">
         <v>1.15</v>
       </c>
       <c r="X39" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="Y39" t="n">
         <v>11.5</v>
@@ -8001,7 +8001,7 @@
         <v>14.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC39" t="n">
         <v>11.5</v>
@@ -8016,13 +8016,13 @@
         <v>65</v>
       </c>
       <c r="AG39" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH39" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ39" t="n">
         <v>240</v>
@@ -8031,25 +8031,25 @@
         <v>90</v>
       </c>
       <c r="AL39" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM39" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN39" t="n">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AO39" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AP39" t="n">
         <v>21</v>
       </c>
       <c r="AQ39" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR39" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AS39" t="n">
         <v>12.5</v>
@@ -8070,19 +8070,19 @@
         <v>23</v>
       </c>
       <c r="AY39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ39" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB39" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BD39" t="n">
         <v>28</v>
@@ -8094,11 +8094,11 @@
         <v>70</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
         <v>3.9</v>
       </c>
       <c r="L40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M40" t="n">
         <v>1.04</v>
@@ -8162,16 +8162,16 @@
         <v>2.66</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R40" t="n">
         <v>1.67</v>
       </c>
       <c r="S40" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="T40" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U40" t="n">
         <v>2.84</v>
@@ -8216,7 +8216,7 @@
         <v>13</v>
       </c>
       <c r="AI40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ40" t="n">
         <v>40</v>
@@ -8246,13 +8246,13 @@
         <v>19.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT40" t="n">
         <v>17</v>
       </c>
       <c r="AU40" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV40" t="n">
         <v>11</v>
@@ -8270,7 +8270,7 @@
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB40" t="n">
         <v>36</v>
@@ -8279,7 +8279,7 @@
         <v>23</v>
       </c>
       <c r="BD40" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE40" t="n">
         <v>44</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -8323,82 +8323,82 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="G41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H41" t="n">
         <v>2.16</v>
       </c>
       <c r="I41" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="J41" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="O41" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P41" t="n">
         <v>1.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="R41" t="n">
         <v>1.22</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T41" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="U41" t="n">
         <v>1.84</v>
       </c>
       <c r="V41" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="W41" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X41" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB41" t="n">
         <v>12</v>
       </c>
-      <c r="Y41" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AC41" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE41" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF41" t="n">
         <v>28</v>
@@ -8407,86 +8407,86 @@
         <v>17.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI41" t="n">
         <v>55</v>
       </c>
       <c r="AJ41" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL41" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AM41" t="n">
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AP41" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ41" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU41" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS41" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AV41" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW41" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AX41" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>4.5</v>
+        <v>14</v>
       </c>
       <c r="AZ41" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="BA41" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BC41" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="BD41" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BE41" t="n">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="BG41" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G42" t="n">
         <v>1.93</v>
       </c>
       <c r="H42" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I42" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J42" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="K42" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8565,16 +8565,16 @@
         <v>1.74</v>
       </c>
       <c r="V42" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W42" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X42" t="n">
         <v>11</v>
       </c>
       <c r="Y42" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z42" t="n">
         <v>55</v>
@@ -8583,25 +8583,25 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC42" t="n">
         <v>8.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE42" t="n">
         <v>1000</v>
       </c>
       <c r="AF42" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG42" t="n">
         <v>12.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI42" t="n">
         <v>1000</v>
@@ -8613,13 +8613,13 @@
         <v>27</v>
       </c>
       <c r="AL42" t="n">
-        <v>60</v>
+        <v>460</v>
       </c>
       <c r="AM42" t="n">
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AO42" t="n">
         <v>1000</v>
@@ -8628,13 +8628,13 @@
         <v>9</v>
       </c>
       <c r="AQ42" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AR42" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AS42" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT42" t="n">
         <v>5.8</v>
@@ -8643,22 +8643,22 @@
         <v>7</v>
       </c>
       <c r="AV42" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AX42" t="n">
         <v>8.4</v>
       </c>
       <c r="AY42" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ42" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA42" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BB42" t="n">
         <v>17</v>
@@ -8667,20 +8667,20 @@
         <v>19.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF42" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="G43" t="n">
         <v>2.88</v>
@@ -8720,10 +8720,10 @@
         <v>3.05</v>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J43" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="K43" t="n">
         <v>3.1</v>
@@ -8735,19 +8735,19 @@
         <v>1.14</v>
       </c>
       <c r="N43" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O43" t="n">
         <v>1.63</v>
       </c>
       <c r="P43" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Q43" t="n">
         <v>2.88</v>
       </c>
       <c r="R43" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S43" t="n">
         <v>6.4</v>
@@ -8768,43 +8768,43 @@
         <v>7.8</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z43" t="n">
         <v>19.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>270</v>
+        <v>300</v>
       </c>
       <c r="AB43" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD43" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AF43" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AG43" t="n">
         <v>14.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI43" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ43" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AK43" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AL43" t="n">
         <v>85</v>
@@ -8813,10 +8813,10 @@
         <v>260</v>
       </c>
       <c r="AN43" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AO43" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP43" t="n">
         <v>6.8</v>
@@ -8825,10 +8825,10 @@
         <v>7.4</v>
       </c>
       <c r="AR43" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS43" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AT43" t="n">
         <v>6.8</v>
@@ -8843,7 +8843,7 @@
         <v>27</v>
       </c>
       <c r="AX43" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY43" t="n">
         <v>12.5</v>
@@ -8852,13 +8852,13 @@
         <v>21</v>
       </c>
       <c r="BA43" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB43" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BC43" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BD43" t="n">
         <v>36</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -8905,31 +8905,31 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G44" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H44" t="n">
         <v>7</v>
       </c>
       <c r="I44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J44" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L44" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M44" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N44" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O44" t="n">
         <v>1.28</v>
@@ -8947,16 +8947,16 @@
         <v>3.05</v>
       </c>
       <c r="T44" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U44" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W44" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="X44" t="n">
         <v>22</v>
@@ -8965,13 +8965,13 @@
         <v>980</v>
       </c>
       <c r="Z44" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA44" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AB44" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC44" t="n">
         <v>10.5</v>
@@ -8986,10 +8986,10 @@
         <v>10.5</v>
       </c>
       <c r="AG44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AH44" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI44" t="n">
         <v>110</v>
@@ -9007,58 +9007,58 @@
         <v>140</v>
       </c>
       <c r="AN44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR44" t="n">
         <v>8.4</v>
       </c>
-      <c r="AO44" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AS44" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT44" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU44" t="n">
         <v>9</v>
       </c>
       <c r="AV44" t="n">
-        <v>21</v>
+        <v>7.2</v>
       </c>
       <c r="AW44" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX44" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY44" t="n">
         <v>8.6</v>
       </c>
       <c r="AZ44" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB44" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF44" t="n">
         <v>7.2</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K45" t="n">
         <v>4.2</v>
@@ -9156,22 +9156,22 @@
         <v>13.5</v>
       </c>
       <c r="Y45" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z45" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA45" t="n">
         <v>340</v>
       </c>
       <c r="AB45" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC45" t="n">
         <v>11</v>
       </c>
       <c r="AD45" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE45" t="n">
         <v>190</v>
@@ -9180,58 +9180,58 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG45" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AI45" t="n">
         <v>190</v>
       </c>
       <c r="AJ45" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK45" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AL45" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM45" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AN45" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO45" t="n">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AP45" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ45" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AR45" t="n">
-        <v>50</v>
+        <v>4.7</v>
       </c>
       <c r="AS45" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AT45" t="n">
         <v>5.7</v>
       </c>
       <c r="AU45" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV45" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AW45" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX45" t="n">
         <v>7</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>7.4</v>
       </c>
       <c r="AY45" t="n">
         <v>9.4</v>
@@ -9240,29 +9240,29 @@
         <v>22</v>
       </c>
       <c r="BA45" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BB45" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC45" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE45" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BF45" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG45" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>
@@ -9293,25 +9293,25 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="G46" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H46" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="I46" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="J46" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="L46" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
         <v>1.07</v>
@@ -9320,67 +9320,67 @@
         <v>3.8</v>
       </c>
       <c r="O46" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P46" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R46" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S46" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T46" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U46" t="n">
         <v>2.1</v>
       </c>
       <c r="V46" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="W46" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X46" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AA46" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB46" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD46" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE46" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AF46" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AG46" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH46" t="n">
         <v>22</v>
       </c>
       <c r="AI46" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AJ46" t="n">
         <v>110</v>
@@ -9398,65 +9398,65 @@
         <v>60</v>
       </c>
       <c r="AO46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ46" t="n">
         <v>8.4</v>
       </c>
       <c r="AR46" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS46" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT46" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU46" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV46" t="n">
         <v>9.4</v>
       </c>
       <c r="AW46" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX46" t="n">
-        <v>5.7</v>
+        <v>27</v>
       </c>
       <c r="AY46" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA46" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB46" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BC46" t="n">
-        <v>6.2</v>
+        <v>44</v>
       </c>
       <c r="BD46" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BE46" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BF46" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BG46" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-03 20:20:12</t>
+          <t>2026-03-03 22:27:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:00:00</t>
+          <t>00:02:03</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
         <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>2.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.63</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.89</v>
+        <v>2.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>2.56</v>
       </c>
       <c r="U2" t="n">
-        <v>2.08</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="X2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>140</v>
+      </c>
+      <c r="BB2" t="n">
         <v>17</v>
       </c>
-      <c r="Y2" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="BC2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>300</v>
+      </c>
+      <c r="BF2" t="n">
         <v>22</v>
       </c>
-      <c r="AE2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>30</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG2" t="n">
-        <v>18.5</v>
+        <v>190</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>00:10:00</t>
+          <t>00:13:03</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I3" t="n">
         <v>2.04</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="M3" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4</v>
+        <v>1.85</v>
       </c>
       <c r="V3" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AH3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AJ3" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AK3" t="n">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AO3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AP3" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
         <v>20</v>
       </c>
       <c r="AT3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AU3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW3" t="n">
+      <c r="AZ3" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>85</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>80</v>
+      </c>
+      <c r="BG3" t="n">
         <v>18</v>
       </c>
-      <c r="AX3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>65</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>40</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>11</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1145,40 +1145,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>1.2</v>
       </c>
       <c r="P4" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R4" t="n">
         <v>1.61</v>
@@ -1187,16 +1187,16 @@
         <v>2.54</v>
       </c>
       <c r="T4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="X4" t="n">
         <v>24</v>
@@ -1211,7 +1211,7 @@
         <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
@@ -1232,10 +1232,10 @@
         <v>18</v>
       </c>
       <c r="AI4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK4" t="n">
         <v>15</v>
@@ -1244,37 +1244,37 @@
         <v>26</v>
       </c>
       <c r="AM4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN4" t="n">
         <v>7.2</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP4" t="n">
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AX4" t="n">
         <v>11</v>
@@ -1283,32 +1283,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD4" t="n">
         <v>24</v>
       </c>
       <c r="BE4" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1345,52 +1345,52 @@
         <v>1.29</v>
       </c>
       <c r="H5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="K5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1.09</v>
       </c>
       <c r="P5" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="S5" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="T5" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V5" t="n">
         <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="X5" t="n">
         <v>150</v>
@@ -1414,7 +1414,7 @@
         <v>980</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF5" t="n">
         <v>980</v>
@@ -1426,7 +1426,7 @@
         <v>980</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AJ5" t="n">
         <v>980</v>
@@ -1438,13 +1438,13 @@
         <v>980</v>
       </c>
       <c r="AM5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AO5" t="n">
         <v>110</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>130</v>
       </c>
       <c r="AP5" t="n">
         <v>15.5</v>
@@ -1459,40 +1459,40 @@
         <v>4.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW5" t="n">
         <v>4.2</v>
       </c>
       <c r="AX5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB5" t="n">
         <v>5.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.71</v>
+        <v>9</v>
       </c>
       <c r="BF5" t="n">
         <v>2.66</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
         <v>3.75</v>
@@ -1545,13 +1545,13 @@
         <v>3.85</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.12</v>
@@ -1560,31 +1560,31 @@
         <v>2.56</v>
       </c>
       <c r="O6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q6" t="n">
         <v>2.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X6" t="n">
         <v>9.6</v>
@@ -1599,7 +1599,7 @@
         <v>500</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC6" t="n">
         <v>8</v>
@@ -1608,10 +1608,10 @@
         <v>29</v>
       </c>
       <c r="AE6" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>24</v>
@@ -1638,65 +1638,65 @@
         <v>980</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>7.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="BC6" t="n">
-        <v>24</v>
+        <v>8.6</v>
       </c>
       <c r="BD6" t="n">
         <v>8.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H7" t="n">
         <v>9.800000000000001</v>
@@ -1841,7 +1841,7 @@
         <v>24</v>
       </c>
       <c r="AR7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS7" t="n">
         <v>17.5</v>
@@ -1850,7 +1850,7 @@
         <v>6.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV7" t="n">
         <v>32</v>
@@ -1868,7 +1868,7 @@
         <v>26</v>
       </c>
       <c r="BA7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB7" t="n">
         <v>10.5</v>
@@ -1877,7 +1877,7 @@
         <v>14.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
         <v>28</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -1963,10 +1963,10 @@
         <v>3.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="V8" t="n">
         <v>1.05</v>
@@ -2032,7 +2032,7 @@
         <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="AR8" t="n">
         <v>4.2</v>
@@ -2059,7 +2059,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="BA8" t="n">
         <v>4.2</v>
@@ -2071,10 +2071,10 @@
         <v>9</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BF8" t="n">
         <v>2.18</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
         <v>110</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>7.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
         <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
@@ -2450,7 +2450,7 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>7.6</v>
@@ -2459,20 +2459,20 @@
         <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE10" t="n">
         <v>8</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
         <v>1.07</v>
@@ -2566,7 +2566,7 @@
         <v>80</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
         <v>9.800000000000001</v>
@@ -2602,7 +2602,7 @@
         <v>200</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
         <v>16.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.78</v>
       </c>
       <c r="G12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="n">
         <v>5.6</v>
@@ -2733,7 +2733,7 @@
         <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S12" t="n">
         <v>4.3</v>
@@ -2748,7 +2748,7 @@
         <v>1.21</v>
       </c>
       <c r="W12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X12" t="n">
         <v>11.5</v>
@@ -2757,10 +2757,10 @@
         <v>16</v>
       </c>
       <c r="Z12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB12" t="n">
         <v>7.2</v>
@@ -2772,7 +2772,7 @@
         <v>22</v>
       </c>
       <c r="AE12" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
         <v>9.199999999999999</v>
@@ -2793,7 +2793,7 @@
         <v>21</v>
       </c>
       <c r="AL12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM12" t="n">
         <v>160</v>
@@ -2802,7 +2802,7 @@
         <v>14.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP12" t="n">
         <v>10.5</v>
@@ -2841,13 +2841,13 @@
         <v>38</v>
       </c>
       <c r="BB12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE12" t="n">
         <v>85</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
         <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.43</v>
@@ -2921,7 +2921,7 @@
         <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
         <v>2.18</v>
@@ -2933,7 +2933,7 @@
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U13" t="n">
         <v>2.12</v>
@@ -2942,7 +2942,7 @@
         <v>1.43</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
         <v>11.5</v>
@@ -2966,7 +2966,7 @@
         <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>190</v>
+        <v>40</v>
       </c>
       <c r="AF13" t="n">
         <v>16.5</v>
@@ -2975,7 +2975,7 @@
         <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AI13" t="n">
         <v>55</v>
@@ -2993,10 +2993,10 @@
         <v>120</v>
       </c>
       <c r="AN13" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
         <v>10</v>
@@ -3005,10 +3005,10 @@
         <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3035,7 +3035,7 @@
         <v>23</v>
       </c>
       <c r="BB13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BC13" t="n">
         <v>24</v>
@@ -3047,14 +3047,14 @@
         <v>28</v>
       </c>
       <c r="BF13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="I14" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="J14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.38</v>
@@ -3124,19 +3124,19 @@
         <v>1.37</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T14" t="n">
         <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V14" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="W14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>16</v>
@@ -3145,13 +3145,13 @@
         <v>7.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AA14" t="n">
         <v>12.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AC14" t="n">
         <v>11</v>
@@ -3163,13 +3163,13 @@
         <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AG14" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI14" t="n">
         <v>42</v>
@@ -3178,16 +3178,16 @@
         <v>330</v>
       </c>
       <c r="AK14" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL14" t="n">
         <v>180</v>
       </c>
       <c r="AM14" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN14" t="n">
         <v>230</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>250</v>
       </c>
       <c r="AO14" t="n">
         <v>8.199999999999999</v>
@@ -3202,13 +3202,13 @@
         <v>7.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT14" t="n">
         <v>21</v>
       </c>
       <c r="AU14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV14" t="n">
         <v>9</v>
@@ -3220,7 +3220,7 @@
         <v>25</v>
       </c>
       <c r="AY14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ14" t="n">
         <v>24</v>
@@ -3229,26 +3229,26 @@
         <v>30</v>
       </c>
       <c r="BB14" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF14" t="n">
         <v>15</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>15</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>15.5</v>
       </c>
       <c r="BG14" t="n">
         <v>7.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3285,10 +3285,10 @@
         <v>1.61</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
         <v>4.4</v>
@@ -3303,28 +3303,28 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O15" t="n">
         <v>1.23</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S15" t="n">
         <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V15" t="n">
         <v>1.16</v>
@@ -3342,13 +3342,13 @@
         <v>60</v>
       </c>
       <c r="AA15" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB15" t="n">
         <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
         <v>30</v>
@@ -3366,7 +3366,7 @@
         <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>95</v>
+        <v>230</v>
       </c>
       <c r="AJ15" t="n">
         <v>18</v>
@@ -3381,10 +3381,10 @@
         <v>390</v>
       </c>
       <c r="AN15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AO15" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AP15" t="n">
         <v>18</v>
@@ -3393,13 +3393,13 @@
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU15" t="n">
         <v>9</v>
@@ -3408,7 +3408,7 @@
         <v>21</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
         <v>8.6</v>
@@ -3420,7 +3420,7 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB15" t="n">
         <v>12.5</v>
@@ -3429,20 +3429,20 @@
         <v>13</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BF15" t="n">
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>3.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -3512,7 +3512,7 @@
         <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T16" t="n">
         <v>1.66</v>
@@ -3587,7 +3587,7 @@
         <v>13</v>
       </c>
       <c r="AR16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS16" t="n">
         <v>8.199999999999999</v>
@@ -3617,13 +3617,13 @@
         <v>7.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE16" t="n">
         <v>8.4</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3799,7 +3799,7 @@
         <v>13.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY17" t="n">
         <v>16.5</v>
@@ -3808,7 +3808,7 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BB17" t="n">
         <v>8.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -3990,7 +3990,7 @@
         <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX18" t="n">
         <v>12.5</v>
@@ -4020,11 +4020,11 @@
         <v>7.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4055,49 +4055,49 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G19" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="H19" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I19" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
         <v>4.3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P19" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
         <v>2.24</v>
@@ -4106,13 +4106,13 @@
         <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Z19" t="n">
         <v>980</v>
@@ -4124,7 +4124,7 @@
         <v>980</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AD19" t="n">
         <v>26</v>
@@ -4163,16 +4163,16 @@
         <v>55</v>
       </c>
       <c r="AP19" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ19" t="n">
         <v>7.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
         <v>7.6</v>
@@ -4184,10 +4184,10 @@
         <v>7</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AY19" t="n">
         <v>7</v>
@@ -4199,13 +4199,13 @@
         <v>4.9</v>
       </c>
       <c r="BB19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
         <v>3.15</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
         <v>2.1</v>
@@ -4291,7 +4291,7 @@
         <v>3.1</v>
       </c>
       <c r="T20" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="U20" t="n">
         <v>1.98</v>
@@ -4306,7 +4306,7 @@
         <v>28</v>
       </c>
       <c r="Y20" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="Z20" t="n">
         <v>160</v>
@@ -4333,10 +4333,10 @@
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="AI20" t="n">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="AJ20" t="n">
         <v>29</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G21" t="n">
         <v>3.4</v>
@@ -4494,13 +4494,13 @@
         <v>1.63</v>
       </c>
       <c r="W21" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X21" t="n">
         <v>11.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z21" t="n">
         <v>16</v>
@@ -4521,7 +4521,7 @@
         <v>30</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG21" t="n">
         <v>14.5</v>
@@ -4530,7 +4530,7 @@
         <v>18.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AJ21" t="n">
         <v>60</v>
@@ -4548,19 +4548,19 @@
         <v>46</v>
       </c>
       <c r="AO21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP21" t="n">
         <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR21" t="n">
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT21" t="n">
         <v>10.5</v>
@@ -4578,7 +4578,7 @@
         <v>19</v>
       </c>
       <c r="AY21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ21" t="n">
         <v>16</v>
@@ -4599,14 +4599,14 @@
         <v>29</v>
       </c>
       <c r="BF21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BG21" t="n">
         <v>22</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
         <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,16 +4661,16 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P22" t="n">
         <v>2.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="R22" t="n">
         <v>1.72</v>
@@ -4682,25 +4682,25 @@
         <v>1.64</v>
       </c>
       <c r="U22" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V22" t="n">
         <v>1.2</v>
       </c>
       <c r="W22" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X22" t="n">
         <v>80</v>
       </c>
       <c r="Y22" t="n">
-        <v>75</v>
+        <v>980</v>
       </c>
       <c r="Z22" t="n">
         <v>55</v>
       </c>
       <c r="AA22" t="n">
-        <v>140</v>
+        <v>700</v>
       </c>
       <c r="AB22" t="n">
         <v>14.5</v>
@@ -4730,7 +4730,7 @@
         <v>17.5</v>
       </c>
       <c r="AK22" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL22" t="n">
         <v>46</v>
@@ -4739,22 +4739,22 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR22" t="n">
         <v>25</v>
       </c>
       <c r="AS22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT22" t="n">
         <v>12</v>
@@ -4796,11 +4796,11 @@
         <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -4837,13 +4837,13 @@
         <v>2.7</v>
       </c>
       <c r="H23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I23" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>3.05</v>
@@ -4852,7 +4852,7 @@
         <v>1.5</v>
       </c>
       <c r="M23" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N23" t="n">
         <v>2.68</v>
@@ -4972,10 +4972,10 @@
         <v>20</v>
       </c>
       <c r="BA23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB23" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="BC23" t="n">
         <v>32</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G24" t="n">
         <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I24" t="n">
         <v>2.28</v>
@@ -5070,7 +5070,7 @@
         <v>1.59</v>
       </c>
       <c r="U24" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="V24" t="n">
         <v>1.78</v>
@@ -5082,7 +5082,7 @@
         <v>21</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
         <v>30</v>
@@ -5094,7 +5094,7 @@
         <v>18.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>11.5</v>
@@ -5145,7 +5145,7 @@
         <v>25</v>
       </c>
       <c r="AT24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AU24" t="n">
         <v>8.4</v>
@@ -5154,7 +5154,7 @@
         <v>10</v>
       </c>
       <c r="AW24" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX24" t="n">
         <v>23</v>
@@ -5169,7 +5169,7 @@
         <v>25</v>
       </c>
       <c r="BB24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC24" t="n">
         <v>23</v>
@@ -5181,14 +5181,14 @@
         <v>32</v>
       </c>
       <c r="BF24" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG24" t="n">
         <v>10.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
         <v>1.81</v>
       </c>
       <c r="U25" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V25" t="n">
         <v>1.34</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.28</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H26" t="n">
         <v>2.98</v>
@@ -5446,13 +5446,13 @@
         <v>3.05</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R26" t="n">
         <v>1.85</v>
       </c>
       <c r="S26" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T26" t="n">
         <v>1.42</v>
@@ -5461,13 +5461,13 @@
         <v>3.15</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y26" t="n">
         <v>24</v>
@@ -5479,7 +5479,7 @@
         <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
         <v>11</v>
@@ -5494,7 +5494,7 @@
         <v>21</v>
       </c>
       <c r="AG26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
         <v>13.5</v>
@@ -5533,7 +5533,7 @@
         <v>36</v>
       </c>
       <c r="AT26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU26" t="n">
         <v>9.800000000000001</v>
@@ -5569,14 +5569,14 @@
         <v>28</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
         <v>12</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5619,7 +5619,7 @@
         <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
         <v>3.85</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5819,7 @@
         <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G29" t="n">
         <v>1.77</v>
@@ -6004,7 +6004,7 @@
         <v>5.8</v>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J29" t="n">
         <v>3.65</v>
@@ -6043,7 +6043,7 @@
         <v>1.83</v>
       </c>
       <c r="V29" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W29" t="n">
         <v>2.3</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -6219,13 +6219,13 @@
         <v>1.25</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R30" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S30" t="n">
         <v>2.88</v>
@@ -6243,7 +6243,7 @@
         <v>1.86</v>
       </c>
       <c r="X30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y30" t="n">
         <v>17</v>
@@ -6261,10 +6261,10 @@
         <v>8.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF30" t="n">
         <v>15</v>
@@ -6288,7 +6288,7 @@
         <v>29</v>
       </c>
       <c r="AM30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN30" t="n">
         <v>12.5</v>
@@ -6303,10 +6303,10 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -6694,7 +6694,7 @@
         <v>13.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT32" t="n">
         <v>14</v>
@@ -6715,10 +6715,10 @@
         <v>13</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB32" t="n">
         <v>50</v>
@@ -6733,14 +6733,14 @@
         <v>40</v>
       </c>
       <c r="BF32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BG32" t="n">
         <v>13</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="G33" t="n">
         <v>5.8</v>
@@ -6789,7 +6789,7 @@
         <v>4.3</v>
       </c>
       <c r="L33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M33" t="n">
         <v>1.07</v>
@@ -6798,7 +6798,7 @@
         <v>3.9</v>
       </c>
       <c r="O33" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P33" t="n">
         <v>1.99</v>
@@ -6813,7 +6813,7 @@
         <v>3.55</v>
       </c>
       <c r="T33" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U33" t="n">
         <v>1.99</v>
@@ -6825,7 +6825,7 @@
         <v>1.2</v>
       </c>
       <c r="X33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y33" t="n">
         <v>8</v>
@@ -6834,7 +6834,7 @@
         <v>9.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AB33" t="n">
         <v>18</v>
@@ -6849,7 +6849,7 @@
         <v>18</v>
       </c>
       <c r="AF33" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG33" t="n">
         <v>21</v>
@@ -6861,7 +6861,7 @@
         <v>36</v>
       </c>
       <c r="AJ33" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AK33" t="n">
         <v>80</v>
@@ -6888,7 +6888,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS33" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT33" t="n">
         <v>16.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="G34" t="n">
         <v>2.96</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.98</v>
       </c>
       <c r="H34" t="n">
         <v>2.54</v>
@@ -6983,7 +6983,7 @@
         <v>3.75</v>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="M34" t="n">
         <v>1.05</v>
@@ -7007,7 +7007,7 @@
         <v>2.9</v>
       </c>
       <c r="T34" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U34" t="n">
         <v>2.52</v>
@@ -7016,16 +7016,16 @@
         <v>1.64</v>
       </c>
       <c r="W34" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X34" t="n">
         <v>18</v>
       </c>
       <c r="Y34" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AA34" t="n">
         <v>36</v>
@@ -7094,7 +7094,7 @@
         <v>11</v>
       </c>
       <c r="AW34" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX34" t="n">
         <v>20</v>
@@ -7103,7 +7103,7 @@
         <v>12</v>
       </c>
       <c r="AZ34" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BA34" t="n">
         <v>30</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -7183,28 +7183,28 @@
         <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O35" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P35" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R35" t="n">
         <v>1.55</v>
       </c>
       <c r="S35" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T35" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U35" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
         <v>1.12</v>
@@ -7213,22 +7213,22 @@
         <v>3.3</v>
       </c>
       <c r="X35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y35" t="n">
         <v>32</v>
       </c>
       <c r="Z35" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AA35" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC35" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD35" t="n">
         <v>32</v>
@@ -7243,7 +7243,7 @@
         <v>9.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI35" t="n">
         <v>110</v>
@@ -7258,13 +7258,13 @@
         <v>32</v>
       </c>
       <c r="AM35" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN35" t="n">
         <v>5.8</v>
       </c>
       <c r="AO35" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP35" t="n">
         <v>22</v>
@@ -7273,16 +7273,16 @@
         <v>29</v>
       </c>
       <c r="AR35" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AS35" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AT35" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV35" t="n">
         <v>29</v>
@@ -7291,25 +7291,25 @@
         <v>95</v>
       </c>
       <c r="AX35" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ35" t="n">
         <v>23</v>
       </c>
       <c r="BA35" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BB35" t="n">
         <v>11.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE35" t="n">
         <v>85</v>
@@ -7318,11 +7318,11 @@
         <v>5.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -7509,14 +7509,14 @@
         <v>8</v>
       </c>
       <c r="BF36" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG36" t="n">
         <v>7.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G37" t="n">
         <v>1.98</v>
@@ -7568,10 +7568,10 @@
         <v>1.24</v>
       </c>
       <c r="M37" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N37" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O37" t="n">
         <v>1.19</v>
@@ -7583,7 +7583,7 @@
         <v>1.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S37" t="n">
         <v>2.42</v>
@@ -7592,7 +7592,7 @@
         <v>1.56</v>
       </c>
       <c r="U37" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="V37" t="n">
         <v>1.27</v>
@@ -7661,7 +7661,7 @@
         <v>6.6</v>
       </c>
       <c r="AR37" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS37" t="n">
         <v>7.2</v>
@@ -7676,7 +7676,7 @@
         <v>8.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX37" t="n">
         <v>12</v>
@@ -7688,29 +7688,29 @@
         <v>9</v>
       </c>
       <c r="BA37" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC37" t="n">
         <v>9</v>
       </c>
       <c r="BD37" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE37" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG37" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
         <v>120</v>
       </c>
       <c r="AE38" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AF38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="G39" t="n">
         <v>7.6</v>
@@ -7959,13 +7959,13 @@
         <v>1.04</v>
       </c>
       <c r="N39" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="O39" t="n">
         <v>1.19</v>
       </c>
       <c r="P39" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q39" t="n">
         <v>1.64</v>
@@ -7977,10 +7977,10 @@
         <v>2.46</v>
       </c>
       <c r="T39" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U39" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V39" t="n">
         <v>2.92</v>
@@ -7992,7 +7992,7 @@
         <v>23</v>
       </c>
       <c r="Y39" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z39" t="n">
         <v>10.5</v>
@@ -8001,7 +8001,7 @@
         <v>14.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AC39" t="n">
         <v>11.5</v>
@@ -8019,10 +8019,10 @@
         <v>26</v>
       </c>
       <c r="AH39" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI39" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AJ39" t="n">
         <v>240</v>
@@ -8037,10 +8037,10 @@
         <v>100</v>
       </c>
       <c r="AN39" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AO39" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AP39" t="n">
         <v>21</v>
@@ -8055,7 +8055,7 @@
         <v>12.5</v>
       </c>
       <c r="AT39" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU39" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
         <v>13</v>
       </c>
       <c r="AX39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY39" t="n">
         <v>23</v>
@@ -8079,13 +8079,13 @@
         <v>25</v>
       </c>
       <c r="BB39" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD39" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BE39" t="n">
         <v>48</v>
@@ -8094,11 +8094,11 @@
         <v>70</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
         <v>3.9</v>
       </c>
       <c r="L40" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M40" t="n">
         <v>1.04</v>
@@ -8162,10 +8162,10 @@
         <v>2.66</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R40" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S40" t="n">
         <v>2.44</v>
@@ -8183,7 +8183,7 @@
         <v>1.56</v>
       </c>
       <c r="X40" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y40" t="n">
         <v>17</v>
@@ -8216,7 +8216,7 @@
         <v>13</v>
       </c>
       <c r="AI40" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ40" t="n">
         <v>40</v>
@@ -8246,10 +8246,10 @@
         <v>19.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT40" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AU40" t="n">
         <v>9</v>
@@ -8270,10 +8270,10 @@
         <v>12.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB40" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC40" t="n">
         <v>23</v>
@@ -8285,14 +8285,14 @@
         <v>44</v>
       </c>
       <c r="BF40" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG40" t="n">
         <v>13</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G41" t="n">
         <v>4.3</v>
@@ -8332,7 +8332,7 @@
         <v>2.16</v>
       </c>
       <c r="I41" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -8341,13 +8341,13 @@
         <v>3.5</v>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M41" t="n">
         <v>1.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="O41" t="n">
         <v>1.45</v>
@@ -8374,13 +8374,13 @@
         <v>1.71</v>
       </c>
       <c r="W41" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X41" t="n">
         <v>10.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z41" t="n">
         <v>14</v>
@@ -8431,7 +8431,7 @@
         <v>28</v>
       </c>
       <c r="AP41" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ41" t="n">
         <v>6.8</v>
@@ -8464,29 +8464,29 @@
         <v>18</v>
       </c>
       <c r="BA41" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD41" t="n">
         <v>9</v>
       </c>
       <c r="BE41" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG41" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
         <v>2.08</v>
       </c>
       <c r="U42" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V42" t="n">
         <v>1.16</v>
@@ -8625,7 +8625,7 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ42" t="n">
         <v>13</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -8714,10 +8714,10 @@
         <v>2.8</v>
       </c>
       <c r="G43" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H43" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I43" t="n">
         <v>3.25</v>
@@ -8735,7 +8735,7 @@
         <v>1.14</v>
       </c>
       <c r="N43" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O43" t="n">
         <v>1.63</v>
@@ -8771,7 +8771,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="n">
         <v>300</v>
@@ -8780,7 +8780,7 @@
         <v>7.8</v>
       </c>
       <c r="AC43" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD43" t="n">
         <v>16.5</v>
@@ -8789,7 +8789,7 @@
         <v>200</v>
       </c>
       <c r="AF43" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AG43" t="n">
         <v>14.5</v>
@@ -8810,13 +8810,13 @@
         <v>85</v>
       </c>
       <c r="AM43" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN43" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AO43" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AP43" t="n">
         <v>6.8</v>
@@ -8846,7 +8846,7 @@
         <v>14</v>
       </c>
       <c r="AY43" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AZ43" t="n">
         <v>21</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -8905,10 +8905,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="G44" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H44" t="n">
         <v>7</v>
@@ -8917,16 +8917,16 @@
         <v>7.6</v>
       </c>
       <c r="J44" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K44" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L44" t="n">
         <v>1.33</v>
       </c>
       <c r="M44" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N44" t="n">
         <v>4.2</v>
@@ -8935,7 +8935,7 @@
         <v>1.28</v>
       </c>
       <c r="P44" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q44" t="n">
         <v>1.81</v>
@@ -8947,7 +8947,7 @@
         <v>3.05</v>
       </c>
       <c r="T44" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U44" t="n">
         <v>2</v>
@@ -8956,7 +8956,7 @@
         <v>1.15</v>
       </c>
       <c r="W44" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="X44" t="n">
         <v>22</v>
@@ -8983,10 +8983,10 @@
         <v>120</v>
       </c>
       <c r="AF44" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG44" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AH44" t="n">
         <v>950</v>
@@ -9019,22 +9019,22 @@
         <v>21</v>
       </c>
       <c r="AR44" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU44" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT44" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>9</v>
-      </c>
       <c r="AV44" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW44" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX44" t="n">
         <v>8.6</v>
@@ -9046,7 +9046,7 @@
         <v>19.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BB44" t="n">
         <v>10.5</v>
@@ -9055,20 +9055,20 @@
         <v>14</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE44" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF44" t="n">
         <v>7.2</v>
       </c>
       <c r="BG44" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K45" t="n">
         <v>4.2</v>
@@ -9198,7 +9198,7 @@
         <v>65</v>
       </c>
       <c r="AM45" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="n">
         <v>14</v>
@@ -9237,7 +9237,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ45" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA45" t="n">
         <v>4.9</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>
@@ -9299,28 +9299,28 @@
         <v>4.4</v>
       </c>
       <c r="H46" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="I46" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J46" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="K46" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M46" t="n">
         <v>1.07</v>
       </c>
       <c r="N46" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O46" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P46" t="n">
         <v>1.94</v>
@@ -9335,13 +9335,13 @@
         <v>3.4</v>
       </c>
       <c r="T46" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U46" t="n">
         <v>2.1</v>
       </c>
       <c r="V46" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W46" t="n">
         <v>1.29</v>
@@ -9353,10 +9353,10 @@
         <v>9.6</v>
       </c>
       <c r="Z46" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB46" t="n">
         <v>15.5</v>
@@ -9365,25 +9365,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD46" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE46" t="n">
         <v>22</v>
       </c>
       <c r="AF46" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AG46" t="n">
         <v>17</v>
       </c>
       <c r="AH46" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI46" t="n">
-        <v>980</v>
+        <v>38</v>
       </c>
       <c r="AJ46" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="n">
         <v>55</v>
@@ -9392,7 +9392,7 @@
         <v>60</v>
       </c>
       <c r="AM46" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN46" t="n">
         <v>60</v>
@@ -9404,7 +9404,7 @@
         <v>13</v>
       </c>
       <c r="AQ46" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR46" t="n">
         <v>11</v>
@@ -9413,7 +9413,7 @@
         <v>21</v>
       </c>
       <c r="AT46" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU46" t="n">
         <v>7.4</v>
@@ -9425,38 +9425,38 @@
         <v>19</v>
       </c>
       <c r="AX46" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AY46" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ46" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA46" t="n">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BB46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC46" t="n">
         <v>44</v>
       </c>
       <c r="BD46" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BE46" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF46" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BG46" t="n">
         <v>12</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-03 22:27:55</t>
+          <t>2026-03-04 00:36:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="G2" t="n">
         <v>1.65</v>
@@ -775,34 +775,34 @@
         <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>2.34</v>
       </c>
       <c r="T2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
@@ -811,19 +811,19 @@
         <v>2.52</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
         <v>11</v>
@@ -832,95 +832,95 @@
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AK2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP2" t="n">
         <v>26</v>
       </c>
-      <c r="AM2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>22</v>
-      </c>
       <c r="AQ2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AR2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AS2" t="n">
         <v>100</v>
       </c>
       <c r="AT2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AU2" t="n">
-        <v>10</v>
-      </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
         <v>50</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -954,25 +954,25 @@
         <v>1.25</v>
       </c>
       <c r="G3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H3" t="n">
         <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
         <v>7.2</v>
       </c>
       <c r="K3" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
         <v>9.199999999999999</v>
@@ -981,28 +981,28 @@
         <v>1.09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="R3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.14</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.2</v>
       </c>
       <c r="V3" t="n">
         <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X3" t="n">
         <v>150</v>
@@ -1056,7 +1056,7 @@
         <v>3.05</v>
       </c>
       <c r="AO3" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP3" t="n">
         <v>15.5</v>
@@ -1074,37 +1074,37 @@
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AW3" t="n">
         <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC3" t="n">
         <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF3" t="n">
         <v>2.66</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G4" t="n">
         <v>2.36</v>
@@ -1154,13 +1154,13 @@
         <v>3.75</v>
       </c>
       <c r="I4" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.58</v>
@@ -1169,13 +1169,13 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
         <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q4" t="n">
         <v>2.68</v>
@@ -1187,128 +1187,128 @@
         <v>5.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
         <v>1.62</v>
       </c>
       <c r="V4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W4" t="n">
         <v>1.73</v>
       </c>
       <c r="X4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y4" t="n">
         <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="AB4" t="n">
         <v>7.2</v>
       </c>
       <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP4" t="n">
         <v>8</v>
       </c>
-      <c r="AD4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU4" t="n">
         <v>6.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX4" t="n">
         <v>10.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16.5</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>32</v>
+        <v>11.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BC4" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BE4" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF4" t="n">
         <v>10</v>
       </c>
-      <c r="BF4" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G5" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O5" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="U5" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="X5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AA5" t="n">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="AB5" t="n">
         <v>7.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AE5" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AF5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>520</v>
+        <v>200</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK5" t="n">
         <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM5" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO5" t="n">
-        <v>270</v>
+        <v>370</v>
       </c>
       <c r="AP5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ5" t="n">
         <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AS5" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX5" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7</v>
-      </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BA5" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BE5" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.31</v>
       </c>
       <c r="G6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="H6" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="I6" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="J6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="K6" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -1560,10 +1560,10 @@
         <v>3.75</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
         <v>1.98</v>
@@ -1575,16 +1575,16 @@
         <v>3.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="X6" t="n">
         <v>15.5</v>
@@ -1605,7 +1605,7 @@
         <v>13.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AE6" t="n">
         <v>480</v>
@@ -1617,40 +1617,40 @@
         <v>12</v>
       </c>
       <c r="AH6" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AI6" t="n">
         <v>360</v>
       </c>
       <c r="AJ6" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK6" t="n">
         <v>17.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AM6" t="n">
         <v>410</v>
       </c>
       <c r="AN6" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>5.7</v>
@@ -1659,10 +1659,10 @@
         <v>11.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AX6" t="n">
         <v>5.8</v>
@@ -1671,32 +1671,32 @@
         <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA6" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BE6" t="n">
         <v>34</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1727,25 +1727,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I7" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>2.9</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
@@ -1754,7 +1754,7 @@
         <v>2.52</v>
       </c>
       <c r="O7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P7" t="n">
         <v>1.49</v>
@@ -1766,19 +1766,19 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="X7" t="n">
         <v>8</v>
@@ -1787,13 +1787,13 @@
         <v>10.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC7" t="n">
         <v>7.2</v>
@@ -1805,7 +1805,7 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
@@ -1817,7 +1817,7 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>170</v>
+        <v>95</v>
       </c>
       <c r="AK7" t="n">
         <v>140</v>
@@ -1829,7 +1829,7 @@
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,28 +1838,28 @@
         <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AS7" t="n">
         <v>11.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
         <v>6.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AX7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY7" t="n">
         <v>10.5</v>
@@ -1868,29 +1868,29 @@
         <v>12</v>
       </c>
       <c r="BA7" t="n">
-        <v>65</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BE7" t="n">
         <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
         <v>12</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>3.35</v>
       </c>
       <c r="H8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I8" t="n">
         <v>2.64</v>
@@ -1957,7 +1957,7 @@
         <v>2.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
         <v>4.1</v>
@@ -1972,7 +1972,7 @@
         <v>1.61</v>
       </c>
       <c r="W8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X8" t="n">
         <v>12</v>
@@ -2014,7 +2014,7 @@
         <v>60</v>
       </c>
       <c r="AK8" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
         <v>150</v>
@@ -2038,7 +2038,7 @@
         <v>13.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>8</v>
+        <v>16.5</v>
       </c>
       <c r="AT8" t="n">
         <v>9.199999999999999</v>
@@ -2050,7 +2050,7 @@
         <v>10</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AX8" t="n">
         <v>18</v>
@@ -2062,13 +2062,13 @@
         <v>16.5</v>
       </c>
       <c r="BA8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC8" t="n">
         <v>8</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>34</v>
       </c>
       <c r="BD8" t="n">
         <v>8.199999999999999</v>
@@ -2077,14 +2077,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF8" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BG8" t="n">
         <v>8.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2115,91 +2115,91 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G9" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
         <v>3.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="M9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.76</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W9" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB9" t="n">
         <v>8.6</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AC9" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
         <v>13</v>
       </c>
-      <c r="Z9" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>310</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
@@ -2208,10 +2208,10 @@
         <v>46</v>
       </c>
       <c r="AK9" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,25 +2223,25 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AT9" t="n">
         <v>7.2</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR9" t="n">
+      <c r="AU9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV9" t="n">
         <v>14.5</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>16.5</v>
       </c>
       <c r="AW9" t="n">
         <v>9</v>
@@ -2250,35 +2250,35 @@
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG9" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.79</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.8</v>
-      </c>
       <c r="H10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
         <v>5.7</v>
@@ -2342,7 +2342,7 @@
         <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
@@ -2366,7 +2366,7 @@
         <v>11.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
         <v>40</v>
@@ -2381,16 +2381,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF10" t="n">
         <v>9.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -2414,7 +2414,7 @@
         <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP10" t="n">
         <v>10.5</v>
@@ -2426,7 +2426,7 @@
         <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT10" t="n">
         <v>6.8</v>
@@ -2438,25 +2438,25 @@
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AX10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BB10" t="n">
         <v>17</v>
       </c>
       <c r="BC10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD10" t="n">
         <v>42</v>
@@ -2465,14 +2465,14 @@
         <v>85</v>
       </c>
       <c r="BF10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
         <v>42</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
         <v>3.25</v>
@@ -2521,37 +2521,37 @@
         <v>3.25</v>
       </c>
       <c r="L11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P11" t="n">
         <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U11" t="n">
         <v>2.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
         <v>1.61</v>
@@ -2560,34 +2560,34 @@
         <v>11.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11" t="n">
         <v>7.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>40</v>
       </c>
       <c r="AF11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>55</v>
@@ -2602,13 +2602,13 @@
         <v>46</v>
       </c>
       <c r="AM11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AO11" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AP11" t="n">
         <v>10.5</v>
@@ -2620,10 +2620,10 @@
         <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AU11" t="n">
         <v>6.6</v>
@@ -2635,7 +2635,7 @@
         <v>34</v>
       </c>
       <c r="AX11" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
         <v>11</v>
@@ -2644,29 +2644,29 @@
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
       </c>
       <c r="BC11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>17.5</v>
       </c>
       <c r="BF11" t="n">
         <v>23</v>
       </c>
       <c r="BG11" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2700,22 +2700,22 @@
         <v>8</v>
       </c>
       <c r="G12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I12" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="J12" t="n">
         <v>4.7</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
@@ -2727,13 +2727,13 @@
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S12" t="n">
         <v>3.5</v>
@@ -2742,34 +2742,34 @@
         <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z12" t="n">
         <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AB12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE12" t="n">
         <v>16.5</v>
@@ -2778,16 +2778,16 @@
         <v>75</v>
       </c>
       <c r="AG12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH12" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AI12" t="n">
         <v>42</v>
       </c>
       <c r="AJ12" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AK12" t="n">
         <v>150</v>
@@ -2799,7 +2799,7 @@
         <v>180</v>
       </c>
       <c r="AN12" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AO12" t="n">
         <v>8.199999999999999</v>
@@ -2808,59 +2808,59 @@
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT12" t="n">
         <v>22</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AY12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BF12" t="n">
-        <v>15</v>
+        <v>19.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>6.4</v>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
         <v>4.5</v>
@@ -2921,25 +2921,25 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U13" t="n">
         <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W13" t="n">
         <v>2.66</v>
@@ -2963,7 +2963,7 @@
         <v>11</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
         <v>260</v>
@@ -2993,7 +2993,7 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
         <v>700</v>
@@ -3005,13 +3005,13 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU13" t="n">
         <v>9</v>
@@ -3020,7 +3020,7 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3032,7 +3032,7 @@
         <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
@@ -3041,20 +3041,20 @@
         <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF13" t="n">
         <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G14" t="n">
         <v>5.2</v>
@@ -3100,7 +3100,7 @@
         <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3130,7 +3130,7 @@
         <v>1.65</v>
       </c>
       <c r="U14" t="n">
-        <v>1.05</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
         <v>2.3</v>
@@ -3232,7 +3232,7 @@
         <v>8.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BD14" t="n">
         <v>23</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I15" t="n">
         <v>4.2</v>
@@ -3300,7 +3300,7 @@
         <v>1.3</v>
       </c>
       <c r="M15" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15" t="n">
         <v>5.5</v>
@@ -3315,22 +3315,22 @@
         <v>1.6</v>
       </c>
       <c r="R15" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
         <v>2.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
         <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X15" t="n">
         <v>24</v>
@@ -3345,10 +3345,10 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>16.5</v>
@@ -3363,10 +3363,10 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AJ15" t="n">
         <v>23</v>
@@ -3378,10 +3378,10 @@
         <v>28</v>
       </c>
       <c r="AM15" t="n">
-        <v>200</v>
+        <v>330</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO15" t="n">
         <v>30</v>
@@ -3390,13 +3390,13 @@
         <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR15" t="n">
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
@@ -3420,29 +3420,29 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB15" t="n">
         <v>20</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>18.5</v>
       </c>
       <c r="BC15" t="n">
         <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BG15" t="n">
         <v>14.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3473,64 +3473,64 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="G16" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H16" t="n">
         <v>2.76</v>
       </c>
       <c r="I16" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K16" t="n">
         <v>3.55</v>
       </c>
       <c r="L16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="M16" t="n">
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
         <v>2.1</v>
       </c>
       <c r="V16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
         <v>75</v>
       </c>
       <c r="Y16" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="Z16" t="n">
         <v>980</v>
@@ -3539,7 +3539,7 @@
         <v>900</v>
       </c>
       <c r="AB16" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AC16" t="n">
         <v>12.5</v>
@@ -3584,7 +3584,7 @@
         <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AR16" t="n">
         <v>10.5</v>
@@ -3593,16 +3593,16 @@
         <v>10</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AV16" t="n">
         <v>7</v>
       </c>
       <c r="AW16" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3614,29 +3614,29 @@
         <v>8.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
@@ -3709,13 +3709,13 @@
         <v>3.05</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
         <v>2.08</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
         <v>1.83</v>
@@ -3772,16 +3772,16 @@
         <v>14.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AP17" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AQ17" t="n">
         <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS17" t="n">
         <v>9</v>
@@ -3811,13 +3811,13 @@
         <v>8.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="BD17" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BE17" t="n">
         <v>9.199999999999999</v>
@@ -3826,11 +3826,11 @@
         <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>1.55</v>
       </c>
       <c r="G18" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H18" t="n">
         <v>6.8</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
         <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L18" t="n">
         <v>1.37</v>
@@ -3885,7 +3885,7 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O18" t="n">
         <v>1.28</v>
@@ -3903,16 +3903,16 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X18" t="n">
         <v>28</v>
@@ -3930,7 +3930,7 @@
         <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
         <v>75</v>
@@ -3939,19 +3939,19 @@
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AI18" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AJ18" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="AK18" t="n">
         <v>34</v>
@@ -3975,10 +3975,10 @@
         <v>19.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT18" t="n">
         <v>8</v>
@@ -3987,7 +3987,7 @@
         <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW18" t="n">
         <v>30</v>
@@ -3999,10 +3999,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ18" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
@@ -4014,17 +4014,17 @@
         <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>3.4</v>
       </c>
       <c r="H19" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I19" t="n">
         <v>2.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K19" t="n">
         <v>3.35</v>
@@ -4085,7 +4085,7 @@
         <v>1.38</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
         <v>2.18</v>
@@ -4100,7 +4100,7 @@
         <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V19" t="n">
         <v>1.66</v>
@@ -4193,7 +4193,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA19" t="n">
         <v>38</v>
@@ -4205,10 +4205,10 @@
         <v>36</v>
       </c>
       <c r="BD19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE19" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="BF19" t="n">
         <v>34</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>1.58</v>
       </c>
       <c r="G20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I20" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J20" t="n">
         <v>4.8</v>
@@ -4267,7 +4267,7 @@
         <v>5.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M20" t="n">
         <v>1.03</v>
@@ -4276,58 +4276,58 @@
         <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P20" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R20" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W20" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X20" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="Y20" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>350</v>
       </c>
       <c r="AA20" t="n">
         <v>700</v>
       </c>
       <c r="AB20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AC20" t="n">
         <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="AE20" t="n">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
         <v>10.5</v>
@@ -4336,52 +4336,52 @@
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AR20" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AS20" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
         <v>10</v>
       </c>
       <c r="AV20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW20" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY20" t="n">
         <v>9.4</v>
@@ -4396,23 +4396,23 @@
         <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD20" t="n">
         <v>21</v>
       </c>
       <c r="BE20" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BG20" t="n">
         <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G21" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H21" t="n">
         <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -4488,7 +4488,7 @@
         <v>2.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
@@ -4497,10 +4497,10 @@
         <v>1.59</v>
       </c>
       <c r="X21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z21" t="n">
         <v>21</v>
@@ -4521,7 +4521,7 @@
         <v>55</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
         <v>13</v>
@@ -4563,7 +4563,7 @@
         <v>50</v>
       </c>
       <c r="AT21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU21" t="n">
         <v>6.4</v>
@@ -4584,7 +4584,7 @@
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>18.5</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
         <v>27</v>
@@ -4596,17 +4596,17 @@
         <v>55</v>
       </c>
       <c r="BE21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BF21" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="BG21" t="n">
         <v>34</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H22" t="n">
         <v>2.98</v>
@@ -4724,7 +4724,7 @@
         <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="AJ22" t="n">
         <v>120</v>
@@ -4733,7 +4733,7 @@
         <v>32</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AM22" t="n">
         <v>580</v>
@@ -4754,7 +4754,7 @@
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AT22" t="n">
         <v>8.199999999999999</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="H23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P23" t="n">
         <v>2.22</v>
       </c>
-      <c r="I23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="J23" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P23" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q23" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="R23" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U23" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="X23" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AA23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AB23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AC23" t="n">
         <v>8.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AG23" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AH23" t="n">
         <v>16</v>
       </c>
       <c r="AI23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ23" t="n">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AL23" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM23" t="n">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="AN23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO23" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AP23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT23" t="n">
         <v>15</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AU23" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ23" t="n">
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB23" t="n">
         <v>23</v>
       </c>
       <c r="BC23" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="BD23" t="n">
         <v>38</v>
       </c>
       <c r="BE23" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BF23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BG23" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G24" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H24" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J24" t="n">
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
         <v>1.42</v>
@@ -5049,37 +5049,37 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.35</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W24" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X24" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="Y24" t="n">
         <v>25</v>
@@ -5091,13 +5091,13 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
@@ -5118,7 +5118,7 @@
         <v>110</v>
       </c>
       <c r="AK24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL24" t="n">
         <v>1000</v>
@@ -5139,10 +5139,10 @@
         <v>12</v>
       </c>
       <c r="AR24" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT24" t="n">
         <v>8.6</v>
@@ -5151,10 +5151,10 @@
         <v>7</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="AX24" t="n">
         <v>11.5</v>
@@ -5163,32 +5163,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="BB24" t="n">
         <v>13</v>
       </c>
       <c r="BC24" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
         <v>18</v>
       </c>
       <c r="BE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF24" t="n">
         <v>14</v>
       </c>
-      <c r="BF24" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BG24" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G25" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H25" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I25" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J25" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -5255,22 +5255,22 @@
         <v>1.51</v>
       </c>
       <c r="R25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S25" t="n">
         <v>2.26</v>
       </c>
       <c r="T25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V25" t="n">
         <v>1.46</v>
       </c>
-      <c r="U25" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.48</v>
-      </c>
       <c r="W25" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="X25" t="n">
         <v>27</v>
@@ -5279,7 +5279,7 @@
         <v>21</v>
       </c>
       <c r="Z25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA25" t="n">
         <v>55</v>
@@ -5288,31 +5288,31 @@
         <v>18</v>
       </c>
       <c r="AC25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD25" t="n">
         <v>14</v>
       </c>
       <c r="AE25" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
         <v>13.5</v>
       </c>
       <c r="AI25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AJ25" t="n">
         <v>34</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
@@ -5321,68 +5321,68 @@
         <v>46</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS25" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT25" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV25" t="n">
         <v>12.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BA25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BC25" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD25" t="n">
         <v>23</v>
       </c>
       <c r="BE25" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="BF25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5413,79 +5413,79 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="M26" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="O26" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P26" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="R26" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="U26" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="V26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X26" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AC26" t="n">
         <v>7.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE26" t="n">
         <v>480</v>
@@ -5494,89 +5494,89 @@
         <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AK26" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT26" t="n">
         <v>5.8</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.2</v>
       </c>
       <c r="AU26" t="n">
         <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="BC26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BE26" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="G27" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L27" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="M27" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.56</v>
+        <v>2.9</v>
       </c>
       <c r="O27" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="P27" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="U27" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W27" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="X27" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>900</v>
+        <v>46</v>
       </c>
       <c r="AK27" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL27" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW27" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>10</v>
       </c>
       <c r="AX27" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
         <v>10.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BC27" t="n">
         <v>10.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -5801,94 +5801,94 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="G28" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="H28" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L28" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
         <v>1.04</v>
       </c>
       <c r="N28" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R28" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="S28" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
         <v>1.89</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V28" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="X28" t="n">
         <v>25</v>
       </c>
       <c r="Y28" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Z28" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AA28" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AE28" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF28" t="n">
         <v>9</v>
       </c>
       <c r="AG28" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ28" t="n">
         <v>12.5</v>
@@ -5897,58 +5897,58 @@
         <v>14</v>
       </c>
       <c r="AL28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM28" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN28" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AO28" t="n">
         <v>130</v>
       </c>
       <c r="AP28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AR28" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AS28" t="n">
         <v>110</v>
       </c>
       <c r="AT28" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28" t="n">
         <v>11</v>
       </c>
       <c r="AV28" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AW28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA28" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BB28" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD28" t="n">
         <v>28</v>
@@ -5957,14 +5957,14 @@
         <v>95</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG28" t="n">
         <v>100</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
         <v>1.49</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N29" t="n">
         <v>3.1</v>
@@ -6025,16 +6025,16 @@
         <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q29" t="n">
         <v>2.26</v>
       </c>
       <c r="R29" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T29" t="n">
         <v>1.85</v>
@@ -6049,7 +6049,7 @@
         <v>1.56</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="n">
         <v>11</v>
@@ -6085,7 +6085,7 @@
         <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK29" t="n">
         <v>34</v>
@@ -6103,10 +6103,10 @@
         <v>75</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
         <v>17</v>
@@ -6124,7 +6124,7 @@
         <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AX29" t="n">
         <v>13</v>
@@ -6136,29 +6136,29 @@
         <v>16</v>
       </c>
       <c r="BA29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="BC29" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD29" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BE29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG29" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="BF29" t="n">
-        <v>9</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="G30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.16</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.18</v>
-      </c>
       <c r="J30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K30" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
@@ -6219,34 +6219,34 @@
         <v>1.27</v>
       </c>
       <c r="P30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R30" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S30" t="n">
         <v>3.05</v>
       </c>
       <c r="T30" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U30" t="n">
         <v>2.34</v>
       </c>
       <c r="V30" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="n">
         <v>14</v>
@@ -6261,16 +6261,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE30" t="n">
         <v>21</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
         <v>15.5</v>
@@ -6282,7 +6282,7 @@
         <v>65</v>
       </c>
       <c r="AK30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL30" t="n">
         <v>44</v>
@@ -6291,7 +6291,7 @@
         <v>75</v>
       </c>
       <c r="AN30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AO30" t="n">
         <v>13.5</v>
@@ -6309,7 +6309,7 @@
         <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU30" t="n">
         <v>7.8</v>
@@ -6318,25 +6318,25 @@
         <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX30" t="n">
         <v>25</v>
       </c>
       <c r="AY30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AZ30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA30" t="n">
         <v>29</v>
       </c>
       <c r="BB30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC30" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD30" t="n">
         <v>40</v>
@@ -6345,14 +6345,14 @@
         <v>55</v>
       </c>
       <c r="BF30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG30" t="n">
         <v>12</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G31" t="n">
         <v>5.7</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5.8</v>
       </c>
       <c r="H31" t="n">
         <v>1.69</v>
@@ -6425,7 +6425,7 @@
         <v>3.55</v>
       </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U31" t="n">
         <v>2</v>
@@ -6434,10 +6434,10 @@
         <v>2.42</v>
       </c>
       <c r="W31" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X31" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y31" t="n">
         <v>8</v>
@@ -6449,7 +6449,7 @@
         <v>16</v>
       </c>
       <c r="AB31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC31" t="n">
         <v>9</v>
@@ -6461,7 +6461,7 @@
         <v>17.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG31" t="n">
         <v>21</v>
@@ -6482,7 +6482,7 @@
         <v>75</v>
       </c>
       <c r="AM31" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
         <v>110</v>
@@ -6500,22 +6500,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AU31" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW31" t="n">
         <v>17</v>
       </c>
       <c r="AX31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AY31" t="n">
         <v>20</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>3.75</v>
       </c>
       <c r="L32" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M32" t="n">
         <v>1.05</v>
@@ -6604,22 +6604,22 @@
         <v>4.8</v>
       </c>
       <c r="O32" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S32" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U32" t="n">
         <v>2.5</v>
@@ -6673,10 +6673,10 @@
         <v>28</v>
       </c>
       <c r="AL32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM32" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN32" t="n">
         <v>22</v>
@@ -6691,13 +6691,13 @@
         <v>12.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS32" t="n">
         <v>34</v>
       </c>
       <c r="AT32" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AU32" t="n">
         <v>7.8</v>
@@ -6706,7 +6706,7 @@
         <v>11</v>
       </c>
       <c r="AW32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX32" t="n">
         <v>20</v>
@@ -6727,7 +6727,7 @@
         <v>27</v>
       </c>
       <c r="BD32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE32" t="n">
         <v>55</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -6783,19 +6783,19 @@
         <v>3.75</v>
       </c>
       <c r="J33" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K33" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
         <v>1.05</v>
       </c>
       <c r="N33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O33" t="n">
         <v>1.24</v>
@@ -6816,7 +6816,7 @@
         <v>1.64</v>
       </c>
       <c r="U33" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V33" t="n">
         <v>1.36</v>
@@ -6837,13 +6837,13 @@
         <v>65</v>
       </c>
       <c r="AB33" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC33" t="n">
         <v>8.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE33" t="n">
         <v>34</v>
@@ -6867,7 +6867,7 @@
         <v>19.5</v>
       </c>
       <c r="AL33" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM33" t="n">
         <v>65</v>
@@ -6900,7 +6900,7 @@
         <v>14.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX33" t="n">
         <v>14</v>
@@ -6912,7 +6912,7 @@
         <v>14</v>
       </c>
       <c r="BA33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB33" t="n">
         <v>24</v>
@@ -6924,7 +6924,7 @@
         <v>27</v>
       </c>
       <c r="BE33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF33" t="n">
         <v>11.5</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -7115,20 +7115,20 @@
         <v>13</v>
       </c>
       <c r="BD34" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BE34" t="n">
         <v>10</v>
       </c>
       <c r="BF34" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BG34" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G35" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H35" t="n">
         <v>4.2</v>
       </c>
       <c r="I35" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K35" t="n">
         <v>4.2</v>
@@ -7189,7 +7189,7 @@
         <v>1.19</v>
       </c>
       <c r="P35" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q35" t="n">
         <v>1.6</v>
@@ -7198,7 +7198,7 @@
         <v>1.61</v>
       </c>
       <c r="S35" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T35" t="n">
         <v>1.56</v>
@@ -7207,7 +7207,7 @@
         <v>2.48</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W35" t="n">
         <v>2.02</v>
@@ -7267,19 +7267,19 @@
         <v>980</v>
       </c>
       <c r="AP35" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AQ35" t="n">
         <v>10.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="AS35" t="n">
         <v>5.4</v>
       </c>
       <c r="AT35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU35" t="n">
         <v>5.6</v>
@@ -7288,41 +7288,41 @@
         <v>8.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX35" t="n">
         <v>12</v>
       </c>
       <c r="AY35" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA35" t="n">
         <v>7.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD35" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="BE35" t="n">
         <v>8</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BG35" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -7353,16 +7353,16 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G36" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="I36" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="J36" t="n">
         <v>3.1</v>
@@ -7377,22 +7377,22 @@
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="O36" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P36" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q36" t="n">
         <v>2.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="T36" t="n">
         <v>2.12</v>
@@ -7401,19 +7401,19 @@
         <v>1.76</v>
       </c>
       <c r="V36" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X36" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Y36" t="n">
         <v>42</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA36" t="n">
         <v>140</v>
@@ -7470,53 +7470,53 @@
         <v>6.2</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AT36" t="n">
         <v>6.4</v>
       </c>
       <c r="AU36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV36" t="n">
         <v>6.4</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AX36" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY36" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="BB36" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.04</v>
+        <v>3.05</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>6.6</v>
       </c>
       <c r="G37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H37" t="n">
         <v>1.55</v>
@@ -7583,13 +7583,13 @@
         <v>1.64</v>
       </c>
       <c r="R37" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S37" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T37" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="U37" t="n">
         <v>2.24</v>
@@ -7598,7 +7598,7 @@
         <v>2.78</v>
       </c>
       <c r="W37" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X37" t="n">
         <v>23</v>
@@ -7610,7 +7610,7 @@
         <v>10.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB37" t="n">
         <v>29</v>
@@ -7625,13 +7625,13 @@
         <v>14.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AG37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH37" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI37" t="n">
         <v>27</v>
@@ -7646,7 +7646,7 @@
         <v>70</v>
       </c>
       <c r="AM37" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN37" t="n">
         <v>80</v>
@@ -7664,10 +7664,10 @@
         <v>9.6</v>
       </c>
       <c r="AS37" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU37" t="n">
         <v>10</v>
@@ -7676,10 +7676,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AW37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AX37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AY37" t="n">
         <v>22</v>
@@ -7688,16 +7688,16 @@
         <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BB37" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BD37" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BE37" t="n">
         <v>48</v>
@@ -7706,11 +7706,11 @@
         <v>60</v>
       </c>
       <c r="BG37" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H38" t="n">
         <v>2.62</v>
@@ -7759,7 +7759,7 @@
         <v>3.9</v>
       </c>
       <c r="L38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M38" t="n">
         <v>1.04</v>
@@ -7783,10 +7783,10 @@
         <v>2.46</v>
       </c>
       <c r="T38" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U38" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="V38" t="n">
         <v>1.6</v>
@@ -7807,7 +7807,7 @@
         <v>36</v>
       </c>
       <c r="AB38" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC38" t="n">
         <v>9</v>
@@ -7822,7 +7822,7 @@
         <v>22</v>
       </c>
       <c r="AG38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH38" t="n">
         <v>13</v>
@@ -7840,7 +7840,7 @@
         <v>28</v>
       </c>
       <c r="AM38" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN38" t="n">
         <v>15.5</v>
@@ -7849,7 +7849,7 @@
         <v>14</v>
       </c>
       <c r="AP38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ38" t="n">
         <v>16</v>
@@ -7861,7 +7861,7 @@
         <v>34</v>
       </c>
       <c r="AT38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU38" t="n">
         <v>8.800000000000001</v>
@@ -7870,7 +7870,7 @@
         <v>11</v>
       </c>
       <c r="AW38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX38" t="n">
         <v>21</v>
@@ -7897,14 +7897,14 @@
         <v>44</v>
       </c>
       <c r="BF38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BG38" t="n">
         <v>13</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
         <v>4.7</v>
       </c>
       <c r="T39" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U39" t="n">
         <v>1.84</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G40" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H40" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I40" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J40" t="n">
         <v>3.35</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L40" t="n">
         <v>1.51</v>
@@ -8174,13 +8174,13 @@
         <v>2.08</v>
       </c>
       <c r="U40" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="V40" t="n">
         <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X40" t="n">
         <v>11</v>
@@ -8243,7 +8243,7 @@
         <v>13</v>
       </c>
       <c r="AR40" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AS40" t="n">
         <v>8.199999999999999</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H41" t="n">
         <v>2.84</v>
       </c>
-      <c r="G41" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2.98</v>
-      </c>
       <c r="I41" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="J41" t="n">
         <v>3.05</v>
@@ -8341,152 +8341,152 @@
         <v>3.1</v>
       </c>
       <c r="L41" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O41" t="n">
         <v>1.65</v>
       </c>
-      <c r="M41" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N41" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O41" t="n">
-        <v>1.63</v>
-      </c>
       <c r="P41" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="R41" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S41" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T41" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U41" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V41" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W41" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="X41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Y41" t="n">
         <v>8</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Z41" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB41" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Z41" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>8</v>
-      </c>
       <c r="AC41" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD41" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG41" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>14.5</v>
       </c>
       <c r="AH41" t="n">
         <v>42</v>
       </c>
       <c r="AI41" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ41" t="n">
-        <v>55</v>
+        <v>230</v>
       </c>
       <c r="AK41" t="n">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="AL41" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM41" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN41" t="n">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AO41" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AP41" t="n">
         <v>7</v>
       </c>
       <c r="AQ41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT41" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR41" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AU41" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX41" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY41" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA41" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB41" t="n">
         <v>40</v>
       </c>
       <c r="BC41" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BD41" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BE41" t="n">
         <v>50</v>
       </c>
       <c r="BF41" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BG41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -8517,58 +8517,58 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="G42" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K42" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="L42" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M42" t="n">
         <v>1.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O42" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P42" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="R42" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S42" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U42" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>1.14</v>
       </c>
       <c r="W42" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="X42" t="n">
         <v>22</v>
@@ -8577,7 +8577,7 @@
         <v>980</v>
       </c>
       <c r="Z42" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AA42" t="n">
         <v>230</v>
@@ -8619,7 +8619,7 @@
         <v>140</v>
       </c>
       <c r="AN42" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AO42" t="n">
         <v>140</v>
@@ -8631,10 +8631,10 @@
         <v>21</v>
       </c>
       <c r="AR42" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT42" t="n">
         <v>7.6</v>
@@ -8646,7 +8646,7 @@
         <v>23</v>
       </c>
       <c r="AW42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX42" t="n">
         <v>8.6</v>
@@ -8658,7 +8658,7 @@
         <v>19.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB42" t="n">
         <v>12</v>
@@ -8667,20 +8667,20 @@
         <v>14</v>
       </c>
       <c r="BD42" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE42" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF42" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BG42" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G43" t="n">
         <v>1.64</v>
@@ -8726,13 +8726,13 @@
         <v>3.9</v>
       </c>
       <c r="K43" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
         <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N43" t="n">
         <v>3.1</v>
@@ -8741,7 +8741,7 @@
         <v>1.45</v>
       </c>
       <c r="P43" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q43" t="n">
         <v>2.38</v>
@@ -8780,7 +8780,7 @@
         <v>7.2</v>
       </c>
       <c r="AC43" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD43" t="n">
         <v>38</v>
@@ -8792,7 +8792,7 @@
         <v>9.6</v>
       </c>
       <c r="AG43" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH43" t="n">
         <v>950</v>
@@ -8807,7 +8807,7 @@
         <v>25</v>
       </c>
       <c r="AL43" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM43" t="n">
         <v>290</v>
@@ -8825,10 +8825,10 @@
         <v>15.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS43" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT43" t="n">
         <v>5.6</v>
@@ -8840,7 +8840,7 @@
         <v>25</v>
       </c>
       <c r="AW43" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX43" t="n">
         <v>7</v>
@@ -8852,7 +8852,7 @@
         <v>25</v>
       </c>
       <c r="BA43" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BB43" t="n">
         <v>13</v>
@@ -8861,20 +8861,20 @@
         <v>17.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF43" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>
@@ -8905,70 +8905,70 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H44" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I44" t="n">
         <v>2.14</v>
-      </c>
-      <c r="I44" t="n">
-        <v>2.18</v>
       </c>
       <c r="J44" t="n">
         <v>3.5</v>
       </c>
       <c r="K44" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L44" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M44" t="n">
         <v>1.08</v>
       </c>
       <c r="N44" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O44" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P44" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R44" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S44" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T44" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="U44" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V44" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="W44" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X44" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z44" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB44" t="n">
         <v>14</v>
@@ -8977,98 +8977,98 @@
         <v>7.8</v>
       </c>
       <c r="AD44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF44" t="n">
         <v>28</v>
       </c>
       <c r="AG44" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI44" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AJ44" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK44" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL44" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN44" t="n">
         <v>60</v>
       </c>
-      <c r="AM44" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>55</v>
-      </c>
       <c r="AO44" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS44" t="n">
         <v>23</v>
       </c>
       <c r="AT44" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU44" t="n">
         <v>7.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW44" t="n">
         <v>20</v>
       </c>
       <c r="AX44" t="n">
-        <v>19.5</v>
+        <v>25</v>
       </c>
       <c r="AY44" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ44" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB44" t="n">
         <v>16</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>15.5</v>
       </c>
       <c r="BC44" t="n">
         <v>40</v>
       </c>
       <c r="BD44" t="n">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="BE44" t="n">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="BF44" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BG44" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-04 02:43:48</t>
+          <t>2026-03-04 04:51:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-04.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.63</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>1.65</v>
+        <v>120</v>
       </c>
       <c r="H2" t="n">
-        <v>5.6</v>
+        <v>1.18</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>1.19</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V2" t="n">
+        <v>6</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.03</v>
       </c>
-      <c r="N2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.52</v>
-      </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>50</v>
+        <v>4.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>5.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>48</v>
+        <v>2.12</v>
       </c>
       <c r="AS2" t="n">
-        <v>100</v>
+        <v>1.33</v>
       </c>
       <c r="AT2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>1.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>65</v>
+        <v>1.33</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.6</v>
+        <v>1.34</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>1.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>50</v>
+        <v>1.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>1.34</v>
       </c>
       <c r="BD2" t="n">
-        <v>23</v>
+        <v>1.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>65</v>
+        <v>1.33</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.7</v>
+        <v>1.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>40</v>
+        <v>1.33</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="I3" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="K3" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="P3" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="R3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U3" t="n">
         <v>2.16</v>
       </c>
-      <c r="S3" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U3" t="n">
-        <v>2.14</v>
-      </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="X3" t="n">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="Y3" t="n">
         <v>950</v>
@@ -1020,7 +1020,7 @@
         <v>980</v>
       </c>
       <c r="AC3" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AD3" t="n">
         <v>980</v>
@@ -1029,10 +1029,10 @@
         <v>150</v>
       </c>
       <c r="AF3" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AG3" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AH3" t="n">
         <v>980</v>
@@ -1041,10 +1041,10 @@
         <v>240</v>
       </c>
       <c r="AJ3" t="n">
-        <v>980</v>
+        <v>13.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AL3" t="n">
         <v>980</v>
@@ -1053,7 +1053,7 @@
         <v>100</v>
       </c>
       <c r="AN3" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="AO3" t="n">
         <v>130</v>
@@ -1062,59 +1062,59 @@
         <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.26</v>
+        <v>7.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC3" t="n">
         <v>6</v>
       </c>
       <c r="BD3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="BG3" t="n">
         <v>10.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="I4" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O4" t="n">
         <v>1.55</v>
       </c>
       <c r="P4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
         <v>5.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG4" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
       <c r="AH4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>180</v>
       </c>
       <c r="AJ4" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AM4" t="n">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN4" t="n">
         <v>40</v>
       </c>
       <c r="AO4" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV4" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW4" t="n">
         <v>27</v>
       </c>
       <c r="AX4" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY4" t="n">
         <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BD4" t="n">
         <v>27</v>
       </c>
       <c r="BE4" t="n">
-        <v>14</v>
+        <v>18.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1339,76 +1339,76 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G5" t="n">
         <v>1.38</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L5" t="n">
         <v>1.4</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.39</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V5" t="n">
         <v>1.09</v>
       </c>
       <c r="W5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="X5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA5" t="n">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
         <v>44</v>
@@ -1423,10 +1423,10 @@
         <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI5" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ5" t="n">
         <v>10.5</v>
@@ -1435,13 +1435,13 @@
         <v>16</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO5" t="n">
         <v>370</v>
@@ -1450,28 +1450,28 @@
         <v>15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU5" t="n">
         <v>10.5</v>
       </c>
       <c r="AV5" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AW5" t="n">
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
@@ -1483,26 +1483,26 @@
         <v>29</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BE5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BF5" t="n">
         <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="G6" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="H6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>13</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>680</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>310</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>270</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>530</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG6" t="n">
         <v>14.5</v>
       </c>
-      <c r="I6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="J6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="X6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>95</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>480</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>130</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>360</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>410</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>12</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1727,46 +1727,46 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="L7" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="M7" t="n">
         <v>1.14</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O7" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="P7" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="T7" t="n">
         <v>2.22</v>
@@ -1775,55 +1775,55 @@
         <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="X7" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AA7" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>95</v>
+        <v>170</v>
       </c>
       <c r="AK7" t="n">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BC7" t="n">
         <v>16</v>
       </c>
       <c r="BD7" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -1921,100 +1921,100 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE8" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AJ8" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AK8" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AL8" t="n">
         <v>150</v>
@@ -2023,31 +2023,31 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>48</v>
+        <v>600</v>
       </c>
       <c r="AO8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS8" t="n">
         <v>16.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW8" t="n">
         <v>13.5</v>
@@ -2056,35 +2056,35 @@
         <v>18</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>8</v>
       </c>
-      <c r="BD8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2115,85 +2115,85 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="G9" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P9" t="n">
         <v>1.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="R9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V9" t="n">
         <v>1.25</v>
       </c>
-      <c r="S9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.26</v>
-      </c>
       <c r="W9" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X9" t="n">
         <v>11.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AA9" t="n">
         <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC9" t="n">
         <v>7.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG9" t="n">
         <v>11</v>
@@ -2202,37 +2202,37 @@
         <v>21</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AJ9" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK9" t="n">
         <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ9" t="n">
         <v>11.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>7.2</v>
@@ -2241,16 +2241,16 @@
         <v>6.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
         <v>16.5</v>
@@ -2265,20 +2265,20 @@
         <v>21</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BF9" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BG9" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.78</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.79</v>
-      </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
         <v>3.8</v>
@@ -2333,16 +2333,16 @@
         <v>1.09</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>1.41</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R10" t="n">
         <v>1.29</v>
@@ -2357,10 +2357,10 @@
         <v>1.86</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
         <v>11.5</v>
@@ -2369,7 +2369,7 @@
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA10" t="n">
         <v>160</v>
@@ -2384,10 +2384,10 @@
         <v>22</v>
       </c>
       <c r="AE10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG10" t="n">
         <v>9.800000000000001</v>
@@ -2396,13 +2396,13 @@
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL10" t="n">
         <v>44</v>
@@ -2411,13 +2411,13 @@
         <v>160</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>15</v>
@@ -2438,41 +2438,41 @@
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC10" t="n">
         <v>19</v>
       </c>
       <c r="BD10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE10" t="n">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="BF10" t="n">
         <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
         <v>3.35</v>
@@ -2518,7 +2518,7 @@
         <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
         <v>1.47</v>
@@ -2533,10 +2533,10 @@
         <v>1.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R11" t="n">
         <v>1.3</v>
@@ -2548,10 +2548,10 @@
         <v>1.86</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
         <v>1.61</v>
@@ -2566,7 +2566,7 @@
         <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB11" t="n">
         <v>9.800000000000001</v>
@@ -2587,7 +2587,7 @@
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
         <v>55</v>
@@ -2608,10 +2608,10 @@
         <v>28</v>
       </c>
       <c r="AO11" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AP11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
         <v>10.5</v>
@@ -2620,7 +2620,7 @@
         <v>19</v>
       </c>
       <c r="AS11" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2644,7 +2644,7 @@
         <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BB11" t="n">
         <v>32</v>
@@ -2653,20 +2653,20 @@
         <v>27</v>
       </c>
       <c r="BD11" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="BE11" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG11" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="H12" t="n">
         <v>1.47</v>
       </c>
       <c r="I12" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="J12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K12" t="n">
         <v>5</v>
@@ -2721,46 +2721,46 @@
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O12" t="n">
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R12" t="n">
         <v>1.39</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V12" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="W12" t="n">
         <v>1.13</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Z12" t="n">
         <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB12" t="n">
         <v>25</v>
@@ -2769,28 +2769,28 @@
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE12" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AH12" t="n">
         <v>27</v>
       </c>
       <c r="AI12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ12" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AK12" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AL12" t="n">
         <v>150</v>
@@ -2799,28 +2799,28 @@
         <v>180</v>
       </c>
       <c r="AN12" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AO12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AP12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR12" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS12" t="n">
         <v>11.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>9</v>
@@ -2829,38 +2829,38 @@
         <v>14.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="AY12" t="n">
         <v>27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA12" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="BF12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG12" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -2903,40 +2903,40 @@
         <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K13" t="n">
         <v>4.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T13" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V13" t="n">
         <v>1.17</v>
@@ -2945,7 +2945,7 @@
         <v>2.66</v>
       </c>
       <c r="X13" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
         <v>25</v>
@@ -2966,19 +2966,19 @@
         <v>26</v>
       </c>
       <c r="AE13" t="n">
-        <v>260</v>
+        <v>100</v>
       </c>
       <c r="AF13" t="n">
         <v>10.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>330</v>
+        <v>85</v>
       </c>
       <c r="AJ13" t="n">
         <v>18</v>
@@ -2993,10 +2993,10 @@
         <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="AP13" t="n">
         <v>17</v>
@@ -3005,10 +3005,10 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>8.4</v>
@@ -3020,7 +3020,7 @@
         <v>21</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX13" t="n">
         <v>8.6</v>
@@ -3032,7 +3032,7 @@
         <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
         <v>12.5</v>
@@ -3041,20 +3041,20 @@
         <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BE13" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF13" t="n">
         <v>6.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         <v>5.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="I14" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="J14" t="n">
         <v>4.3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L14" t="n">
         <v>1.29</v>
@@ -3109,37 +3109,37 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="S14" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
         <v>1.65</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="W14" t="n">
         <v>1.23</v>
       </c>
       <c r="X14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3163,7 +3163,7 @@
         <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AG14" t="n">
         <v>21</v>
@@ -3172,25 +3172,25 @@
         <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
         <v>700</v>
       </c>
       <c r="AK14" t="n">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AL14" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>300</v>
+        <v>42</v>
       </c>
       <c r="AO14" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AP14" t="n">
         <v>21</v>
@@ -3226,29 +3226,29 @@
         <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.5</v>
+        <v>22</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC14" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BD14" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
         <v>6.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
         <v>1.96</v>
@@ -3288,13 +3288,13 @@
         <v>3.95</v>
       </c>
       <c r="I15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J15" t="n">
         <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.3</v>
@@ -3303,64 +3303,64 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O15" t="n">
         <v>1.19</v>
       </c>
       <c r="P15" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T15" t="n">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="U15" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W15" t="n">
         <v>2.04</v>
       </c>
       <c r="X15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z15" t="n">
         <v>34</v>
       </c>
       <c r="AA15" t="n">
-        <v>900</v>
+        <v>190</v>
       </c>
       <c r="AB15" t="n">
         <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE15" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
         <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
         <v>15.5</v>
@@ -3369,19 +3369,19 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
         <v>330</v>
       </c>
       <c r="AN15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO15" t="n">
         <v>30</v>
@@ -3390,13 +3390,13 @@
         <v>20</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR15" t="n">
         <v>16.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AT15" t="n">
         <v>11.5</v>
@@ -3408,7 +3408,7 @@
         <v>14.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AX15" t="n">
         <v>12.5</v>
@@ -3420,29 +3420,29 @@
         <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BB15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC15" t="n">
         <v>15.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="BE15" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="BF15" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="H16" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
         <v>3.55</v>
@@ -3497,40 +3497,40 @@
         <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
         <v>1.29</v>
       </c>
       <c r="P16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
         <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U16" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="X16" t="n">
         <v>75</v>
       </c>
       <c r="Y16" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="Z16" t="n">
         <v>980</v>
@@ -3578,31 +3578,31 @@
         <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AP16" t="n">
         <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR16" t="n">
         <v>10.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="AX16" t="n">
         <v>10.5</v>
@@ -3614,29 +3614,29 @@
         <v>8.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>13</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BG16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3670,82 +3670,82 @@
         <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H17" t="n">
         <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.37</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O17" t="n">
         <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
         <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X17" t="n">
-        <v>34</v>
+        <v>17.5</v>
       </c>
       <c r="Y17" t="n">
         <v>75</v>
       </c>
       <c r="Z17" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AA17" t="n">
-        <v>900</v>
+        <v>250</v>
       </c>
       <c r="AB17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC17" t="n">
         <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>80</v>
+        <v>16.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="AF17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
         <v>11.5</v>
@@ -3754,7 +3754,7 @@
         <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>980</v>
+        <v>330</v>
       </c>
       <c r="AJ17" t="n">
         <v>65</v>
@@ -3763,7 +3763,7 @@
         <v>42</v>
       </c>
       <c r="AL17" t="n">
-        <v>200</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
         <v>580</v>
@@ -3772,22 +3772,22 @@
         <v>14.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>600</v>
+        <v>210</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR17" t="n">
         <v>13</v>
       </c>
-      <c r="AR17" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AS17" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17" t="n">
         <v>7.4</v>
@@ -3796,7 +3796,7 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX17" t="n">
         <v>12</v>
@@ -3808,10 +3808,10 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC17" t="n">
         <v>18</v>
@@ -3820,17 +3820,17 @@
         <v>27</v>
       </c>
       <c r="BE17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BF17" t="n">
         <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G18" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I18" t="n">
         <v>7.2</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K18" t="n">
         <v>4.7</v>
@@ -3885,16 +3885,16 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R18" t="n">
         <v>1.43</v>
@@ -3912,13 +3912,13 @@
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="X18" t="n">
         <v>28</v>
       </c>
       <c r="Y18" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
         <v>280</v>
@@ -3927,7 +3927,7 @@
         <v>700</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
         <v>10</v>
@@ -3939,7 +3939,7 @@
         <v>700</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AG18" t="n">
         <v>10.5</v>
@@ -3957,74 +3957,74 @@
         <v>34</v>
       </c>
       <c r="AL18" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM18" t="n">
         <v>700</v>
       </c>
       <c r="AN18" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO18" t="n">
         <v>700</v>
       </c>
       <c r="AP18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>19.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU18" t="n">
         <v>8.6</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AX18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="BB18" t="n">
         <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BD18" t="n">
         <v>16</v>
       </c>
       <c r="BE18" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BF18" t="n">
         <v>7.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
         <v>2.46</v>
@@ -4067,10 +4067,10 @@
         <v>2.5</v>
       </c>
       <c r="J19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K19" t="n">
         <v>3.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.35</v>
       </c>
       <c r="L19" t="n">
         <v>1.47</v>
@@ -4082,13 +4082,13 @@
         <v>3.45</v>
       </c>
       <c r="O19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
         <v>1.3</v>
@@ -4100,19 +4100,19 @@
         <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V19" t="n">
         <v>1.66</v>
       </c>
       <c r="W19" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X19" t="n">
         <v>11.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z19" t="n">
         <v>16</v>
@@ -4151,13 +4151,13 @@
         <v>42</v>
       </c>
       <c r="AL19" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
         <v>120</v>
       </c>
       <c r="AN19" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO19" t="n">
         <v>25</v>
@@ -4166,7 +4166,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR19" t="n">
         <v>13.5</v>
@@ -4190,7 +4190,7 @@
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ19" t="n">
         <v>16</v>
@@ -4214,11 +4214,11 @@
         <v>34</v>
       </c>
       <c r="BG19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G20" t="n">
         <v>1.58</v>
       </c>
-      <c r="G20" t="n">
-        <v>1.6</v>
-      </c>
       <c r="H20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
         <v>6.4</v>
@@ -4264,7 +4264,7 @@
         <v>4.8</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L20" t="n">
         <v>1.28</v>
@@ -4276,40 +4276,40 @@
         <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P20" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q20" t="n">
         <v>1.53</v>
       </c>
       <c r="R20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
         <v>1.66</v>
       </c>
       <c r="U20" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y20" t="n">
         <v>32</v>
       </c>
       <c r="Z20" t="n">
-        <v>350</v>
+        <v>60</v>
       </c>
       <c r="AA20" t="n">
         <v>700</v>
@@ -4318,67 +4318,67 @@
         <v>13</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE20" t="n">
         <v>65</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH20" t="n">
         <v>18</v>
       </c>
       <c r="AI20" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="AJ20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AK20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM20" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN20" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AO20" t="n">
         <v>60</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR20" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AS20" t="n">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX20" t="n">
         <v>11</v>
@@ -4390,29 +4390,29 @@
         <v>15.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB20" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC20" t="n">
         <v>13</v>
       </c>
       <c r="BD20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE20" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG20" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G21" t="n">
         <v>2.7</v>
@@ -4467,7 +4467,7 @@
         <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O21" t="n">
         <v>1.56</v>
@@ -4476,7 +4476,7 @@
         <v>1.55</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R21" t="n">
         <v>1.19</v>
@@ -4488,19 +4488,19 @@
         <v>2.14</v>
       </c>
       <c r="U21" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Z21" t="n">
         <v>21</v>
@@ -4509,7 +4509,7 @@
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC21" t="n">
         <v>6.8</v>
@@ -4548,7 +4548,7 @@
         <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
         <v>7.6</v>
@@ -4575,16 +4575,16 @@
         <v>44</v>
       </c>
       <c r="AX21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
         <v>20</v>
       </c>
       <c r="BA21" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BB21" t="n">
         <v>27</v>
@@ -4596,7 +4596,7 @@
         <v>55</v>
       </c>
       <c r="BE21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BF21" t="n">
         <v>18.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H22" t="n">
         <v>2.98</v>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J22" t="n">
         <v>3.2</v>
@@ -4661,22 +4661,22 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
         <v>1.74</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
         <v>1.86</v>
@@ -4685,7 +4685,7 @@
         <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
         <v>1.58</v>
@@ -4706,7 +4706,7 @@
         <v>9.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
         <v>14</v>
@@ -4715,7 +4715,7 @@
         <v>120</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
@@ -4739,7 +4739,7 @@
         <v>580</v>
       </c>
       <c r="AN22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO22" t="n">
         <v>110</v>
@@ -4748,13 +4748,13 @@
         <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR22" t="n">
         <v>18</v>
       </c>
       <c r="AS22" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AT22" t="n">
         <v>8.199999999999999</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>10</v>
+        <v>18.5</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
@@ -4778,29 +4778,29 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD22" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BE22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF22" t="n">
         <v>9.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H23" t="n">
         <v>2.06</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J23" t="n">
         <v>3.8</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L23" t="n">
         <v>1.36</v>
@@ -4864,34 +4864,34 @@
         <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
         <v>2.98</v>
       </c>
       <c r="T23" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U23" t="n">
         <v>2.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X23" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Y23" t="n">
         <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA23" t="n">
         <v>25</v>
@@ -4918,16 +4918,16 @@
         <v>16</v>
       </c>
       <c r="AI23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AJ23" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>200</v>
@@ -4936,10 +4936,10 @@
         <v>36</v>
       </c>
       <c r="AO23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ23" t="n">
         <v>10.5</v>
@@ -4960,10 +4960,10 @@
         <v>9.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AY23" t="n">
         <v>14</v>
@@ -4972,19 +4972,19 @@
         <v>14</v>
       </c>
       <c r="BA23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB23" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BC23" t="n">
         <v>36</v>
       </c>
       <c r="BD23" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="BE23" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BF23" t="n">
         <v>30</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G24" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I24" t="n">
         <v>3.85</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V24" t="n">
         <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X24" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF24" t="n">
         <v>13.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>17</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>27</v>
       </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>110</v>
-      </c>
       <c r="AK24" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>580</v>
+        <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="AO24" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP24" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV24" t="n">
         <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF24" t="n">
         <v>14.5</v>
       </c>
-      <c r="BA24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>14</v>
-      </c>
       <c r="BG24" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H25" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I25" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -5243,58 +5243,58 @@
         <v>1.03</v>
       </c>
       <c r="N25" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P25" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="R25" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="S25" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="T25" t="n">
         <v>1.47</v>
       </c>
       <c r="U25" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="V25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X25" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z25" t="n">
         <v>28</v>
       </c>
       <c r="AA25" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB25" t="n">
         <v>18</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="AF25" t="n">
         <v>20</v>
@@ -5309,31 +5309,31 @@
         <v>30</v>
       </c>
       <c r="AJ25" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AK25" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
       </c>
       <c r="AM25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AN25" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP25" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
         <v>42</v>
@@ -5342,19 +5342,19 @@
         <v>16.5</v>
       </c>
       <c r="AU25" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV25" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>12</v>
@@ -5363,26 +5363,26 @@
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC25" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG25" t="n">
         <v>14</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J26" t="n">
         <v>3.1</v>
@@ -5431,46 +5431,46 @@
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M26" t="n">
         <v>1.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="O26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P26" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R26" t="n">
         <v>1.17</v>
       </c>
       <c r="S26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="U26" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="V26" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W26" t="n">
         <v>1.92</v>
       </c>
       <c r="X26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z26" t="n">
         <v>36</v>
@@ -5479,13 +5479,13 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC26" t="n">
         <v>7.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
         <v>480</v>
@@ -5494,10 +5494,10 @@
         <v>11</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI26" t="n">
         <v>1000</v>
@@ -5506,22 +5506,22 @@
         <v>26</v>
       </c>
       <c r="AK26" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL26" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ26" t="n">
         <v>10.5</v>
@@ -5530,10 +5530,10 @@
         <v>15.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AU26" t="n">
         <v>6.4</v>
@@ -5542,7 +5542,7 @@
         <v>17</v>
       </c>
       <c r="AW26" t="n">
-        <v>9.6</v>
+        <v>30</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
@@ -5551,10 +5551,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ26" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB26" t="n">
         <v>20</v>
@@ -5563,20 +5563,20 @@
         <v>13.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="BE26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.6</v>
+        <v>23</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -5607,46 +5607,46 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="G27" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="H27" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="I27" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="L27" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O27" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="P27" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
         <v>2.08</v>
@@ -5655,37 +5655,37 @@
         <v>1.78</v>
       </c>
       <c r="V27" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="X27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z27" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG27" t="n">
         <v>10.5</v>
@@ -5709,22 +5709,22 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AT27" t="n">
         <v>6.2</v>
@@ -5733,13 +5733,13 @@
         <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW27" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY27" t="n">
         <v>9</v>
@@ -5748,29 +5748,29 @@
         <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BD27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG27" t="n">
         <v>9.6</v>
       </c>
-      <c r="BE27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>11</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G28" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="I28" t="n">
         <v>8</v>
       </c>
-      <c r="I28" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="J28" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="K28" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L28" t="n">
         <v>1.32</v>
@@ -5843,28 +5843,28 @@
         <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="V28" t="n">
         <v>1.14</v>
       </c>
       <c r="W28" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="X28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y28" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Z28" t="n">
         <v>70</v>
       </c>
       <c r="AA28" t="n">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="AB28" t="n">
         <v>9.199999999999999</v>
@@ -5876,64 +5876,64 @@
         <v>28</v>
       </c>
       <c r="AE28" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG28" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AH28" t="n">
         <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK28" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
       </c>
       <c r="AM28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO28" t="n">
         <v>120</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>6</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>130</v>
       </c>
       <c r="AP28" t="n">
         <v>23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AR28" t="n">
         <v>60</v>
       </c>
       <c r="AS28" t="n">
-        <v>110</v>
+        <v>190</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU28" t="n">
         <v>11</v>
       </c>
       <c r="AV28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY28" t="n">
         <v>9</v>
@@ -5942,29 +5942,29 @@
         <v>22</v>
       </c>
       <c r="BA28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BC28" t="n">
         <v>13.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE28" t="n">
         <v>95</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG28" t="n">
         <v>100</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="H29" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
         <v>3.4</v>
@@ -6019,61 +6019,61 @@
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
         <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="U29" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V29" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X29" t="n">
         <v>11</v>
       </c>
       <c r="Y29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
         <v>160</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="AF29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG29" t="n">
         <v>12.5</v>
@@ -6082,34 +6082,34 @@
         <v>19.5</v>
       </c>
       <c r="AI29" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AJ29" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AK29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL29" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM29" t="n">
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO29" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
         <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>18</v>
@@ -6124,7 +6124,7 @@
         <v>12</v>
       </c>
       <c r="AW29" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AX29" t="n">
         <v>13</v>
@@ -6136,7 +6136,7 @@
         <v>16</v>
       </c>
       <c r="BA29" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BB29" t="n">
         <v>16.5</v>
@@ -6145,7 +6145,7 @@
         <v>15</v>
       </c>
       <c r="BD29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE29" t="n">
         <v>10.5</v>
@@ -6154,11 +6154,11 @@
         <v>11.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-04 04:51:44</t>
+          <t>2026-03-04 06:59:45</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>3.75</v>
       </c>
       <c r="H30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.14</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.16</v>
       </c>
       <c r="J30" t="n">
         <v>3.75</v>
@@ -6231,19 +6231,19 @@
         <v>3.05</v>
       </c>
       <c r="T30" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U30" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V30" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W30" t="n">
         <v>1.36</v>
       </c>
       <c r="X30" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y30" t="n">
         <v>11</v>
@@ -6264,7 +6264,7 @@
         <v>10.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF30" t="n">
         <v>27</v>
@@ -6309,7 +6309,7 @@
         <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AU30" t="n">
         <v>7.8</v>
@@ -6342,7 +6342,7 @@
    